--- a/exports/lote4_questoes_autorais.xlsx
+++ b/exports/lote4_questoes_autorais.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A espirometria mede apenas volumes mobilizáveis: capacidade vital e seus componentes. O volume residual e, por consequência, a capacidade residual funcional e a capacidade pulmonar total exigem métodos indiretos — diluição de gás inerte, lavagem de nitrogênio ou pletismografia de corpo inteiro.&lt;/p&gt;&lt;p&gt;Os métodos de diluição e de lavagem dependem do equilíbrio do gás traçador com o gás alveolar dentro do tempo do exame. Regiões com obstrução grave, bolhas ou aprisionamento aéreo têm constante de tempo muito longa e simplesmente não participam desse equilíbrio, ficando fora da medida: o resultado é &lt;strong&gt;subestimativa&lt;/strong&gt; dos volumes. Já a pletismografia aplica a lei de Boyle a todo o gás compressível intratorácico durante manobras de ofegar contra via aérea ocluída, incluindo o gás não comunicante. Por isso, no enfisematoso, o valor pletismográfico supera o da diluição, e a diferença entre eles serve como estimativa do gás aprisionado (A).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a retenção do traçador em unidades lentas leva à subestimativa, não à superestimativa; (C) a pletismografia não exige expiração forçada máxima, e sim ofegar de baixa amplitude contra oclusão; (D) a espirometria não mede volume residual em nenhuma circunstância, de modo que a divergência não pode ser atribuída a erro de calibração.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A espirometria mede apenas volumes mobilizáveis: capacidade vital e seus componentes. O volume residual e, por consequência, a capacidade residual funcional e a capacidade pulmonar total exigem métodos indiretos: diluição de gás inerte, lavagem de nitrogênio ou pletismografia de corpo inteiro.&lt;/p&gt;&lt;p&gt;Os métodos de diluição e de lavagem dependem do equilíbrio do gás traçador com o gás alveolar dentro do tempo do exame. Regiões com obstrução grave, bolhas ou aprisionamento aéreo têm constante de tempo muito longa e simplesmente não participam desse equilíbrio, ficando fora da medida: o resultado é &lt;strong&gt;subestimativa&lt;/strong&gt; dos volumes. Já a pletismografia aplica a lei de Boyle a todo o gás compressível intratorácico durante manobras de ofegar contra via aérea ocluída, incluindo o gás não comunicante. Por isso, no enfisematoso, o valor pletismográfico supera o da diluição, e a diferença entre eles serve como estimativa do gás aprisionado (A).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a retenção do traçador em unidades lentas leva à subestimativa, não à superestimativa; (C) a pletismografia não exige expiração forçada máxima, e sim ofegar de baixa amplitude contra oclusão; (D) a espirometria não mede volume residual em nenhuma circunstância, de modo que a divergência não pode ser atribuída a erro de calibração.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O modelo de West descreve a distribuição do fluxo pulmonar pela relação entre três pressões: alveolar (PA), arterial pulmonar (Pa) e venosa pulmonar (Pv). Na zona 1, PA &amp;gt; Pa &amp;gt; Pv e o capilar colapsa: há ventilação sem perfusão, isto é, espaço morto alveolar. Na zona 2, Pa &amp;gt; PA &amp;gt; Pv, e o fluxo depende da diferença entre pressão arterial e alveolar. Na zona 3, Pa &amp;gt; Pv &amp;gt; PA, com fluxo contínuo.&lt;/p&gt;&lt;p&gt;Em condições normais a zona 1 é virtual. Ela aparece justamente quando se eleva a pressão alveolar (PEEP alta, hiperinsuflação) e/ou se reduz a pressão arterial pulmonar (hipovolemia, baixo débito) — exatamente o cenário descrito. O aumento do espaço morto alveolar dilui o CO&lt;sub&gt;2&lt;/sub&gt; expirado e alarga o gradiente entre PaCO&lt;sub&gt;2&lt;/sub&gt; e EtCO&lt;sub&gt;2&lt;/sub&gt; (B). O tratamento passa por restaurar volemia e débito, e não por aumentar ainda mais a PEEP.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o shunt causa hipoxemia e tende a reduzir, não a alargar, o gradiente de CO&lt;sub&gt;2&lt;/sub&gt; por unidade ventilada; (C) a zona 3 predomina nas bases e sua redução não desvia fluxo para os ápices desse modo; (D) a vasoconstrição hipóxica é resposta regional a alvéolos hipoventilados e não inverte o gradiente gravitacional de perfusão.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O modelo de West descreve a distribuição do fluxo pulmonar pela relação entre três pressões: alveolar (PA), arterial pulmonar (Pa) e venosa pulmonar (Pv). Na zona 1, PA &amp;gt; Pa &amp;gt; Pv e o capilar colapsa: há ventilação sem perfusão, isto é, espaço morto alveolar. Na zona 2, Pa &amp;gt; PA &amp;gt; Pv, e o fluxo depende da diferença entre pressão arterial e alveolar. Na zona 3, Pa &amp;gt; Pv &amp;gt; PA, com fluxo contínuo.&lt;/p&gt;&lt;p&gt;Em condições normais a zona 1 é virtual. Ela aparece justamente quando se eleva a pressão alveolar (PEEP alta, hiperinsuflação) e/ou se reduz a pressão arterial pulmonar (hipovolemia, baixo débito), exatamente o cenário descrito. O aumento do espaço morto alveolar dilui o CO&lt;sub&gt;2&lt;/sub&gt; expirado e alarga o gradiente entre PaCO&lt;sub&gt;2&lt;/sub&gt; e EtCO&lt;sub&gt;2&lt;/sub&gt; (B). O tratamento passa por restaurar volemia e débito, e não por aumentar ainda mais a PEEP.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o shunt causa hipoxemia e tende a reduzir, não a alargar, o gradiente de CO&lt;sub&gt;2&lt;/sub&gt; por unidade ventilada; (C) a zona 3 predomina nas bases e sua redução não desvia fluxo para os ápices desse modo; (D) a vasoconstrição hipóxica é resposta regional a alvéolos hipoventilados e não inverte o gradiente gravitacional de perfusão.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A equação do gás alveolar simplificada é PAO&lt;sub&gt;2&lt;/sub&gt; = FiO&lt;sub&gt;2&lt;/sub&gt; × (Patm − PH&lt;sub&gt;2&lt;/sub&gt;O) − PaCO&lt;sub&gt;2&lt;/sub&gt;/R. Ao nível do mar, em ar ambiente: 0,21 × (760 − 47) = 149,7 mmHg de oxigênio inspirado umidificado. Com PaCO&lt;sub&gt;2&lt;/sub&gt; de 62 mmHg e R = 0,8, subtrai-se 77,5 mmHg, resultando em PAO&lt;sub&gt;2&lt;/sub&gt; de aproximadamente 72 mmHg.&lt;/p&gt;&lt;p&gt;O gradiente alveoloarterial é, portanto, 72 − 60 = 12 mmHg, valor dentro do esperado para a idade (aceita-se cerca de 4 + idade/4). Gradiente normal com PaCO&lt;sub&gt;2&lt;/sub&gt; elevada define &lt;strong&gt;hipoventilação alveolar pura&lt;/strong&gt; como causa da hipoxemia (C) — no caso, depressão respiratória por opioide. A conduta é estimular a ventilação, considerar naloxona em titulação e ofertar oxigênio, lembrando que a oferta de O&lt;sub&gt;2&lt;/sub&gt; corrige a saturação sem corrigir a hipercapnia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o gradiente calculado é de cerca de 12 mmHg, não superior a 40; (B) o CO&lt;sub&gt;2&lt;/sub&gt; alveolar ocupa espaço na mistura e reduz diretamente a PAO&lt;sub&gt;2&lt;/sub&gt;, sendo parte central da equação; (D) o valor de 149,7 mmHg corresponde ao gás inspirado, e não ao alveolar, erro que leva a superestimar o gradiente e a diagnosticar shunt inexistente.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A equação do gás alveolar simplificada é PAO&lt;sub&gt;2&lt;/sub&gt; = FiO&lt;sub&gt;2&lt;/sub&gt; × (Patm − PH&lt;sub&gt;2&lt;/sub&gt;O) − PaCO&lt;sub&gt;2&lt;/sub&gt;/R. Ao nível do mar, em ar ambiente: 0,21 × (760 − 47) = 149,7 mmHg de oxigênio inspirado umidificado. Com PaCO&lt;sub&gt;2&lt;/sub&gt; de 62 mmHg e R = 0,8, subtrai-se 77,5 mmHg, resultando em PAO&lt;sub&gt;2&lt;/sub&gt; de aproximadamente 72 mmHg.&lt;/p&gt;&lt;p&gt;O gradiente alveoloarterial é, portanto, 72 − 60 = 12 mmHg, valor dentro do esperado para a idade (aceita-se cerca de 4 + idade/4). Gradiente normal com PaCO&lt;sub&gt;2&lt;/sub&gt; elevada define &lt;strong&gt;hipoventilação alveolar pura&lt;/strong&gt; como causa da hipoxemia (C); no caso, depressão respiratória por opioide. A conduta é estimular a ventilação, considerar naloxona em titulação e ofertar oxigênio, lembrando que a oferta de O&lt;sub&gt;2&lt;/sub&gt; corrige a saturação sem corrigir a hipercapnia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o gradiente calculado é de cerca de 12 mmHg, não superior a 40; (B) o CO&lt;sub&gt;2&lt;/sub&gt; alveolar ocupa espaço na mistura e reduz diretamente a PAO&lt;sub&gt;2&lt;/sub&gt;, sendo parte central da equação; (D) o valor de 149,7 mmHg corresponde ao gás inspirado, e não ao alveolar, erro que leva a superestimar o gradiente e a diagnosticar shunt inexistente.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O diafragma é inervado pelos nervos frênicos, formados pelas raízes C3, C4 e C5 — daí a máxima clássica sobre a manutenção da respiração diafragmática em lesões medulares abaixo de C5. A lesão unilateral do frênico eleva a hemicúpula do &lt;em&gt;mesmo&lt;/em&gt; lado.&lt;/p&gt;&lt;p&gt;Na vigília e em decúbito dorsal, o tônus diafragmático mantém as porções dorsais dependentes em posição relativamente caudal, contrapondo a pressão hidrostática do conteúdo abdominal. Com a indução anestésica e, sobretudo, com o bloqueio neuromuscular, esse tônus desaparece: o diafragma passa a ser deslocado cefalicamente de forma &lt;strong&gt;desigual&lt;/strong&gt;, com maior migração das porções dorsais dependentes, que sofrem a maior pressão abdominal. Some-se a isso a redução do volume da caixa torácica e a absorção de oxigênio a altas frações inspiradas, e resulta a queda da capacidade residual funcional (cerca de 15% a 20%) com atelectasias dorsais em poucos minutos (D).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a origem é C3-C5, e a elevação da cúpula é ipsilateral à lesão; (B) o padrão descrito está invertido, pois são as regiões dorsais dependentes as mais deslocadas; (C) o tônus expiratório abdominal contribui pouco, e a queda da capacidade residual funcional não tem causa exclusiva, envolvendo perda de tônus, compressão e absorção de gás.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O diafragma é inervado pelos nervos frênicos, formados pelas raízes C3, C4 e C5; daí a máxima clássica sobre a manutenção da respiração diafragmática em lesões medulares abaixo de C5. A lesão unilateral do frênico eleva a hemicúpula do &lt;em&gt;mesmo&lt;/em&gt; lado.&lt;/p&gt;&lt;p&gt;Na vigília e em decúbito dorsal, o tônus diafragmático mantém as porções dorsais dependentes em posição relativamente caudal, contrapondo a pressão hidrostática do conteúdo abdominal. Com a indução anestésica e, sobretudo, com o bloqueio neuromuscular, esse tônus desaparece: o diafragma passa a ser deslocado cefalicamente de forma &lt;strong&gt;desigual&lt;/strong&gt;, com maior migração das porções dorsais dependentes, que sofrem a maior pressão abdominal. Some-se a isso a redução do volume da caixa torácica e a absorção de oxigênio a altas frações inspiradas, e resulta a queda da capacidade residual funcional (cerca de 15% a 20%) com atelectasias dorsais em poucos minutos (D).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a origem é C3-C5, e a elevação da cúpula é ipsilateral à lesão; (B) o padrão descrito está invertido, pois são as regiões dorsais dependentes as mais deslocadas; (C) o tônus expiratório abdominal contribui pouco, e a queda da capacidade residual funcional não tem causa exclusiva, envolvendo perda de tônus, compressão e absorção de gás.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O objetivo no asmático é chegar à sala com a doença controlada e evitar os estímulos que deflagram broncoespasmo. A terapia inalatória de manutenção — corticoide inalatório e broncodilatador de longa duração — deve ser &lt;strong&gt;mantida&lt;/strong&gt;, inclusive na manhã da cirurgia, e vale considerar broncodilatador de curta duração antes da indução. Em pacientes que usaram corticoide sistêmico recentemente, avalia-se suplementação.&lt;/p&gt;&lt;p&gt;O estímulo mais broncoconstritor do ato anestésico é a instrumentação da via aérea em plano superficial. Aprofundar a anestesia (propofol, cetamina, halogenado, lidocaína, opioide) antes da laringoscopia é a medida isolada mais eficaz. Entre os bloqueadores, preferem-se os que não liberam histamina — rocurônio, vecurônio, cisatracúrio (B). O propofol é a escolha habitual para indução por atenuar o reflexo da via aérea.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o atracúrio libera histamina de forma dose e velocidade dependente, sendo evitável nesse contexto, ao contrário do cisatracúrio; (C) suspender o corticoide inalatório desestabiliza a doença, e o suxametônio pode liberar histamina; (D) a neostigmina é agonista colinérgico indireto e pode &lt;em&gt;causar&lt;/em&gt; broncoconstrição e hipersecreção, exigindo antimuscarínico associado — o sugamadex é alternativa vantajosa quando se usou rocurônio.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O objetivo no asmático é chegar à sala com a doença controlada e evitar os estímulos que deflagram broncoespasmo. A terapia inalatória de manutenção (corticoide inalatório e broncodilatador de longa duração) deve ser &lt;strong&gt;mantida&lt;/strong&gt;, inclusive na manhã da cirurgia, e vale considerar broncodilatador de curta duração antes da indução. Em pacientes que usaram corticoide sistêmico recentemente, avalia-se suplementação.&lt;/p&gt;&lt;p&gt;O estímulo mais broncoconstritor do ato anestésico é a instrumentação da via aérea em plano superficial. Aprofundar a anestesia (propofol, cetamina, halogenado, lidocaína, opioide) antes da laringoscopia é a medida isolada mais eficaz. Entre os bloqueadores, preferem-se os que não liberam histamina: rocurônio, vecurônio, cisatracúrio (B). O propofol é a escolha habitual para indução por atenuar o reflexo da via aérea.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o atracúrio libera histamina de forma dose e velocidade dependente, sendo evitável nesse contexto, ao contrário do cisatracúrio; (C) suspender o corticoide inalatório desestabiliza a doença, e o suxametônio pode liberar histamina; (D) a neostigmina é agonista colinérgico indireto e pode &lt;em&gt;causar&lt;/em&gt; broncoconstrição e hipersecreção, exigindo antimuscarínico associado; o sugamadex é alternativa vantajosa quando se usou rocurônio.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;No paciente desperto em decúbito lateral, ventilação e perfusão continuam acopladas: o pulmão dependente recebe mais fluxo sanguíneo (gravidade) e também mais ventilação, porque parte de um volume expiratório menor e opera na porção íngreme da curva pressão-volume, além de contar com a contração ativa da hemicúpula diafragmática dependente.&lt;/p&gt;&lt;p&gt;A anestesia geral com paralisia inverte esse equilíbrio ventilatório. A capacidade residual funcional cai, o diafragma dependente é empurrado cefalicamente pelo conteúdo abdominal, e o mediastino comprime o pulmão inferior: ele migra para a porção plana da curva de complacência. Ao mesmo tempo, a abertura do tórax libera o pulmão superior, que passa a ser o mais complacente e a receber a maior fração do volume corrente. A perfusão, entretanto, continua predominando embaixo, por gravidade. Resultado: unidades bem perfundidas e mal ventiladas no pulmão dependente — aumento do shunt e queda da oxigenação (C).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) sob paralisia o pulmão dependente sai da porção íngreme da curva; (B) a gravidade favorece a perfusão do pulmão inferior, e não do superior; (D) a abertura do tórax &lt;em&gt;aumenta&lt;/em&gt; a complacência e a ventilação do pulmão não dependente.&lt;/p&gt;</t>
+          <t>&lt;p&gt;No paciente desperto em decúbito lateral, ventilação e perfusão continuam acopladas: o pulmão dependente recebe mais fluxo sanguíneo (gravidade) e também mais ventilação, porque parte de um volume expiratório menor e opera na porção íngreme da curva pressão-volume, além de contar com a contração ativa da hemicúpula diafragmática dependente.&lt;/p&gt;&lt;p&gt;A anestesia geral com paralisia inverte esse equilíbrio ventilatório. A capacidade residual funcional cai, o diafragma dependente é empurrado cefalicamente pelo conteúdo abdominal, e o mediastino comprime o pulmão inferior: ele migra para a porção plana da curva de complacência. Ao mesmo tempo, a abertura do tórax libera o pulmão superior, que passa a ser o mais complacente e a receber a maior fração do volume corrente. A perfusão, entretanto, continua predominando embaixo, por gravidade. Resultado: unidades bem perfundidas e mal ventiladas no pulmão dependente, com aumento do shunt e queda da oxigenação (C).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) sob paralisia o pulmão dependente sai da porção íngreme da curva; (B) a gravidade favorece a perfusão do pulmão inferior, e não do superior; (D) a abertura do tórax &lt;em&gt;aumenta&lt;/em&gt; a complacência e a ventilação do pulmão não dependente.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A traqueia adulta mede cerca de 10 a 12 cm e bifurca-se na carina, aproximadamente na altura de T4-T5. O brônquio principal &lt;strong&gt;direito&lt;/strong&gt; é mais curto, mais calibroso e mais verticalizado (ângulo em torno de 25 graus contra cerca de 45 graus à esquerda), o que explica a maior frequência de intubação seletiva e de aspiração desse lado. O brônquio lobar superior direito emerge a apenas 1,5 a 2 cm da carina — e em alguns indivíduos diretamente da traqueia —, o que torna o tubo de duplo lúmen direito tecnicamente mais exigente, pois o orifício de Murphy precisa ficar alinhado a esse óstio.&lt;/p&gt;&lt;p&gt;A circulação brônquica é sistêmica, com origem na aorta e em intercostais, e representa cerca de 1% a 2% do débito cardíaco. As veias brônquicas superficiais drenam para o sistema ázigo e hemiázigo, mas as profundas desembocam nas veias pulmonares, devolvendo sangue não oxigenado ao átrio esquerdo. Com as veias de Tebésio, compõem o shunt anatômico fisiológico de 2% a 5% do débito (D).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) as características descritas pertencem ao brônquio direito; (B) o lobar superior direito emerge a 1,5-2 cm da carina, o que dificulta o posicionamento; (C) as artérias brônquicas nascem da circulação sistêmica e conduzem sangue arterial.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A traqueia adulta mede cerca de 10 a 12 cm e bifurca-se na carina, aproximadamente na altura de T4-T5. O brônquio principal &lt;strong&gt;direito&lt;/strong&gt; é mais curto, mais calibroso e mais verticalizado (ângulo em torno de 25 graus contra cerca de 45 graus à esquerda), o que explica a maior frequência de intubação seletiva e de aspiração desse lado. O brônquio lobar superior direito emerge a apenas 1,5 a 2 cm da carina (e em alguns indivíduos diretamente da traqueia), o que torna o tubo de duplo lúmen direito tecnicamente mais exigente, pois o orifício de Murphy precisa ficar alinhado a esse óstio.&lt;/p&gt;&lt;p&gt;A circulação brônquica é sistêmica, com origem na aorta e em intercostais, e representa cerca de 1% a 2% do débito cardíaco. As veias brônquicas superficiais drenam para o sistema ázigo e hemiázigo, mas as profundas desembocam nas veias pulmonares, devolvendo sangue não oxigenado ao átrio esquerdo. Com as veias de Tebésio, compõem o shunt anatômico fisiológico de 2% a 5% do débito (D).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) as características descritas pertencem ao brônquio direito; (B) o lobar superior direito emerge a 1,5-2 cm da carina, o que dificulta o posicionamento; (C) as artérias brônquicas nascem da circulação sistêmica e conduzem sangue arterial.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A obesidade impõe um padrão restritivo extrapulmonar. O peso da parede torácica e a pressão do conteúdo abdominal reduzem a complacência do sistema respiratório e deslocam o volume pulmonar de repouso para baixo. O volume mais afetado é o &lt;strong&gt;volume de reserva expiratório&lt;/strong&gt;, que pode cair de forma exponencial com o aumento do IMC; como a capacidade residual funcional é a soma do volume de reserva expiratório com o volume residual, e este último é relativamente preservado, a queda da capacidade residual funcional segue a do volume de reserva expiratório (A).&lt;/p&gt;&lt;p&gt;A capacidade pulmonar total costuma reduzir-se pouco, exceto em obesidade extrema. Como capacidade vital forçada e VEF1 caem juntos, a relação VEF1/CVF permanece normal — daí o padrão restritivo, e não obstrutivo. A consequência anestésica é direta: com capacidade residual funcional próxima ou abaixo do volume de fechamento, há colapso de pequenas vias em ventilação corrente, dessaturação rápida na apneia e necessidade de pré-oxigenação otimizada, posição em rampa e proclive, além de PEEP e recrutamento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o volume residual é o componente mais preservado, e não há obstrução característica; (C) a capacidade residual funcional diminui, e a complacência da parede torácica está reduzida; (D) a redução não é homogênea, e a capacidade pulmonar total raramente cai a esse ponto.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A obesidade impõe um padrão restritivo extrapulmonar. O peso da parede torácica e a pressão do conteúdo abdominal reduzem a complacência do sistema respiratório e deslocam o volume pulmonar de repouso para baixo. O volume mais afetado é o &lt;strong&gt;volume de reserva expiratório&lt;/strong&gt;, que pode cair de forma exponencial com o aumento do IMC; como a capacidade residual funcional é a soma do volume de reserva expiratório com o volume residual, e este último é relativamente preservado, a queda da capacidade residual funcional segue a do volume de reserva expiratório (A).&lt;/p&gt;&lt;p&gt;A capacidade pulmonar total costuma reduzir-se pouco, exceto em obesidade extrema. Como capacidade vital forçada e VEF1 caem juntos, a relação VEF1/CVF permanece normal; daí o padrão restritivo, e não obstrutivo. A consequência anestésica é direta: com capacidade residual funcional próxima ou abaixo do volume de fechamento, há colapso de pequenas vias em ventilação corrente, dessaturação rápida na apneia e necessidade de pré-oxigenação otimizada, posição em rampa e proclive, além de PEEP e recrutamento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o volume residual é o componente mais preservado, e não há obstrução característica; (C) a capacidade residual funcional diminui, e a complacência da parede torácica está reduzida; (D) a redução não é homogênea, e a capacidade pulmonar total raramente cai a esse ponto.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A auto-PEEP surge quando o tempo expiratório é insuficiente para o esvaziamento pulmonar, situação típica da limitação ao fluxo expiratório da DPOC e da asma. Para deflagrar um ciclo assistido, o paciente precisa primeiro anular essa pressão alveolar positiva residual antes de gerar queda de pressão ou fluxo no sensor: é uma &lt;strong&gt;carga limiar&lt;/strong&gt; que consome trabalho e produz esforços ineficazes, exatamente como descrito.&lt;/p&gt;&lt;p&gt;Na limitação ao fluxo expiratório existe um ponto de colapso dinâmico das vias aéreas que se comporta como resistor de Starling. Aplicar PEEP externa até cerca de 75% a 85% da auto-PEEP eleva a pressão a jusante desse ponto sem aumentar a pressão alveolar nem o volume pulmonar expiratório final, aproximando a pressão do circuito da pressão alveolar e reduzindo o esforço de disparo (D). Complementam a conduta: broncodilatadores, tubo de maior calibre, redução da demanda ventilatória e ajuste de sensibilidade.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) PEEP externa acima da auto-PEEP ultrapassa o ponto de colapso e agrava a hiperinsuflação, com queda do retorno venoso; (B) aumentar a frequência encurta o tempo expiratório e piora o aprisionamento; (C) o raciocínio está invertido — o esvaziamento exige tempo expiratório &lt;em&gt;maior&lt;/em&gt;, obtido com fluxo inspiratório mais alto e frequência menor.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A auto-PEEP surge quando o tempo expiratório é insuficiente para o esvaziamento pulmonar, situação típica da limitação ao fluxo expiratório da DPOC e da asma. Para deflagrar um ciclo assistido, o paciente precisa primeiro anular essa pressão alveolar positiva residual antes de gerar queda de pressão ou fluxo no sensor: é uma &lt;strong&gt;carga limiar&lt;/strong&gt; que consome trabalho e produz esforços ineficazes, exatamente como descrito.&lt;/p&gt;&lt;p&gt;Na limitação ao fluxo expiratório existe um ponto de colapso dinâmico das vias aéreas que se comporta como resistor de Starling. Aplicar PEEP externa até cerca de 75% a 85% da auto-PEEP eleva a pressão a jusante desse ponto sem aumentar a pressão alveolar nem o volume pulmonar expiratório final, aproximando a pressão do circuito da pressão alveolar e reduzindo o esforço de disparo (D). Complementam a conduta: broncodilatadores, tubo de maior calibre, redução da demanda ventilatória e ajuste de sensibilidade.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) PEEP externa acima da auto-PEEP ultrapassa o ponto de colapso e agrava a hiperinsuflação, com queda do retorno venoso; (B) aumentar a frequência encurta o tempo expiratório e piora o aprisionamento; (C) o raciocínio está invertido: o esvaziamento exige tempo expiratório &lt;em&gt;maior&lt;/em&gt;, obtido com fluxo inspiratório mais alto e frequência menor.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O princípio é simples e cai com frequência: &lt;strong&gt;o que se programa é a variável independente; o que resta é dependente da mecânica&lt;/strong&gt;. Na ventilação a volume controlado, programam-se volume corrente e fluxo; a pressão nas vias aéreas é consequência da complacência e da resistência. Na ventilação a pressão controlada, programa-se a pressão inspiratória; o volume corrente e o fluxo tornam-se dependentes da mecânica e do tempo inspiratório.&lt;/p&gt;&lt;p&gt;No caso, o pneumoperitônio e o Trendelenburg elevam a pressão intra-abdominal, empurram o diafragma cefalicamente e reduzem a complacência do sistema respiratório. Com pressão motriz fixa, o volume corrente cai proporcionalmente, e a hipoventilação resultante eleva a EtCO&lt;sub&gt;2&lt;/sub&gt; — agravada pela absorção de CO&lt;sub&gt;2&lt;/sub&gt; do pneumoperitônio (B). A conduta é reajustar a pressão inspiratória ou a frequência, monitorando o volume entregue.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a lógica do modo, pois na pressão controlada o volume é justamente a variável que flutua; (C) na ventilação a volume o volume é fixo e a pressão é que varia; (D) o padrão de fluxo está trocado — a pressão controlada gera fluxo desacelerado, enquanto a ventilação a volume costuma usar fluxo quadrado, embora possa ser configurada com onda desacelerada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O princípio é simples e cai com frequência: &lt;strong&gt;o que se programa é a variável independente; o que resta é dependente da mecânica&lt;/strong&gt;. Na ventilação a volume controlado, programam-se volume corrente e fluxo; a pressão nas vias aéreas é consequência da complacência e da resistência. Na ventilação a pressão controlada, programa-se a pressão inspiratória; o volume corrente e o fluxo tornam-se dependentes da mecânica e do tempo inspiratório.&lt;/p&gt;&lt;p&gt;No caso, o pneumoperitônio e o Trendelenburg elevam a pressão intra-abdominal, empurram o diafragma cefalicamente e reduzem a complacência do sistema respiratório. Com pressão motriz fixa, o volume corrente cai proporcionalmente, e a hipoventilação resultante eleva a EtCO&lt;sub&gt;2&lt;/sub&gt;, agravada pela absorção de CO&lt;sub&gt;2&lt;/sub&gt; do pneumoperitônio (B). A conduta é reajustar a pressão inspiratória ou a frequência, monitorando o volume entregue.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a lógica do modo, pois na pressão controlada o volume é justamente a variável que flutua; (C) na ventilação a volume o volume é fixo e a pressão é que varia; (D) o padrão de fluxo está trocado: a pressão controlada gera fluxo desacelerado, enquanto a ventilação a volume costuma usar fluxo quadrado, embora possa ser configurada com onda desacelerada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Diante de hipoxemia na ventilação monopulmonar, a sequência clássica começa por elevar a FiO&lt;sub&gt;2&lt;/sub&gt; — já em 1,0 neste caso — e, imediatamente, por &lt;strong&gt;verificar a posição do tubo&lt;/strong&gt;. A mudança do decúbito dorsal para o lateral desloca o tubo de duplo lúmen com frequência: o tubo pode migrar distalmente e ocluir o lobo superior esquerdo, ou recuar para a traqueia, comprometendo o isolamento. A combinação descrita — queda da saturação com &lt;em&gt;aumento&lt;/em&gt; da pressão de pico e redução do volume corrente expirado — é altamente sugestiva de má posição, e a broncoscopia resolve a dúvida em segundos (C). Também se avalia o estado hemodinâmico, pois baixo débito reduz a saturação venosa mista e agrava o efeito do shunt.&lt;/p&gt;&lt;p&gt;Só depois de tubo conferido e hemodinâmica ajustada é que se recorre a recrutamento e PEEP no pulmão dependente, CPAP ou oxigênio no pulmão operado e, em último caso, clampeamento da artéria pulmonar pelo cirurgião.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o CPAP é medida subsequente e pode atrapalhar a videotoracoscopia ao insuflar o campo; (B) volumes correntes altos aumentam a lesão induzida pela ventilação e a resistência vascular do pulmão dependente, desviando fluxo para o pulmão colapsado; (D) o retorno à ventilação bipulmonar é reservado à hipoxemia refratária, e vasodilatador inalatório não é a medida inicial.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Diante de hipoxemia na ventilação monopulmonar, a sequência clássica começa por elevar a FiO&lt;sub&gt;2&lt;/sub&gt; (já em 1,0 neste caso) e, imediatamente, por &lt;strong&gt;verificar a posição do tubo&lt;/strong&gt;. A mudança do decúbito dorsal para o lateral desloca o tubo de duplo lúmen com frequência: o tubo pode migrar distalmente e ocluir o lobo superior esquerdo, ou recuar para a traqueia, comprometendo o isolamento. A combinação descrita, queda da saturação com &lt;em&gt;aumento&lt;/em&gt; da pressão de pico e redução do volume corrente expirado, é altamente sugestiva de má posição, e a broncoscopia resolve a dúvida em segundos (C). Também se avalia o estado hemodinâmico, pois baixo débito reduz a saturação venosa mista e agrava o efeito do shunt.&lt;/p&gt;&lt;p&gt;Só depois de tubo conferido e hemodinâmica ajustada é que se recorre a recrutamento e PEEP no pulmão dependente, CPAP ou oxigênio no pulmão operado e, em último caso, clampeamento da artéria pulmonar pelo cirurgião.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o CPAP é medida subsequente e pode atrapalhar a videotoracoscopia ao insuflar o campo; (B) volumes correntes altos aumentam a lesão induzida pela ventilação e a resistência vascular do pulmão dependente, desviando fluxo para o pulmão colapsado; (D) o retorno à ventilação bipulmonar é reservado à hipoxemia refratária, e vasodilatador inalatório não é a medida inicial.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O tubo de duplo lúmen continua sendo o padrão para isolamento pulmonar por permitir colapso rápido, aspiração eficaz de cada pulmão, alternância imediata de lados e aplicação simples de CPAP no pulmão operado. Há, porém, situações em que ele é má escolha: via aérea difícil, paciente já intubado, traqueostomia, criança, distorção anatômica ou previsão de ventilação prolongada no pós-operatório.&lt;/p&gt;&lt;p&gt;Nesses casos, o bloqueador brônquico — passado por dentro do tubo traqueal já posicionado, sob visão broncoscópica — resolve o problema sem nova instrumentação da via aérea, e a mesma prótese permanece para o pós-operatório. As desvantagens são reais e devem ser conhecidas: o colapso é mais lento, porque depende da reabsorção do gás distal através do canal central estreito; o balão desloca-se com facilidade durante a manipulação cirúrgica, exigindo broncoscópio disponível; e a aspiração de secreções é limitada (A).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o bloqueio seletivo de um brônquio lobar é, ao contrário, uma vantagem exclusiva do bloqueador; (C) aspiração ampla e CPAP fácil são atributos do tubo de duplo lúmen; (D) o tubo com bloqueador integrado é usado em adultos e permite ventilação bipulmonar convencional com o bloqueador recolhido em seu canal lateral.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O tubo de duplo lúmen continua sendo o padrão para isolamento pulmonar por permitir colapso rápido, aspiração eficaz de cada pulmão, alternância imediata de lados e aplicação simples de CPAP no pulmão operado. Há, porém, situações em que ele é má escolha: via aérea difícil, paciente já intubado, traqueostomia, criança, distorção anatômica ou previsão de ventilação prolongada no pós-operatório.&lt;/p&gt;&lt;p&gt;Nesses casos, o bloqueador brônquico (passado por dentro do tubo traqueal já posicionado, sob visão broncoscópica) resolve o problema sem nova instrumentação da via aérea, e a mesma prótese permanece para o pós-operatório. As desvantagens são reais e devem ser conhecidas: o colapso é mais lento, porque depende da reabsorção do gás distal através do canal central estreito; o balão desloca-se com facilidade durante a manipulação cirúrgica, exigindo broncoscópio disponível; e a aspiração de secreções é limitada (A).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o bloqueio seletivo de um brônquio lobar é, ao contrário, uma vantagem exclusiva do bloqueador; (C) aspiração ampla e CPAP fácil são atributos do tubo de duplo lúmen; (D) o tubo com bloqueador integrado é usado em adultos e permite ventilação bipulmonar convencional com o bloqueador recolhido em seu canal lateral.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A esofagectomia reúne três desafios: paciente frequentemente desnutrido e sarcopênico, esôfago obstruído com conteúdo retido e um tempo torácico que exige ventilação monopulmonar. A obstrução com regurgitação noturna torna o estômago e o esôfago cheios independentemente do jejum, o que indica &lt;strong&gt;indução em sequência rápida&lt;/strong&gt; com cabeceira elevada e aspiração prévia de sonda quando disponível.&lt;/p&gt;&lt;p&gt;Durante a ventilação monopulmonar, adota-se estratégia protetora: volume corrente de 4 a 6 mL/kg de peso predito no pulmão dependente, PEEP titulada, recrutamento e limitação da pressão de platô e da pressão motriz, com hipercapnia permissiva tolerada. O balanço hídrico deve ser &lt;strong&gt;restritivo&lt;/strong&gt; e guiado por metas, pois o excesso de cristaloide associa-se a lesão pulmonar aguda, edema do tubo gástrico e complicações da anastomose. Analgesia eficaz — peridural torácica ou bloqueios de parede — permite extubação ao final da cirurgia, meta que reduz complicações respiratórias (C).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a indução inalatória lenta prolonga o período de risco de aspiração em paciente com estômago cheio; (B) a reposição liberal piora o edema tecidual e a função pulmonar, sem proteger a anastomose; (D) a ventilação prolongada programada aumenta pneumonia e tempo de internação, sendo a extubação precoce a estratégia preferida.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A esofagectomia reúne três desafios: paciente frequentemente desnutrido e sarcopênico, esôfago obstruído com conteúdo retido e um tempo torácico que exige ventilação monopulmonar. A obstrução com regurgitação noturna torna o estômago e o esôfago cheios independentemente do jejum, o que indica &lt;strong&gt;indução em sequência rápida&lt;/strong&gt; com cabeceira elevada e aspiração prévia de sonda quando disponível.&lt;/p&gt;&lt;p&gt;Durante a ventilação monopulmonar, adota-se estratégia protetora: volume corrente de 4 a 6 mL/kg de peso predito no pulmão dependente, PEEP titulada, recrutamento e limitação da pressão de platô e da pressão motriz, com hipercapnia permissiva tolerada. O balanço hídrico deve ser &lt;strong&gt;restritivo&lt;/strong&gt; e guiado por metas, pois o excesso de cristaloide associa-se a lesão pulmonar aguda, edema do tubo gástrico e complicações da anastomose. Analgesia eficaz (peridural torácica ou bloqueios de parede) permite extubação ao final da cirurgia, meta que reduz complicações respiratórias (C).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a indução inalatória lenta prolonga o período de risco de aspiração em paciente com estômago cheio; (B) a reposição liberal piora o edema tecidual e a função pulmonar, sem proteger a anastomose; (D) a ventilação prolongada programada aumenta pneumonia e tempo de internação, sendo a extubação precoce a estratégia preferida.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A mediastinoscopia cervical é feita por incisão supraesternal, com dissecção romba ao longo da traqueia. O instrumento trafega em vizinhança perigosa: tronco braquiocefálico (artéria inominada), arco aórtico, artéria pulmonar direita, veia cava superior, ázigo, nervo laríngeo recorrente e nervo vago.&lt;/p&gt;&lt;p&gt;A compressão do tronco braquiocefálico pelo mediastinoscópio interrompe o fluxo para a artéria subclávia direita e para a &lt;strong&gt;carótida comum direita&lt;/strong&gt;. O sinal aparece à direita: perda da onda de pulso do oxímetro e queda da pressão arterial daquele membro. Por isso a monitorização recomendada é justamente essa — oximetria ou pressão arterial no braço direito para detectar a compressão, e pressão no braço esquerdo para refletir a pressão sistêmica verdadeira. A conduta é comunicação imediata ao cirurgião para alívio da compressão, pelo risco de isquemia cerebral no território carotídeo direito (B). Outras complicações a antecipar são hemorragia maciça, pneumotórax, rouquidão por lesão do recorrente e bradicardia reflexa por estímulo vagal ou compressão traqueal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) atribuir a artefato posterga a correção de uma isquemia potencialmente encefálica; (C) hemorragia venosa significativa causaria hipotensão sistêmica, detectável também à esquerda; (D) bloqueio simpático não explica a assimetria nem coincide com a manipulação do instrumento.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A mediastinoscopia cervical é feita por incisão supraesternal, com dissecção romba ao longo da traqueia. O instrumento trafega em vizinhança perigosa: tronco braquiocefálico (artéria inominada), arco aórtico, artéria pulmonar direita, veia cava superior, ázigo, nervo laríngeo recorrente e nervo vago.&lt;/p&gt;&lt;p&gt;A compressão do tronco braquiocefálico pelo mediastinoscópio interrompe o fluxo para a artéria subclávia direita e para a &lt;strong&gt;carótida comum direita&lt;/strong&gt;. O sinal aparece à direita: perda da onda de pulso do oxímetro e queda da pressão arterial daquele membro. Por isso a monitorização recomendada é justamente essa: oximetria ou pressão arterial no braço direito para detectar a compressão, e pressão no braço esquerdo para refletir a pressão sistêmica verdadeira. A conduta é comunicação imediata ao cirurgião para alívio da compressão, pelo risco de isquemia cerebral no território carotídeo direito (B). Outras complicações a antecipar são hemorragia maciça, pneumotórax, rouquidão por lesão do recorrente e bradicardia reflexa por estímulo vagal ou compressão traqueal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) atribuir a artefato posterga a correção de uma isquemia potencialmente encefálica; (C) hemorragia venosa significativa causaria hipotensão sistêmica, detectável também à esquerda; (D) bloqueio simpático não explica a assimetria nem coincide com a manipulação do instrumento.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Todo derrame parapneumônico deve ser classificado, porque a conduta muda. O derrame não complicado é exsudato estéril, com pH acima de 7,20 e glicose preservada, e responde ao antibiótico isoladamente. O derrame &lt;strong&gt;complicado&lt;/strong&gt; resulta da invasão bacteriana do espaço pleural: o metabolismo anaeróbio de neutrófilos e bactérias consome glicose e produz ácido láctico e dióxido de carbono, gerando a tríade pH baixo, glicose baixa e desidrogenase láctica alta. O empiema é a etapa seguinte, com pus franco.&lt;/p&gt;&lt;p&gt;Os valores do caso — pH 7,05, glicose 28 mg/dL e desidrogenase láctica de 1400 U/L, com líquido turvo e septado — caracterizam derrame parapneumônico complicado. A indicação é de &lt;strong&gt;drenagem pleural&lt;/strong&gt; associada ao antibiótico (D), pois o espaço infectado não é esterilizado apenas por via sistêmica. Na loculação persistente, consideram-se fibrinolítico intrapleural com desoxirribonuclease ou abordagem cirúrgica videotoracoscópica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o Gram negativo é frequente e não exclui infecção pleural, sendo o perfil bioquímico suficiente para indicar drenagem; (B) desidrogenase láctica elevada e aspecto turvo definem exsudato pelos critérios de Light, e não transudato; (C) a cirurgia não é a primeira medida na fase fibrinopurulenta, e a fibrinólise intrapleural é justamente uma alternativa nas coleções septadas.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Todo derrame parapneumônico deve ser classificado, porque a conduta muda. O derrame não complicado é exsudato estéril, com pH acima de 7,20 e glicose preservada, e responde ao antibiótico isoladamente. O derrame &lt;strong&gt;complicado&lt;/strong&gt; resulta da invasão bacteriana do espaço pleural: o metabolismo anaeróbio de neutrófilos e bactérias consome glicose e produz ácido láctico e dióxido de carbono, gerando a tríade pH baixo, glicose baixa e desidrogenase láctica alta. O empiema é a etapa seguinte, com pus franco.&lt;/p&gt;&lt;p&gt;Os valores do caso (pH 7,05, glicose 28 mg/dL e desidrogenase láctica de 1400 U/L, com líquido turvo e septado) caracterizam derrame parapneumônico complicado. A indicação é de &lt;strong&gt;drenagem pleural&lt;/strong&gt; associada ao antibiótico (D), pois o espaço infectado não é esterilizado apenas por via sistêmica. Na loculação persistente, consideram-se fibrinolítico intrapleural com desoxirribonuclease ou abordagem cirúrgica videotoracoscópica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o Gram negativo é frequente e não exclui infecção pleural, sendo o perfil bioquímico suficiente para indicar drenagem; (B) desidrogenase láctica elevada e aspecto turvo definem exsudato pelos critérios de Light, e não transudato; (C) a cirurgia não é a primeira medida na fase fibrinopurulenta, e a fibrinólise intrapleural é justamente uma alternativa nas coleções septadas.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os &lt;strong&gt;bloqueadores dos canais de cálcio&lt;/strong&gt; dividem-se em di-hidropiridínicos (nifedipino, anlodipino), de ação predominantemente vasodilatadora arteriolar, e não di-hidropiridínicos (verapamil e diltiazem), que além de vasodilatar deprimem a contratilidade e a condução no nó atrioventricular. Os &lt;strong&gt;halogenados&lt;/strong&gt; reduzem a disponibilidade de cálcio no miócito e deprimem automaticidade e condução, de modo que seus efeitos se somam aos das duas classes usadas pelo paciente.&lt;/p&gt;&lt;p&gt;A associação de betabloqueador, verapamil e halogenado produz efeito &lt;em&gt;aditivo&lt;/em&gt; sobre o nó atrioventricular e sobre o inotropismo, com risco de bradicardia grave, bloqueio atrioventricular avançado e hipotensão. A conduta não é suspender as medicações, e sim antecipar a interação: titular cuidadosamente o halogenado, manter disponíveis atropina, marca-passo transcutâneo e sais de cálcio — o cloreto ou gluconato de cálcio reverte parcialmente o efeito inotrópico negativo do verapamil.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; não existe indicação de trocar verapamil por anlodipino na véspera (A), conduta sem respaldo e que perderia o controle da resposta ventricular da fibrilação atrial. Suspender o betabloqueador (C) é o erro clássico: a retirada abrupta causa hipertensão e taquicardia de rebote e associa-se a mais isquemia perioperatória, devendo o fármaco ser mantido inclusive no dia da cirurgia. Os halogenados potencializam, e não antagonizam, o bloqueio dos canais de cálcio (D). A alternativa (B) descreve a interação real.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os &lt;strong&gt;bloqueadores dos canais de cálcio&lt;/strong&gt; dividem-se em di-hidropiridínicos (nifedipino, anlodipino), de ação predominantemente vasodilatadora arteriolar, e não di-hidropiridínicos (verapamil e diltiazem), que além de vasodilatar deprimem a contratilidade e a condução no nó atrioventricular. Os &lt;strong&gt;halogenados&lt;/strong&gt; reduzem a disponibilidade de cálcio no miócito e deprimem automaticidade e condução, de modo que seus efeitos se somam aos das duas classes usadas pelo paciente.&lt;/p&gt;&lt;p&gt;A associação de betabloqueador, verapamil e halogenado produz efeito &lt;em&gt;aditivo&lt;/em&gt; sobre o nó atrioventricular e sobre o inotropismo, com risco de bradicardia grave, bloqueio atrioventricular avançado e hipotensão. A conduta não é suspender as medicações, e sim antecipar a interação: titular cuidadosamente o halogenado, manter disponíveis atropina, marca-passo transcutâneo e sais de cálcio; o cloreto ou gluconato de cálcio reverte parcialmente o efeito inotrópico negativo do verapamil.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; não existe indicação de trocar verapamil por anlodipino na véspera (A), conduta sem respaldo e que perderia o controle da resposta ventricular da fibrilação atrial. Suspender o betabloqueador (C) é o erro clássico: a retirada abrupta causa hipertensão e taquicardia de rebote e associa-se a mais isquemia perioperatória, devendo o fármaco ser mantido inclusive no dia da cirurgia. Os halogenados potencializam, e não antagonizam, o bloqueio dos canais de cálcio (D). A alternativa (B) descreve a interação real.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O tônus vascular é sustentado por três sistemas paralelos: o &lt;strong&gt;simpático&lt;/strong&gt;, o &lt;strong&gt;eixo renina-angiotensina-aldosterona&lt;/strong&gt; e a &lt;strong&gt;vasopressina&lt;/strong&gt;. A indução anestésica deprime o primeiro; se o paciente tomou inibidor da ECA ou bloqueador do receptor de angiotensina nas horas anteriores, o segundo também está bloqueado, restando apenas o terceiro. Daí a hipotensão precoce, profunda e caracteristicamente &lt;em&gt;refratária a efedrina e fenilefrina&lt;/em&gt;.&lt;/p&gt;&lt;p&gt;Nesse cenário, a &lt;strong&gt;vasopressina&lt;/strong&gt; em bolus de 1 a 2 unidades, seguida de infusão de 0,01 a 0,04 U/min quando necessário, restaura o tônus por uma via independente — o receptor V1 acoplado à proteína Gq — e é o resgate mais eficaz. A prevenção consiste em suspender o anti-hipertensivo na manhã do procedimento, com antecedência maior para os bloqueadores do receptor de angiotensina, de meia-vida mais longa. A exceção é o paciente com insuficiência cardíaca de fração de ejeção reduzida, em que a decisão é individualizada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; insistir em doses crescentes de fenilefrina (A) repete a via alfa-adrenérgica já demonstrada ineficaz e apenas retarda o tratamento. A atropina (B) não corrige vasoplegia, e a frequência de 78 bpm é adequada. A dobutamina (C) trata baixo débito por falência contrátil, que não é o mecanismo aqui, e seu componente beta-2 pode aprofundar a hipotensão. A alternativa (D) contorna o bloqueio farmacológico existente.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O tônus vascular é sustentado por três sistemas paralelos: o &lt;strong&gt;simpático&lt;/strong&gt;, o &lt;strong&gt;eixo renina-angiotensina-aldosterona&lt;/strong&gt; e a &lt;strong&gt;vasopressina&lt;/strong&gt;. A indução anestésica deprime o primeiro; se o paciente tomou inibidor da ECA ou bloqueador do receptor de angiotensina nas horas anteriores, o segundo também está bloqueado, restando apenas o terceiro. Daí a hipotensão precoce, profunda e caracteristicamente &lt;em&gt;refratária a efedrina e fenilefrina&lt;/em&gt;.&lt;/p&gt;&lt;p&gt;Nesse cenário, a &lt;strong&gt;vasopressina&lt;/strong&gt; em bolus de 1 a 2 unidades, seguida de infusão de 0,01 a 0,04 U/min quando necessário, restaura o tônus por uma via independente, o receptor V1 acoplado à proteína Gq, e é o resgate mais eficaz. A prevenção consiste em suspender o anti-hipertensivo na manhã do procedimento, com antecedência maior para os bloqueadores do receptor de angiotensina, de meia-vida mais longa. A exceção é o paciente com insuficiência cardíaca de fração de ejeção reduzida, em que a decisão é individualizada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; insistir em doses crescentes de fenilefrina (A) repete a via alfa-adrenérgica já demonstrada ineficaz e apenas retarda o tratamento. A atropina (B) não corrige vasoplegia, e a frequência de 78 bpm é adequada. A dobutamina (C) trata baixo débito por falência contrátil, que não é o mecanismo aqui, e seu componente beta-2 pode aprofundar a hipotensão. A alternativa (D) contorna o bloqueio farmacológico existente.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Ao início da &lt;strong&gt;circulação extracorpórea&lt;/strong&gt;, o volume de perfusato do circuito — habitualmente 1200 a 1800 mL de solução cristaloide — mistura-se de forma abrupta ao sangue do paciente. A consequência imediata é &lt;strong&gt;hemodiluição aguda&lt;/strong&gt;, com queda do hematócrito para valores em torno de 20 a 25% e redução proporcional da viscosidade sanguínea.&lt;/p&gt;&lt;p&gt;Como a resistência ao fluxo é diretamente proporcional à viscosidade, a resistência vascular sistêmica despenca e, mantido o fluxo de bomba constante, a pressão arterial média cai de forma característica para 30 a 40 mmHg nos primeiros minutos. Contribuem ainda a diluição das catecolaminas circulantes e a natureza não pulsátil do fluxo. É fenômeno esperado e em geral transitório: a pressão recupera-se nos minutos seguintes com a liberação de catecolaminas endógenas. Persistindo, corrige-se com vasoconstritor, mantendo-se o fluxo indexado. A proteção miocárdica nessa fase passa a depender da cardioplegia e da hipotermia, que reduzem o consumo de oxigênio do coração parado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a obstrução da cânula venosa (B) foi afastada pelo enunciado, que descreve reservatório adequado, e cursaria com queda do volume do reservatório e ingurgitamento venoso visível. A cardioplegia (C) sequer foi administrada, pois a aorta ainda não foi pinçada, e atua sobre o coração excluído da circulação. A vasoplegia inflamatória (D) existe, mas se instala ao longo da perfusão e no pós-operatório, não nos primeiros segundos. A alternativa (A) explica o achado.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Ao início da &lt;strong&gt;circulação extracorpórea&lt;/strong&gt;, o volume de perfusato do circuito (habitualmente 1200 a 1800 mL de solução cristaloide) mistura-se de forma abrupta ao sangue do paciente. A consequência imediata é &lt;strong&gt;hemodiluição aguda&lt;/strong&gt;, com queda do hematócrito para valores em torno de 20 a 25% e redução proporcional da viscosidade sanguínea.&lt;/p&gt;&lt;p&gt;Como a resistência ao fluxo é diretamente proporcional à viscosidade, a resistência vascular sistêmica despenca e, mantido o fluxo de bomba constante, a pressão arterial média cai de forma característica para 30 a 40 mmHg nos primeiros minutos. Contribuem ainda a diluição das catecolaminas circulantes e a natureza não pulsátil do fluxo. É fenômeno esperado e em geral transitório: a pressão recupera-se nos minutos seguintes com a liberação de catecolaminas endógenas. Persistindo, corrige-se com vasoconstritor, mantendo-se o fluxo indexado. A proteção miocárdica nessa fase passa a depender da cardioplegia e da hipotermia, que reduzem o consumo de oxigênio do coração parado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a obstrução da cânula venosa (B) foi afastada pelo enunciado, que descreve reservatório adequado, e cursaria com queda do volume do reservatório e ingurgitamento venoso visível. A cardioplegia (C) sequer foi administrada, pois a aorta ainda não foi pinçada, e atua sobre o coração excluído da circulação. A vasoplegia inflamatória (D) existe, mas se instala ao longo da perfusão e no pós-operatório, não nos primeiros segundos. A alternativa (A) explica o achado.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O código internacional de estimulação cardíaca identifica, nas três primeiras letras, a câmara estimulada, a câmara sentida e a resposta à detecção. No modo &lt;strong&gt;VVI&lt;/strong&gt;, o ventrículo é estimulado e sentido, e a detecção de um batimento espontâneo &lt;em&gt;inibe&lt;/em&gt; o estímulo programado. É justamente essa inibição que torna perigoso o eletrocautério monopolar: a corrente pode ser interpretada como atividade ventricular própria e suprimir a estimulação, o que em bloqueio atrioventricular total significa assistolia.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;ímã&lt;/strong&gt; aplicado sobre um marca-passo definitivo suspende a função de sensibilidade e converte o gerador para o modo &lt;strong&gt;assíncrono&lt;/strong&gt; — VOO, no caso de um VVI —, em frequência fixa predefinida pelo fabricante, habitualmente entre 80 e 100 bpm com bateria plena e progressivamente menor com o esgotamento. O efeito cessa ao remover o ímã. Medidas complementares incluem posicionar a placa de retorno de modo que a corrente não atravesse o gerador, preferir o bisturi bipolar e limitar a duração de cada aplicação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o ímã não inibe a estimulação (A) nem deixa alteração permanente que exija reprogramação. Não há conversão para DDD (C): o ímã não altera modos programados, apenas ativa a resposta assíncrona predefinida. Em cardioversores-desfibriladores implantáveis (D), o ímã suspende as terapias de taquiarritmia, mas não modifica a estimulação antibradicardia, que continua inibida pela sensibilidade. A alternativa (B) está correta.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O código internacional de estimulação cardíaca identifica, nas três primeiras letras, a câmara estimulada, a câmara sentida e a resposta à detecção. No modo &lt;strong&gt;VVI&lt;/strong&gt;, o ventrículo é estimulado e sentido, e a detecção de um batimento espontâneo &lt;em&gt;inibe&lt;/em&gt; o estímulo programado. É justamente essa inibição que torna perigoso o eletrocautério monopolar: a corrente pode ser interpretada como atividade ventricular própria e suprimir a estimulação, o que em bloqueio atrioventricular total significa assistolia.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;ímã&lt;/strong&gt; aplicado sobre um marca-passo definitivo suspende a função de sensibilidade e converte o gerador para o modo &lt;strong&gt;assíncrono&lt;/strong&gt; (VOO, no caso de um VVI), em frequência fixa predefinida pelo fabricante, habitualmente entre 80 e 100 bpm com bateria plena e progressivamente menor com o esgotamento. O efeito cessa ao remover o ímã. Medidas complementares incluem posicionar a placa de retorno de modo que a corrente não atravesse o gerador, preferir o bisturi bipolar e limitar a duração de cada aplicação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; o ímã não inibe a estimulação (A) nem deixa alteração permanente que exija reprogramação. Não há conversão para DDD (C): o ímã não altera modos programados, apenas ativa a resposta assíncrona predefinida. Em cardioversores-desfibriladores implantáveis (D), o ímã suspende as terapias de taquiarritmia, mas não modifica a estimulação antibradicardia, que continua inibida pela sensibilidade. A alternativa (B) está correta.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Tanto a &lt;strong&gt;insuficiência aórtica&lt;/strong&gt; quanto a insuficiência mitral são lesões de &lt;em&gt;sobrecarga de volume&lt;/em&gt;, e suas metas hemodinâmicas resumem-se na regra prática cheio, rápido e para frente. A pressão de pulso alargada do caso, com diastólica de 48 mmHg, é a assinatura clínica do grande volume regurgitante.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Frequência de 80 a 100 bpm:&lt;/strong&gt; a taquicardia relativa encurta a diástole, período em que ocorre a regurgitação aórtica, reduzindo o volume que retorna ao ventrículo a cada ciclo.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Resistência vascular sistêmica baixa:&lt;/strong&gt; a redução da impedância aórtica direciona o volume sistólico para a frente; qualquer aumento da pós-carga amplia a fração regurgitante.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pré-carga elevada:&lt;/strong&gt; o ventrículo dilatado e complacente depende de volume adequado para manter o volume sistólico efetivo.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Complementam o manejo a manutenção do ritmo sinusal, a evitação da bradicardia e cautela com o pneumoperitônio, que eleva a pós-carga. Na insuficiência mitral valem os mesmos princípios, com atenção adicional à pressão da artéria pulmonar.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; as frequências de 50 a 60 bpm (A e B) prolongam a diástole e aumentam o volume regurgitante — são metas da estenose aórtica e da coronariopatia, não da regurgitação. A combinação de resistência vascular elevada com pré-carga reduzida (A e C) piora simultaneamente a fração regurgitante e o débito anterógrado. A alternativa (D) reúne as três metas corretas.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Tanto a &lt;strong&gt;insuficiência aórtica&lt;/strong&gt; quanto a insuficiência mitral são lesões de &lt;em&gt;sobrecarga de volume&lt;/em&gt;, e suas metas hemodinâmicas resumem-se na regra prática cheio, rápido e para frente. A pressão de pulso alargada do caso, com diastólica de 48 mmHg, é a assinatura clínica do grande volume regurgitante.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Frequência de 80 a 100 bpm:&lt;/strong&gt; a taquicardia relativa encurta a diástole, período em que ocorre a regurgitação aórtica, reduzindo o volume que retorna ao ventrículo a cada ciclo.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Resistência vascular sistêmica baixa:&lt;/strong&gt; a redução da impedância aórtica direciona o volume sistólico para a frente; qualquer aumento da pós-carga amplia a fração regurgitante.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pré-carga elevada:&lt;/strong&gt; o ventrículo dilatado e complacente depende de volume adequado para manter o volume sistólico efetivo.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Complementam o manejo a manutenção do ritmo sinusal, a evitação da bradicardia e cautela com o pneumoperitônio, que eleva a pós-carga. Na insuficiência mitral valem os mesmos princípios, com atenção adicional à pressão da artéria pulmonar.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; as frequências de 50 a 60 bpm (A e B) prolongam a diástole e aumentam o volume regurgitante; são metas da estenose aórtica e da coronariopatia, não da regurgitação. A combinação de resistência vascular elevada com pré-carga reduzida (A e C) piora simultaneamente a fração regurgitante e o débito anterógrado. A alternativa (D) reúne as três metas corretas.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Na &lt;strong&gt;revascularização miocárdica sem circulação extracorpórea&lt;/strong&gt;, a exposição das artérias da parede lateral e inferior exige luxar o coração para fora da cavidade pericárdica. A manobra distorce a geometria ventricular, comprime as câmaras direitas e angula as veias cavas, produzindo &lt;strong&gt;queda do retorno venoso e do débito cardíaco com elevação paradoxal das pressões de enchimento&lt;/strong&gt; — exatamente o padrão descrito, com pressão venosa central subindo de 8 para 18 mmHg enquanto o débito cai para 2,4 L/min. Trata-se de obstrução mecânica ao enchimento, e não de falência contrátil primária.&lt;/p&gt;&lt;p&gt;A conduta inicial é simultaneamente hemodinâmica e cirúrgica: comunicar o achado ao cirurgião e solicitar &lt;strong&gt;reposicionamento do coração&lt;/strong&gt; ou alívio temporário do estabilizador, colocar o paciente em &lt;strong&gt;Trendelenburg&lt;/strong&gt; para aumentar o retorno venoso e expandir a volemia. Abertura da pleura direita, uso criterioso de vasopressor e correção imediata de arritmias completam o manejo. A conversão para circulação extracorpórea fica reservada aos casos que não respondem a essas medidas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a conversão imediata (B) é desproporcional diante de um evento transitório e reversível com manobras simples. A noradrenalina em dose alta (C) eleva a pressão sem corrigir a causa mecânica e aumenta a pós-carga de um ventrículo direito já comprimido. Elevar a pressão positiva expiratória final (D) reduz ainda mais o retorno venoso e agrava o quadro. A alternativa (A) reúne as medidas de primeira linha.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Na &lt;strong&gt;revascularização miocárdica sem circulação extracorpórea&lt;/strong&gt;, a exposição das artérias da parede lateral e inferior exige luxar o coração para fora da cavidade pericárdica. A manobra distorce a geometria ventricular, comprime as câmaras direitas e angula as veias cavas, produzindo &lt;strong&gt;queda do retorno venoso e do débito cardíaco com elevação paradoxal das pressões de enchimento&lt;/strong&gt;, exatamente o padrão descrito, com pressão venosa central subindo de 8 para 18 mmHg enquanto o débito cai para 2,4 L/min. Trata-se de obstrução mecânica ao enchimento, e não de falência contrátil primária.&lt;/p&gt;&lt;p&gt;A conduta inicial é simultaneamente hemodinâmica e cirúrgica: comunicar o achado ao cirurgião e solicitar &lt;strong&gt;reposicionamento do coração&lt;/strong&gt; ou alívio temporário do estabilizador, colocar o paciente em &lt;strong&gt;Trendelenburg&lt;/strong&gt; para aumentar o retorno venoso e expandir a volemia. Abertura da pleura direita, uso criterioso de vasopressor e correção imediata de arritmias completam o manejo. A conversão para circulação extracorpórea fica reservada aos casos que não respondem a essas medidas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a conversão imediata (B) é desproporcional diante de um evento transitório e reversível com manobras simples. A noradrenalina em dose alta (C) eleva a pressão sem corrigir a causa mecânica e aumenta a pós-carga de um ventrículo direito já comprimido. Elevar a pressão positiva expiratória final (D) reduz ainda mais o retorno venoso e agrava o quadro. A alternativa (A) reúne as medidas de primeira linha.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;desdobramento fixo da segunda bulha&lt;/strong&gt; — aquele que não varia entre inspiração e expiração — é o sinal semiológico característico da &lt;strong&gt;comunicação interatrial&lt;/strong&gt;. Na CIA, o shunt da esquerda para a direita em nível atrial mantém constante o volume de enchimento do ventrículo direito ao longo do ciclo respiratório: o aumento inspiratório do retorno venoso sistêmico é compensado por redução recíproca do shunt, de modo que o fechamento da valva pulmonar permanece igualmente atrasado nas duas fases.&lt;/p&gt;&lt;p&gt;O sopro sistólico ejetivo em foco pulmonar não é gerado pela passagem através do defeito septal, cujo gradiente é mínimo, e sim pelo &lt;strong&gt;hiperfluxo&lt;/strong&gt; através da valva pulmonar. Quando o shunt é grande, com relação de fluxo pulmonar/sistêmico acima de 2:1, pode surgir também ruflar diastólico tricúspide. A forma &lt;em&gt;ostium secundum&lt;/em&gt; é a mais frequente e costuma ser reconhecida apenas na vida adulta, com sintomas discretos, como no caso apresentado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; na estenose pulmonar (A) o desdobramento é amplo, porém &lt;em&gt;variável&lt;/em&gt; com a respiração, com clique de ejeção e segunda bulha pulmonar hipofonética. A comunicação interventricular restritiva (B) produz sopro holossistólico rude em borda esternal esquerda baixa, e não sopro ejetivo pulmonar. A persistência do canal arterial (D) caracteriza-se por sopro &lt;em&gt;contínuo&lt;/em&gt;, em maquinaria, infraclavicular esquerdo. A alternativa (C) é a única compatível com o conjunto descrito.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;desdobramento fixo da segunda bulha&lt;/strong&gt;, aquele que não varia entre inspiração e expiração, é o sinal semiológico característico da &lt;strong&gt;comunicação interatrial&lt;/strong&gt;. Na CIA, o shunt da esquerda para a direita em nível atrial mantém constante o volume de enchimento do ventrículo direito ao longo do ciclo respiratório: o aumento inspiratório do retorno venoso sistêmico é compensado por redução recíproca do shunt, de modo que o fechamento da valva pulmonar permanece igualmente atrasado nas duas fases.&lt;/p&gt;&lt;p&gt;O sopro sistólico ejetivo em foco pulmonar não é gerado pela passagem através do defeito septal, cujo gradiente é mínimo, e sim pelo &lt;strong&gt;hiperfluxo&lt;/strong&gt; através da valva pulmonar. Quando o shunt é grande, com relação de fluxo pulmonar/sistêmico acima de 2:1, pode surgir também ruflar diastólico tricúspide. A forma &lt;em&gt;ostium secundum&lt;/em&gt; é a mais frequente e costuma ser reconhecida apenas na vida adulta, com sintomas discretos, como no caso apresentado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; na estenose pulmonar (A) o desdobramento é amplo, porém &lt;em&gt;variável&lt;/em&gt; com a respiração, com clique de ejeção e segunda bulha pulmonar hipofonética. A comunicação interventricular restritiva (B) produz sopro holossistólico rude em borda esternal esquerda baixa, e não sopro ejetivo pulmonar. A persistência do canal arterial (D) caracteriza-se por sopro &lt;em&gt;contínuo&lt;/em&gt;, em maquinaria, infraclavicular esquerdo. A alternativa (C) é a única compatível com o conjunto descrito.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os dados ecocardiográficos configuram &lt;strong&gt;estenose aórtica grave&lt;/strong&gt; e são internamente coerentes: área valvar de 0,7 cm&lt;sup&gt;2&lt;/sup&gt; (grave abaixo de 1,0 cm&lt;sup&gt;2&lt;/sup&gt;), velocidade máxima de 4,4 m/s (grave acima de 4,0 m/s) e gradiente médio de 48 mmHg (grave acima de 40 mmHg), com fração de ejeção preservada. A presença de &lt;strong&gt;sintomas&lt;/strong&gt; — dispneia e síncope — muda radicalmente o prognóstico e impõe intervenção, já que a sobrevida da estenose aórtica sintomática não tratada é medida em poucos anos.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;implante valvar aórtico transcateter&lt;/strong&gt; surgiu como opção para pacientes inoperáveis ou de alto risco cirúrgico e teve suas indicações progressivamente ampliadas para risco intermediário e, em idosos com valva tricúspide e anatomia favorável, também para risco baixo. Esta paciente reúne precisamente os fatores que penalizam a cirurgia aberta: idade avançada, DPOC grave, reoperação e &lt;em&gt;aorta em porcelana&lt;/em&gt;, que praticamente inviabiliza o pinçamento aórtico. O acesso transfemoral é o preferencial, com alternativas transapical, transaórtica ou transubclávia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a valvoplastia por balão (A) produz alívio transitório, com reestenose em poucos meses, servindo apenas como ponte ou medida paliativa. A abstenção terapêutica (B) ignora que a idade isolada não contraindica intervenção e condena a paciente a alta mortalidade. A cirurgia convencional (C) é inadequada diante da aorta em porcelana e do risco proibitivo. A alternativa (D) corresponde à indicação clássica do procedimento.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os dados ecocardiográficos configuram &lt;strong&gt;estenose aórtica grave&lt;/strong&gt; e são internamente coerentes: área valvar de 0,7 cm&lt;sup&gt;2&lt;/sup&gt; (grave abaixo de 1,0 cm&lt;sup&gt;2&lt;/sup&gt;), velocidade máxima de 4,4 m/s (grave acima de 4,0 m/s) e gradiente médio de 48 mmHg (grave acima de 40 mmHg), com fração de ejeção preservada. A presença de &lt;strong&gt;sintomas&lt;/strong&gt; (dispneia e síncope) muda radicalmente o prognóstico e impõe intervenção, já que a sobrevida da estenose aórtica sintomática não tratada é medida em poucos anos.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;implante valvar aórtico transcateter&lt;/strong&gt; surgiu como opção para pacientes inoperáveis ou de alto risco cirúrgico e teve suas indicações progressivamente ampliadas para risco intermediário e, em idosos com valva tricúspide e anatomia favorável, também para risco baixo. Esta paciente reúne precisamente os fatores que penalizam a cirurgia aberta: idade avançada, DPOC grave, reoperação e &lt;em&gt;aorta em porcelana&lt;/em&gt;, que praticamente inviabiliza o pinçamento aórtico. O acesso transfemoral é o preferencial, com alternativas transapical, transaórtica ou transubclávia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; a valvoplastia por balão (A) produz alívio transitório, com reestenose em poucos meses, servindo apenas como ponte ou medida paliativa. A abstenção terapêutica (B) ignora que a idade isolada não contraindica intervenção e condena a paciente a alta mortalidade. A cirurgia convencional (C) é inadequada diante da aorta em porcelana e do risco proibitivo. A alternativa (D) corresponde à indicação clássica do procedimento.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nos &lt;strong&gt;dispositivos de assistência ventricular esquerda de fluxo contínuo&lt;/strong&gt;, o fluxo gerado depende da rotação programada, da pré-carga do ventrículo esquerdo e da diferença de pressão entre a cavidade e a aorta. O alarme de &lt;strong&gt;baixo fluxo&lt;/strong&gt; tem quatro causas principais: hipovolemia, tamponamento, aumento excessivo da pós-carga sistêmica e &lt;strong&gt;falência do ventrículo direito&lt;/strong&gt;, esta a mais temida no intraoperatório, sobretudo com pneumoperitônio e ventilação com pressão positiva.&lt;/p&gt;&lt;p&gt;O caso descreve o padrão típico da disfunção ventricular direita: pressão venosa central em ascensão, ventrículo direito dilatado e hipocontrátil, desvio do septo para a esquerda e cavidade esquerda pequena — o dispositivo simplesmente não consegue encher. O tratamento é &lt;strong&gt;sustentar o ventrículo direito&lt;/strong&gt;: inotrópico (milrinona ou dobutamina), vasodilatador pulmonar inalatório (óxido nítrico ou prostaciclina), volume cauteloso, correção de hipoxemia, hipercapnia e acidose e manutenção da pressão de perfusão coronariana direita. Lembre-se de que esses pacientes podem não ter pulso palpável, tornando a oximetria e a pressão não invasiva pouco confiáveis: a linha arterial é indispensável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; aumentar a rotação (B) acentua o desvio septal e provoca eventos de sucção, com colapso da cavidade esquerda e arritmias. A noradrenalina isolada em dose alta (C) eleva a pós-carga e reduz o fluxo do dispositivo, sem tratar a falência direita. Não há dados de trombose de bomba (D), que cursaria com hemólise e elevação do consumo de potência. A alternativa (A) trata a causa.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Nos &lt;strong&gt;dispositivos de assistência ventricular esquerda de fluxo contínuo&lt;/strong&gt;, o fluxo gerado depende da rotação programada, da pré-carga do ventrículo esquerdo e da diferença de pressão entre a cavidade e a aorta. O alarme de &lt;strong&gt;baixo fluxo&lt;/strong&gt; tem quatro causas principais: hipovolemia, tamponamento, aumento excessivo da pós-carga sistêmica e &lt;strong&gt;falência do ventrículo direito&lt;/strong&gt;, esta a mais temida no intraoperatório, sobretudo com pneumoperitônio e ventilação com pressão positiva.&lt;/p&gt;&lt;p&gt;O caso descreve o padrão típico da disfunção ventricular direita: pressão venosa central em ascensão, ventrículo direito dilatado e hipocontrátil, desvio do septo para a esquerda e cavidade esquerda pequena; o dispositivo simplesmente não consegue encher. O tratamento é &lt;strong&gt;sustentar o ventrículo direito&lt;/strong&gt;: inotrópico (milrinona ou dobutamina), vasodilatador pulmonar inalatório (óxido nítrico ou prostaciclina), volume cauteloso, correção de hipoxemia, hipercapnia e acidose e manutenção da pressão de perfusão coronariana direita. Lembre-se de que esses pacientes podem não ter pulso palpável, tornando a oximetria e a pressão não invasiva pouco confiáveis: a linha arterial é indispensável.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; aumentar a rotação (B) acentua o desvio septal e provoca eventos de sucção, com colapso da cavidade esquerda e arritmias. A noradrenalina isolada em dose alta (C) eleva a pós-carga e reduz o fluxo do dispositivo, sem tratar a falência direita. Não há dados de trombose de bomba (D), que cursaria com hemólise e elevação do consumo de potência. A alternativa (A) trata a causa.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A resistência ao fluxo laminar em um tubo é descrita pela &lt;strong&gt;lei de Poiseuille&lt;/strong&gt;, em que a resistência é diretamente proporcional à viscosidade do fluido e ao comprimento do tubo e &lt;strong&gt;inversamente proporcional à quarta potência do raio&lt;/strong&gt;. Disso decorre que reduzir o raio à metade multiplica a resistência por 2&lt;sup&gt;4&lt;/sup&gt;, ou seja, &lt;strong&gt;dezesseis vezes&lt;/strong&gt; — razão pela qual pequenas variações do tônus arteriolar produzem efeito hemodinâmico desproporcional.&lt;/p&gt;&lt;p&gt;As &lt;strong&gt;arteríolas&lt;/strong&gt;, vasos com cerca de 10 a 100 micrômetros de diâmetro, espessa camada de músculo liso e rica inervação simpática, são por isso denominadas &lt;em&gt;vasos de resistência&lt;/em&gt;: nelas ocorre a maior queda pressórica do circuito sistêmico, e é sobre elas que atuam os vasoconstritores e vasodilatadores empregados em anestesia. As vênulas e veias, ao contrário, são os &lt;em&gt;vasos de capacitância&lt;/em&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; embora o capilar individual tenha o menor diâmetro (A), a área de secção transversal total do leito capilar é imensa e sua resistência somada é baixa, com pequena queda pressórica ao longo dele. O sistema venoso (C) abriga cerca de 65 a 70% do volume sanguíneo, e não 20%, e contribui pouco para a resistência. A relação descrita em (D) está invertida nos dois termos: a resistência é &lt;em&gt;inversamente&lt;/em&gt; proporcional à quarta potência do raio e &lt;em&gt;diretamente&lt;/em&gt; proporcional à viscosidade. A alternativa (B) está correta.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A resistência ao fluxo laminar em um tubo é descrita pela &lt;strong&gt;lei de Poiseuille&lt;/strong&gt;, em que a resistência é diretamente proporcional à viscosidade do fluido e ao comprimento do tubo e &lt;strong&gt;inversamente proporcional à quarta potência do raio&lt;/strong&gt;. Disso decorre que reduzir o raio à metade multiplica a resistência por 2&lt;sup&gt;4&lt;/sup&gt;, ou seja, &lt;strong&gt;dezesseis vezes&lt;/strong&gt;, razão pela qual pequenas variações do tônus arteriolar produzem efeito hemodinâmico desproporcional.&lt;/p&gt;&lt;p&gt;As &lt;strong&gt;arteríolas&lt;/strong&gt;, vasos com cerca de 10 a 100 micrômetros de diâmetro, espessa camada de músculo liso e rica inervação simpática, são por isso denominadas &lt;em&gt;vasos de resistência&lt;/em&gt;: nelas ocorre a maior queda pressórica do circuito sistêmico, e é sobre elas que atuam os vasoconstritores e vasodilatadores empregados em anestesia. As vênulas e veias, ao contrário, são os &lt;em&gt;vasos de capacitância&lt;/em&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; embora o capilar individual tenha o menor diâmetro (A), a área de secção transversal total do leito capilar é imensa e sua resistência somada é baixa, com pequena queda pressórica ao longo dele. O sistema venoso (C) abriga cerca de 65 a 70% do volume sanguíneo, e não 20%, e contribui pouco para a resistência. A relação descrita em (D) está invertida nos dois termos: a resistência é &lt;em&gt;inversamente&lt;/em&gt; proporcional à quarta potência do raio e &lt;em&gt;diretamente&lt;/em&gt; proporcional à viscosidade. A alternativa (B) está correta.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A ciclo-oxigenase converte o ácido araquidônico em prostaglandinas e tromboxano. A &lt;strong&gt;COX-1&lt;/strong&gt; é constitutiva e responde pela citoproteção gástrica, pela autorregulação do fluxo renal e pela síntese plaquetária de &lt;strong&gt;tromboxano A&lt;sub&gt;2&lt;/sub&gt;&lt;/strong&gt;, indispensável à agregação. A &lt;strong&gt;COX-2&lt;/strong&gt; é predominantemente induzível pela inflamação, embora também tenha expressão constitutiva no rim e no endotélio, onde gera prostaciclina.&lt;/p&gt;&lt;p&gt;O ácido acetilsalicílico difere dos demais AINEs por &lt;strong&gt;acetilar covalentemente&lt;/strong&gt; o sítio ativo da COX-1. Como a plaqueta é anucleada e não sintetiza nova enzima, a inibição dura toda a vida daquela plaqueta; a recuperação depende da renovação do pool circulante, o que consome cerca de 7 a 10 dias, com retorno funcional relevante em torno do quinto dia. Os AINEs não seletivos, como o ibuprofeno e o cetoprofeno, ligam-se de forma &lt;em&gt;competitiva e reversível&lt;/em&gt;: a função plaquetária normaliza em um a três intervalos de meia-vida após a suspensão, em geral 24 a 72 horas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) inverte o mecanismo — o ibuprofeno é inibidor reversível e não requer janela de 7 a 10 dias; curiosamente, quando administrado antes do ácido acetilsalicílico, pode bloquear o sítio e impedir a acetilação. (C) a plaqueta expressa essencialmente COX-1; a COX-2 tem papel desprezível na agregação. (D) os coxibes poupam a COX-1 plaquetária e não prolongam o tempo de sangramento, o que explica justamente o desequilíbrio entre tromboxano e prostaciclina implicado no seu risco cardiovascular.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A ciclo-oxigenase converte o ácido araquidônico em prostaglandinas e tromboxano. A &lt;strong&gt;COX-1&lt;/strong&gt; é constitutiva e responde pela citoproteção gástrica, pela autorregulação do fluxo renal e pela síntese plaquetária de &lt;strong&gt;tromboxano A&lt;sub&gt;2&lt;/sub&gt;&lt;/strong&gt;, indispensável à agregação. A &lt;strong&gt;COX-2&lt;/strong&gt; é predominantemente induzível pela inflamação, embora também tenha expressão constitutiva no rim e no endotélio, onde gera prostaciclina.&lt;/p&gt;&lt;p&gt;O ácido acetilsalicílico difere dos demais AINEs por &lt;strong&gt;acetilar covalentemente&lt;/strong&gt; o sítio ativo da COX-1. Como a plaqueta é anucleada e não sintetiza nova enzima, a inibição dura toda a vida daquela plaqueta; a recuperação depende da renovação do pool circulante, o que consome cerca de 7 a 10 dias, com retorno funcional relevante em torno do quinto dia. Os AINEs não seletivos, como o ibuprofeno e o cetoprofeno, ligam-se de forma &lt;em&gt;competitiva e reversível&lt;/em&gt;: a função plaquetária normaliza em um a três intervalos de meia-vida após a suspensão, em geral 24 a 72 horas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) inverte o mecanismo: o ibuprofeno é inibidor reversível e não requer janela de 7 a 10 dias; curiosamente, quando administrado antes do ácido acetilsalicílico, pode bloquear o sítio e impedir a acetilação. (C) a plaqueta expressa essencialmente COX-1; a COX-2 tem papel desprezível na agregação. (D) os coxibes poupam a COX-1 plaquetária e não prolongam o tempo de sangramento, o que explica justamente o desequilíbrio entre tromboxano e prostaciclina implicado no seu risco cardiovascular.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Somente a forma &lt;strong&gt;não ionizada&lt;/strong&gt; de um fármaco atravessa livremente membranas lipídicas. No túbulo renal, isso significa que a fração não ionizada presente no filtrado é reabsorvida de volta para o sangue, enquanto a fração ionizada permanece aprisionada na urina e é excretada — fenômeno conhecido como &lt;strong&gt;aprisionamento iônico&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O salicilato é um &lt;em&gt;ácido fraco&lt;/em&gt;, com pKa em torno de 3. Elevar o pH urinário desloca o equilíbrio para a forma dissociada, impedindo a reabsorção tubular e aumentando várias vezes a depuração renal. O mesmo princípio se aplica ao fenobarbital e ao metotrexato. Para bases fracas, como a anfetamina, a lógica se inverte: a acidificação urinária é que favorece a eliminação.&lt;/p&gt;&lt;p&gt;Vale lembrar o outro determinante da fração livre: a &lt;strong&gt;ligação proteica&lt;/strong&gt;. Fármacos ácidos ligam-se preferencialmente à albumina; os básicos, como lidocaína, bupivacaína e alfentanil, à &lt;strong&gt;alfa-1-glicoproteína ácida&lt;/strong&gt;, cuja concentração se eleva no pós-operatório, no trauma e nas neoplasias, reduzindo a fração livre ativa.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a lógica — a alcalinização aumenta a forma &lt;em&gt;ionizada&lt;/em&gt;, e a filtração glomerular depende da fração livre, não do estado de ionização. (C) o bicarbonato não desloca o salicilato da albumina de modo clinicamente relevante, e a conjugação hepática já se encontra saturada nas doses tóxicas. (D) não há indução de secreção tubular ativa pela carga de sódio; o transportador de ânions orgânicos, quando muito, sofre competição.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Somente a forma &lt;strong&gt;não ionizada&lt;/strong&gt; de um fármaco atravessa livremente membranas lipídicas. No túbulo renal, isso significa que a fração não ionizada presente no filtrado é reabsorvida de volta para o sangue, enquanto a fração ionizada permanece aprisionada na urina e é excretada, fenômeno conhecido como &lt;strong&gt;aprisionamento iônico&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O salicilato é um &lt;em&gt;ácido fraco&lt;/em&gt;, com pKa em torno de 3. Elevar o pH urinário desloca o equilíbrio para a forma dissociada, impedindo a reabsorção tubular e aumentando várias vezes a depuração renal. O mesmo princípio se aplica ao fenobarbital e ao metotrexato. Para bases fracas, como a anfetamina, a lógica se inverte: a acidificação urinária é que favorece a eliminação.&lt;/p&gt;&lt;p&gt;Vale lembrar o outro determinante da fração livre: a &lt;strong&gt;ligação proteica&lt;/strong&gt;. Fármacos ácidos ligam-se preferencialmente à albumina; os básicos, como lidocaína, bupivacaína e alfentanil, à &lt;strong&gt;alfa-1-glicoproteína ácida&lt;/strong&gt;, cuja concentração se eleva no pós-operatório, no trauma e nas neoplasias, reduzindo a fração livre ativa.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a lógica: a alcalinização aumenta a forma &lt;em&gt;ionizada&lt;/em&gt;, e a filtração glomerular depende da fração livre, não do estado de ionização. (C) o bicarbonato não desloca o salicilato da albumina de modo clinicamente relevante, e a conjugação hepática já se encontra saturada nas doses tóxicas. (D) não há indução de secreção tubular ativa pela carga de sódio; o transportador de ânions orgânicos, quando muito, sofre competição.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os inibidores da monoaminoxidase impedem a degradação intraneuronal de noradrenalina, dopamina e serotonina, criando dois riscos perioperatórios distintos.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Reação excitatória (tipo I) ou síndrome serotoninérgica:&lt;/strong&gt; hipertermia, rigidez muscular, hiper-reflexia, agitação e instabilidade autonômica. É precipitada por fármacos com atividade serotoninérgica — &lt;em&gt;meperidina&lt;/em&gt;, &lt;em&gt;tramadol&lt;/em&gt;, dextrometorfano, azul de metileno e linezolida. Os opioides fenilpiperidínicos puramente agonistas mu, como fentanil, sufentanil e remifentanil, são considerados a escolha mais segura; a morfina também é aceitável.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Crise hipertensiva:&lt;/strong&gt; desencadeada por simpatomiméticos de &lt;em&gt;ação indireta&lt;/em&gt;, como efedrina e metaraminol, que liberam as catecolaminas acumuladas nas vesículas.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Por isso, a hipotensão deve ser tratada com volume, redução da profundidade anestésica e, se necessário, um agonista de &lt;strong&gt;ação direta&lt;/strong&gt; — fenilefrina ou noradrenalina — iniciado em dose reduzida e titulado, já que a resposta pode estar exagerada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) reúne exatamente os dois fármacos proscritos, meperidina e efedrina. (B) o tramadol inibe a recaptação de serotonina e é um dos maiores desencadeantes de síndrome serotoninérgica, e a efedrina permanece contraindicada. (D) além do risco da meperidina, iniciar noradrenalina em infusão profilática antes de qualquer hipotensão expõe o paciente a resposta pressora exagerada sem indicação.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os inibidores da monoaminoxidase impedem a degradação intraneuronal de noradrenalina, dopamina e serotonina, criando dois riscos perioperatórios distintos.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Reação excitatória (tipo I) ou síndrome serotoninérgica:&lt;/strong&gt; hipertermia, rigidez muscular, hiper-reflexia, agitação e instabilidade autonômica. É precipitada por fármacos com atividade serotoninérgica: &lt;em&gt;meperidina&lt;/em&gt;, &lt;em&gt;tramadol&lt;/em&gt;, dextrometorfano, azul de metileno e linezolida. Os opioides fenilpiperidínicos puramente agonistas mu, como fentanil, sufentanil e remifentanil, são considerados a escolha mais segura; a morfina também é aceitável.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Crise hipertensiva:&lt;/strong&gt; desencadeada por simpatomiméticos de &lt;em&gt;ação indireta&lt;/em&gt;, como efedrina e metaraminol, que liberam as catecolaminas acumuladas nas vesículas.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Por isso, a hipotensão deve ser tratada com volume, redução da profundidade anestésica e, se necessário, um agonista de &lt;strong&gt;ação direta&lt;/strong&gt; (fenilefrina ou noradrenalina) iniciado em dose reduzida e titulado, já que a resposta pode estar exagerada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) reúne exatamente os dois fármacos proscritos, meperidina e efedrina. (B) o tramadol inibe a recaptação de serotonina e é um dos maiores desencadeantes de síndrome serotoninérgica, e a efedrina permanece contraindicada. (D) além do risco da meperidina, iniciar noradrenalina em infusão profilática antes de qualquer hipotensão expõe o paciente a resposta pressora exagerada sem indicação.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Em doses terapêuticas, mais de 90% do paracetamol é eliminado por &lt;strong&gt;conjugação de fase II&lt;/strong&gt; (glicuronidação e sulfatação). Uma fração pequena sofre oxidação pelo &lt;strong&gt;CYP2E1&lt;/strong&gt;, gerando a &lt;em&gt;N-acetil-p-benzoquinonaimina&lt;/em&gt; (NAPQI), metabólito eletrofílico prontamente neutralizado pela glutationa hepática.&lt;/p&gt;&lt;p&gt;Na superdosagem, as vias conjugativas saturam, a produção de NAPQI aumenta e as reservas de glutationa se esgotam. O metabólito livre liga-se covalentemente a proteínas dos hepatócitos e provoca &lt;strong&gt;necrose centrolobular&lt;/strong&gt;, que se manifesta clinicamente entre 24 e 72 horas — daí o período inicial enganosamente assintomático. Álcool crônico, jejum e desnutrição agravam o quadro por induzirem o CYP2E1 e reduzirem a glutationa. A dose máxima habitual no adulto é de 4 g/dia, reduzida para cerca de 3 g/dia em idosos, hepatopatas e etilistas.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;N-acetilcisteína&lt;/strong&gt; fornece cisteína para a ressíntese de glutationa, além de conjugar diretamente o NAPQI e servir como substrato alternativo de sulfatação. Sua eficácia é máxima nas primeiras 8 a 10 horas e decresce depois, o que torna imperativo iniciá-la com base no nomograma, e não na lesão já instalada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) esperar a alteração laboratorial desperdiça a janela terapêutica. (C) o carvão ativado é útil apenas nas primeiras horas e como adjuvante, jamais como tratamento isolado em intoxicação com nível acima da linha de tratamento. (D) a naloxona antagoniza receptores opioides e não tem qualquer ação sobre o CYP2E1.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Em doses terapêuticas, mais de 90% do paracetamol é eliminado por &lt;strong&gt;conjugação de fase II&lt;/strong&gt; (glicuronidação e sulfatação). Uma fração pequena sofre oxidação pelo &lt;strong&gt;CYP2E1&lt;/strong&gt;, gerando a &lt;em&gt;N-acetil-p-benzoquinonaimina&lt;/em&gt; (NAPQI), metabólito eletrofílico prontamente neutralizado pela glutationa hepática.&lt;/p&gt;&lt;p&gt;Na superdosagem, as vias conjugativas saturam, a produção de NAPQI aumenta e as reservas de glutationa se esgotam. O metabólito livre liga-se covalentemente a proteínas dos hepatócitos e provoca &lt;strong&gt;necrose centrolobular&lt;/strong&gt;, que se manifesta clinicamente entre 24 e 72 horas; daí o período inicial enganosamente assintomático. Álcool crônico, jejum e desnutrição agravam o quadro por induzirem o CYP2E1 e reduzirem a glutationa. A dose máxima habitual no adulto é de 4 g/dia, reduzida para cerca de 3 g/dia em idosos, hepatopatas e etilistas.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;N-acetilcisteína&lt;/strong&gt; fornece cisteína para a ressíntese de glutationa, além de conjugar diretamente o NAPQI e servir como substrato alternativo de sulfatação. Sua eficácia é máxima nas primeiras 8 a 10 horas e decresce depois, o que torna imperativo iniciá-la com base no nomograma, e não na lesão já instalada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) esperar a alteração laboratorial desperdiça a janela terapêutica. (C) o carvão ativado é útil apenas nas primeiras horas e como adjuvante, jamais como tratamento isolado em intoxicação com nível acima da linha de tratamento. (D) a naloxona antagoniza receptores opioides e não tem qualquer ação sobre o CYP2E1.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A velocidade de indução inalatória depende de quão rapidamente a fração alveolar (FA) do agente se aproxima da fração inspirada (FI). O &lt;strong&gt;efeito de concentração&lt;/strong&gt; descreve o fato de que, quanto maior a concentração inspirada de um gás captado em grande volume, mais rápida é essa aproximação. Dois componentes o explicam: o de &lt;em&gt;concentração&lt;/em&gt; propriamente dito — a retirada de grande volume do alvéolo reduz o volume no qual o gás remanescente está diluído, elevando sua concentração — e o de &lt;em&gt;influxo aumentado&lt;/em&gt;, pois o volume captado é reposto por gás fresco vindo das vias aéreas superiores.&lt;/p&gt;&lt;p&gt;Quando um segundo agente é administrado junto com o óxido nitroso em alta concentração, ele se beneficia dos mesmos dois componentes: é o &lt;strong&gt;efeito do segundo gás&lt;/strong&gt;. A fração expirada do sevoflurano sobe mais depressa do que subiria se administrado apenas em oxigênio. Trata-se de fenômeno real, embora de magnitude modesta, mais evidente nos primeiros minutos e com agentes de solubilidade intermediária.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o coeficiente de partição sangue:gás é propriedade físico-química do agente e não é alterado pela mistura de gases. (B) o raciocínio está invertido — aumento do débito cardíaco amplia a captação sanguínea e &lt;em&gt;retarda&lt;/em&gt; a elevação da FA/FI, ao passo que o baixo débito a acelera. (D) o óxido nitroso não estimula quimiorreceptores centrais; ventilação aumentada acelera a indução, mas não é o mecanismo aqui descrito.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A velocidade de indução inalatória depende de quão rapidamente a fração alveolar (FA) do agente se aproxima da fração inspirada (FI). O &lt;strong&gt;efeito de concentração&lt;/strong&gt; descreve o fato de que, quanto maior a concentração inspirada de um gás captado em grande volume, mais rápida é essa aproximação. Dois componentes o explicam: o de &lt;em&gt;concentração&lt;/em&gt; propriamente dito (a retirada de grande volume do alvéolo reduz o volume no qual o gás remanescente está diluído, elevando sua concentração) e o de &lt;em&gt;influxo aumentado&lt;/em&gt;, pois o volume captado é reposto por gás fresco vindo das vias aéreas superiores.&lt;/p&gt;&lt;p&gt;Quando um segundo agente é administrado junto com o óxido nitroso em alta concentração, ele se beneficia dos mesmos dois componentes: é o &lt;strong&gt;efeito do segundo gás&lt;/strong&gt;. A fração expirada do sevoflurano sobe mais depressa do que subiria se administrado apenas em oxigênio. Trata-se de fenômeno real, embora de magnitude modesta, mais evidente nos primeiros minutos e com agentes de solubilidade intermediária.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o coeficiente de partição sangue:gás é propriedade físico-química do agente e não é alterado pela mistura de gases. (B) o raciocínio está invertido: aumento do débito cardíaco amplia a captação sanguínea e &lt;em&gt;retarda&lt;/em&gt; a elevação da FA/FI, ao passo que o baixo débito a acelera. (D) o óxido nitroso não estimula quimiorreceptores centrais; ventilação aumentada acelera a indução, mas não é o mecanismo aqui descrito.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os clássicos estágios de Guedel — analgesia, excitação, plano cirúrgico e paralisia bulbar — foram descritos com éter em ventilação espontânea, sem opioides nem bloqueadores neuromusculares. Com a anestesia balanceada moderna, restam como sinais de profundidade insuficiente as manifestações &lt;strong&gt;autonômicas e motoras&lt;/strong&gt;: hipertensão, taquicardia, sudorese, lacrimejamento, midríase e movimento.&lt;/p&gt;&lt;p&gt;O problema é que cada um desses sinais pode ser abolido por fármacos usados na própria anestesia. O &lt;strong&gt;betabloqueio crônico&lt;/strong&gt; impede a taquicardia; o &lt;strong&gt;bloqueio neuromuscular&lt;/strong&gt; abole o movimento, que é o marcador mais específico; e opioides potentes atenuam a resposta hemodinâmica sem produzir hipnose ou amnésia confiáveis. Assim, um paciente betabloqueado, curarizado e sob remifentanil pode estar consciente e permanecer hemodinamicamente estável — combinação reconhecidamente associada a &lt;em&gt;consciência intraoperatória&lt;/em&gt;. A salvaguarda prática mais robusta é manter a fração expirada do halogenado em torno de &lt;strong&gt;0,7 CAM ou mais&lt;/strong&gt;, com alarme configurado, ou empregar monitorização eletroencefalográfica processada quando se utiliza técnica venosa total.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) confunde estabilidade hemodinâmica com hipnose; é exatamente a armadilha do paciente betabloqueado. (C) sinais oculares e lacrimejamento têm baixa sensibilidade e são modificados por anticolinérgicos, opioides e pela própria idade. (D) o remifentanil produz analgesia intensa, mas amnésia inconsistente; reduzir o hipnótico apoiado no opioide é justamente o cenário de maior risco de despertar.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os clássicos estágios de Guedel (analgesia, excitação, plano cirúrgico e paralisia bulbar) foram descritos com éter em ventilação espontânea, sem opioides nem bloqueadores neuromusculares. Com a anestesia balanceada moderna, restam como sinais de profundidade insuficiente as manifestações &lt;strong&gt;autonômicas e motoras&lt;/strong&gt;: hipertensão, taquicardia, sudorese, lacrimejamento, midríase e movimento.&lt;/p&gt;&lt;p&gt;O problema é que cada um desses sinais pode ser abolido por fármacos usados na própria anestesia. O &lt;strong&gt;betabloqueio crônico&lt;/strong&gt; impede a taquicardia; o &lt;strong&gt;bloqueio neuromuscular&lt;/strong&gt; abole o movimento, que é o marcador mais específico; e opioides potentes atenuam a resposta hemodinâmica sem produzir hipnose ou amnésia confiáveis. Assim, um paciente betabloqueado, curarizado e sob remifentanil pode estar consciente e permanecer hemodinamicamente estável, combinação reconhecidamente associada a &lt;em&gt;consciência intraoperatória&lt;/em&gt;. A salvaguarda prática mais robusta é manter a fração expirada do halogenado em torno de &lt;strong&gt;0,7 CAM ou mais&lt;/strong&gt;, com alarme configurado, ou empregar monitorização eletroencefalográfica processada quando se utiliza técnica venosa total.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) confunde estabilidade hemodinâmica com hipnose; é exatamente a armadilha do paciente betabloqueado. (C) sinais oculares e lacrimejamento têm baixa sensibilidade e são modificados por anticolinérgicos, opioides e pela própria idade. (D) o remifentanil produz analgesia intensa, mas amnésia inconsistente; reduzir o hipnótico apoiado no opioide é justamente o cenário de maior risco de despertar.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Após um bolus de indução de propofol (habitualmente 1,5 a 2,5 mg/kg no adulto hígido), a consciência retorna em 5 a 10 minutos. Esse despertar rápido não se deve à eliminação, e sim à &lt;strong&gt;redistribuição&lt;/strong&gt; do fármaco do compartimento central para músculo e tecido adiposo. Ainda assim, o propofol tem depuração excepcionalmente alta — em torno de 20 a 30 mL/kg/min, valor que &lt;strong&gt;supera o fluxo sanguíneo hepático&lt;/strong&gt; e denuncia metabolismo extra-hepático, com contribuição pulmonar e renal. A conjugação hepática gera metabólitos &lt;em&gt;inativos&lt;/em&gt;. Entre os efeitos sistêmicos, destacam-se hipotensão por vasodilatação e depressão miocárdica, apneia dose-dependente, ação antiemética e redução do metabolismo e do fluxo sanguíneo cerebrais.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;fospropofol&lt;/strong&gt; é um éster fosfatado hidrossolúvel, hidrolisado por fosfatases alcalinas endoteliais em propofol, fosfato e formaldeído. Por depender dessa conversão, seu início é &lt;em&gt;mais lento&lt;/em&gt;, com pico de efeito por volta de 4 a 8 minutos. Não provoca dor à injeção, por não conter a emulsão lipídica, mas causa de forma característica &lt;em&gt;parestesia e prurido perineais&lt;/em&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o pró-fármaco necessariamente tem início mais lento, pois a hidrólise antecede o efeito. (B) atribui à eliminação o que é fenômeno de distribuição; a eliminação determina o tempo de meia-vida contexto-dependente em infusões prolongadas. (D) inverte os perfis — a dor à injeção é queixa clássica do propofol, atenuada por lidocaína e por veias calibrosas, e o fospropofol é justamente indolor.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Após um bolus de indução de propofol (habitualmente 1,5 a 2,5 mg/kg no adulto hígido), a consciência retorna em 5 a 10 minutos. Esse despertar rápido não se deve à eliminação, e sim à &lt;strong&gt;redistribuição&lt;/strong&gt; do fármaco do compartimento central para músculo e tecido adiposo. Ainda assim, o propofol tem depuração excepcionalmente alta, em torno de 20 a 30 mL/kg/min, valor que &lt;strong&gt;supera o fluxo sanguíneo hepático&lt;/strong&gt; e denuncia metabolismo extra-hepático, com contribuição pulmonar e renal. A conjugação hepática gera metabólitos &lt;em&gt;inativos&lt;/em&gt;. Entre os efeitos sistêmicos, destacam-se hipotensão por vasodilatação e depressão miocárdica, apneia dose-dependente, ação antiemética e redução do metabolismo e do fluxo sanguíneo cerebrais.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;fospropofol&lt;/strong&gt; é um éster fosfatado hidrossolúvel, hidrolisado por fosfatases alcalinas endoteliais em propofol, fosfato e formaldeído. Por depender dessa conversão, seu início é &lt;em&gt;mais lento&lt;/em&gt;, com pico de efeito por volta de 4 a 8 minutos. Não provoca dor à injeção, por não conter a emulsão lipídica, mas causa de forma característica &lt;em&gt;parestesia e prurido perineais&lt;/em&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o pró-fármaco necessariamente tem início mais lento, pois a hidrólise antecede o efeito. (B) atribui à eliminação o que é fenômeno de distribuição; a eliminação determina o tempo de meia-vida contexto-dependente em infusões prolongadas. (D) inverte os perfis: a dor à injeção é queixa clássica do propofol, atenuada por lidocaína e por veias calibrosas, e o fospropofol é justamente indolor.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A cetamina é antagonista não competitivo do receptor NMDA e produz o chamado &lt;strong&gt;estado dissociativo&lt;/strong&gt;, com dissociação funcional entre os sistemas talamocortical e límbico: o paciente pode manter os olhos abertos e apresentar nistagmo, mas está inconsciente e analgesiado. Preserva melhor o drive respiratório e o tônus da via aérea, é broncodilatadora e aumenta as secreções.&lt;/p&gt;&lt;p&gt;O ponto que a questão cobra é a dualidade hemodinâmica. In vivo, a cetamina inibe a recaptação de catecolaminas e estimula centralmente o sistema simpático, elevando pressão arterial, frequência cardíaca e débito. Isolada do sistema nervoso autônomo, porém, a molécula é &lt;strong&gt;depressora miocárdica direta&lt;/strong&gt;. No paciente com choque prolongado, sepse ou uso crônico de catecolaminas, as reservas simpáticas já estão esgotadas: o componente estimulante não se manifesta e a depressão direta predomina, produzindo &lt;strong&gt;hipotensão paradoxal&lt;/strong&gt;. A conduta é reduzir a dose, garantir reposição volêmica e ter vasopressor pronto.&lt;/p&gt;&lt;p&gt;Merece nota ainda o &lt;em&gt;delirium de emergência&lt;/em&gt; — sonhos vívidos, alucinações e agitação —, mais frequente em adultos jovens e mulheres, atenuado pela associação de benzodiazepínico e por ambiente tranquilo no despertar.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a norcetamina é metabólito &lt;em&gt;ativo&lt;/em&gt;, com cerca de um terço da potência do fármaco original, e não tem ação alfabloqueadora. (C) a cetamina não é histaminoliberadora, e sua formulação aquosa não contém veículo lipídico. (D) a cetamina de fato aumenta o fluxo sanguíneo cerebral, mas isso não gera queda da resistência vascular sistêmica.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A cetamina é antagonista não competitivo do receptor NMDA e produz o chamado &lt;strong&gt;estado dissociativo&lt;/strong&gt;, com dissociação funcional entre os sistemas talamocortical e límbico: o paciente pode manter os olhos abertos e apresentar nistagmo, mas está inconsciente e analgesiado. Preserva melhor o drive respiratório e o tônus da via aérea, é broncodilatadora e aumenta as secreções.&lt;/p&gt;&lt;p&gt;O ponto que a questão cobra é a dualidade hemodinâmica. In vivo, a cetamina inibe a recaptação de catecolaminas e estimula centralmente o sistema simpático, elevando pressão arterial, frequência cardíaca e débito. Isolada do sistema nervoso autônomo, porém, a molécula é &lt;strong&gt;depressora miocárdica direta&lt;/strong&gt;. No paciente com choque prolongado, sepse ou uso crônico de catecolaminas, as reservas simpáticas já estão esgotadas: o componente estimulante não se manifesta e a depressão direta predomina, produzindo &lt;strong&gt;hipotensão paradoxal&lt;/strong&gt;. A conduta é reduzir a dose, garantir reposição volêmica e ter vasopressor pronto.&lt;/p&gt;&lt;p&gt;Merece nota ainda o &lt;em&gt;delirium de emergência&lt;/em&gt; (sonhos vívidos, alucinações e agitação), mais frequente em adultos jovens e mulheres, atenuado pela associação de benzodiazepínico e por ambiente tranquilo no despertar.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a norcetamina é metabólito &lt;em&gt;ativo&lt;/em&gt;, com cerca de um terço da potência do fármaco original, e não tem ação alfabloqueadora. (C) a cetamina não é histaminoliberadora, e sua formulação aquosa não contém veículo lipídico. (D) a cetamina de fato aumenta o fluxo sanguíneo cerebral, mas isso não gera queda da resistência vascular sistêmica.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os benzodiazepínicos potencializam a ação do GABA no receptor GABA-A, aumentando a &lt;em&gt;frequência&lt;/em&gt; de abertura do canal de cloro, e produzem ansiólise, sedação, anticonvulsão, relaxamento muscular e &lt;strong&gt;amnésia anterógrada&lt;/strong&gt; — a memória de fatos anteriores à administração é preservada.&lt;/p&gt;&lt;p&gt;As diferenças clínicas entre eles derivam em grande parte do metabolismo:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Midazolam:&lt;/strong&gt; hidroxilado pelo CYP3A4 a &lt;em&gt;alfa-hidroximidazolam&lt;/em&gt;, metabólito com atividade sedativa apreciável, posteriormente glicuronidado. O glicuronídeo, também ativo, depende de excreção renal e &lt;strong&gt;acumula-se na insuficiência renal&lt;/strong&gt;, explicando sedação prolongada após infusões contínuas, sobretudo em idosos e após dias de uso.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Diazepam:&lt;/strong&gt; gera desmetildiazepam, oxazepam e temazepam; o desmetildiazepam tem meia-vida muito longa, o que produz sedação residual e efeito rebote.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Lorazepam:&lt;/strong&gt; sofre &lt;em&gt;glicuronidação direta&lt;/em&gt;, sem metabólitos ativos, e é o mais previsível na disfunção hepática.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;O flumazenil reverte o quadro, mas sua meia-vida de cerca de uma hora impõe risco de ressedação, além de poder precipitar convulsões em usuários crônicos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o midazolam é depurado por metabolismo hepático, e praticamente nada é excretado íntegro na urina. (B) afirma justamente o oposto do que ocorre — o midazolam possui metabólito ativo clinicamente relevante. (D) a amnésia anterógrada limita-se ao período de ação do fármaco e não se manifesta como rebaixamento do nível de consciência.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os benzodiazepínicos potencializam a ação do GABA no receptor GABA-A, aumentando a &lt;em&gt;frequência&lt;/em&gt; de abertura do canal de cloro, e produzem ansiólise, sedação, anticonvulsão, relaxamento muscular e &lt;strong&gt;amnésia anterógrada&lt;/strong&gt;: a memória de fatos anteriores à administração é preservada.&lt;/p&gt;&lt;p&gt;As diferenças clínicas entre eles derivam em grande parte do metabolismo:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Midazolam:&lt;/strong&gt; hidroxilado pelo CYP3A4 a &lt;em&gt;alfa-hidroximidazolam&lt;/em&gt;, metabólito com atividade sedativa apreciável, posteriormente glicuronidado. O glicuronídeo, também ativo, depende de excreção renal e &lt;strong&gt;acumula-se na insuficiência renal&lt;/strong&gt;, explicando sedação prolongada após infusões contínuas, sobretudo em idosos e após dias de uso.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Diazepam:&lt;/strong&gt; gera desmetildiazepam, oxazepam e temazepam; o desmetildiazepam tem meia-vida muito longa, o que produz sedação residual e efeito rebote.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Lorazepam:&lt;/strong&gt; sofre &lt;em&gt;glicuronidação direta&lt;/em&gt;, sem metabólitos ativos, e é o mais previsível na disfunção hepática.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;O flumazenil reverte o quadro, mas sua meia-vida de cerca de uma hora impõe risco de ressedação, além de poder precipitar convulsões em usuários crônicos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o midazolam é depurado por metabolismo hepático, e praticamente nada é excretado íntegro na urina. (B) afirma justamente o oposto do que ocorre: o midazolam possui metabólito ativo clinicamente relevante. (D) a amnésia anterógrada limita-se ao período de ação do fármaco e não se manifesta como rebaixamento do nível de consciência.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O sistema de exaustão tem quatro componentes: o dispositivo coletor, o tubo de transferência, a &lt;strong&gt;interface&lt;/strong&gt; e o sistema de eliminação, que pode ser &lt;em&gt;ativo&lt;/em&gt; (vácuo, gerando pressão subatmosférica) ou &lt;em&gt;passivo&lt;/em&gt; (pressão positiva do próprio circuito empurrando os gases para fora). A interface é o elemento de segurança: protege o paciente tanto do excesso de pressão positiva quanto da pressão negativa transmitida ao circuito respiratório.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Interface aberta:&lt;/strong&gt; reservatório rígido continuamente aberto à atmosfera, sem válvulas. O alívio de qualquer excesso de pressão, positiva ou negativa, é feito pelas próprias aberturas. Justamente por isso, &lt;strong&gt;só pode ser usada com sistema de eliminação ativo&lt;/strong&gt;: sem o vácuo aspirando o reservatório, os gases escapariam para a sala.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Interface fechada:&lt;/strong&gt; comunica-se com a atmosfera exclusivamente por válvulas. A &lt;strong&gt;válvula de alívio de pressão positiva é obrigatória&lt;/strong&gt;, abrindo em torno de 5 cmH&lt;sub&gt;2&lt;/sub&gt;O para prevenir barotrauma se a via de eliminação obstruir. Quando a eliminação é ativa, acrescenta-se &lt;strong&gt;válvula de alívio negativa&lt;/strong&gt;, que abre por volta de -0,5 cmH&lt;sub&gt;2&lt;/sub&gt;O e admite ar ambiente, impedindo que o vácuo esvazie o balão e o circuito.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a interface aberta não possui válvulas, e essa é sua característica definidora. (C) a válvula positiva nunca é dispensável na interface fechada — é a proteção contra barotrauma. (D) a válvula negativa só se justifica quando existe fonte de sucção; na eliminação passiva não há como gerar pressão subatmosférica.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O sistema de exaustão tem quatro componentes: o dispositivo coletor, o tubo de transferência, a &lt;strong&gt;interface&lt;/strong&gt; e o sistema de eliminação, que pode ser &lt;em&gt;ativo&lt;/em&gt; (vácuo, gerando pressão subatmosférica) ou &lt;em&gt;passivo&lt;/em&gt; (pressão positiva do próprio circuito empurrando os gases para fora). A interface é o elemento de segurança: protege o paciente tanto do excesso de pressão positiva quanto da pressão negativa transmitida ao circuito respiratório.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Interface aberta:&lt;/strong&gt; reservatório rígido continuamente aberto à atmosfera, sem válvulas. O alívio de qualquer excesso de pressão, positiva ou negativa, é feito pelas próprias aberturas. Justamente por isso, &lt;strong&gt;só pode ser usada com sistema de eliminação ativo&lt;/strong&gt;: sem o vácuo aspirando o reservatório, os gases escapariam para a sala.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Interface fechada:&lt;/strong&gt; comunica-se com a atmosfera exclusivamente por válvulas. A &lt;strong&gt;válvula de alívio de pressão positiva é obrigatória&lt;/strong&gt;, abrindo em torno de 5 cmH&lt;sub&gt;2&lt;/sub&gt;O para prevenir barotrauma se a via de eliminação obstruir. Quando a eliminação é ativa, acrescenta-se &lt;strong&gt;válvula de alívio negativa&lt;/strong&gt;, que abre por volta de -0,5 cmH&lt;sub&gt;2&lt;/sub&gt;O e admite ar ambiente, impedindo que o vácuo esvazie o balão e o circuito.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a interface aberta não possui válvulas, e essa é sua característica definidora. (C) a válvula positiva nunca é dispensável na interface fechada: é a proteção contra barotrauma. (D) a válvula negativa só se justifica quando existe fonte de sucção; na eliminação passiva não há como gerar pressão subatmosférica.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A suscetibilidade à hipertermia maligna tem herança &lt;strong&gt;autossômica dominante&lt;/strong&gt; com penetrância variável, mais frequentemente ligada a variantes do gene &lt;em&gt;RYR1&lt;/em&gt;. Para uma gestante suscetível, a probabilidade de o concepto herdar a característica é de cerca de 50%, independentemente do genótipo paterno.&lt;/p&gt;&lt;p&gt;O bloqueio de neuroeixo é a técnica de escolha na cesariana dessa paciente: os anestésicos locais, amidas ou ésteres, são seguros, assim como propofol, opioides, benzodiazepínicos, óxido nitroso e bloqueadores adespolarizantes. Se a crise ocorrer, o dantroleno deve ser usado sem hesitação — ele atua sobre o receptor de rianodina do &lt;em&gt;músculo esquelético&lt;/em&gt;, e não há relato consistente de atonia uterina atribuível ao fármaco; atravessa a placenta em concentrações baixas e é considerado compatível com a gestação e a lactação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a profilaxia rotineira com dantroleno foi abandonada: com sala preparada e agentes seguros, ela não reduz eventos e causa fraqueza muscular materna, flebite e sedação neonatal. (C) a succinilcolina é agente desencadeante clássico, junto aos halogenados, e está formalmente contraindicada em suscetíveis. (D) a herança é dominante e não recessiva; o risco de transmissão ao concepto é de aproximadamente 50%, sem depender do pai.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A suscetibilidade à hipertermia maligna tem herança &lt;strong&gt;autossômica dominante&lt;/strong&gt; com penetrância variável, mais frequentemente ligada a variantes do gene &lt;em&gt;RYR1&lt;/em&gt;. Para uma gestante suscetível, a probabilidade de o concepto herdar a característica é de cerca de 50%, independentemente do genótipo paterno.&lt;/p&gt;&lt;p&gt;O bloqueio de neuroeixo é a técnica de escolha na cesariana dessa paciente: os anestésicos locais, amidas ou ésteres, são seguros, assim como propofol, opioides, benzodiazepínicos, óxido nitroso e bloqueadores adespolarizantes. Se a crise ocorrer, o dantroleno deve ser usado sem hesitação: ele atua sobre o receptor de rianodina do &lt;em&gt;músculo esquelético&lt;/em&gt;, e não há relato consistente de atonia uterina atribuível ao fármaco; atravessa a placenta em concentrações baixas e é considerado compatível com a gestação e a lactação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a profilaxia rotineira com dantroleno foi abandonada: com sala preparada e agentes seguros, ela não reduz eventos e causa fraqueza muscular materna, flebite e sedação neonatal. (C) a succinilcolina é agente desencadeante clássico, junto aos halogenados, e está formalmente contraindicada em suscetíveis. (D) a herança é dominante e não recessiva; o risco de transmissão ao concepto é de aproximadamente 50%, sem depender do pai.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>&lt;p&gt;À medida que a onda de pressão se propaga da aorta para as artérias periféricas, ela sofre &lt;strong&gt;amplificação distal&lt;/strong&gt;: a reflexão de ondas nas bifurcações e o enrijecimento progressivo da parede arterial elevam o pico sistólico e reduzem a pressão diastólica, alargando a pressão de pulso. O componente que permanece estável ao longo da árvore arterial é a &lt;strong&gt;pressão arterial média&lt;/strong&gt;, que cai apenas discretamente no sentido distal por perda de energia friccional.&lt;/p&gt;&lt;p&gt;Conferindo os números do caso: pela radial, PAM = 72 + (130-72)/3 ≈ 91 mmHg; pela pediosa, PAM = 60 + (145-60)/3 ≈ 88 mmHg. Sistólica maior, diastólica menor e média praticamente igual é a assinatura clássica do fenômeno, e não de artefato. Por isso, quando se comparam sítios diferentes, a PAM é o parâmetro que deve orientar metas de perfusão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) transdutor abaixo do átrio direito elevaria sistólica &lt;em&gt;e&lt;/em&gt; diastólica na mesma proporção, mantendo a pressão de pulso — aqui a diastólica está menor. (C) o amortecimento excessivo reduz a sistólica e eleva a diastólica, estreitando a pressão de pulso, e foi afastado pelo teste de onda quadrada. (D) estenose proximal reduziria a PAM do lado afetado de forma significativa, o que não ocorre com diferença de apenas 3 mmHg entre as médias.&lt;/p&gt;</t>
+          <t>&lt;p&gt;À medida que a onda de pressão se propaga da aorta para as artérias periféricas, ela sofre &lt;strong&gt;amplificação distal&lt;/strong&gt;: a reflexão de ondas nas bifurcações e o enrijecimento progressivo da parede arterial elevam o pico sistólico e reduzem a pressão diastólica, alargando a pressão de pulso. O componente que permanece estável ao longo da árvore arterial é a &lt;strong&gt;pressão arterial média&lt;/strong&gt;, que cai apenas discretamente no sentido distal por perda de energia friccional.&lt;/p&gt;&lt;p&gt;Conferindo os números do caso: pela radial, PAM = 72 + (130-72)/3 ≈ 91 mmHg; pela pediosa, PAM = 60 + (145-60)/3 ≈ 88 mmHg. Sistólica maior, diastólica menor e média praticamente igual é a assinatura clássica do fenômeno, e não de artefato. Por isso, quando se comparam sítios diferentes, a PAM é o parâmetro que deve orientar metas de perfusão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) transdutor abaixo do átrio direito elevaria sistólica &lt;em&gt;e&lt;/em&gt; diastólica na mesma proporção, mantendo a pressão de pulso; aqui a diastólica está menor. (C) o amortecimento excessivo reduz a sistólica e eleva a diastólica, estreitando a pressão de pulso, e foi afastado pelo teste de onda quadrada. (D) estenose proximal reduziria a PAM do lado afetado de forma significativa, o que não ocorre com diferença de apenas 3 mmHg entre as médias.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A escolha do sítio de acesso venoso central pondera três eixos: risco mecânico, risco infeccioso e risco trombótico. A &lt;strong&gt;subclávia&lt;/strong&gt; tem a menor incidência de infecção e trombose, mas o maior risco de pneumotórax e, sobretudo, é um sítio &lt;em&gt;não compressível&lt;/em&gt; — uma punção arterial ou uma laceração venosa nesse território não pode ser controlada por compressão externa. A &lt;strong&gt;femoral&lt;/strong&gt; é compressível, porém concentra as maiores taxas de colonização e de trombose venosa profunda. A &lt;strong&gt;jugular interna&lt;/strong&gt; ocupa posição intermediária no risco infeccioso e é compressível contra a coluna cervical.&lt;/p&gt;&lt;p&gt;Em coagulopatia grave, como neste cirrótico com INR de 2,4 e plaquetopenia, a variável dominante passa a ser a possibilidade de conter um sangramento. A jugular interna direita guiada por ultrassonografia soma trajeto curto e retilíneo até a cava superior, visualização em tempo real da agulha e possibilidade de compressão, sendo a opção mais segura.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o menor risco infeccioso da subclávia não compensa, neste contexto, a impossibilidade de compressão. (C) a femoral é compressível, mas a afirmativa inverte os fatos ao atribuir a ela o menor risco trombótico e infeccioso, que na verdade é o maior. (D) além de manter o problema da não compressibilidade, o lado esquerdo tem trajeto mais anguloso e maior risco de lesão do ducto torácico.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A escolha do sítio de acesso venoso central pondera três eixos: risco mecânico, risco infeccioso e risco trombótico. A &lt;strong&gt;subclávia&lt;/strong&gt; tem a menor incidência de infecção e trombose, mas o maior risco de pneumotórax e, sobretudo, é um sítio &lt;em&gt;não compressível&lt;/em&gt;: uma punção arterial ou uma laceração venosa nesse território não pode ser controlada por compressão externa. A &lt;strong&gt;femoral&lt;/strong&gt; é compressível, porém concentra as maiores taxas de colonização e de trombose venosa profunda. A &lt;strong&gt;jugular interna&lt;/strong&gt; ocupa posição intermediária no risco infeccioso e é compressível contra a coluna cervical.&lt;/p&gt;&lt;p&gt;Em coagulopatia grave, como neste cirrótico com INR de 2,4 e plaquetopenia, a variável dominante passa a ser a possibilidade de conter um sangramento. A jugular interna direita guiada por ultrassonografia soma trajeto curto e retilíneo até a cava superior, visualização em tempo real da agulha e possibilidade de compressão, sendo a opção mais segura.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o menor risco infeccioso da subclávia não compensa, neste contexto, a impossibilidade de compressão. (C) a femoral é compressível, mas a afirmativa inverte os fatos ao atribuir a ela o menor risco trombótico e infeccioso, que na verdade é o maior. (D) além de manter o problema da não compressibilidade, o lado esquerdo tem trajeto mais anguloso e maior risco de lesão do ducto torácico.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A espectroscopia por infravermelho depende da existência de um &lt;strong&gt;momento de dipolo elétrico&lt;/strong&gt; que varie durante a vibração molecular. Moléculas com dois ou mais átomos &lt;em&gt;diferentes&lt;/em&gt; — CO&lt;sub&gt;2&lt;/sub&gt;, N&lt;sub&gt;2&lt;/sub&gt;O, sevoflurano, isoflurano, desflurano — apresentam essa assimetria de cargas e absorvem energia em comprimentos de onda característicos, o que permite quantificá-las pela lei de Beer-Lambert. Moléculas diatômicas &lt;strong&gt;homonucleares&lt;/strong&gt;, como O&lt;sub&gt;2&lt;/sub&gt;, N&lt;sub&gt;2&lt;/sub&gt; e o argônio monoatômico, não têm dipolo e são transparentes ao infravermelho.&lt;/p&gt;&lt;p&gt;Por isso o oxigênio é medido por outros princípios: a &lt;strong&gt;célula galvânica&lt;/strong&gt; e o sensor polarográfico usam reação eletroquímica de redução do oxigênio, com resposta lenta e consumo do elemento sensor; o &lt;strong&gt;analisador paramagnético&lt;/strong&gt; aproveita o fato de o oxigênio ser fortemente paramagnético, sendo atraído por campo magnético, o que garante resposta rápida e permite medida respiração a respiração.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a massa molecular não determina absorção no infravermelho; o que determina é a estrutura de dipolo. (C) o oxigênio não absorve infravermelho em faixa útil; a sobreposição espectral é problema real entre agentes halogenados e N&lt;sub&gt;2&lt;/sub&gt;O, não com o oxigênio. (D) a célula galvânica fica em ramo próprio do circuito e não subtrai oxigênio da amostra de infravermelho; além disso, mesmo sem ela o oxigênio continuaria indetectável.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A espectroscopia por infravermelho depende da existência de um &lt;strong&gt;momento de dipolo elétrico&lt;/strong&gt; que varie durante a vibração molecular. Moléculas com dois ou mais átomos &lt;em&gt;diferentes&lt;/em&gt; (CO&lt;sub&gt;2&lt;/sub&gt;, N&lt;sub&gt;2&lt;/sub&gt;O, sevoflurano, isoflurano, desflurano) apresentam essa assimetria de cargas e absorvem energia em comprimentos de onda característicos, o que permite quantificá-las pela lei de Beer-Lambert. Moléculas diatômicas &lt;strong&gt;homonucleares&lt;/strong&gt;, como O&lt;sub&gt;2&lt;/sub&gt;, N&lt;sub&gt;2&lt;/sub&gt; e o argônio monoatômico, não têm dipolo e são transparentes ao infravermelho.&lt;/p&gt;&lt;p&gt;Por isso o oxigênio é medido por outros princípios: a &lt;strong&gt;célula galvânica&lt;/strong&gt; e o sensor polarográfico usam reação eletroquímica de redução do oxigênio, com resposta lenta e consumo do elemento sensor; o &lt;strong&gt;analisador paramagnético&lt;/strong&gt; aproveita o fato de o oxigênio ser fortemente paramagnético, sendo atraído por campo magnético, o que garante resposta rápida e permite medida respiração a respiração.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a massa molecular não determina absorção no infravermelho; o que determina é a estrutura de dipolo. (C) o oxigênio não absorve infravermelho em faixa útil; a sobreposição espectral é problema real entre agentes halogenados e N&lt;sub&gt;2&lt;/sub&gt;O, não com o oxigênio. (D) a célula galvânica fica em ramo próprio do circuito e não subtrai oxigênio da amostra de infravermelho; além disso, mesmo sem ela o oxigênio continuaria indetectável.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A pressão de oclusão da artéria pulmonar é obtida quando o balão interrompe o fluxo e cria uma coluna estática de sangue entre a ponta do cateter e o átrio esquerdo. O valor medido é, portanto, uma estimativa da &lt;strong&gt;pressão atrial esquerda&lt;/strong&gt;. A cadeia de equivalências habitualmente ensinada — pressão de oclusão igual a pressão atrial esquerda, igual a pressão diastólica final do ventrículo esquerdo, proporcional ao volume diastólico final — só se sustenta quando a valva mitral é normal e a complacência ventricular é preservada.&lt;/p&gt;&lt;p&gt;Na &lt;strong&gt;estenose mitral&lt;/strong&gt; existe um gradiente diastólico transvalvar: a pressão atrial esquerda precisa ser mais alta que a ventricular para vencer a obstrução. A pressão de oclusão de 24 mmHg reflete esse átrio hipertenso e &lt;em&gt;superestima&lt;/em&gt; a pressão diastólica final do ventrículo esquerdo, que pode estar normal ou até baixa. Tratar esse número como hipervolemia e administrar diurético pode reduzir de forma perigosa o enchimento ventricular já limitado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a direção do erro: o gradiente faz a medida superestimar, não subestimar, a pressão ventricular. (B) desconsidera a obstrução valvar e conduz a intervenção potencialmente deletéria. (D) a relação entre pressão e volume depende da complacência; pressão nunca mede volume diretamente, e essa dissociação é ainda maior no ventrículo hipertrofiado ou subenchido.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A pressão de oclusão da artéria pulmonar é obtida quando o balão interrompe o fluxo e cria uma coluna estática de sangue entre a ponta do cateter e o átrio esquerdo. O valor medido é, portanto, uma estimativa da &lt;strong&gt;pressão atrial esquerda&lt;/strong&gt;. A cadeia de equivalências habitualmente ensinada (pressão de oclusão igual a pressão atrial esquerda, igual a pressão diastólica final do ventrículo esquerdo, proporcional ao volume diastólico final) só se sustenta quando a valva mitral é normal e a complacência ventricular é preservada.&lt;/p&gt;&lt;p&gt;Na &lt;strong&gt;estenose mitral&lt;/strong&gt; existe um gradiente diastólico transvalvar: a pressão atrial esquerda precisa ser mais alta que a ventricular para vencer a obstrução. A pressão de oclusão de 24 mmHg reflete esse átrio hipertenso e &lt;em&gt;superestima&lt;/em&gt; a pressão diastólica final do ventrículo esquerdo, que pode estar normal ou até baixa. Tratar esse número como hipervolemia e administrar diurético pode reduzir de forma perigosa o enchimento ventricular já limitado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a direção do erro: o gradiente faz a medida superestimar, não subestimar, a pressão ventricular. (B) desconsidera a obstrução valvar e conduz a intervenção potencialmente deletéria. (D) a relação entre pressão e volume depende da complacência; pressão nunca mede volume diretamente, e essa dissociação é ainda maior no ventrículo hipertrofiado ou subenchido.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A pressão arterial média é, rigorosamente, a integral da curva de pressão dividida pela duração do ciclo cardíaco. A fórmula prática de estimativa — &lt;strong&gt;PAM = pressão diastólica + (pressão de pulso ÷ 3)&lt;/strong&gt; — existe porque, em frequências cardíacas normais, a diástole ocupa cerca de dois terços do ciclo e a sístole cerca de um terço, de modo que a média ponderada fica mais próxima da diastólica.&lt;/p&gt;&lt;p&gt;No caso, a pressão de pulso é 170 − 60 = 110 mmHg. Logo, PAM = 60 + 110/3 ≈ 60 + 37 ≈ &lt;strong&gt;97 mmHg&lt;/strong&gt;. Vale lembrar que a fórmula perde acurácia na taquicardia, quando a diástole encurta e a PAM real se aproxima da média aritmética, e em pacientes idosos com grande rigidez arterial, nos quais a pressão de pulso alargada amplia o erro da estimativa.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a média aritmética simples entre sistólica e diastólica ignora a assimetria temporal do ciclo e superestima sistematicamente a PAM, aqui em cerca de 18 mmHg. (C) subtrair um terço da pressão de pulso da sistólica resulta em 133 mmHg, valor muito acima do real, por partir do extremo errado da curva. (D) usar um quarto em vez de um terço da pressão de pulso resulta em 87 mmHg e subestima a perfusão, podendo motivar intervenção vasopressora desnecessária.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A pressão arterial média é, rigorosamente, a integral da curva de pressão dividida pela duração do ciclo cardíaco. A fórmula prática de estimativa, &lt;strong&gt;PAM = pressão diastólica + (pressão de pulso ÷ 3)&lt;/strong&gt;, existe porque, em frequências cardíacas normais, a diástole ocupa cerca de dois terços do ciclo e a sístole cerca de um terço, de modo que a média ponderada fica mais próxima da diastólica.&lt;/p&gt;&lt;p&gt;No caso, a pressão de pulso é 170 − 60 = 110 mmHg. Logo, PAM = 60 + 110/3 ≈ 60 + 37 ≈ &lt;strong&gt;97 mmHg&lt;/strong&gt;. Vale lembrar que a fórmula perde acurácia na taquicardia, quando a diástole encurta e a PAM real se aproxima da média aritmética, e em pacientes idosos com grande rigidez arterial, nos quais a pressão de pulso alargada amplia o erro da estimativa.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a média aritmética simples entre sistólica e diastólica ignora a assimetria temporal do ciclo e superestima sistematicamente a PAM, aqui em cerca de 18 mmHg. (C) subtrair um terço da pressão de pulso da sistólica resulta em 133 mmHg, valor muito acima do real, por partir do extremo errado da curva. (D) usar um quarto em vez de um terço da pressão de pulso resulta em 87 mmHg e subestima a perfusão, podendo motivar intervenção vasopressora desnecessária.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A cascata isquêmica tem ordem temporal bem definida. A redução do fluxo coronariano produz, primeiro, alteração do relaxamento diastólico, em seguida &lt;strong&gt;alteração segmentar da motilidade parietal&lt;/strong&gt; — que aparece em segundos —, depois modificações do segmento ST e, por último, dor e queda do débito. Por isso a ecocardiografia transesofágica é mais sensível e mais precoce que a monitorização eletrocardiográfica para isquemia intraoperatória.&lt;/p&gt;&lt;p&gt;O plano &lt;strong&gt;transgástrico de eixo curto ao nível dos músculos papilares&lt;/strong&gt; é o mais usado no intraoperatório porque, em um único corte, exibe segmentos irrigados pelos três territórios coronarianos principais: descendente anterior, circunflexa e coronária direita. Hipocinesia nova da parede inferior aponta para o território da coronária direita, e o clampeamento aórtico, ao elevar bruscamente a pós-carga e o consumo miocárdico de oxigênio, é gatilho clássico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a ausência de alteração do segmento ST é esperada nessa fase e não exclui isquemia. (C) o aumento da pós-carga é o mecanismo desencadeante, mas a repercussão é regional e isquêmica; atribuí-la a fenômeno puramente mecânico retarda o tratamento. (D) a queda do débito cardíaco é evento tardio da cascata e a termodiluição tem resolução temporal insuficiente para detecção precoce.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A cascata isquêmica tem ordem temporal bem definida. A redução do fluxo coronariano produz, primeiro, alteração do relaxamento diastólico, em seguida &lt;strong&gt;alteração segmentar da motilidade parietal&lt;/strong&gt; (que aparece em segundos), depois modificações do segmento ST e, por último, dor e queda do débito. Por isso a ecocardiografia transesofágica é mais sensível e mais precoce que a monitorização eletrocardiográfica para isquemia intraoperatória.&lt;/p&gt;&lt;p&gt;O plano &lt;strong&gt;transgástrico de eixo curto ao nível dos músculos papilares&lt;/strong&gt; é o mais usado no intraoperatório porque, em um único corte, exibe segmentos irrigados pelos três territórios coronarianos principais: descendente anterior, circunflexa e coronária direita. Hipocinesia nova da parede inferior aponta para o território da coronária direita, e o clampeamento aórtico, ao elevar bruscamente a pós-carga e o consumo miocárdico de oxigênio, é gatilho clássico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a ausência de alteração do segmento ST é esperada nessa fase e não exclui isquemia. (C) o aumento da pós-carga é o mecanismo desencadeante, mas a repercussão é regional e isquêmica; atribuí-la a fenômeno puramente mecânico retarda o tratamento. (D) a queda do débito cardíaco é evento tardio da cascata e a termodiluição tem resolução temporal insuficiente para detecção precoce.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O teste do despertar consiste em reduzir a profundidade anestésica até que o paciente atenda a comandos simples e movimente voluntariamente os membros inferiores, confirmando integridade das vias motoras após uma manobra de correção. É, portanto, uma avaliação da &lt;strong&gt;função motora&lt;/strong&gt;, e não sensitiva, e exige ausência de bloqueio neuromuscular residual — normalmente confirmada por monitorização da junção neuromuscular antes da tentativa.&lt;/p&gt;&lt;p&gt;Suas limitações são significativas. Trata-se de avaliação &lt;strong&gt;pontual&lt;/strong&gt;, que informa sobre um único instante e não substitui a monitorização contínua. Os riscos incluem:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;recordação intraoperatória e experiência desagradável, mitigada pelo preparo pré-operatório;&lt;/li&gt;&lt;li&gt;movimentação abrupta com deslocamento de hastes, extubação acidental ou perda de acessos;&lt;/li&gt;&lt;li&gt;dor intensa e resposta adrenérgica com hipertensão e sangramento;&lt;/li&gt;&lt;li&gt;embolia gasosa venosa, favorecida pela inspiração profunda do paciente com ferida aberta acima do nível do coração.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) confunde o teste com os potenciais evocados somatossensitivos, que avaliam as colunas dorsais. (B) qualquer bloqueio neuromuscular residual compromete a interpretação do teste, cujo desfecho é justamente a resposta motora voluntária. (D) o teste é intermitente por definição e não fornece vigilância contínua, sendo complemento e não substituto dos potenciais evocados.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O teste do despertar consiste em reduzir a profundidade anestésica até que o paciente atenda a comandos simples e movimente voluntariamente os membros inferiores, confirmando integridade das vias motoras após uma manobra de correção. É, portanto, uma avaliação da &lt;strong&gt;função motora&lt;/strong&gt;, e não sensitiva, e exige ausência de bloqueio neuromuscular residual, normalmente confirmada por monitorização da junção neuromuscular antes da tentativa.&lt;/p&gt;&lt;p&gt;Suas limitações são significativas. Trata-se de avaliação &lt;strong&gt;pontual&lt;/strong&gt;, que informa sobre um único instante e não substitui a monitorização contínua. Os riscos incluem:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;recordação intraoperatória e experiência desagradável, mitigada pelo preparo pré-operatório;&lt;/li&gt;&lt;li&gt;movimentação abrupta com deslocamento de hastes, extubação acidental ou perda de acessos;&lt;/li&gt;&lt;li&gt;dor intensa e resposta adrenérgica com hipertensão e sangramento;&lt;/li&gt;&lt;li&gt;embolia gasosa venosa, favorecida pela inspiração profunda do paciente com ferida aberta acima do nível do coração.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) confunde o teste com os potenciais evocados somatossensitivos, que avaliam as colunas dorsais. (B) qualquer bloqueio neuromuscular residual compromete a interpretação do teste, cujo desfecho é justamente a resposta motora voluntária. (D) o teste é intermitente por definição e não fornece vigilância contínua, sendo complemento e não substituto dos potenciais evocados.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O índice biespectral é um número adimensional de 0 a 100 derivado de análise do eletroencefalograma frontal, com faixa-alvo de &lt;strong&gt;40 a 60&lt;/strong&gt; para anestesia geral. Seu algoritmo foi construído a partir de dados de pacientes recebendo agentes que produzem lentificação progressiva do traçado — halogenados, propofol e benzodiazepínicos. Fármacos com padrão eletroencefalográfico distinto quebram essa relação.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;quetamina&lt;/strong&gt;, antagonista NMDA, aumenta a atividade de alta frequência beta e gama, e o algoritmo interpreta esse aumento como sinal de despertar, elevando o índice apesar de plano anestésico adequado ou até aprofundado. O &lt;strong&gt;óxido nitroso&lt;/strong&gt; e os agonistas alfa-2 produzem dissociações análogas em sentidos diversos. Outras limitações relevantes: atraso de processamento de 15 a 30 segundos, contaminação por eletromiografia frontal quando não há relaxante, interferência de dispositivos elétricos, valores não validados em lactentes e alterações por hipotermia e hipoglicemia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) aprofundar às cegas por causa do número, sem sinais clínicos de superficialização, expõe a paciente a depressão hemodinâmica desnecessária. (B) o artefato eletromiográfico é causa real de elevação do índice, mas está afastado pelo bloqueio neuromuscular profundo documentado. (C) o comportamento descrito é previsível e farmacológico, não um defeito de sensor; a troca não modificaria a leitura.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O índice biespectral é um número adimensional de 0 a 100 derivado de análise do eletroencefalograma frontal, com faixa-alvo de &lt;strong&gt;40 a 60&lt;/strong&gt; para anestesia geral. Seu algoritmo foi construído a partir de dados de pacientes recebendo agentes que produzem lentificação progressiva do traçado: halogenados, propofol e benzodiazepínicos. Fármacos com padrão eletroencefalográfico distinto quebram essa relação.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;quetamina&lt;/strong&gt;, antagonista NMDA, aumenta a atividade de alta frequência beta e gama, e o algoritmo interpreta esse aumento como sinal de despertar, elevando o índice apesar de plano anestésico adequado ou até aprofundado. O &lt;strong&gt;óxido nitroso&lt;/strong&gt; e os agonistas alfa-2 produzem dissociações análogas em sentidos diversos. Outras limitações relevantes: atraso de processamento de 15 a 30 segundos, contaminação por eletromiografia frontal quando não há relaxante, interferência de dispositivos elétricos, valores não validados em lactentes e alterações por hipotermia e hipoglicemia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) aprofundar às cegas por causa do número, sem sinais clínicos de superficialização, expõe a paciente a depressão hemodinâmica desnecessária. (B) o artefato eletromiográfico é causa real de elevação do índice, mas está afastado pelo bloqueio neuromuscular profundo documentado. (C) o comportamento descrito é previsível e farmacológico, não um defeito de sensor; a troca não modificaria a leitura.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A distinção entre macrochoque e microchoque depende de &lt;strong&gt;onde&lt;/strong&gt; a corrente entra e de quanto dela alcança o miocárdio. No &lt;strong&gt;macrochoque&lt;/strong&gt;, a corrente atravessa a pele íntegra, cuja resistência elevada dispersa o fluxo por todo o corpo; apenas uma fração mínima chega ao coração. Os limiares clássicos, para corrente alternada de 60 Hz, são aproximadamente: 1 mA para percepção, 5 mA como limite considerado inofensivo, 10 a 20 mA para tetania com perda da capacidade de soltar o objeto, cerca de 100 mA para fibrilação ventricular e acima de 1 a 5 A para contração miocárdica sustentada, queimaduras e lesão térmica.&lt;/p&gt;&lt;p&gt;No &lt;strong&gt;microchoque&lt;/strong&gt;, um condutor — eletrodo de marca-passo, fio epicárdico, cateter venoso central com coluna salina — leva a corrente diretamente ao miocárdio, eliminando a proteção da resistência cutânea. Nessa condição, correntes da ordem de &lt;strong&gt;100 microampères&lt;/strong&gt;, imperceptíveis à pele, já podem deflagrar fibrilação ventricular. Por isso equipamentos com contato cardíaco direto têm limite de corrente de fuga da ordem de 10 microampères, com margem de segurança de dez vezes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) 1 mA na pele apenas é percebido como formigamento. (B) 10 mA na pele causa tetania e é perigoso pela impossibilidade de soltar o condutor, mas não é o limiar de fibrilação. (D) correntes de vários ampères produzem contração miocárdica sustentada e queimadura, mecanismo do próprio desfibrilador, e não fibrilação ventricular.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A distinção entre macrochoque e microchoque depende de &lt;strong&gt;onde&lt;/strong&gt; a corrente entra e de quanto dela alcança o miocárdio. No &lt;strong&gt;macrochoque&lt;/strong&gt;, a corrente atravessa a pele íntegra, cuja resistência elevada dispersa o fluxo por todo o corpo; apenas uma fração mínima chega ao coração. Os limiares clássicos, para corrente alternada de 60 Hz, são aproximadamente: 1 mA para percepção, 5 mA como limite considerado inofensivo, 10 a 20 mA para tetania com perda da capacidade de soltar o objeto, cerca de 100 mA para fibrilação ventricular e acima de 1 a 5 A para contração miocárdica sustentada, queimaduras e lesão térmica.&lt;/p&gt;&lt;p&gt;No &lt;strong&gt;microchoque&lt;/strong&gt;, um condutor (eletrodo de marca-passo, fio epicárdico, cateter venoso central com coluna salina) leva a corrente diretamente ao miocárdio, eliminando a proteção da resistência cutânea. Nessa condição, correntes da ordem de &lt;strong&gt;100 microampères&lt;/strong&gt;, imperceptíveis à pele, já podem deflagrar fibrilação ventricular. Por isso equipamentos com contato cardíaco direto têm limite de corrente de fuga da ordem de 10 microampères, com margem de segurança de dez vezes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) 1 mA na pele apenas é percebido como formigamento. (B) 10 mA na pele causa tetania e é perigoso pela impossibilidade de soltar o condutor, mas não é o limiar de fibrilação. (D) correntes de vários ampères produzem contração miocárdica sustentada e queimadura, mecanismo do próprio desfibrilador, e não fibrilação ventricular.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A cal sodada é composta majoritariamente por &lt;strong&gt;hidróxido de cálcio&lt;/strong&gt;, com pequena proporção de hidróxido de sódio como ativador e cerca de 15% de &lt;strong&gt;água&lt;/strong&gt;, indispensável à reação de neutralização, que ocorre em fase aquosa e gera carbonato de cálcio, água e calor. O indicador colorimétrico habitual é o &lt;strong&gt;etil violeta&lt;/strong&gt;, que muda de branco para &lt;strong&gt;roxo&lt;/strong&gt; quando a queda do pH sinaliza esgotamento — e não o contrário. Duas armadilhas importam: a cor pode reverter ao branco após repouso, mascarando um absorvente exaurido, e o indicador informa sobre esgotamento químico, não sobre &lt;strong&gt;ressecamento&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O fluxo prolongado de gás seco através do canister, situação exatamente descrita no caso, desidrata os grânulos. Cal sodada ressecada degrada agentes halogenados: com desflurano, isoflurano e enflurano produz quantidades relevantes de &lt;strong&gt;monóxido de carbono&lt;/strong&gt;; com sevoflurano, gera composto A e reações fortemente exotérmicas, com relatos de calor extremo e incêndio no canister. A conduta correta é a substituição do absorvente antes do caso e, como prevenção, desligar os fluxos ao término da jornada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) grânulos brancos não excluem ressecamento nem esgotamento com reversão de cor. (C) inverte o sentido da viragem do etil violeta. (D) aguardar CO&lt;sub&gt;2&lt;/sub&gt; inspirado detecta apenas o esgotamento absortivo e não previne a produção de monóxido de carbono, que já ocorre desde as primeiras respirações.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A cal sodada é composta majoritariamente por &lt;strong&gt;hidróxido de cálcio&lt;/strong&gt;, com pequena proporção de hidróxido de sódio como ativador e cerca de 15% de &lt;strong&gt;água&lt;/strong&gt;, indispensável à reação de neutralização, que ocorre em fase aquosa e gera carbonato de cálcio, água e calor. O indicador colorimétrico habitual é o &lt;strong&gt;etil violeta&lt;/strong&gt;, que muda de branco para &lt;strong&gt;roxo&lt;/strong&gt; quando a queda do pH sinaliza esgotamento, e não o contrário. Duas armadilhas importam: a cor pode reverter ao branco após repouso, mascarando um absorvente exaurido, e o indicador informa sobre esgotamento químico, não sobre &lt;strong&gt;ressecamento&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O fluxo prolongado de gás seco através do canister, situação exatamente descrita no caso, desidrata os grânulos. Cal sodada ressecada degrada agentes halogenados: com desflurano, isoflurano e enflurano produz quantidades relevantes de &lt;strong&gt;monóxido de carbono&lt;/strong&gt;; com sevoflurano, gera composto A e reações fortemente exotérmicas, com relatos de calor extremo e incêndio no canister. A conduta correta é a substituição do absorvente antes do caso e, como prevenção, desligar os fluxos ao término da jornada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) grânulos brancos não excluem ressecamento nem esgotamento com reversão de cor. (C) inverte o sentido da viragem do etil violeta. (D) aguardar CO&lt;sub&gt;2&lt;/sub&gt; inspirado detecta apenas o esgotamento absortivo e não previne a produção de monóxido de carbono, que já ocorre desde as primeiras respirações.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O nervo ulnar é o mais frequentemente acometido nas lesões nervosas perioperatórias porque atravessa o &lt;strong&gt;sulco do epicôndilo medial&lt;/strong&gt; do úmero em posição superficial, protegido apenas por pele e tecido subcutâneo. Homens, obesos, diabéticos e pacientes com procedimentos prolongados concentram o risco. Dois mecanismos importam: a compressão externa contra superfície rígida e o estiramento com a flexão acentuada do cotovelo, que tensiona o nervo dentro do túnel cubital.&lt;/p&gt;&lt;p&gt;As medidas consagradas para o decúbito dorsal são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;abdução do braço limitada a 90 graus, para evitar estiramento do plexo braquial;&lt;/li&gt;&lt;li&gt;antebraço em &lt;strong&gt;supinação ou posição neutra&lt;/strong&gt;, o que afasta o epicôndilo medial da superfície de apoio;&lt;/li&gt;&lt;li&gt;acolchoamento do cotovelo e das talas, evitando contato com bordas rígidas;&lt;/li&gt;&lt;li&gt;cotovelo com flexão moderada e cabeça em posição neutra;&lt;/li&gt;&lt;li&gt;proteção de occipúcio, sacro e calcâneos, e verificação periódica do posicionamento em cirurgias longas.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) reúne três erros — abdução acima de 90 graus estira o plexo, a pronação expõe o epicôndilo medial e o apoio em borda rígida concentra pressão. (C) a pronação com o braço junto ao corpo mantém o nervo comprimido contra o colchão ou a lateral da mesa, e omitir o acolchoamento agrava o risco. (D) abdução de 120 graus com rotação externa e flexão acentuada do cotovelo combina estiramento do plexo braquial e tensão do nervo ulnar no túnel cubital.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O nervo ulnar é o mais frequentemente acometido nas lesões nervosas perioperatórias porque atravessa o &lt;strong&gt;sulco do epicôndilo medial&lt;/strong&gt; do úmero em posição superficial, protegido apenas por pele e tecido subcutâneo. Homens, obesos, diabéticos e pacientes com procedimentos prolongados concentram o risco. Dois mecanismos importam: a compressão externa contra superfície rígida e o estiramento com a flexão acentuada do cotovelo, que tensiona o nervo dentro do túnel cubital.&lt;/p&gt;&lt;p&gt;As medidas consagradas para o decúbito dorsal são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;abdução do braço limitada a 90 graus, para evitar estiramento do plexo braquial;&lt;/li&gt;&lt;li&gt;antebraço em &lt;strong&gt;supinação ou posição neutra&lt;/strong&gt;, o que afasta o epicôndilo medial da superfície de apoio;&lt;/li&gt;&lt;li&gt;acolchoamento do cotovelo e das talas, evitando contato com bordas rígidas;&lt;/li&gt;&lt;li&gt;cotovelo com flexão moderada e cabeça em posição neutra;&lt;/li&gt;&lt;li&gt;proteção de occipúcio, sacro e calcâneos, e verificação periódica do posicionamento em cirurgias longas.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) reúne três erros: abdução acima de 90 graus estira o plexo, a pronação expõe o epicôndilo medial e o apoio em borda rígida concentra pressão. (C) a pronação com o braço junto ao corpo mantém o nervo comprimido contra o colchão ou a lateral da mesa, e omitir o acolchoamento agrava o risco. (D) abdução de 120 graus com rotação externa e flexão acentuada do cotovelo combina estiramento do plexo braquial e tensão do nervo ulnar no túnel cubital.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A posição sentada oferece exposição cirúrgica excelente e boa drenagem venosa, mas concentra riscos específicos. O mais temido é a &lt;strong&gt;embolia gasosa venosa&lt;/strong&gt;, favorecida pelo gradiente entre o campo cirúrgico e o átrio direito; o método mais sensível de detecção é a ecocardiografia transesofágica, seguida do &lt;strong&gt;Doppler precordial&lt;/strong&gt;, sendo a queda do dióxido de carbono expirado um sinal precoce e prático. Hipotensão e queda da saturação são manifestações tardias. A presença de &lt;strong&gt;forame oval patente&lt;/strong&gt; com shunt direita-esquerda é considerada contraindicação relevante pelo risco de embolia paradoxal.&lt;/p&gt;&lt;p&gt;As complicações neurológicas ligadas ao próprio posicionamento decorrem da &lt;strong&gt;hiperflexão cervical&lt;/strong&gt; necessária para a exposição. A regra prática é preservar pelo menos &lt;strong&gt;dois dedos de distância entre o mento e o manúbrio esternal&lt;/strong&gt;. A hiperflexão pode causar quadriplegia por isquemia da medula cervical, já vulnerável pela hipotensão e pelo gradiente de pressão de perfusão no paciente sentado, além de obstrução da drenagem venosa e linfática com macroglossia e edema de via aérea superior — motivo pelo qual dispositivos supraglóticos e cânulas orofaríngeas volumosas devem ser evitados nesse contexto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a flexão máxima é exatamente o mecanismo da lesão medular e do edema lingual. (B) a queda da SpO&lt;sub&gt;2&lt;/sub&gt; é tardia; esperar por ela retarda o tratamento da embolia. (C) o shunt direita-esquerda documentado é fator de risco maior para embolia paradoxal, e nenhum monitor o neutraliza.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A posição sentada oferece exposição cirúrgica excelente e boa drenagem venosa, mas concentra riscos específicos. O mais temido é a &lt;strong&gt;embolia gasosa venosa&lt;/strong&gt;, favorecida pelo gradiente entre o campo cirúrgico e o átrio direito; o método mais sensível de detecção é a ecocardiografia transesofágica, seguida do &lt;strong&gt;Doppler precordial&lt;/strong&gt;, sendo a queda do dióxido de carbono expirado um sinal precoce e prático. Hipotensão e queda da saturação são manifestações tardias. A presença de &lt;strong&gt;forame oval patente&lt;/strong&gt; com shunt direita-esquerda é considerada contraindicação relevante pelo risco de embolia paradoxal.&lt;/p&gt;&lt;p&gt;As complicações neurológicas ligadas ao próprio posicionamento decorrem da &lt;strong&gt;hiperflexão cervical&lt;/strong&gt; necessária para a exposição. A regra prática é preservar pelo menos &lt;strong&gt;dois dedos de distância entre o mento e o manúbrio esternal&lt;/strong&gt;. A hiperflexão pode causar quadriplegia por isquemia da medula cervical, já vulnerável pela hipotensão e pelo gradiente de pressão de perfusão no paciente sentado, além de obstrução da drenagem venosa e linfática com macroglossia e edema de via aérea superior, motivo pelo qual dispositivos supraglóticos e cânulas orofaríngeas volumosas devem ser evitados nesse contexto.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a flexão máxima é exatamente o mecanismo da lesão medular e do edema lingual. (B) a queda da SpO&lt;sub&gt;2&lt;/sub&gt; é tardia; esperar por ela retarda o tratamento da embolia. (C) o shunt direita-esquerda documentado é fator de risco maior para embolia paradoxal, e nenhum monitor o neutraliza.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Diante de déficit neurológico no pós-parto de uma paciente que recebeu bloqueio neuroaxial, a primeira tarefa é distinguir uma &lt;strong&gt;neuropatia periférica por compressão&lt;/strong&gt; — muito mais comum — de uma complicação do bloqueio. O padrão do exame é o que decide.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;nervo fibular comum&lt;/strong&gt; contorna o colo da fíbula em posição superficial e é comprimido pelo apoio lateral das perneiras ou pela mão de um auxiliar durante o período expulsivo. O quadro resultante é o pé caído com perda de &lt;strong&gt;dorsiflexão e eversão&lt;/strong&gt;, hipoestesia no dorso do pé e na face lateral da perna, com &lt;strong&gt;inversão preservada&lt;/strong&gt; (tibial posterior) e reflexos aquileu e patelar normais. É lesão unilateral, indolor e com bom prognóstico na maioria dos casos.&lt;/p&gt;&lt;p&gt;Sinais de alarme que apontariam para causa central e exigiriam imagem urgente incluem déficit bilateral, progressão, dor lombar intensa, disfunção esfincteriana e nível sensitivo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a compressão do tronco lombossacro pela cabeça fetal também causa pé caído, mas costuma associar déficit proximal e comprometimento sensitivo mais extenso, o que a paciente não apresenta. (B) o hematoma peridural produz déficit bilateral, progressivo e doloroso, incompatível com um achado focal unilateral no segundo dia. (D) a neuropatia femoral, também descrita na litotomia prolongada, cursa com fraqueza de extensão do joelho e reflexo patelar reduzido, ambos normais no caso.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Diante de déficit neurológico no pós-parto de uma paciente que recebeu bloqueio neuroaxial, a primeira tarefa é distinguir uma &lt;strong&gt;neuropatia periférica por compressão&lt;/strong&gt; (muito mais comum) de uma complicação do bloqueio. O padrão do exame é o que decide.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;nervo fibular comum&lt;/strong&gt; contorna o colo da fíbula em posição superficial e é comprimido pelo apoio lateral das perneiras ou pela mão de um auxiliar durante o período expulsivo. O quadro resultante é o pé caído com perda de &lt;strong&gt;dorsiflexão e eversão&lt;/strong&gt;, hipoestesia no dorso do pé e na face lateral da perna, com &lt;strong&gt;inversão preservada&lt;/strong&gt; (tibial posterior) e reflexos aquileu e patelar normais. É lesão unilateral, indolor e com bom prognóstico na maioria dos casos.&lt;/p&gt;&lt;p&gt;Sinais de alarme que apontariam para causa central e exigiriam imagem urgente incluem déficit bilateral, progressão, dor lombar intensa, disfunção esfincteriana e nível sensitivo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a compressão do tronco lombossacro pela cabeça fetal também causa pé caído, mas costuma associar déficit proximal e comprometimento sensitivo mais extenso, o que a paciente não apresenta. (B) o hematoma peridural produz déficit bilateral, progressivo e doloroso, incompatível com um achado focal unilateral no segundo dia. (D) a neuropatia femoral, também descrita na litotomia prolongada, cursa com fraqueza de extensão do joelho e reflexo patelar reduzido, ambos normais no caso.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A anestesia regional impõe os mesmos padrões mínimos de segurança da anestesia geral, porque suas duas complicações mais graves — &lt;strong&gt;toxicidade sistêmica por anestésico local&lt;/strong&gt; e bloqueio neuroaxial alto — surgem de forma abrupta e exigem resposta imediata. Antes de qualquer punção, devem estar assegurados: monitorização com oximetria, cardioscopia e pressão arterial, acesso venoso pérvio, fonte de oxigênio e material de via aérea, fármacos de reanimação e &lt;strong&gt;emulsão lipídica a 20%&lt;/strong&gt; prontamente disponível, com dose inicial de cerca de 1,5 mL/kg em bolus seguida de infusão.&lt;/p&gt;&lt;p&gt;A dimensão organizacional é igualmente relevante. A conferência do &lt;strong&gt;sítio e da lateralidade&lt;/strong&gt; imediatamente antes da punção, com pausa formal, previne bloqueios no lado errado, evento que figura entre os erros graves evitáveis. O consentimento deve ser informado e registrado, mencionando explicitamente o risco de lesão neurológica, falha do bloqueio e toxicidade. O seguimento pós-operatório é parte do padrão, pois permite identificar precocemente déficits persistentes, documentar sua evolução e diferenciar lesão relacionada ao bloqueio de causas cirúrgicas ou posturais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a toxicidade sistêmica pode ocorrer já durante a injeção, tornando a monitorização indispensável exatamente nesse momento. (B) a lesão neurológica, ainda que infrequente, é risco material que deve constar do consentimento documentado. (C) a ultrassonografia reduz, mas não elimina, lesão nervosa e injeção intravascular, e não substitui o seguimento clínico.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A anestesia regional impõe os mesmos padrões mínimos de segurança da anestesia geral, porque suas duas complicações mais graves, &lt;strong&gt;toxicidade sistêmica por anestésico local&lt;/strong&gt; e bloqueio neuroaxial alto, surgem de forma abrupta e exigem resposta imediata. Antes de qualquer punção, devem estar assegurados: monitorização com oximetria, cardioscopia e pressão arterial, acesso venoso pérvio, fonte de oxigênio e material de via aérea, fármacos de reanimação e &lt;strong&gt;emulsão lipídica a 20%&lt;/strong&gt; prontamente disponível, com dose inicial de cerca de 1,5 mL/kg em bolus seguida de infusão.&lt;/p&gt;&lt;p&gt;A dimensão organizacional é igualmente relevante. A conferência do &lt;strong&gt;sítio e da lateralidade&lt;/strong&gt; imediatamente antes da punção, com pausa formal, previne bloqueios no lado errado, evento que figura entre os erros graves evitáveis. O consentimento deve ser informado e registrado, mencionando explicitamente o risco de lesão neurológica, falha do bloqueio e toxicidade. O seguimento pós-operatório é parte do padrão, pois permite identificar precocemente déficits persistentes, documentar sua evolução e diferenciar lesão relacionada ao bloqueio de causas cirúrgicas ou posturais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a toxicidade sistêmica pode ocorrer já durante a injeção, tornando a monitorização indispensável exatamente nesse momento. (B) a lesão neurológica, ainda que infrequente, é risco material que deve constar do consentimento documentado. (C) a ultrassonografia reduz, mas não elimina, lesão nervosa e injeção intravascular, e não substitui o seguimento clínico.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O incêndio em via aérea depende da tríade combustível, comburente e fonte de ignição. Na cirurgia a laser, o laser é a ignição, o tubo traqueal e as compressas são o combustível, e o &lt;strong&gt;oxigênio e o óxido nitroso&lt;/strong&gt; são os comburentes — o óxido nitroso mantém a combustão tão bem quanto o oxigênio e deve ser evitado. A prevenção inclui manter a fração inspirada de oxigênio em 0,3 ou menos, usar tubo resistente a laser, preencher o balonete com solução salina corada com azul de metileno, para que a perfuração seja evidente e o líquido ajude a extinguir a chama, e proteger o campo com compressas úmidas.&lt;/p&gt;&lt;p&gt;Instalado o fogo, a sequência é padronizada e simultânea: &lt;strong&gt;interromper todos os gases&lt;/strong&gt;, &lt;strong&gt;remover imediatamente o tubo em chamas&lt;/strong&gt; e &lt;strong&gt;derramar solução salina na via aérea e no campo&lt;/strong&gt;. Só depois de extinta a chama retoma-se a ventilação, agora com ar ambiente até que seja seguro reintroduzir oxigênio, procede-se à reintubação e realiza-se broncoscopia para avaliar a extensão da lesão térmica e remover fragmentos. Segue-se internação com vigilância de edema de via aérea.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) aumentar o oxigênio alimenta a combustão e agrava o incêndio. (B) manter no lugar um tubo em chamas prolonga a queima dentro da traqueia e amplia a lesão térmica. (D) corticoide não tem prioridade sobre a extinção do fogo, e sua eficácia na lesão térmica de via aérea não é estabelecida.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O incêndio em via aérea depende da tríade combustível, comburente e fonte de ignição. Na cirurgia a laser, o laser é a ignição, o tubo traqueal e as compressas são o combustível, e o &lt;strong&gt;oxigênio e o óxido nitroso&lt;/strong&gt; são os comburentes: o óxido nitroso mantém a combustão tão bem quanto o oxigênio e deve ser evitado. A prevenção inclui manter a fração inspirada de oxigênio em 0,3 ou menos, usar tubo resistente a laser, preencher o balonete com solução salina corada com azul de metileno, para que a perfuração seja evidente e o líquido ajude a extinguir a chama, e proteger o campo com compressas úmidas.&lt;/p&gt;&lt;p&gt;Instalado o fogo, a sequência é padronizada e simultânea: &lt;strong&gt;interromper todos os gases&lt;/strong&gt;, &lt;strong&gt;remover imediatamente o tubo em chamas&lt;/strong&gt; e &lt;strong&gt;derramar solução salina na via aérea e no campo&lt;/strong&gt;. Só depois de extinta a chama retoma-se a ventilação, agora com ar ambiente até que seja seguro reintroduzir oxigênio, procede-se à reintubação e realiza-se broncoscopia para avaliar a extensão da lesão térmica e remover fragmentos. Segue-se internação com vigilância de edema de via aérea.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) aumentar o oxigênio alimenta a combustão e agrava o incêndio. (B) manter no lugar um tubo em chamas prolonga a queima dentro da traqueia e amplia a lesão térmica. (D) corticoide não tem prioridade sobre a extinção do fogo, e sua eficácia na lesão térmica de via aérea não é estabelecida.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A reversão com &lt;strong&gt;anticolinesterásicos&lt;/strong&gt; não age sobre o bloqueador: ela inibe a acetilcolinesterase, aumenta a concentração de acetilcolina na fenda e desloca competitivamente o relaxante do receptor nicotínico. Como o mecanismo depende de enzima disponível para ser inibida, existe &lt;em&gt;efeito teto&lt;/em&gt; — acima de cerca de 0,07 mg/kg (aproximadamente 5 mg no adulto) a neostigmina não acrescenta reversão, apenas efeitos muscarínicos.&lt;/p&gt;&lt;p&gt;Esse excesso de acetilcolina também alcança receptores muscarínicos, com bradicardia, hipersecreção salivar e brônquica e broncoespasmo. Daí a obrigatoriedade do anticolinérgico, escolhido por compatibilidade farmacocinética: a neostigmina tem instalação relativamente lenta, com pico de efeito em torno de 7 a 11 minutos, e combina melhor com o &lt;strong&gt;glicopirrolato&lt;/strong&gt;, de início igualmente gradual, na proporção clássica de 0,2 mg para cada 1 mg de neostigmina. A atropina, de instalação rápida, é a parceira lógica do edrofônio.&lt;/p&gt;&lt;p&gt;A contagem de três respostas indica bloqueio moderado, situação em que o anticolinesterásico é eficaz; na ausência de respostas ao estímulo de quatro, a neostigmina é insuficiente e a reversão exige outra estratégia ou espera.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a atropina age muito mais rápido que a neostigmina, produzindo taquicardia inicial seguida de bradicardia quando o efeito muscarínico do anticolinesterásico se instala. (C) doses acima do teto não melhoram a força muscular e podem cursar com fraqueza paradoxal e efeitos colinérgicos intensos. (D) o edrofônio tem início rápido e deve ser pareado com atropina; a associação descrita inverte a lógica temporal.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A reversão com &lt;strong&gt;anticolinesterásicos&lt;/strong&gt; não age sobre o bloqueador: ela inibe a acetilcolinesterase, aumenta a concentração de acetilcolina na fenda e desloca competitivamente o relaxante do receptor nicotínico. Como o mecanismo depende de enzima disponível para ser inibida, existe &lt;em&gt;efeito teto&lt;/em&gt;: acima de cerca de 0,07 mg/kg (aproximadamente 5 mg no adulto) a neostigmina não acrescenta reversão, apenas efeitos muscarínicos.&lt;/p&gt;&lt;p&gt;Esse excesso de acetilcolina também alcança receptores muscarínicos, com bradicardia, hipersecreção salivar e brônquica e broncoespasmo. Daí a obrigatoriedade do anticolinérgico, escolhido por compatibilidade farmacocinética: a neostigmina tem instalação relativamente lenta, com pico de efeito em torno de 7 a 11 minutos, e combina melhor com o &lt;strong&gt;glicopirrolato&lt;/strong&gt;, de início igualmente gradual, na proporção clássica de 0,2 mg para cada 1 mg de neostigmina. A atropina, de instalação rápida, é a parceira lógica do edrofônio.&lt;/p&gt;&lt;p&gt;A contagem de três respostas indica bloqueio moderado, situação em que o anticolinesterásico é eficaz; na ausência de respostas ao estímulo de quatro, a neostigmina é insuficiente e a reversão exige outra estratégia ou espera.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a atropina age muito mais rápido que a neostigmina, produzindo taquicardia inicial seguida de bradicardia quando o efeito muscarínico do anticolinesterásico se instala. (C) doses acima do teto não melhoram a força muscular e podem cursar com fraqueza paradoxal e efeitos colinérgicos intensos. (D) o edrofônio tem início rápido e deve ser pareado com atropina; a associação descrita inverte a lógica temporal.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A chave é conhecer o território do &lt;strong&gt;nervo femoral&lt;/strong&gt; (L2-L4): motor para o quadríceps e o sartório, portanto responsável pela &lt;strong&gt;extensão do joelho&lt;/strong&gt;, e sensitivo para a face anterior da coxa e, por meio do seu ramo terminal &lt;strong&gt;safeno&lt;/strong&gt;, para a face medial da perna até o maléolo medial. O nervo femoral &lt;em&gt;não&lt;/em&gt; inerva nenhum músculo abaixo do joelho e não participa da dorsiflexão do pé.&lt;/p&gt;&lt;p&gt;Dorsiflexão ausente com hipoestesia no dorso do pé e na face lateral da perna é o quadro típico de lesão do &lt;strong&gt;nervo fibular comum&lt;/strong&gt;, tipicamente por compressão no colo da fíbula — posicionamento, garrote pneumático, imobilizador ou curativo compressivo — ou por estiramento durante a correção de deformidade em valgo na artroplastia. Atribuir esse déficit ao cateter femoral é o erro clássico, e ele atrasa a investigação de uma lesão potencialmente reversível.&lt;/p&gt;&lt;p&gt;A conduta é examinar o membro, retirar fontes de compressão, suspender temporariamente a infusão para reavaliar sem confundimento e solicitar avaliação especializada se o déficit persistir.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o bloqueio femoral não se estende ao compartimento anterior da perna, e simplesmente aguardar retarda o diagnóstico. (C) a ropivacaína a 0,2% é concentração analgésica habitual, e neurotoxicidade nessa faixa é excepcional e não teria distribuição de um único nervo distal. (D) o nervo obturatório inerva os adutores da coxa e uma pequena área cutânea medial; não tem qualquer relação com a dorsiflexão do pé.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A chave é conhecer o território do &lt;strong&gt;nervo femoral&lt;/strong&gt; (L2-L4): motor para o quadríceps e o sartório, portanto responsável pela &lt;strong&gt;extensão do joelho&lt;/strong&gt;, e sensitivo para a face anterior da coxa e, por meio do seu ramo terminal &lt;strong&gt;safeno&lt;/strong&gt;, para a face medial da perna até o maléolo medial. O nervo femoral &lt;em&gt;não&lt;/em&gt; inerva nenhum músculo abaixo do joelho e não participa da dorsiflexão do pé.&lt;/p&gt;&lt;p&gt;Dorsiflexão ausente com hipoestesia no dorso do pé e na face lateral da perna é o quadro típico de lesão do &lt;strong&gt;nervo fibular comum&lt;/strong&gt;, tipicamente por compressão no colo da fíbula (posicionamento, garrote pneumático, imobilizador ou curativo compressivo) ou por estiramento durante a correção de deformidade em valgo na artroplastia. Atribuir esse déficit ao cateter femoral é o erro clássico, e ele atrasa a investigação de uma lesão potencialmente reversível.&lt;/p&gt;&lt;p&gt;A conduta é examinar o membro, retirar fontes de compressão, suspender temporariamente a infusão para reavaliar sem confundimento e solicitar avaliação especializada se o déficit persistir.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o bloqueio femoral não se estende ao compartimento anterior da perna, e simplesmente aguardar retarda o diagnóstico. (C) a ropivacaína a 0,2% é concentração analgésica habitual, e neurotoxicidade nessa faixa é excepcional e não teria distribuição de um único nervo distal. (D) o nervo obturatório inerva os adutores da coxa e uma pequena área cutânea medial; não tem qualquer relação com a dorsiflexão do pé.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Duas informações anatômicas explicam o padrão observado. A pele que recobre a parte superior do ombro, a clavícula e a região do trapézio — a chamada capa do ombro — é suprida pelos &lt;strong&gt;nervos supraclaviculares&lt;/strong&gt;, ramos do plexo cervical superficial originados de &lt;strong&gt;C3-C4&lt;/strong&gt;. Já a pele sobre a face lateral do deltoide é território do nervo &lt;strong&gt;axilar&lt;/strong&gt; (C5-C6), ramo do plexo braquial. Por isso incisões e portais superiores podem doer mesmo com bloqueio do plexo braquial tecnicamente perfeito, e o complemento do plexo cervical superficial é útil em alguns acessos.&lt;/p&gt;&lt;p&gt;Na mão, o &lt;strong&gt;nervo ulnar&lt;/strong&gt; (C8-T1) supre o quinto dedo e a metade medial do quarto, além da borda medial da palma e do dorso. O bloqueio interescalênico é depositado em nível de raízes superiores e médias, e caracteristicamente &lt;em&gt;poupa C8-T1&lt;/em&gt;: a sensibilidade preservada no quinto dedo é o achado esperado, não sinal de falha, e é a razão de a via interescalênica ser inadequada para cirurgia de mão e antebraço distal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o nervo axilar cobre a pele sobre o deltoide, não a capa superior do ombro, e o quinto dedo não é território do mediano. (C) o nervo supraescapular é essencialmente motor e articular para o ombro, com contribuição cutânea desprezível, e o radial não inerva o quinto dedo. (D) o nervo torácico longo é puramente motor, destinado ao músculo serrátil anterior, sem território cutâneo.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Duas informações anatômicas explicam o padrão observado. A pele que recobre a parte superior do ombro, a clavícula e a região do trapézio (a chamada capa do ombro) é suprida pelos &lt;strong&gt;nervos supraclaviculares&lt;/strong&gt;, ramos do plexo cervical superficial originados de &lt;strong&gt;C3-C4&lt;/strong&gt;. Já a pele sobre a face lateral do deltoide é território do nervo &lt;strong&gt;axilar&lt;/strong&gt; (C5-C6), ramo do plexo braquial. Por isso incisões e portais superiores podem doer mesmo com bloqueio do plexo braquial tecnicamente perfeito, e o complemento do plexo cervical superficial é útil em alguns acessos.&lt;/p&gt;&lt;p&gt;Na mão, o &lt;strong&gt;nervo ulnar&lt;/strong&gt; (C8-T1) supre o quinto dedo e a metade medial do quarto, além da borda medial da palma e do dorso. O bloqueio interescalênico é depositado em nível de raízes superiores e médias, e caracteristicamente &lt;em&gt;poupa C8-T1&lt;/em&gt;: a sensibilidade preservada no quinto dedo é o achado esperado, não sinal de falha, e é a razão de a via interescalênica ser inadequada para cirurgia de mão e antebraço distal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o nervo axilar cobre a pele sobre o deltoide, não a capa superior do ombro, e o quinto dedo não é território do mediano. (C) o nervo supraescapular é essencialmente motor e articular para o ombro, com contribuição cutânea desprezível, e o radial não inerva o quinto dedo. (D) o nervo torácico longo é puramente motor, destinado ao músculo serrátil anterior, sem território cutâneo.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;nervo femoral&lt;/strong&gt; deriva de L2-L4 e emerge sob o ligamento inguinal lateralmente à artéria femoral, já dividido em ramos, abaixo da &lt;em&gt;fáscia ilíaca&lt;/em&gt; — plano que orienta a injeção guiada por ultrassom. Ele é o nervo motor do &lt;strong&gt;quadríceps&lt;/strong&gt;, único extensor do joelho, e fornece inervação sensitiva à face anterior da coxa, à cápsula anterior do joelho e, por seu ramo terminal &lt;strong&gt;safeno&lt;/strong&gt;, à &lt;strong&gt;face medial da perna até o maléolo medial&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;A consequência clínica mais relevante é a &lt;strong&gt;fraqueza do quadríceps&lt;/strong&gt;, com incapacidade de travar o joelho em extensão e risco real de queda ao tentar apoio no membro operado. Por isso o bloqueio femoral exige orientação explícita ao paciente e à enfermagem, imobilizador em extensão e deambulação assistida. Essa é justamente a limitação que motivou a difusão do bloqueio do canal dos adutores, que preserva parte da força do quadríceps por atuar principalmente sobre o safeno.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o bloqueio femoral compromete a extensão do joelho e alcança território sensitivo distal pelo safeno; a ausência de precauções é justamente o erro que resulta em quedas. (C) a flexão do joelho e a face posterior da coxa dependem do nervo ciático e de ramos do plexo lombossacral, não do femoral. (D) a face lateral da perna e o dorso do pé são território fibular, ramo do ciático, e a ausência de restrição para deambular é inadequada com quadríceps bloqueado.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;nervo femoral&lt;/strong&gt; deriva de L2-L4 e emerge sob o ligamento inguinal lateralmente à artéria femoral, já dividido em ramos, abaixo da &lt;em&gt;fáscia ilíaca&lt;/em&gt;, plano que orienta a injeção guiada por ultrassom. Ele é o nervo motor do &lt;strong&gt;quadríceps&lt;/strong&gt;, único extensor do joelho, e fornece inervação sensitiva à face anterior da coxa, à cápsula anterior do joelho e, por seu ramo terminal &lt;strong&gt;safeno&lt;/strong&gt;, à &lt;strong&gt;face medial da perna até o maléolo medial&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;A consequência clínica mais relevante é a &lt;strong&gt;fraqueza do quadríceps&lt;/strong&gt;, com incapacidade de travar o joelho em extensão e risco real de queda ao tentar apoio no membro operado. Por isso o bloqueio femoral exige orientação explícita ao paciente e à enfermagem, imobilizador em extensão e deambulação assistida. Essa é justamente a limitação que motivou a difusão do bloqueio do canal dos adutores, que preserva parte da força do quadríceps por atuar principalmente sobre o safeno.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o bloqueio femoral compromete a extensão do joelho e alcança território sensitivo distal pelo safeno; a ausência de precauções é justamente o erro que resulta em quedas. (C) a flexão do joelho e a face posterior da coxa dependem do nervo ciático e de ramos do plexo lombossacral, não do femoral. (D) a face lateral da perna e o dorso do pé são território fibular, ramo do ciático, e a ausência de restrição para deambular é inadequada com quadríceps bloqueado.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os &lt;strong&gt;nervos dorsais do pênis&lt;/strong&gt; são ramos terminais do nervo pudendo (S2-S4) e correm sob a &lt;strong&gt;fáscia de Buck&lt;/strong&gt;, de cada lado da linha média, junto aos vasos dorsais. A injeção bilateral logo abaixo da sínfise púbica, com volumes pequenos — da ordem de &lt;strong&gt;0,1 mL/kg por lado&lt;/strong&gt;, tipicamente 1 a 2 mL em uma criança desse porte — produz analgesia confiável para postectomia por várias horas.&lt;/p&gt;&lt;p&gt;A regra inegociável é a &lt;strong&gt;ausência de vasoconstritor&lt;/strong&gt;. O pênis é irrigado por circulação de tipo terminal, e a adrenalina pode causar vasoconstrição prolongada com isquemia e necrose da glande. Nenhuma vantagem de duração justifica esse risco.&lt;/p&gt;&lt;p&gt;O volume também importa por outra razão: injeções excessivas nesse espaço fechado podem comprometer a perfusão por efeito puramente mecânico. Com bupivacaína a 0,25%, 4 mL totais correspondem a 10 mg, cerca de 0,6 mg/kg nessa criança, bem abaixo do limite de 2 a 2,5 mg/kg. A aspiração antes de injetar é obrigatória pela proximidade dos vasos dorsais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) e (C) incluem adrenalina, contraindicada em bloqueio peniano pelo risco de isquemia; a alternativa C ainda usa concentração elevada e plano anatômico inadequado. (B) associa vasoconstritor ao volume excessivo de 10 mL totais em criança de 16 kg, somando risco isquêmico, risco de compressão local e aproximação desnecessária das doses tóxicas.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os &lt;strong&gt;nervos dorsais do pênis&lt;/strong&gt; são ramos terminais do nervo pudendo (S2-S4) e correm sob a &lt;strong&gt;fáscia de Buck&lt;/strong&gt;, de cada lado da linha média, junto aos vasos dorsais. A injeção bilateral logo abaixo da sínfise púbica, com volumes pequenos (da ordem de &lt;strong&gt;0,1 mL/kg por lado&lt;/strong&gt;, tipicamente 1 a 2 mL em uma criança desse porte), produz analgesia confiável para postectomia por várias horas.&lt;/p&gt;&lt;p&gt;A regra inegociável é a &lt;strong&gt;ausência de vasoconstritor&lt;/strong&gt;. O pênis é irrigado por circulação de tipo terminal, e a adrenalina pode causar vasoconstrição prolongada com isquemia e necrose da glande. Nenhuma vantagem de duração justifica esse risco.&lt;/p&gt;&lt;p&gt;O volume também importa por outra razão: injeções excessivas nesse espaço fechado podem comprometer a perfusão por efeito puramente mecânico. Com bupivacaína a 0,25%, 4 mL totais correspondem a 10 mg, cerca de 0,6 mg/kg nessa criança, bem abaixo do limite de 2 a 2,5 mg/kg. A aspiração antes de injetar é obrigatória pela proximidade dos vasos dorsais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) e (C) incluem adrenalina, contraindicada em bloqueio peniano pelo risco de isquemia; a alternativa C ainda usa concentração elevada e plano anatômico inadequado. (B) associa vasoconstritor ao volume excessivo de 10 mL totais em criança de 16 kg, somando risco isquêmico, risco de compressão local e aproximação desnecessária das doses tóxicas.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Alergia verdadeira, mediada por IgE, aos anestésicos locais do grupo &lt;strong&gt;amida&lt;/strong&gt; é excepcionalmente rara. Quando há reação, os suspeitos habituais são outros componentes da solução ou os ésteres, cujo metabólito &lt;strong&gt;ácido paraminobenzoico (PABA)&lt;/strong&gt; é reconhecidamente alergênico.&lt;/p&gt;&lt;p&gt;Duas substâncias merecem atenção. O &lt;strong&gt;metilparabeno&lt;/strong&gt;, conservante antimicrobiano dos frascos multidose, tem estrutura semelhante ao PABA e pode desencadear reação. O &lt;strong&gt;metabissulfito de sódio&lt;/strong&gt; é o antioxidante adicionado às soluções que contêm &lt;strong&gt;adrenalina&lt;/strong&gt;, para impedir sua degradação; sulfitos são reconhecidos desencadeantes de broncoespasmo em asmáticos sensíveis, exatamente o quadro descrito. A presença do antioxidante também explica o pH mais ácido dessas apresentações, com latência maior do bloqueio.&lt;/p&gt;&lt;p&gt;A conduta racional é usar um anestésico amida em &lt;strong&gt;ampola de dose única&lt;/strong&gt;, isenta de conservante, e &lt;strong&gt;sem vasoconstritor&lt;/strong&gt;, portanto sem metabissulfito. Se houver necessidade de esclarecimento definitivo, o encaminhamento para teste alergológico com o agente e os aditivos separadamente é o caminho.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) contraindicar toda a classe amida com base em um episódio provavelmente ligado a aditivo priva a paciente de opções seguras, e os ésteres são justamente os mais alergênicos. (B) o metilparabeno não é o único conservante relevante nem é o que caracteristicamente acompanha a adrenalina — esse papel é do metabissulfito. (C) a história clínica é sugestiva mas não confirma mecanismo IgE contra a lidocaína, e abandonar a investigação perpetua um rótulo equivocado no prontuário.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Alergia verdadeira, mediada por IgE, aos anestésicos locais do grupo &lt;strong&gt;amida&lt;/strong&gt; é excepcionalmente rara. Quando há reação, os suspeitos habituais são outros componentes da solução ou os ésteres, cujo metabólito &lt;strong&gt;ácido paraminobenzoico (PABA)&lt;/strong&gt; é reconhecidamente alergênico.&lt;/p&gt;&lt;p&gt;Duas substâncias merecem atenção. O &lt;strong&gt;metilparabeno&lt;/strong&gt;, conservante antimicrobiano dos frascos multidose, tem estrutura semelhante ao PABA e pode desencadear reação. O &lt;strong&gt;metabissulfito de sódio&lt;/strong&gt; é o antioxidante adicionado às soluções que contêm &lt;strong&gt;adrenalina&lt;/strong&gt;, para impedir sua degradação; sulfitos são reconhecidos desencadeantes de broncoespasmo em asmáticos sensíveis, exatamente o quadro descrito. A presença do antioxidante também explica o pH mais ácido dessas apresentações, com latência maior do bloqueio.&lt;/p&gt;&lt;p&gt;A conduta racional é usar um anestésico amida em &lt;strong&gt;ampola de dose única&lt;/strong&gt;, isenta de conservante, e &lt;strong&gt;sem vasoconstritor&lt;/strong&gt;, portanto sem metabissulfito. Se houver necessidade de esclarecimento definitivo, o encaminhamento para teste alergológico com o agente e os aditivos separadamente é o caminho.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) contraindicar toda a classe amida com base em um episódio provavelmente ligado a aditivo priva a paciente de opções seguras, e os ésteres são justamente os mais alergênicos. (B) o metilparabeno não é o único conservante relevante nem é o que caracteristicamente acompanha a adrenalina: esse papel é do metabissulfito. (C) a história clínica é sugestiva mas não confirma mecanismo IgE contra a lidocaína, e abandonar a investigação perpetua um rótulo equivocado no prontuário.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os anestésicos locais são bases fracas comercializadas como sais de cloridrato, com pH ácido — mais ainda nas apresentações com adrenalina, que contêm antioxidante. Apenas a forma &lt;strong&gt;não ionizada&lt;/strong&gt; atravessa a membrana axonal; elevar o pH da solução aumenta essa fração e &lt;strong&gt;encurta a latência&lt;/strong&gt; do bloqueio.&lt;/p&gt;&lt;p&gt;A proporção consagrada para a &lt;strong&gt;lidocaína&lt;/strong&gt; é de aproximadamente &lt;strong&gt;1 mEq de bicarbonato de sódio a 8,4% para cada 10 mL&lt;/strong&gt; de solução, ou seja, cerca de 0,1 mEq/mL. Para a &lt;strong&gt;bupivacaína&lt;/strong&gt;, cuja margem antes da precipitação é estreitíssima, a quantidade deve ser dez vezes menor — da ordem de 0,1 mEq para cada 10 mL — sob pena de a solução turvar e precipitar, tornando-se inutilizável.&lt;/p&gt;&lt;p&gt;Quanto à &lt;strong&gt;adrenalina&lt;/strong&gt;, seu papel é distinto e complementar: por vasoconstrição local reduz a absorção sistêmica, prolonga a duração, diminui o pico plasmático e funciona como marcador de injeção intravascular na dose-teste. Ela não acelera a latência; ao contrário, acidifica a solução.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a proporção descrita é dez vezes maior que a recomendada e produziria alcalinização excessiva com precipitação do fármaco. (B) transpor a proporção da lidocaína para a bupivacaína é o erro clássico que resulta em precipitação imediata. (D) os dois adjuvantes têm mecanismos e finalidades diferentes; o bicarbonato altera o equilíbrio de ionização, mas não reduz a absorção sistêmica nem substitui a função da adrenalina.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os anestésicos locais são bases fracas comercializadas como sais de cloridrato, com pH ácido, mais ainda nas apresentações com adrenalina, que contêm antioxidante. Apenas a forma &lt;strong&gt;não ionizada&lt;/strong&gt; atravessa a membrana axonal; elevar o pH da solução aumenta essa fração e &lt;strong&gt;encurta a latência&lt;/strong&gt; do bloqueio.&lt;/p&gt;&lt;p&gt;A proporção consagrada para a &lt;strong&gt;lidocaína&lt;/strong&gt; é de aproximadamente &lt;strong&gt;1 mEq de bicarbonato de sódio a 8,4% para cada 10 mL&lt;/strong&gt; de solução, ou seja, cerca de 0,1 mEq/mL. Para a &lt;strong&gt;bupivacaína&lt;/strong&gt;, cuja margem antes da precipitação é estreitíssima, a quantidade deve ser dez vezes menor (da ordem de 0,1 mEq para cada 10 mL), sob pena de a solução turvar e precipitar, tornando-se inutilizável.&lt;/p&gt;&lt;p&gt;Quanto à &lt;strong&gt;adrenalina&lt;/strong&gt;, seu papel é distinto e complementar: por vasoconstrição local reduz a absorção sistêmica, prolonga a duração, diminui o pico plasmático e funciona como marcador de injeção intravascular na dose-teste. Ela não acelera a latência; ao contrário, acidifica a solução.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a proporção descrita é dez vezes maior que a recomendada e produziria alcalinização excessiva com precipitação do fármaco. (B) transpor a proporção da lidocaína para a bupivacaína é o erro clássico que resulta em precipitação imediata. (D) os dois adjuvantes têm mecanismos e finalidades diferentes; o bicarbonato altera o equilíbrio de ionização, mas não reduz a absorção sistêmica nem substitui a função da adrenalina.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A liberação de acetilcolina depende de uma cascata bem definida: o potencial de ação despolariza o terminal nervoso, abre &lt;strong&gt;canais de cálcio voltagem-dependentes&lt;/strong&gt; do tipo P/Q, e o influxo de cálcio dispara a fusão das vesículas com a membrana pré-sináptica, mediada pelas proteínas do complexo &lt;strong&gt;SNARE&lt;/strong&gt; — entre elas SNAP-25, sintaxina e sinaptobrevina.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;toxina botulínica&lt;/strong&gt; atua exatamente nesse ponto: internalizada no terminal, cliva proteoliticamente componentes do complexo SNARE e impede a exocitose, produzindo paralisia flácida &lt;em&gt;sem&lt;/em&gt; qualquer ação sobre o receptor pós-sináptico. O efeito é duradouro, pois exige a formação de novas terminações, e residualmente aumenta a sensibilidade aos bloqueadores não despolarizantes.&lt;/p&gt;&lt;p&gt;Outros exemplos pré-sinápticos: na &lt;strong&gt;síndrome de Eaton-Lambert&lt;/strong&gt;, anticorpos dirigidos aos canais de cálcio pré-sinápticos reduzem a liberação de acetilcolina; os &lt;strong&gt;aminoglicosídeos&lt;/strong&gt; e o &lt;strong&gt;magnésio&lt;/strong&gt; inibem o influxo de cálcio; e o &lt;strong&gt;lítio&lt;/strong&gt;, por interferir no trânsito iônico do terminal, &lt;em&gt;prolonga&lt;/em&gt; o bloqueio tanto de despolarizantes quanto de não despolarizantes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) descreve o mecanismo dos relaxantes não despolarizantes, e não o da toxina botulínica, que é pré-sináptica e não competitiva. (B) confunde as duas síndromes: os anticorpos da Eaton-Lambert são contra canais de cálcio pré-sinápticos, enquanto na miastenia gravis o alvo é o receptor nicotínico pós-juncional. (C) inverte o efeito do lítio, que potencializa e prolonga o bloqueio neuromuscular em vez de antagonizá-lo.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A liberação de acetilcolina depende de uma cascata bem definida: o potencial de ação despolariza o terminal nervoso, abre &lt;strong&gt;canais de cálcio voltagem-dependentes&lt;/strong&gt; do tipo P/Q, e o influxo de cálcio dispara a fusão das vesículas com a membrana pré-sináptica, mediada pelas proteínas do complexo &lt;strong&gt;SNARE&lt;/strong&gt;, entre elas SNAP-25, sintaxina e sinaptobrevina.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;toxina botulínica&lt;/strong&gt; atua exatamente nesse ponto: internalizada no terminal, cliva proteoliticamente componentes do complexo SNARE e impede a exocitose, produzindo paralisia flácida &lt;em&gt;sem&lt;/em&gt; qualquer ação sobre o receptor pós-sináptico. O efeito é duradouro, pois exige a formação de novas terminações, e residualmente aumenta a sensibilidade aos bloqueadores não despolarizantes.&lt;/p&gt;&lt;p&gt;Outros exemplos pré-sinápticos: na &lt;strong&gt;síndrome de Eaton-Lambert&lt;/strong&gt;, anticorpos dirigidos aos canais de cálcio pré-sinápticos reduzem a liberação de acetilcolina; os &lt;strong&gt;aminoglicosídeos&lt;/strong&gt; e o &lt;strong&gt;magnésio&lt;/strong&gt; inibem o influxo de cálcio; e o &lt;strong&gt;lítio&lt;/strong&gt;, por interferir no trânsito iônico do terminal, &lt;em&gt;prolonga&lt;/em&gt; o bloqueio tanto de despolarizantes quanto de não despolarizantes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) descreve o mecanismo dos relaxantes não despolarizantes, e não o da toxina botulínica, que é pré-sináptica e não competitiva. (B) confunde as duas síndromes: os anticorpos da Eaton-Lambert são contra canais de cálcio pré-sinápticos, enquanto na miastenia gravis o alvo é o receptor nicotínico pós-juncional. (C) inverte o efeito do lítio, que potencializa e prolonga o bloqueio neuromuscular em vez de antagonizá-lo.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O conjunto fraqueza proximal de membros inferiores, sintomas autonômicos (boca seca, constipação) e &lt;strong&gt;facilitação&lt;/strong&gt; — ganho transitório de força após contração repetida — em paciente com &lt;strong&gt;carcinoma de pequenas células de pulmão&lt;/strong&gt; caracteriza a &lt;strong&gt;síndrome miastênica de Eaton-Lambert&lt;/strong&gt;. O mecanismo é &lt;em&gt;pré-sináptico&lt;/em&gt;: autoanticorpos contra os &lt;strong&gt;canais de cálcio voltagem-dependentes&lt;/strong&gt; do terminal nervoso reduzem a liberação de acetilcolina. A estimulação repetida acumula cálcio no terminal e melhora momentaneamente a transmissão, o que explica a facilitação clínica e o incremento na estimulação de alta frequência.&lt;/p&gt;&lt;p&gt;A implicação anestésica decisiva é a &lt;strong&gt;sensibilidade acentuada a todos os bloqueadores neuromusculares&lt;/strong&gt;, tanto despolarizantes quanto não despolarizantes, com bloqueio profundo e prolongado por doses convencionais. Sempre que possível o relaxante deve ser evitado ou usado em fração da dose, com monitorização quantitativa obrigatória e reversão documentada. A resposta aos anticolinesterásicos é habitualmente pobre, ao contrário do que ocorre na miastenia gravis.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) na miastenia gravis a fraqueza &lt;em&gt;piora&lt;/em&gt; com o esforço repetido, é tipicamente ocular e bulbar no início e não se associa a disautonomia; a boa resposta a anticolinesterásicos não se aplica ao caso descrito. (C) descreve corretamente o perfil farmacológico da miastenia gravis — resistência à succinilcolina e sensibilidade aos não despolarizantes — mas o diagnóstico do caso é outro. (D) atribui à Eaton-Lambert mecanismo pós-sináptico, anticorpos anti-MuSK e alteração tímica, todos característicos da miastenia gravis.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O conjunto fraqueza proximal de membros inferiores, sintomas autonômicos (boca seca, constipação) e &lt;strong&gt;facilitação&lt;/strong&gt; (ganho transitório de força após contração repetida) em paciente com &lt;strong&gt;carcinoma de pequenas células de pulmão&lt;/strong&gt; caracteriza a &lt;strong&gt;síndrome miastênica de Eaton-Lambert&lt;/strong&gt;. O mecanismo é &lt;em&gt;pré-sináptico&lt;/em&gt;: autoanticorpos contra os &lt;strong&gt;canais de cálcio voltagem-dependentes&lt;/strong&gt; do terminal nervoso reduzem a liberação de acetilcolina. A estimulação repetida acumula cálcio no terminal e melhora momentaneamente a transmissão, o que explica a facilitação clínica e o incremento na estimulação de alta frequência.&lt;/p&gt;&lt;p&gt;A implicação anestésica decisiva é a &lt;strong&gt;sensibilidade acentuada a todos os bloqueadores neuromusculares&lt;/strong&gt;, tanto despolarizantes quanto não despolarizantes, com bloqueio profundo e prolongado por doses convencionais. Sempre que possível o relaxante deve ser evitado ou usado em fração da dose, com monitorização quantitativa obrigatória e reversão documentada. A resposta aos anticolinesterásicos é habitualmente pobre, ao contrário do que ocorre na miastenia gravis.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) na miastenia gravis a fraqueza &lt;em&gt;piora&lt;/em&gt; com o esforço repetido, é tipicamente ocular e bulbar no início e não se associa a disautonomia; a boa resposta a anticolinesterásicos não se aplica ao caso descrito. (C) descreve corretamente o perfil farmacológico da miastenia gravis (resistência à succinilcolina e sensibilidade aos não despolarizantes), mas o diagnóstico do caso é outro. (D) atribui à Eaton-Lambert mecanismo pós-sináptico, anticorpos anti-MuSK e alteração tímica, todos característicos da miastenia gravis.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O comportamento dos bloqueadores neuromusculares no neonato resulta de fatores que se opõem e explicam por que a dose por quilograma é semelhante à do adulto, mas a duração é maior.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Farmacodinâmica:&lt;/strong&gt; a junção neuromuscular é &lt;em&gt;imatura&lt;/em&gt; até cerca de dois meses de idade, com menor reserva de acetilcolina e receptores ainda de subtipo fetal. Isso confere &lt;strong&gt;sensibilidade aumentada&lt;/strong&gt; aos não despolarizantes.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Farmacocinética:&lt;/strong&gt; o neonato tem &lt;strong&gt;água extracelular proporcionalmente maior&lt;/strong&gt;, e como os relaxantes são fármacos hidrossolúveis e pouco lipossolúveis, o &lt;em&gt;volume de distribuição é maior&lt;/em&gt;. Isso dilui a dose e neutraliza em boa parte a maior sensibilidade — daí a dose por quilograma acabar semelhante.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Eliminação:&lt;/strong&gt; a imaturidade hepática e renal reduz a depuração e prolonga a meia-vida de eliminação, o que se traduz em &lt;strong&gt;duração de ação e recuperação mais lentas&lt;/strong&gt;.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Por isso a monitorização quantitativa e a cautela com doses de manutenção são regra nessa faixa etária. Com a succinilcolina o raciocínio é análogo, mas o efeito dominante é o volume de distribuição, motivo pelo qual o neonato requer dose &lt;em&gt;maior&lt;/em&gt; por quilograma, da ordem de 2 a 3 mg/kg.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o neonato é sensível, e não resistente, aos não despolarizantes; a duração prolongada é achado esperado, não evidência de erro de dose. (B) o volume de distribuição do neonato é maior, e não menor, que o do adulto. (D) a recuperação é mais lenta nessa idade, e a colinesterase plasmática não participa do metabolismo do vecurônio.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O comportamento dos bloqueadores neuromusculares no neonato resulta de fatores que se opõem e explicam por que a dose por quilograma é semelhante à do adulto, mas a duração é maior.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Farmacodinâmica:&lt;/strong&gt; a junção neuromuscular é &lt;em&gt;imatura&lt;/em&gt; até cerca de dois meses de idade, com menor reserva de acetilcolina e receptores ainda de subtipo fetal. Isso confere &lt;strong&gt;sensibilidade aumentada&lt;/strong&gt; aos não despolarizantes.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Farmacocinética:&lt;/strong&gt; o neonato tem &lt;strong&gt;água extracelular proporcionalmente maior&lt;/strong&gt;, e como os relaxantes são fármacos hidrossolúveis e pouco lipossolúveis, o &lt;em&gt;volume de distribuição é maior&lt;/em&gt;. Isso dilui a dose e neutraliza em boa parte a maior sensibilidade; daí a dose por quilograma acabar semelhante.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Eliminação:&lt;/strong&gt; a imaturidade hepática e renal reduz a depuração e prolonga a meia-vida de eliminação, o que se traduz em &lt;strong&gt;duração de ação e recuperação mais lentas&lt;/strong&gt;.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Por isso a monitorização quantitativa e a cautela com doses de manutenção são regra nessa faixa etária. Com a succinilcolina o raciocínio é análogo, mas o efeito dominante é o volume de distribuição, motivo pelo qual o neonato requer dose &lt;em&gt;maior&lt;/em&gt; por quilograma, da ordem de 2 a 3 mg/kg.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o neonato é sensível, e não resistente, aos não despolarizantes; a duração prolongada é achado esperado, não evidência de erro de dose. (B) o volume de distribuição do neonato é maior, e não menor, que o do adulto. (D) a recuperação é mais lenta nessa idade, e a colinesterase plasmática não participa do metabolismo do vecurônio.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O magnésio é o fármaco de escolha na profilaxia e no tratamento da eclâmpsia. Age como &lt;strong&gt;antagonista do cálcio&lt;/strong&gt;, reduzindo a liberação pré-sináptica de acetilcolina na junção neuromuscular e a excitabilidade do sistema nervoso central. A faixa terapêutica situa-se aproximadamente entre &lt;strong&gt;4,8 e 8,4 mg/dL&lt;/strong&gt; (2 a 3,5 mmol/L), e a toxicidade segue uma progressão razoavelmente previsível: perda do reflexo patelar em torno de 10 mg/dL, depressão respiratória acima de 12 a 15 mg/dL e parada cardíaca em valores muito elevados.&lt;/p&gt;&lt;p&gt;A paciente descrita já perdeu o reflexo patelar e hipoventila, com magnesemia de 11 mg/dL e oligúria — o magnésio tem eliminação exclusivamente renal, e a queda do débito urinário é o principal fator de acúmulo. A conduta é &lt;strong&gt;interromper a infusão&lt;/strong&gt;, garantir oxigenação e antagonizar o efeito com &lt;strong&gt;gluconato de cálcio 1 g&lt;/strong&gt; (10 mL a 10%) por via venosa lenta, mantendo prontidão para ventilação assistida. Lembrar ainda que o magnésio potencializa de forma marcante os bloqueadores adespolarizantes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) 11 mg/dL está acima da faixa terapêutica e já há sinais clínicos de toxicidade, o que exige suspensão, não apenas redução. (C) a furosemida não é o tratamento da intoxicação e pode agravar a hipovolemia relativa da pré-eclâmpsia. (D) o bloqueio pelo magnésio é pré-sináptico e não responde a anticolinesterásicos; manter a infusão perpetuaria a intoxicação.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O magnésio é o fármaco de escolha na profilaxia e no tratamento da eclâmpsia. Age como &lt;strong&gt;antagonista do cálcio&lt;/strong&gt;, reduzindo a liberação pré-sináptica de acetilcolina na junção neuromuscular e a excitabilidade do sistema nervoso central. A faixa terapêutica situa-se aproximadamente entre &lt;strong&gt;4,8 e 8,4 mg/dL&lt;/strong&gt; (2 a 3,5 mmol/L), e a toxicidade segue uma progressão razoavelmente previsível: perda do reflexo patelar em torno de 10 mg/dL, depressão respiratória acima de 12 a 15 mg/dL e parada cardíaca em valores muito elevados.&lt;/p&gt;&lt;p&gt;A paciente descrita já perdeu o reflexo patelar e hipoventila, com magnesemia de 11 mg/dL e oligúria; o magnésio tem eliminação exclusivamente renal, e a queda do débito urinário é o principal fator de acúmulo. A conduta é &lt;strong&gt;interromper a infusão&lt;/strong&gt;, garantir oxigenação e antagonizar o efeito com &lt;strong&gt;gluconato de cálcio 1 g&lt;/strong&gt; (10 mL a 10%) por via venosa lenta, mantendo prontidão para ventilação assistida. Lembrar ainda que o magnésio potencializa de forma marcante os bloqueadores adespolarizantes.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) 11 mg/dL está acima da faixa terapêutica e já há sinais clínicos de toxicidade, o que exige suspensão, não apenas redução. (C) a furosemida não é o tratamento da intoxicação e pode agravar a hipovolemia relativa da pré-eclâmpsia. (D) o bloqueio pelo magnésio é pré-sináptico e não responde a anticolinesterásicos; manter a infusão perpetuaria a intoxicação.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A gestante desenvolve &lt;strong&gt;hipervolemia com anemia dilucional&lt;/strong&gt;: o volume plasmático aumenta cerca de 40% a 50%, enquanto a massa eritrocitária sobe apenas 20% a 30%, resultando em hemoglobina em torno de 11 a 12 g/dL. Em paralelo, instala-se um estado pró-trombótico fisiológico, com elevação dos fatores VII, VIII, X, XII e do fator de von Willebrand, queda da proteína S e redução da fibrinólise. O &lt;strong&gt;fibrinogênio sobe de 200-400 para 400-650 mg/dL&lt;/strong&gt;, de modo que um valor de 520 mg/dL é esperado — e, aliás, um fibrinogênio de 300 mg/dL em uma gestante sangrando já deve ser lido como consumo.&lt;/p&gt;&lt;p&gt;Outras adaptações úteis: leucocitose de 10.000 a 14.000/mm3 sem infecção, queda da albumina e da pressão coloidosmótica, redução de cerca de 25% a 30% da colinesterase plasmática (raramente com repercussão clínica no uso do suxametônio) e elevação da fosfatase alcalina de origem placentária.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a trombocitopenia gestacional é discreta, raramente abaixo de 100.000/mm3; 78.000/mm3 exige investigar pré-eclâmpsia, HELLP ou púrpura antes do bloqueio. (B) a filtração glomerular aumenta cerca de 50%, de modo que ureia e creatinina &lt;em&gt;caem&lt;/em&gt;; 1,2 mg/dL sinaliza disfunção renal. (D) os tempos de coagulação permanecem normais ou discretamente encurtados; alargamento do TTPa é patológico.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A gestante desenvolve &lt;strong&gt;hipervolemia com anemia dilucional&lt;/strong&gt;: o volume plasmático aumenta cerca de 40% a 50%, enquanto a massa eritrocitária sobe apenas 20% a 30%, resultando em hemoglobina em torno de 11 a 12 g/dL. Em paralelo, instala-se um estado pró-trombótico fisiológico, com elevação dos fatores VII, VIII, X, XII e do fator de von Willebrand, queda da proteína S e redução da fibrinólise. O &lt;strong&gt;fibrinogênio sobe de 200-400 para 400-650 mg/dL&lt;/strong&gt;, de modo que um valor de 520 mg/dL é esperado; aliás, um fibrinogênio de 300 mg/dL em uma gestante sangrando já deve ser lido como consumo.&lt;/p&gt;&lt;p&gt;Outras adaptações úteis: leucocitose de 10.000 a 14.000/mm3 sem infecção, queda da albumina e da pressão coloidosmótica, redução de cerca de 25% a 30% da colinesterase plasmática (raramente com repercussão clínica no uso do suxametônio) e elevação da fosfatase alcalina de origem placentária.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a trombocitopenia gestacional é discreta, raramente abaixo de 100.000/mm3; 78.000/mm3 exige investigar pré-eclâmpsia, HELLP ou púrpura antes do bloqueio. (B) a filtração glomerular aumenta cerca de 50%, de modo que ureia e creatinina &lt;em&gt;caem&lt;/em&gt;; 1,2 mg/dL sinaliza disfunção renal. (D) os tempos de coagulação permanecem normais ou discretamente encurtados; alargamento do TTPa é patológico.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A amostra de sangue do couro cabeludo fetal foi historicamente utilizada como teste confirmatório diante de cardiotocografia não tranquilizadora, que tem alta sensibilidade mas baixa especificidade para acidose. A interpretação clássica é: &lt;strong&gt;pH ≥ 7,25 normal&lt;/strong&gt;, &lt;strong&gt;7,20 a 7,25 limítrofe&lt;/strong&gt; (repetir em 20 a 30 minutos) e &lt;strong&gt;pH &amp;lt; 7,20 acidose significativa&lt;/strong&gt;, indicando resolução imediata da gestação pela via mais rápida.&lt;/p&gt;&lt;p&gt;O valor de 7,18, somado a desacelerações tardias — marcador de insuficiência uteroplacentária — e à perda de variabilidade, configura padrão de comprometimento fetal que não admite espera. Para o anestesiologista, a implicação prática é o preparo para &lt;strong&gt;cesariana de urgência&lt;/strong&gt;: se já há cateter peridural funcionante, a extensão rápida do bloqueio com anestésico local em concentração alta costuma ser a via mais segura; caso contrário, raquianestesia ou anestesia geral, conforme o tempo disponível e as condições maternas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a faixa limítrofe é 7,20 a 7,25; abaixo de 7,20 a conduta é intervir, não repetir. (C) 7,18 não é valor normal, e desacelerações &lt;em&gt;tardias&lt;/em&gt; refletem insuficiência uteroplacentária, ao passo que as &lt;em&gt;variáveis&lt;/em&gt; é que sugerem compressão de cordão. (D) o bicarbonato materno não corrige acidose fetal por hipóxia e apenas retarda a intervenção definitiva, que é a extração fetal.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A amostra de sangue do couro cabeludo fetal foi historicamente utilizada como teste confirmatório diante de cardiotocografia não tranquilizadora, que tem alta sensibilidade mas baixa especificidade para acidose. A interpretação clássica é: &lt;strong&gt;pH ≥ 7,25 normal&lt;/strong&gt;, &lt;strong&gt;7,20 a 7,25 limítrofe&lt;/strong&gt; (repetir em 20 a 30 minutos) e &lt;strong&gt;pH &amp;lt; 7,20 acidose significativa&lt;/strong&gt;, indicando resolução imediata da gestação pela via mais rápida.&lt;/p&gt;&lt;p&gt;O valor de 7,18, somado a desacelerações tardias (marcador de insuficiência uteroplacentária) e à perda de variabilidade, configura padrão de comprometimento fetal que não admite espera. Para o anestesiologista, a implicação prática é o preparo para &lt;strong&gt;cesariana de urgência&lt;/strong&gt;: se já há cateter peridural funcionante, a extensão rápida do bloqueio com anestésico local em concentração alta costuma ser a via mais segura; caso contrário, raquianestesia ou anestesia geral, conforme o tempo disponível e as condições maternas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a faixa limítrofe é 7,20 a 7,25; abaixo de 7,20 a conduta é intervir, não repetir. (C) 7,18 não é valor normal, e desacelerações &lt;em&gt;tardias&lt;/em&gt; refletem insuficiência uteroplacentária, ao passo que as &lt;em&gt;variáveis&lt;/em&gt; é que sugerem compressão de cordão. (D) o bicarbonato materno não corrige acidose fetal por hipóxia e apenas retarda a intervenção definitiva, que é a extração fetal.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Cerca de 1% a 2% das gestantes é submetido a cirurgia não obstétrica, sendo apendicite e colecistite as causas mais comuns. Duas regras organizam a conduta: &lt;strong&gt;cirurgia de urgência não se adia por causa da gestação&lt;/strong&gt; — a peritonite materna é muito mais deletéria ao feto do que a anestesia — e cirurgia eletiva se posterga para o puerpério. Quando há escolha, o &lt;strong&gt;segundo trimestre&lt;/strong&gt; é o período preferencial, por evitar a organogênese e a maior irritabilidade uterina do terceiro trimestre.&lt;/p&gt;&lt;p&gt;O bem-estar fetal depende essencialmente da manutenção da homeostase materna. Deve-se evitar hipotensão, hipoxemia, hipovolemia, hipertermia e, muito especialmente, a &lt;strong&gt;hipocapnia&lt;/strong&gt;, que reduz o fluxo sanguíneo uterino por vasoconstrição e desvia a curva de dissociação materna para a esquerda. Deslocamento uterino à esquerda a partir de aproximadamente 18 a 20 semanas, profilaxia de aspiração e monitorização da frequência cardíaca fetal antes e depois do ato completam o cuidado; a monitorização contínua intraoperatória só é considerada após a viabilidade e quando puder alterar a conduta.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) postergar apendicite aguda expõe a perfuração, sepse e perda fetal. (C) nenhum anestésico geral, nas doses clínicas, tem teratogenicidade demonstrada em humanos; a técnica se escolhe pelo procedimento. (D) a hipocapnia materna &lt;em&gt;reduz&lt;/em&gt; a perfusão uteroplacentária e piora a oxigenação fetal.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Cerca de 1% a 2% das gestantes é submetido a cirurgia não obstétrica, sendo apendicite e colecistite as causas mais comuns. Duas regras organizam a conduta: &lt;strong&gt;cirurgia de urgência não se adia por causa da gestação&lt;/strong&gt; (a peritonite materna é muito mais deletéria ao feto do que a anestesia) e cirurgia eletiva se posterga para o puerpério. Quando há escolha, o &lt;strong&gt;segundo trimestre&lt;/strong&gt; é o período preferencial, por evitar a organogênese e a maior irritabilidade uterina do terceiro trimestre.&lt;/p&gt;&lt;p&gt;O bem-estar fetal depende essencialmente da manutenção da homeostase materna. Deve-se evitar hipotensão, hipoxemia, hipovolemia, hipertermia e, muito especialmente, a &lt;strong&gt;hipocapnia&lt;/strong&gt;, que reduz o fluxo sanguíneo uterino por vasoconstrição e desvia a curva de dissociação materna para a esquerda. Deslocamento uterino à esquerda a partir de aproximadamente 18 a 20 semanas, profilaxia de aspiração e monitorização da frequência cardíaca fetal antes e depois do ato completam o cuidado; a monitorização contínua intraoperatória só é considerada após a viabilidade e quando puder alterar a conduta.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) postergar apendicite aguda expõe a perfuração, sepse e perda fetal. (C) nenhum anestésico geral, nas doses clínicas, tem teratogenicidade demonstrada em humanos; a técnica se escolhe pelo procedimento. (D) a hipocapnia materna &lt;em&gt;reduz&lt;/em&gt; a perfusão uteroplacentária e piora a oxigenação fetal.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O quadro é de &lt;strong&gt;disreflexia autonômica&lt;/strong&gt;, complicação de lesões medulares acima de T6. Um estímulo aferente abaixo da lesão — distensão uterina, contrações, bexiga cheia, toque retal — desencadeia descarga simpática reflexa que não sofre a modulação inibitória supraespinal, porque esta é interrompida pela lesão. O resultado é vasoconstrição intensa abaixo do nível da lesão (palidez, piloereção) com &lt;strong&gt;hipertensão paroxística&lt;/strong&gt;, enquanto acima dele predomina a vasodilatação mediada pelos barorreceptores (rubor, sudorese, congestão nasal) e surge &lt;strong&gt;bradicardia reflexa&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O tratamento definitivo é &lt;strong&gt;abolir a via aferente&lt;/strong&gt;: a analgesia peridural (ou raquidiana) instalada precocemente no trabalho de parto é a medida mais eficaz de prevenção e de tratamento, devendo ser mantida durante o parto e o período de dequitação. Enquanto o bloqueio se estabelece, controla-se a pressão com anti-hipertensivo de curta ação e titulável. A distinção com pré-eclâmpsia é clínica: aqui a hipertensão é paroxística, ligada às contrações, acompanha bradicardia e não há proteinúria.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) não há critérios de pré-eclâmpsia; o magnésio não trata a causa da descarga simpática. (B) a anestesia neuraxial não só é permitida como é o tratamento de escolha; a bradicardia é reflexa e se resolve com o controle da hipertensão. (D) a paciente está hipertensa, e a efedrina agravaria o quadro.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O quadro é de &lt;strong&gt;disreflexia autonômica&lt;/strong&gt;, complicação de lesões medulares acima de T6. Um estímulo aferente abaixo da lesão (distensão uterina, contrações, bexiga cheia, toque retal) desencadeia descarga simpática reflexa que não sofre a modulação inibitória supraespinal, porque esta é interrompida pela lesão. O resultado é vasoconstrição intensa abaixo do nível da lesão (palidez, piloereção) com &lt;strong&gt;hipertensão paroxística&lt;/strong&gt;, enquanto acima dele predomina a vasodilatação mediada pelos barorreceptores (rubor, sudorese, congestão nasal) e surge &lt;strong&gt;bradicardia reflexa&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O tratamento definitivo é &lt;strong&gt;abolir a via aferente&lt;/strong&gt;: a analgesia peridural (ou raquidiana) instalada precocemente no trabalho de parto é a medida mais eficaz de prevenção e de tratamento, devendo ser mantida durante o parto e o período de dequitação. Enquanto o bloqueio se estabelece, controla-se a pressão com anti-hipertensivo de curta ação e titulável. A distinção com pré-eclâmpsia é clínica: aqui a hipertensão é paroxística, ligada às contrações, acompanha bradicardia e não há proteinúria.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) não há critérios de pré-eclâmpsia; o magnésio não trata a causa da descarga simpática. (B) a anestesia neuraxial não só é permitida como é o tratamento de escolha; a bradicardia é reflexa e se resolve com o controle da hipertensão. (D) a paciente está hipertensa, e a efedrina agravaria o quadro.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O EXIT é indicado quando se antecipa via aérea fetal impraticável ao nascimento — massas cervicais volumosas, síndrome de obstrução congênita das vias aéreas superiores, hérnia diafragmática com oclusão traqueal. Sua premissa é manter a &lt;strong&gt;placenta como oxigenador&lt;/strong&gt; por dezenas de minutos, o que exige &lt;strong&gt;útero profundamente relaxado&lt;/strong&gt;: a contração uterina reduz o volume da cavidade, descola a placenta e interrompe a troca gasosa.&lt;/p&gt;&lt;p&gt;Na prática, emprega-se anestesia geral com halogenado em 2 a 3 CAM, eventualmente complementado por nitroglicerina venosa, mantendo-se o líquido amniótico ou infusão de solução aquecida para preservar o volume uterino. A hipotensão materna induzida por essa profundidade anestésica é combatida com vasopressor e volume, pois a perfusão placentária depende diretamente da pressão de perfusão uterina. O feto recebe analgesia e bloqueio neuromuscular por via intramuscular, e a monitorização inclui oximetria e ecocardiografia fetal. Ao final, o halogenado é reduzido e inicia-se uterotônico, já que o &lt;strong&gt;risco de atonia e hemorragia materna é elevado&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) uterotônico durante a fase de manutenção provoca descolamento placentário e perda do suporte fetal. (B) o bloqueio do neuroeixo isolado não produz relaxamento uterino, requisito central do procedimento. (C) o clampeamento precoce elimina justamente a oxigenação placentária que o EXIT existe para preservar.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O EXIT é indicado quando se antecipa via aérea fetal impraticável ao nascimento: massas cervicais volumosas, síndrome de obstrução congênita das vias aéreas superiores, hérnia diafragmática com oclusão traqueal. Sua premissa é manter a &lt;strong&gt;placenta como oxigenador&lt;/strong&gt; por dezenas de minutos, o que exige &lt;strong&gt;útero profundamente relaxado&lt;/strong&gt;: a contração uterina reduz o volume da cavidade, descola a placenta e interrompe a troca gasosa.&lt;/p&gt;&lt;p&gt;Na prática, emprega-se anestesia geral com halogenado em 2 a 3 CAM, eventualmente complementado por nitroglicerina venosa, mantendo-se o líquido amniótico ou infusão de solução aquecida para preservar o volume uterino. A hipotensão materna induzida por essa profundidade anestésica é combatida com vasopressor e volume, pois a perfusão placentária depende diretamente da pressão de perfusão uterina. O feto recebe analgesia e bloqueio neuromuscular por via intramuscular, e a monitorização inclui oximetria e ecocardiografia fetal. Ao final, o halogenado é reduzido e inicia-se uterotônico, já que o &lt;strong&gt;risco de atonia e hemorragia materna é elevado&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) uterotônico durante a fase de manutenção provoca descolamento placentário e perda do suporte fetal. (B) o bloqueio do neuroeixo isolado não produz relaxamento uterino, requisito central do procedimento. (C) o clampeamento precoce elimina justamente a oxigenação placentária que o EXIT existe para preservar.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Teratogenicidade depende de &lt;strong&gt;agente, dose e momento da exposição&lt;/strong&gt;. A organogênese ocorre entre a terceira e a oitava semanas pós-concepção; antes disso vale a regra do tudo ou nada, e depois predominam efeitos sobre crescimento e maturação funcional, não sobre a formação de estruturas.&lt;/p&gt;&lt;p&gt;A varfarina é teratógeno humano bem estabelecido. Exposição entre a &lt;strong&gt;sexta e a décima segunda semanas&lt;/strong&gt; produz a embriopatia varfarínica — hipoplasia nasal e condrodisplasia punctata, por interferência na carboxilação de proteínas dependentes de vitamina K na cartilagem; exposições mais tardias associam-se a hemorragia fetal e anomalias do sistema nervoso central. Por isso substitui-se por heparina de baixo peso molecular, que não atravessa a placenta.&lt;/p&gt;&lt;p&gt;Quanto aos anestésicos, &lt;strong&gt;nenhum agente em uso clínico tem teratogenicidade comprovada em humanos&lt;/strong&gt; nas doses habituais. A cautela histórica com o óxido nitroso decorre da inibição da metionina sintetase e de dados em roedores com exposições prolongadas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o suxametônio é altamente ionizado e pouco lipossolúvel, praticamente não atravessando a placenta em doses clínicas. (B) os inibidores da ECA causam lesão sobretudo no segundo e terceiro trimestres, com displasia tubular renal, oligoâmnio e hipoplasia pulmonar. (C) o propofol não é teratógeno reconhecido; o etomidato, ao contrário, traria supressão adrenal sem qualquer vantagem.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Teratogenicidade depende de &lt;strong&gt;agente, dose e momento da exposição&lt;/strong&gt;. A organogênese ocorre entre a terceira e a oitava semanas pós-concepção; antes disso vale a regra do tudo ou nada, e depois predominam efeitos sobre crescimento e maturação funcional, não sobre a formação de estruturas.&lt;/p&gt;&lt;p&gt;A varfarina é teratógeno humano bem estabelecido. Exposição entre a &lt;strong&gt;sexta e a décima segunda semanas&lt;/strong&gt; produz a embriopatia varfarínica: hipoplasia nasal e condrodisplasia punctata, por interferência na carboxilação de proteínas dependentes de vitamina K na cartilagem; exposições mais tardias associam-se a hemorragia fetal e anomalias do sistema nervoso central. Por isso substitui-se por heparina de baixo peso molecular, que não atravessa a placenta.&lt;/p&gt;&lt;p&gt;Quanto aos anestésicos, &lt;strong&gt;nenhum agente em uso clínico tem teratogenicidade comprovada em humanos&lt;/strong&gt; nas doses habituais. A cautela histórica com o óxido nitroso decorre da inibição da metionina sintetase e de dados em roedores com exposições prolongadas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o suxametônio é altamente ionizado e pouco lipossolúvel, praticamente não atravessando a placenta em doses clínicas. (B) os inibidores da ECA causam lesão sobretudo no segundo e terceiro trimestres, com displasia tubular renal, oligoâmnio e hipoplasia pulmonar. (C) o propofol não é teratógeno reconhecido; o etomidato, ao contrário, traria supressão adrenal sem qualquer vantagem.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A pré-eclâmpsia é uma doença de disfunção endotelial sistêmica, mas a mortalidade materna concentra-se no &lt;strong&gt;sistema nervoso central&lt;/strong&gt;: a &lt;strong&gt;hemorragia intracraniana&lt;/strong&gt; é a causa mais frequente de óbito, seguida por edema agudo de pulmão e complicações hepáticas. A hipertensão grave rompe o limite superior da autorregulação cerebral, produzindo hiperperfusão, edema vasogênico e ruptura de pequenos vasos.&lt;/p&gt;&lt;p&gt;A consequência prática é direta: o determinante mais forte do acidente vascular encefálico nessas pacientes é a &lt;strong&gt;pressão sistólica&lt;/strong&gt;, e não a diastólica. Por isso a recomendação de tratar sem demora valores sistólicos sustentados &lt;strong&gt;acima de 160 mmHg&lt;/strong&gt; (ou diastólicos acima de 110 mmHg), com hidralazina, labetalol ou nifedipino, mirando redução gradual para a faixa de 140-150 por 90-100 mmHg — quedas abruptas comprometem a perfusão uteroplacentária. O sulfato de magnésio previne convulsão, mas &lt;strong&gt;não substitui o anti-hipertensivo&lt;/strong&gt;: são objetivos distintos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a lesão renal na pré-eclâmpsia costuma ser reversível e raramente é causa direta de óbito; perseguir diurese com sobrecarga hídrica favorece edema pulmonar. (C) o hematoma hepático é complicação grave da síndrome HELLP, porém rara, e não justifica tomografia de rotina. (D) o edema agudo de pulmão é causa importante de morbidade e óbito, mas não a principal; restrição hídrica absoluta e diurético profilático não são conduta padrão.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A pré-eclâmpsia é uma doença de disfunção endotelial sistêmica, mas a mortalidade materna concentra-se no &lt;strong&gt;sistema nervoso central&lt;/strong&gt;: a &lt;strong&gt;hemorragia intracraniana&lt;/strong&gt; é a causa mais frequente de óbito, seguida por edema agudo de pulmão e complicações hepáticas. A hipertensão grave rompe o limite superior da autorregulação cerebral, produzindo hiperperfusão, edema vasogênico e ruptura de pequenos vasos.&lt;/p&gt;&lt;p&gt;A consequência prática é direta: o determinante mais forte do acidente vascular encefálico nessas pacientes é a &lt;strong&gt;pressão sistólica&lt;/strong&gt;, e não a diastólica. Por isso a recomendação de tratar sem demora valores sistólicos sustentados &lt;strong&gt;acima de 160 mmHg&lt;/strong&gt; (ou diastólicos acima de 110 mmHg), com hidralazina, labetalol ou nifedipino, mirando redução gradual para a faixa de 140-150 por 90-100 mmHg, pois quedas abruptas comprometem a perfusão uteroplacentária. O sulfato de magnésio previne convulsão, mas &lt;strong&gt;não substitui o anti-hipertensivo&lt;/strong&gt;: são objetivos distintos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a lesão renal na pré-eclâmpsia costuma ser reversível e raramente é causa direta de óbito; perseguir diurese com sobrecarga hídrica favorece edema pulmonar. (C) o hematoma hepático é complicação grave da síndrome HELLP, porém rara, e não justifica tomografia de rotina. (D) o edema agudo de pulmão é causa importante de morbidade e óbito, mas não a principal; restrição hídrica absoluta e diurético profilático não são conduta padrão.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A distinção entre os dois defeitos de parede abdominal é anatômica e tem consequências práticas imediatas.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Onfalocele&lt;/strong&gt;: defeito &lt;em&gt;central&lt;/em&gt;, no anel umbilical, com as vísceras recobertas por saco de peritônio e âmnio, no qual se insere o cordão. Justamente por ser um erro precoce do fechamento embrionário, associa-se a outras anomalias em cerca de metade a três quartos dos casos — cardiopatias congênitas, trissomias, síndrome de Beckwith-Wiedemann (macroglossia, hipoglicemia, visceromegalia) e pentalogia de Cantrell.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gastrosquise&lt;/strong&gt;: defeito &lt;em&gt;paraumbilical&lt;/em&gt;, quase sempre à direita, sem saco, com alças livres no líquido amniótico. Anomalias associadas são incomuns, exceto atresia intestinal, mas a exposição visceral direta gera &lt;strong&gt;perdas evaporativas e de calor muito maiores&lt;/strong&gt;, hipovolemia, distúrbio eletrolítico e risco infeccioso.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Daí o manejo: proteção das alças, aquecimento agressivo, descompressão gástrica, reposição volêmica frequentemente de duas a três vezes a manutenção e atenção à pressão intra-abdominal no fechamento — a queda da complacência pulmonar, a compressão da veia cava e a oligúria sinalizam a necessidade de fechamento estagiado com silo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte as definições; a ausência de saco caracteriza a gastrosquise. (B) o óxido nitroso difunde para cavidades aéreas e &lt;em&gt;distende&lt;/em&gt; as alças, devendo ser evitado. (D) as associações sindrômicas e cardíacas são típicas da onfalocele.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A distinção entre os dois defeitos de parede abdominal é anatômica e tem consequências práticas imediatas.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Onfalocele&lt;/strong&gt;: defeito &lt;em&gt;central&lt;/em&gt;, no anel umbilical, com as vísceras recobertas por saco de peritônio e âmnio, no qual se insere o cordão. Justamente por ser um erro precoce do fechamento embrionário, associa-se a outras anomalias em cerca de metade a três quartos dos casos: cardiopatias congênitas, trissomias, síndrome de Beckwith-Wiedemann (macroglossia, hipoglicemia, visceromegalia) e pentalogia de Cantrell.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gastrosquise&lt;/strong&gt;: defeito &lt;em&gt;paraumbilical&lt;/em&gt;, quase sempre à direita, sem saco, com alças livres no líquido amniótico. Anomalias associadas são incomuns, exceto atresia intestinal, mas a exposição visceral direta gera &lt;strong&gt;perdas evaporativas e de calor muito maiores&lt;/strong&gt;, hipovolemia, distúrbio eletrolítico e risco infeccioso.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Daí o manejo: proteção das alças, aquecimento agressivo, descompressão gástrica, reposição volêmica frequentemente de duas a três vezes a manutenção e atenção à pressão intra-abdominal no fechamento; a queda da complacência pulmonar, a compressão da veia cava e a oligúria sinalizam a necessidade de fechamento estagiado com silo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte as definições; a ausência de saco caracteriza a gastrosquise. (B) o óxido nitroso difunde para cavidades aéreas e &lt;em&gt;distende&lt;/em&gt; as alças, devendo ser evitado. (D) as associações sindrômicas e cardíacas são típicas da onfalocele.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>&lt;p&gt;No enfisema lobar congênito há um mecanismo valvular: o ar entra no lobo doente na inspiração e não sai completamente na expiração. O lobo hiperinsufla progressivamente, comprime o parênquima sadio adjacente, desvia o mediastino e pode reduzir o retorno venoso.&lt;/p&gt;&lt;p&gt;A implicação anestésica é a regra central da lesão: &lt;strong&gt;a ventilação com pressão positiva pode agravar de forma catastrófica a hiperinsuflação&lt;/strong&gt;, levando a colapso cardiorrespiratório na indução. Por isso a conduta clássica é manter a &lt;strong&gt;ventilação espontânea&lt;/strong&gt; — indução inalatória cuidadosa, evitando apneia — até que o cirurgião abra o tórax e descomprima o lobo. Se for indispensável assistir a ventilação, usam-se pressões baixas, volumes pequenos e frequências mais altas. O &lt;strong&gt;óxido nitroso é proscrito&lt;/strong&gt;, pois difunde para o espaço aéreo aprisionado e expande o lobo. Deterioração súbita durante a indução exige toracotomia imediata.&lt;/p&gt;&lt;p&gt;O raciocínio vale, com nuances, para outras pneumopatias neonatais: na doença da membrana hialina o problema é o oposto — complacência baixa por deficiência de surfactante, exigindo recrutamento e PEEP; na aspiração meconial predominam aprisionamento aéreo, risco de pneumotórax e hipertensão pulmonar persistente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) PEEP elevada agrava o aprisionamento aéreo no lobo doente. (B) o óxido nitroso expande cavidades aéreas fechadas e é formalmente desaconselhado. (C) pressões inspiratórias elevadas são exatamente o que precipita a hiperinsuflação e o colapso hemodinâmico.&lt;/p&gt;</t>
+          <t>&lt;p&gt;No enfisema lobar congênito há um mecanismo valvular: o ar entra no lobo doente na inspiração e não sai completamente na expiração. O lobo hiperinsufla progressivamente, comprime o parênquima sadio adjacente, desvia o mediastino e pode reduzir o retorno venoso.&lt;/p&gt;&lt;p&gt;A implicação anestésica é a regra central da lesão: &lt;strong&gt;a ventilação com pressão positiva pode agravar de forma catastrófica a hiperinsuflação&lt;/strong&gt;, levando a colapso cardiorrespiratório na indução. Por isso a conduta clássica é manter a &lt;strong&gt;ventilação espontânea&lt;/strong&gt; (indução inalatória cuidadosa, evitando apneia) até que o cirurgião abra o tórax e descomprima o lobo. Se for indispensável assistir a ventilação, usam-se pressões baixas, volumes pequenos e frequências mais altas. O &lt;strong&gt;óxido nitroso é proscrito&lt;/strong&gt;, pois difunde para o espaço aéreo aprisionado e expande o lobo. Deterioração súbita durante a indução exige toracotomia imediata.&lt;/p&gt;&lt;p&gt;O raciocínio vale, com nuances, para outras pneumopatias neonatais: na doença da membrana hialina o problema é o oposto, complacência baixa por deficiência de surfactante, exigindo recrutamento e PEEP; na aspiração meconial predominam aprisionamento aéreo, risco de pneumotórax e hipertensão pulmonar persistente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) PEEP elevada agrava o aprisionamento aéreo no lobo doente. (B) o óxido nitroso expande cavidades aéreas fechadas e é formalmente desaconselhado. (C) pressões inspiratórias elevadas são exatamente o que precipita a hiperinsuflação e o colapso hemodinâmico.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A margem de segurança na apneia depende de uma razão simples: &lt;strong&gt;reserva de oxigênio dividida pela taxa de consumo&lt;/strong&gt;. A reserva é essencialmente o oxigênio contido na capacidade residual funcional (CRF); o consumo é o metabólico.&lt;/p&gt;&lt;p&gt;No lactente, o denominador é desproporcionalmente grande: o consumo de oxigênio é de &lt;strong&gt;6 a 9 mL/kg/min&lt;/strong&gt;, contra 3 a 4 mL/kg/min no adulto. O numerador, por sua vez, não acompanha: a CRF por quilo é semelhante à do adulto (cerca de 25 a 30 mL/kg), mas a &lt;strong&gt;relação ventilação alveolar/CRF é de aproximadamente 5:1&lt;/strong&gt;, contra 1,5:1 no adulto — ou seja, o conteúdo dos alvéolos é renovado muito mais rapidamente e a CRF funciona mal como reservatório. Soma-se a isso o fato de a capacidade de fechamento situar-se acima da CRF até os 6 a 8 anos, favorecendo colapso alveolar sob anestesia, e a alta complacência da caixa torácica, que reduz ainda mais a CRF dinâmica quando cessa a atividade dos músculos respiratórios.&lt;/p&gt;&lt;p&gt;Na prática: a pré-oxigenação é eficaz, mas compra poucos segundos; o tempo disponível para a laringoscopia é curto e a estratégia deve prever ventilação de resgate precoce.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a CRF por quilo não é maior que a do adulto, e o mecanismo proposto de redistribuição muscular não existe. (C) a hemoglobina fetal tem &lt;em&gt;maior&lt;/em&gt; afinidade pelo oxigênio, com curva desviada à esquerda, e aos 4 meses já foi em grande parte substituída. (D) não há shunt fixo de 20% no lactente hígido.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A margem de segurança na apneia depende de uma razão simples: &lt;strong&gt;reserva de oxigênio dividida pela taxa de consumo&lt;/strong&gt;. A reserva é essencialmente o oxigênio contido na capacidade residual funcional (CRF); o consumo é o metabólico.&lt;/p&gt;&lt;p&gt;No lactente, o denominador é desproporcionalmente grande: o consumo de oxigênio é de &lt;strong&gt;6 a 9 mL/kg/min&lt;/strong&gt;, contra 3 a 4 mL/kg/min no adulto. O numerador, por sua vez, não acompanha: a CRF por quilo é semelhante à do adulto (cerca de 25 a 30 mL/kg), mas a &lt;strong&gt;relação ventilação alveolar/CRF é de aproximadamente 5:1&lt;/strong&gt;, contra 1,5:1 no adulto; ou seja, o conteúdo dos alvéolos é renovado muito mais rapidamente e a CRF funciona mal como reservatório. Soma-se a isso o fato de a capacidade de fechamento situar-se acima da CRF até os 6 a 8 anos, favorecendo colapso alveolar sob anestesia, e a alta complacência da caixa torácica, que reduz ainda mais a CRF dinâmica quando cessa a atividade dos músculos respiratórios.&lt;/p&gt;&lt;p&gt;Na prática: a pré-oxigenação é eficaz, mas compra poucos segundos; o tempo disponível para a laringoscopia é curto e a estratégia deve prever ventilação de resgate precoce.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a CRF por quilo não é maior que a do adulto, e o mecanismo proposto de redistribuição muscular não existe. (C) a hemoglobina fetal tem &lt;em&gt;maior&lt;/em&gt; afinidade pelo oxigênio, com curva desviada à esquerda, e aos 4 meses já foi em grande parte substituída. (D) não há shunt fixo de 20% no lactente hígido.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O uso crônico de fenitoína e carbamazepina induz o sistema microssomal hepático e aumenta a depuração de diversos fármacos. Somado a isso, ocorre &lt;strong&gt;proliferação de receptores nicotínicos extrajuncionais&lt;/strong&gt; e ligação do bloqueador a proteínas plasmáticas em maior proporção. O resultado clínico é característico: &lt;strong&gt;resistência aos bloqueadores adespolarizantes&lt;/strong&gt;, com início mais lento, menor efeito e duração encurtada, exigindo doses maiores e reinjeções frequentes — o mesmo se aplica a opioides e a alguns benzodiazepínicos.&lt;/p&gt;&lt;p&gt;Outros pontos práticos da paralisia cerebral:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Hipotermia&lt;/strong&gt; fácil, por baixa massa muscular e escasso tecido adiposo — aquecimento ativo desde o início.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Refluxo e disfagia&lt;/strong&gt;, com risco de aspiração e pneumopatia crônica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;CAM reduzida&lt;/strong&gt; em cerca de 20% a 25%, e maior sensibilidade aos efeitos hipotensores dos anestésicos.&lt;/li&gt;&lt;li&gt;Se houver &lt;strong&gt;baclofeno intratecal&lt;/strong&gt;, jamais interromper abruptamente, pela síndrome de retirada com hipertermia, rigidez e rabdomiólise.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a CAM na paralisia cerebral é &lt;em&gt;menor&lt;/em&gt;, não maior. (B) não há desnervação nem proliferação de receptores no padrão que gera hipercalemia perigosa; o suxametônio é considerado seguro nesses pacientes. (D) a paralisia cerebral não constitui fator de risco reconhecido para hipertermia maligna, ao contrário de miopatias como as distrofias e a doença do núcleo central.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O uso crônico de fenitoína e carbamazepina induz o sistema microssomal hepático e aumenta a depuração de diversos fármacos. Somado a isso, ocorre &lt;strong&gt;proliferação de receptores nicotínicos extrajuncionais&lt;/strong&gt; e ligação do bloqueador a proteínas plasmáticas em maior proporção. O resultado clínico é característico: &lt;strong&gt;resistência aos bloqueadores adespolarizantes&lt;/strong&gt;, com início mais lento, menor efeito e duração encurtada, exigindo doses maiores e reinjeções frequentes; o mesmo se aplica a opioides e a alguns benzodiazepínicos.&lt;/p&gt;&lt;p&gt;Outros pontos práticos da paralisia cerebral:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Hipotermia&lt;/strong&gt; fácil, por baixa massa muscular e escasso tecido adiposo: aquecimento ativo desde o início.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Refluxo e disfagia&lt;/strong&gt;, com risco de aspiração e pneumopatia crônica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;CAM reduzida&lt;/strong&gt; em cerca de 20% a 25%, e maior sensibilidade aos efeitos hipotensores dos anestésicos.&lt;/li&gt;&lt;li&gt;Se houver &lt;strong&gt;baclofeno intratecal&lt;/strong&gt;, jamais interromper abruptamente, pela síndrome de retirada com hipertermia, rigidez e rabdomiólise.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a CAM na paralisia cerebral é &lt;em&gt;menor&lt;/em&gt;, não maior. (B) não há desnervação nem proliferação de receptores no padrão que gera hipercalemia perigosa; o suxametônio é considerado seguro nesses pacientes. (D) a paralisia cerebral não constitui fator de risco reconhecido para hipertermia maligna, ao contrário de miopatias como as distrofias e a doença do núcleo central.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A correção da mielomeningocele é realizada nas primeiras 24 a 72 horas de vida para reduzir infecção do sistema nervoso central. Dois cuidados dominam a condução anestésica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Posicionamento&lt;/strong&gt;: o saco herniário não pode ser comprimido, sob risco de rotura, extravasamento de liquor e lesão de tecido neural. A intubação é feita em &lt;strong&gt;decúbito lateral&lt;/strong&gt; ou, se em decúbito dorsal, com o defeito acomodado no interior de um coxim circular ou entre coxins laterais que o mantenham suspenso. A cirurgia transcorre em decúbito ventral, com atenção a pontos de pressão, olhos e ventilação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Látex&lt;/strong&gt;: portadores de disrafismo espinhal e de anomalias urológicas complexas têm a maior incidência de sensibilização ao látex de toda a população pediátrica, e a prevenção deve começar na &lt;strong&gt;primeira exposição&lt;/strong&gt; — todo o material, do centro cirúrgico à enfermaria, deve ser livre de látex desde o nascimento.&lt;/p&gt;&lt;p&gt;Acrescente-se a associação com &lt;strong&gt;malformação de Chiari II&lt;/strong&gt; (o estridor descrito sugere disfunção de tronco, com risco de apneia pós-operatória e disfunção de cordas vocais), hidrocefalia frequentemente exigindo derivação, perdas de calor e de líquido pelo defeito exposto e hipovolemia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a profilaxia de látex é obrigatória desde a primeira cirurgia, e não após exposições repetidas. (B) o bloqueio do neuroeixo é inadequado na presença de disrafismo e não protege a via aérea de um neonato com sinais de Chiari II. (D) a compressão do saco é justamente o que se busca evitar.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A correção da mielomeningocele é realizada nas primeiras 24 a 72 horas de vida para reduzir infecção do sistema nervoso central. Dois cuidados dominam a condução anestésica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Posicionamento&lt;/strong&gt;: o saco herniário não pode ser comprimido, sob risco de rotura, extravasamento de liquor e lesão de tecido neural. A intubação é feita em &lt;strong&gt;decúbito lateral&lt;/strong&gt; ou, se em decúbito dorsal, com o defeito acomodado no interior de um coxim circular ou entre coxins laterais que o mantenham suspenso. A cirurgia transcorre em decúbito ventral, com atenção a pontos de pressão, olhos e ventilação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Látex&lt;/strong&gt;: portadores de disrafismo espinhal e de anomalias urológicas complexas têm a maior incidência de sensibilização ao látex de toda a população pediátrica, e a prevenção deve começar na &lt;strong&gt;primeira exposição&lt;/strong&gt;: todo o material, do centro cirúrgico à enfermaria, deve ser livre de látex desde o nascimento.&lt;/p&gt;&lt;p&gt;Acrescente-se a associação com &lt;strong&gt;malformação de Chiari II&lt;/strong&gt; (o estridor descrito sugere disfunção de tronco, com risco de apneia pós-operatória e disfunção de cordas vocais), hidrocefalia frequentemente exigindo derivação, perdas de calor e de líquido pelo defeito exposto e hipovolemia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a profilaxia de látex é obrigatória desde a primeira cirurgia, e não após exposições repetidas. (B) o bloqueio do neuroeixo é inadequado na presença de disrafismo e não protege a via aérea de um neonato com sinais de Chiari II. (D) a compressão do saco é justamente o que se busca evitar.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O receptor &lt;strong&gt;NMDA&lt;/strong&gt; é um canal iônico ativado por glutamato, permeável a sódio e sobretudo a &lt;strong&gt;cálcio&lt;/strong&gt;. Sua peculiaridade é a dupla porta: além do ligante, exige remoção do &lt;strong&gt;bloqueio pelo íon magnésio&lt;/strong&gt; alojado no poro, que só sai quando a membrana está suficientemente despolarizada. Precisa ainda de um coagonista, glicina ou D-serina.&lt;/p&gt;&lt;p&gt;Isso faz do NMDA um &lt;em&gt;detector de coincidência&lt;/em&gt;: estímulos nociceptivos isolados não o ativam, mas a estimulação repetida de fibras C despolariza progressivamente o neurônio de segunda ordem e retira o magnésio. O resultado é o &lt;strong&gt;wind-up&lt;/strong&gt; e, adiante, a sensibilização central — expansão do campo receptivo, redução do limiar e resposta exagerada, expressas clinicamente como alodínia e hiperalgesia, exatamente o que o paciente descreve. O influxo de cálcio ativa proteína quinase C, óxido nítrico sintase e ciclo-oxigenase-2, perpetuando a plasticidade.&lt;/p&gt;&lt;p&gt;Antagonistas do canal, como &lt;strong&gt;cetamina&lt;/strong&gt; em doses subanestésicas, revertem parte desse estado e reduzem a hiperalgesia induzida por opioides.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o NMDA é ionotrópico, não metabotrópico, e seu agonista é o glutamato, não a substância P; (C) a ativação abre corrente catiônica com influxo de cálcio e despolarização, não hiperpolarização por cloreto, que é a ação de GABA-A e glicina; (D) a transmissão rápida do estímulo agudo cabe aos receptores &lt;strong&gt;AMPA&lt;/strong&gt;, entrando o NMDA apenas com estimulação sustentada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O receptor &lt;strong&gt;NMDA&lt;/strong&gt; é um canal iônico ativado por glutamato, permeável a sódio e sobretudo a &lt;strong&gt;cálcio&lt;/strong&gt;. Sua peculiaridade é a dupla porta: além do ligante, exige remoção do &lt;strong&gt;bloqueio pelo íon magnésio&lt;/strong&gt; alojado no poro, que só sai quando a membrana está suficientemente despolarizada. Precisa ainda de um coagonista, glicina ou D-serina.&lt;/p&gt;&lt;p&gt;Isso faz do NMDA um &lt;em&gt;detector de coincidência&lt;/em&gt;: estímulos nociceptivos isolados não o ativam, mas a estimulação repetida de fibras C despolariza progressivamente o neurônio de segunda ordem e retira o magnésio. O resultado é o &lt;strong&gt;wind-up&lt;/strong&gt; e, adiante, a sensibilização central: expansão do campo receptivo, redução do limiar e resposta exagerada, expressas clinicamente como alodínia e hiperalgesia, exatamente o que o paciente descreve. O influxo de cálcio ativa proteína quinase C, óxido nítrico sintase e ciclo-oxigenase-2, perpetuando a plasticidade.&lt;/p&gt;&lt;p&gt;Antagonistas do canal, como &lt;strong&gt;cetamina&lt;/strong&gt; em doses subanestésicas, revertem parte desse estado e reduzem a hiperalgesia induzida por opioides.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o NMDA é ionotrópico, não metabotrópico, e seu agonista é o glutamato, não a substância P; (C) a ativação abre corrente catiônica com influxo de cálcio e despolarização, não hiperpolarização por cloreto, que é a ação de GABA-A e glicina; (D) a transmissão rápida do estímulo agudo cabe aos receptores &lt;strong&gt;AMPA&lt;/strong&gt;, entrando o NMDA apenas com estimulação sustentada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A dose de manutenção de &lt;strong&gt;metadona&lt;/strong&gt; cobre a dependência física, mas &lt;em&gt;não&lt;/em&gt; fornece analgesia para a dor aguda cirúrgica — sua meia-vida analgésica é de poucas horas, muito menor que a meia-vida de eliminação, que varia amplamente (aproximadamente 15 a 60 horas). A regra é &lt;strong&gt;manter a dose basal&lt;/strong&gt; e tratar a dor incidental à parte. Como esses pacientes são tolerantes e frequentemente hiperálgicos, as doses de resgate costumam ser &lt;strong&gt;maiores&lt;/strong&gt; que as de um paciente virgem de opioides, e não menores.&lt;/p&gt;&lt;p&gt;A metadona ainda é agonista mu, antagonista NMDA e inibidora da recaptação de monoaminas, combinação útil na dor com componente neuropático; exige atenção ao &lt;strong&gt;prolongamento do intervalo QT&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;cetorolaco&lt;/strong&gt; é um anti-inflamatório não esteroidal parenteral potente, excelente poupador de opioide, sem qualquer risco de precipitar abstinência — mas seu uso é limitado a cerca de &lt;strong&gt;cinco dias&lt;/strong&gt; pelos riscos gastrintestinal, renal e hemorrágico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) suspender a metadona precipita abstinência, e a naltrexona, antagonista puro, agravaria o quadro e bloquearia qualquer analgesia opioide; (B) condicionar a metadona à dor ignora sua função de manutenção, e o cetorolaco isolado por dez dias excede o limite seguro de uso; (C) a buprenorfina, agonista parcial de alta afinidade, desloca a metadona e precipita abstinência, além de dificultar o resgate.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A dose de manutenção de &lt;strong&gt;metadona&lt;/strong&gt; cobre a dependência física, mas &lt;em&gt;não&lt;/em&gt; fornece analgesia para a dor aguda cirúrgica; sua meia-vida analgésica é de poucas horas, muito menor que a meia-vida de eliminação, que varia amplamente (aproximadamente 15 a 60 horas). A regra é &lt;strong&gt;manter a dose basal&lt;/strong&gt; e tratar a dor incidental à parte. Como esses pacientes são tolerantes e frequentemente hiperálgicos, as doses de resgate costumam ser &lt;strong&gt;maiores&lt;/strong&gt; que as de um paciente virgem de opioides, e não menores.&lt;/p&gt;&lt;p&gt;A metadona ainda é agonista mu, antagonista NMDA e inibidora da recaptação de monoaminas, combinação útil na dor com componente neuropático; exige atenção ao &lt;strong&gt;prolongamento do intervalo QT&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;cetorolaco&lt;/strong&gt; é um anti-inflamatório não esteroidal parenteral potente, excelente poupador de opioide, sem qualquer risco de precipitar abstinência, mas seu uso é limitado a cerca de &lt;strong&gt;cinco dias&lt;/strong&gt; pelos riscos gastrintestinal, renal e hemorrágico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) suspender a metadona precipita abstinência, e a naltrexona, antagonista puro, agravaria o quadro e bloquearia qualquer analgesia opioide; (B) condicionar a metadona à dor ignora sua função de manutenção, e o cetorolaco isolado por dez dias excede o limite seguro de uso; (C) a buprenorfina, agonista parcial de alta afinidade, desloca a metadona e precipita abstinência, além de dificultar o resgate.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os &lt;strong&gt;nociceptores&lt;/strong&gt; não são estruturas encapsuladas: são &lt;strong&gt;terminações nervosas livres&lt;/strong&gt; das fibras aferentes primárias, distribuídas em pele, músculo, articulações, periósteo e vísceras. Isso os diferencia dos mecanorreceptores especializados (Pacini, Meissner, Ruffini), que são encapsulados e servem ao tato e à propriocepção.&lt;/p&gt;&lt;p&gt;Dois tipos de fibra conduzem a nocicepção:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;A-delta&lt;/strong&gt;: finamente mielinizadas, velocidade em torno de 5 a 30 m/s, responsáveis pela &lt;em&gt;primeira dor&lt;/em&gt; — rápida, aguda, em pontada e bem localizada, que dispara o reflexo de retirada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;C&lt;/strong&gt;: amielínicas, velocidade aproximada de 0,5 a 2 m/s, &lt;strong&gt;polimodais&lt;/strong&gt; (respondem a estímulos mecânicos, térmicos e químicos), responsáveis pela &lt;em&gt;segunda dor&lt;/em&gt; — tardia, em queimação, difusa e de pior localização, com forte carga afetiva.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;As fibras A-beta, de grosso calibre e alta velocidade, conduzem tato e vibração e, quando estimuladas, inibem a transmissão nociceptiva no corno dorsal — base fisiológica da teoria das comportas e da neuroestimulação transcutânea.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) as fibras A-beta não são nociceptivas em condições fisiológicas; (C) os nociceptores são terminações livres, e não corpúsculos encapsulados; (D) a fibra C é a &lt;strong&gt;mais lenta&lt;/strong&gt; das aferentes primárias, sendo responsável pela segunda dor.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os &lt;strong&gt;nociceptores&lt;/strong&gt; não são estruturas encapsuladas: são &lt;strong&gt;terminações nervosas livres&lt;/strong&gt; das fibras aferentes primárias, distribuídas em pele, músculo, articulações, periósteo e vísceras. Isso os diferencia dos mecanorreceptores especializados (Pacini, Meissner, Ruffini), que são encapsulados e servem ao tato e à propriocepção.&lt;/p&gt;&lt;p&gt;Dois tipos de fibra conduzem a nocicepção:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;A-delta&lt;/strong&gt;: finamente mielinizadas, velocidade em torno de 5 a 30 m/s, responsáveis pela &lt;em&gt;primeira dor&lt;/em&gt;, rápida, aguda, em pontada e bem localizada, que dispara o reflexo de retirada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;C&lt;/strong&gt;: amielínicas, velocidade aproximada de 0,5 a 2 m/s, &lt;strong&gt;polimodais&lt;/strong&gt; (respondem a estímulos mecânicos, térmicos e químicos), responsáveis pela &lt;em&gt;segunda dor&lt;/em&gt;, tardia, em queimação, difusa e de pior localização, com forte carga afetiva.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;As fibras A-beta, de grosso calibre e alta velocidade, conduzem tato e vibração e, quando estimuladas, inibem a transmissão nociceptiva no corno dorsal, base fisiológica da teoria das comportas e da neuroestimulação transcutânea.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) as fibras A-beta não são nociceptivas em condições fisiológicas; (C) os nociceptores são terminações livres, e não corpúsculos encapsulados; (D) a fibra C é a &lt;strong&gt;mais lenta&lt;/strong&gt; das aferentes primárias, sendo responsável pela segunda dor.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Tanto a &lt;strong&gt;cetamina&lt;/strong&gt; quanto a &lt;strong&gt;memantina&lt;/strong&gt; são antagonistas &lt;em&gt;não competitivos&lt;/em&gt; do receptor NMDA: ligam-se dentro do poro do canal, no sítio da fenciclidina, e não ao sítio do glutamato ou da glicina. O bloqueio é &lt;strong&gt;uso-dependente&lt;/strong&gt; — só ocorre com o canal aberto —, o que direciona o efeito para sinapses hiperativas, exatamente as envolvidas na sensibilização central.&lt;/p&gt;&lt;p&gt;Em doses subanestésicas (bolus em torno de 0,15 a 0,5 mg/kg seguido de infusão de aproximadamente 0,1 a 0,3 mg/kg/h), a cetamina reduz o consumo de opioide, atenua o &lt;strong&gt;wind-up&lt;/strong&gt; e previne ou reverte a &lt;strong&gt;hiperalgesia induzida por opioides&lt;/strong&gt;, sendo particularmente útil no paciente tolerante e na dor com componente neuropático.&lt;/p&gt;&lt;p&gt;A memantina tem afinidade menor e cinética de dissociação rápida, o que explica sua tolerabilidade no uso crônico oral, com resultados modestos na dor neuropática.&lt;/p&gt;&lt;p&gt;Efeitos adversos psicotomiméticos — alucinações, sonhos vívidos, disforia — são dose-dependentes e limitam o escalonamento; benzodiazepínicos ou alfa-2-agonistas os atenuam.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a cetamina atua no interior do canal, não no sítio da glicina, e o bloqueio é não competitivo; (B) a memantina é &lt;strong&gt;antagonista&lt;/strong&gt;, e o efeito buscado é justamente a redução do influxo de cálcio; (D) ambos os fármacos, sobretudo a cetamina, produzem efeitos psicotomiméticos dose-dependentes que impõem teto ao tratamento.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Tanto a &lt;strong&gt;cetamina&lt;/strong&gt; quanto a &lt;strong&gt;memantina&lt;/strong&gt; são antagonistas &lt;em&gt;não competitivos&lt;/em&gt; do receptor NMDA: ligam-se dentro do poro do canal, no sítio da fenciclidina, e não ao sítio do glutamato ou da glicina. O bloqueio é &lt;strong&gt;uso-dependente&lt;/strong&gt; (só ocorre com o canal aberto), o que direciona o efeito para sinapses hiperativas, exatamente as envolvidas na sensibilização central.&lt;/p&gt;&lt;p&gt;Em doses subanestésicas (bolus em torno de 0,15 a 0,5 mg/kg seguido de infusão de aproximadamente 0,1 a 0,3 mg/kg/h), a cetamina reduz o consumo de opioide, atenua o &lt;strong&gt;wind-up&lt;/strong&gt; e previne ou reverte a &lt;strong&gt;hiperalgesia induzida por opioides&lt;/strong&gt;, sendo particularmente útil no paciente tolerante e na dor com componente neuropático.&lt;/p&gt;&lt;p&gt;A memantina tem afinidade menor e cinética de dissociação rápida, o que explica sua tolerabilidade no uso crônico oral, com resultados modestos na dor neuropática.&lt;/p&gt;&lt;p&gt;Efeitos adversos psicotomiméticos (alucinações, sonhos vívidos, disforia) são dose-dependentes e limitam o escalonamento; benzodiazepínicos ou alfa-2-agonistas os atenuam.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a cetamina atua no interior do canal, não no sítio da glicina, e o bloqueio é não competitivo; (B) a memantina é &lt;strong&gt;antagonista&lt;/strong&gt;, e o efeito buscado é justamente a redução do influxo de cálcio; (D) ambos os fármacos, sobretudo a cetamina, produzem efeitos psicotomiméticos dose-dependentes que impõem teto ao tratamento.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O terminal central das fibras aferentes primárias nociceptivas libera dois grupos de mensageiros com cinéticas muito distintas.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Glutamato&lt;/strong&gt;: aminoácido excitatório presente em fibras A-delta e C. Atua sobre receptores ionotrópicos &lt;strong&gt;AMPA&lt;/strong&gt; e cainato, gerando potenciais pós-sinápticos excitatórios &lt;em&gt;rápidos&lt;/em&gt;, de milissegundos, que codificam localização e intensidade. Com estimulação repetida, recruta também os receptores NMDA.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Substância P&lt;/strong&gt;: neuropeptídeo armazenado em vesículas de núcleo denso das fibras C, liberado sobretudo com estimulação de alta frequência. Age em receptores metabotrópicos &lt;strong&gt;NK-1&lt;/strong&gt;, produzindo despolarização &lt;em&gt;lenta&lt;/em&gt;, de segundos, que se somam temporalmente e contribuem para remover o bloqueio de magnésio do NMDA — passo essencial do wind-up.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Outros peptídeos coliberados incluem o peptídeo relacionado ao gene da calcitonina, que prolonga a ação da substância P e participa da inflamação neurogênica periférica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte os papéis: a substância P atua em receptores NK-1 e produz resposta lenta, não rápida via AMPA; (B) o glutamato não se liga a receptores de neurocinina, que são específicos das taquicininas; (C) o ácido gama-aminobutírico é o principal neurotransmissor &lt;strong&gt;inibitório&lt;/strong&gt; do corno dorsal, liberado por interneurônios, e não pelas fibras C.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O terminal central das fibras aferentes primárias nociceptivas libera dois grupos de mensageiros com cinéticas muito distintas.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Glutamato&lt;/strong&gt;: aminoácido excitatório presente em fibras A-delta e C. Atua sobre receptores ionotrópicos &lt;strong&gt;AMPA&lt;/strong&gt; e cainato, gerando potenciais pós-sinápticos excitatórios &lt;em&gt;rápidos&lt;/em&gt;, de milissegundos, que codificam localização e intensidade. Com estimulação repetida, recruta também os receptores NMDA.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Substância P&lt;/strong&gt;: neuropeptídeo armazenado em vesículas de núcleo denso das fibras C, liberado sobretudo com estimulação de alta frequência. Age em receptores metabotrópicos &lt;strong&gt;NK-1&lt;/strong&gt;, produzindo despolarização &lt;em&gt;lenta&lt;/em&gt;, de segundos, que se somam temporalmente e contribuem para remover o bloqueio de magnésio do NMDA, passo essencial do wind-up.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Outros peptídeos coliberados incluem o peptídeo relacionado ao gene da calcitonina, que prolonga a ação da substância P e participa da inflamação neurogênica periférica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte os papéis: a substância P atua em receptores NK-1 e produz resposta lenta, não rápida via AMPA; (B) o glutamato não se liga a receptores de neurocinina, que são específicos das taquicininas; (C) o ácido gama-aminobutírico é o principal neurotransmissor &lt;strong&gt;inibitório&lt;/strong&gt; do corno dorsal, liberado por interneurônios, e não pelas fibras C.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O neurônio de segunda ordem, situado no corno dorsal, &lt;strong&gt;cruza a linha média&lt;/strong&gt; pela comissura branca anterior em poucos segmentos e ascende pelo quadrante anterolateral contralateral — daí a dissociação clássica descrita no caso, com perda termoalgésica contralateral e perda proprioceptiva ipsilateral (funículo posterior, que só cruza no bulbo).&lt;/p&gt;&lt;p&gt;Esse sistema anterolateral tem duas divisões funcionais:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Neoespinotalâmico&lt;/strong&gt; (lateral): projeta-se ao &lt;strong&gt;núcleo ventral posterolateral&lt;/strong&gt; do tálamo e deste ao &lt;strong&gt;córtex somatossensorial primário e secundário&lt;/strong&gt;. É a via somatotopicamente organizada, responsável pelos aspectos &lt;em&gt;sensitivo-discriminativos&lt;/em&gt;: onde dói, quanto dói, que tipo de dor.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Paleoespinotalâmico&lt;/strong&gt; e projeções espinorreticulares e espinomesencefálicas (medial): terminam em formação reticular, substância cinzenta periaquedutal e núcleos talâmicos intralaminares, com difusão para ínsula, cingulado anterior e sistema límbico. Sustentam os componentes &lt;em&gt;afetivo-motivacional&lt;/em&gt; e autonômico, além da ativação das vias descendentes inibitórias.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;O núcleo ventral posteromedial recebe a aferência trigeminal, ou seja, a face.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a nocicepção ascende contralateralmente pelo quadrante anterolateral, cruzando na própria medula; (C) o paleoespinotalâmico termina em núcleos mediais e intralaminares e não confere localização precisa; (D) o tálamo é a principal estação de relé da nocicepção antes do córtex.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O neurônio de segunda ordem, situado no corno dorsal, &lt;strong&gt;cruza a linha média&lt;/strong&gt; pela comissura branca anterior em poucos segmentos e ascende pelo quadrante anterolateral contralateral; daí a dissociação clássica descrita no caso, com perda termoalgésica contralateral e perda proprioceptiva ipsilateral (funículo posterior, que só cruza no bulbo).&lt;/p&gt;&lt;p&gt;Esse sistema anterolateral tem duas divisões funcionais:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Neoespinotalâmico&lt;/strong&gt; (lateral): projeta-se ao &lt;strong&gt;núcleo ventral posterolateral&lt;/strong&gt; do tálamo e deste ao &lt;strong&gt;córtex somatossensorial primário e secundário&lt;/strong&gt;. É a via somatotopicamente organizada, responsável pelos aspectos &lt;em&gt;sensitivo-discriminativos&lt;/em&gt;: onde dói, quanto dói, que tipo de dor.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Paleoespinotalâmico&lt;/strong&gt; e projeções espinorreticulares e espinomesencefálicas (medial): terminam em formação reticular, substância cinzenta periaquedutal e núcleos talâmicos intralaminares, com difusão para ínsula, cingulado anterior e sistema límbico. Sustentam os componentes &lt;em&gt;afetivo-motivacional&lt;/em&gt; e autonômico, além da ativação das vias descendentes inibitórias.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;O núcleo ventral posteromedial recebe a aferência trigeminal, ou seja, a face.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a nocicepção ascende contralateralmente pelo quadrante anterolateral, cruzando na própria medula; (C) o paleoespinotalâmico termina em núcleos mediais e intralaminares e não confere localização precisa; (D) o tálamo é a principal estação de relé da nocicepção antes do córtex.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O conceito nasceu da observação experimental de que o bloqueio da aferência nociceptiva &lt;em&gt;antes&lt;/em&gt; do estímulo produz menos sensibilização central do que o mesmo bloqueio instituído depois. &lt;strong&gt;Analgesia preemptiva&lt;/strong&gt;, no sentido estrito, é a intervenção instituída &lt;strong&gt;antes da incisão&lt;/strong&gt;, com o objetivo de impedir o estabelecimento da hiperexcitabilidade no corno dorsal.&lt;/p&gt;&lt;p&gt;Como os ensaios clínicos que compararam apenas o &lt;em&gt;momento&lt;/em&gt; da mesma intervenção geraram resultados inconsistentes, o conceito evoluiu para &lt;strong&gt;analgesia preventiva&lt;/strong&gt;: o que importa é cobrir todo o período de aferência nociceptiva — pré, intra e pós-operatório, incluindo a fase inflamatória — e o critério de sucesso é um efeito analgésico que &lt;strong&gt;ultrapassa a duração farmacológica&lt;/strong&gt; esperada do agente (classicamente mais de cinco meias-vidas).&lt;/p&gt;&lt;p&gt;Fatores de risco reconhecidos para dor crônica pós-cirúrgica incluem dor pré-operatória intensa, dor aguda pós-operatória mal controlada, lesão nervosa intraoperatória, cirurgias como toracotomia, mastectomia e herniorrafia, além de catastrofização e ansiedade. Estratégias com maior plausibilidade são analgesia regional contínua, cetamina, gabapentinoides e lidocaína venosa dentro de um plano multimodal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) tratar apenas quando a dor já se instalou é o oposto do conceito; (C) a analgesia preventiva não se define pelo momento isolado nem se restringe a bloqueio ao fim da cirurgia; (D) fatores genéticos participam, mas a dor crônica pós-cirúrgica é multifatorial e parcialmente modificável.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O conceito nasceu da observação experimental de que o bloqueio da aferência nociceptiva &lt;em&gt;antes&lt;/em&gt; do estímulo produz menos sensibilização central do que o mesmo bloqueio instituído depois. &lt;strong&gt;Analgesia preemptiva&lt;/strong&gt;, no sentido estrito, é a intervenção instituída &lt;strong&gt;antes da incisão&lt;/strong&gt;, com o objetivo de impedir o estabelecimento da hiperexcitabilidade no corno dorsal.&lt;/p&gt;&lt;p&gt;Como os ensaios clínicos que compararam apenas o &lt;em&gt;momento&lt;/em&gt; da mesma intervenção geraram resultados inconsistentes, o conceito evoluiu para &lt;strong&gt;analgesia preventiva&lt;/strong&gt;: o que importa é cobrir todo o período de aferência nociceptiva (pré, intra e pós-operatório, incluindo a fase inflamatória) e o critério de sucesso é um efeito analgésico que &lt;strong&gt;ultrapassa a duração farmacológica&lt;/strong&gt; esperada do agente (classicamente mais de cinco meias-vidas).&lt;/p&gt;&lt;p&gt;Fatores de risco reconhecidos para dor crônica pós-cirúrgica incluem dor pré-operatória intensa, dor aguda pós-operatória mal controlada, lesão nervosa intraoperatória, cirurgias como toracotomia, mastectomia e herniorrafia, além de catastrofização e ansiedade. Estratégias com maior plausibilidade são analgesia regional contínua, cetamina, gabapentinoides e lidocaína venosa dentro de um plano multimodal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) tratar apenas quando a dor já se instalou é o oposto do conceito; (C) a analgesia preventiva não se define pelo momento isolado nem se restringe a bloqueio ao fim da cirurgia; (D) fatores genéticos participam, mas a dor crônica pós-cirúrgica é multifatorial e parcialmente modificável.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os receptores opioides — mu, delta, kappa e o receptor de nociceptina — são &lt;strong&gt;metabotrópicos&lt;/strong&gt;, acoplados a proteínas &lt;strong&gt;Gi/Go&lt;/strong&gt;. Sua ativação desencadeia três eventos:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Inibição da adenilato-ciclase, com queda do &lt;strong&gt;monofosfato de adenosina cíclico&lt;/strong&gt;;&lt;/li&gt;&lt;li&gt;Abertura de &lt;strong&gt;canais de potássio&lt;/strong&gt; retificadores de influxo no neurônio pós-sináptico, com efluxo de potássio, hiperpolarização e menor probabilidade de disparo;&lt;/li&gt;&lt;li&gt;Inibição de &lt;strong&gt;canais de cálcio dependentes de voltagem&lt;/strong&gt; no terminal pré-sináptico, reduzindo o influxo de cálcio e, com ele, a liberação de glutamato, substância P e peptídeo relacionado ao gene da calcitonina.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A ação pré-sináptica explica por que o opioide espinhal reduz a chegada do sinal ao neurônio de segunda ordem, e a pós-sináptica explica a menor resposta desse neurônio ao sinal que chega. Somam-se ainda a ativação das vias descendentes inibitórias, por desinibição de neurônios da substância cinzenta periaquedutal e do bulbo rostroventromedial.&lt;/p&gt;&lt;p&gt;A tolerância envolve fosforilação do receptor, recrutamento de beta-arrestina, internalização e supra-regulação compensatória do sistema do monofosfato de adenosina cíclico — a mesma supra-regulação que se manifesta como abstinência quando o opioide é retirado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o acoplamento é a Gi/Go, com &lt;em&gt;redução&lt;/em&gt; do monofosfato de adenosina cíclico; (B) não há bloqueio direto de canais de sódio axonais, mecanismo dos anestésicos locais; (C) os receptores opioides não são canais iônicos de cloreto.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os receptores opioides (mu, delta, kappa e o receptor de nociceptina) são &lt;strong&gt;metabotrópicos&lt;/strong&gt;, acoplados a proteínas &lt;strong&gt;Gi/Go&lt;/strong&gt;. Sua ativação desencadeia três eventos:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Inibição da adenilato-ciclase, com queda do &lt;strong&gt;monofosfato de adenosina cíclico&lt;/strong&gt;;&lt;/li&gt;&lt;li&gt;Abertura de &lt;strong&gt;canais de potássio&lt;/strong&gt; retificadores de influxo no neurônio pós-sináptico, com efluxo de potássio, hiperpolarização e menor probabilidade de disparo;&lt;/li&gt;&lt;li&gt;Inibição de &lt;strong&gt;canais de cálcio dependentes de voltagem&lt;/strong&gt; no terminal pré-sináptico, reduzindo o influxo de cálcio e, com ele, a liberação de glutamato, substância P e peptídeo relacionado ao gene da calcitonina.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A ação pré-sináptica explica por que o opioide espinhal reduz a chegada do sinal ao neurônio de segunda ordem, e a pós-sináptica explica a menor resposta desse neurônio ao sinal que chega. Somam-se ainda a ativação das vias descendentes inibitórias, por desinibição de neurônios da substância cinzenta periaquedutal e do bulbo rostroventromedial.&lt;/p&gt;&lt;p&gt;A tolerância envolve fosforilação do receptor, recrutamento de beta-arrestina, internalização e supra-regulação compensatória do sistema do monofosfato de adenosina cíclico, a mesma supra-regulação que se manifesta como abstinência quando o opioide é retirado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o acoplamento é a Gi/Go, com &lt;em&gt;redução&lt;/em&gt; do monofosfato de adenosina cíclico; (B) não há bloqueio direto de canais de sódio axonais, mecanismo dos anestésicos locais; (C) os receptores opioides não são canais iônicos de cloreto.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Os opioides agem em receptores mu de núcleos bulbares e pontinos que geram e modulam o ritmo respiratório, sobretudo o complexo pré-Bötzinger. A consequência funcional é dupla: a curva que relaciona ventilação-minuto à PaCO&lt;sub&gt;2&lt;/sub&gt; desloca-se &lt;strong&gt;para a direita&lt;/strong&gt; (é preciso PaCO&lt;sub&gt;2&lt;/sub&gt; maior para deflagrar a mesma ventilação) e sua &lt;strong&gt;inclinação diminui&lt;/strong&gt; (cada milímetro de mercúrio adicional gera menos aumento de ventilação). Some-se a depressão da resposta ventilatória à &lt;strong&gt;hipóxia&lt;/strong&gt;, mediada por quimiorreceptores periféricos, que retira a rede de segurança do paciente.&lt;/p&gt;&lt;p&gt;Clinicamente, o padrão típico é &lt;strong&gt;bradipneia com volume corrente preservado ou aumentado&lt;/strong&gt;, exatamente como descrito, e não taquipneia superficial. Sedação progressiva costuma preceder a queda da frequência respiratória, e é o sinal de alarme mais precoce.&lt;/p&gt;&lt;p&gt;A idade avançada, o baixo peso, a apneia obstrutiva do sono e a associação com benzodiazepínicos amplificam o risco.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a inclinação da curva &lt;em&gt;reduz&lt;/em&gt;-se e o deslocamento é para a direita; (B) não há efeito na junção neuromuscular — o sítio é central, embora a rigidez torácica por opioide em bolus rápido possa dificultar a ventilação; (D) sob oxigênio suplementar a saturação permanece normal apesar de hipoventilação importante, motivo pelo qual a oximetria isolada é um monitor tardio e insuficiente, sendo preferível a avaliação da sedação e da capnografia.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Os opioides agem em receptores mu de núcleos bulbares e pontinos que geram e modulam o ritmo respiratório, sobretudo o complexo pré-Bötzinger. A consequência funcional é dupla: a curva que relaciona ventilação-minuto à PaCO&lt;sub&gt;2&lt;/sub&gt; desloca-se &lt;strong&gt;para a direita&lt;/strong&gt; (é preciso PaCO&lt;sub&gt;2&lt;/sub&gt; maior para deflagrar a mesma ventilação) e sua &lt;strong&gt;inclinação diminui&lt;/strong&gt; (cada milímetro de mercúrio adicional gera menos aumento de ventilação). Some-se a depressão da resposta ventilatória à &lt;strong&gt;hipóxia&lt;/strong&gt;, mediada por quimiorreceptores periféricos, que retira a rede de segurança do paciente.&lt;/p&gt;&lt;p&gt;Clinicamente, o padrão típico é &lt;strong&gt;bradipneia com volume corrente preservado ou aumentado&lt;/strong&gt;, exatamente como descrito, e não taquipneia superficial. Sedação progressiva costuma preceder a queda da frequência respiratória, e é o sinal de alarme mais precoce.&lt;/p&gt;&lt;p&gt;A idade avançada, o baixo peso, a apneia obstrutiva do sono e a associação com benzodiazepínicos amplificam o risco.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a inclinação da curva &lt;em&gt;reduz&lt;/em&gt;-se e o deslocamento é para a direita; (B) não há efeito na junção neuromuscular: o sítio é central, embora a rigidez torácica por opioide em bolus rápido possa dificultar a ventilação; (D) sob oxigênio suplementar a saturação permanece normal apesar de hipoventilação importante, motivo pelo qual a oximetria isolada é um monitor tardio e insuficiente, sendo preferível a avaliação da sedação e da capnografia.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A injeção peridural de corticoide tem seu melhor desempenho na &lt;strong&gt;dor radicular&lt;/strong&gt; por hérnia discal contida, sobretudo na fase inflamatória inicial — o corticoide reduz o edema e a inflamação perirradicular e estabiliza membranas de fibras lesadas. O benefício é predominantemente de &lt;strong&gt;curto e médio prazo&lt;/strong&gt;, funcionando como janela para reabilitação, e é menor na lombalgia axial pura e na estenose de canal.&lt;/p&gt;&lt;p&gt;Embora administrado no neuroeixo, o corticoide é &lt;strong&gt;absorvido sistemicamente&lt;/strong&gt;. As consequências relevantes na prática são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Supressão do eixo hipotálamo-hipófise-adrenal&lt;/strong&gt;, que pode durar de algumas semanas a cerca de três meses;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hiperglicemia&lt;/strong&gt;, com pico nos primeiros dias, importante no diabético;&lt;/li&gt;&lt;li&gt;Retenção hídrica, insônia, rubor facial e, com repetições frequentes, perda de massa óssea.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Por isso limita-se o número de aplicações e respeita-se intervalo entre elas, guiando a repetição pela resposta obtida.&lt;/p&gt;&lt;p&gt;Na via &lt;strong&gt;transforaminal cervical&lt;/strong&gt;, a recomendação consagrada é usar corticoide &lt;em&gt;não&lt;/em&gt; particulado, pois partículas injetadas inadvertidamente em artéria radicular ou vertebral podem causar infarto medular ou de tronco encefálico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a indicação de eleição é a dor radicular, não a lombalgia axial; (C) na transforaminal cervical prefere-se o não particulado, justamente pelo risco embólico; (D) há efeitos sistêmicos mensuráveis, que impõem limite de dose e intervalo.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A injeção peridural de corticoide tem seu melhor desempenho na &lt;strong&gt;dor radicular&lt;/strong&gt; por hérnia discal contida, sobretudo na fase inflamatória inicial: o corticoide reduz o edema e a inflamação perirradicular e estabiliza membranas de fibras lesadas. O benefício é predominantemente de &lt;strong&gt;curto e médio prazo&lt;/strong&gt;, funcionando como janela para reabilitação, e é menor na lombalgia axial pura e na estenose de canal.&lt;/p&gt;&lt;p&gt;Embora administrado no neuroeixo, o corticoide é &lt;strong&gt;absorvido sistemicamente&lt;/strong&gt;. As consequências relevantes na prática são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Supressão do eixo hipotálamo-hipófise-adrenal&lt;/strong&gt;, que pode durar de algumas semanas a cerca de três meses;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hiperglicemia&lt;/strong&gt;, com pico nos primeiros dias, importante no diabético;&lt;/li&gt;&lt;li&gt;Retenção hídrica, insônia, rubor facial e, com repetições frequentes, perda de massa óssea.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Por isso limita-se o número de aplicações e respeita-se intervalo entre elas, guiando a repetição pela resposta obtida.&lt;/p&gt;&lt;p&gt;Na via &lt;strong&gt;transforaminal cervical&lt;/strong&gt;, a recomendação consagrada é usar corticoide &lt;em&gt;não&lt;/em&gt; particulado, pois partículas injetadas inadvertidamente em artéria radicular ou vertebral podem causar infarto medular ou de tronco encefálico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a indicação de eleição é a dor radicular, não a lombalgia axial; (C) na transforaminal cervical prefere-se o não particulado, justamente pelo risco embólico; (D) há efeitos sistêmicos mensuráveis, que impõem limite de dose e intervalo.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A cadeia simpática lombar corre na face &lt;strong&gt;anterolateral dos corpos vertebrais de L2 a L4&lt;/strong&gt;, anteriormente ao músculo psoas — relação anatômica que orienta a punção posterolateral guiada por imagem e explica a proximidade com aorta à esquerda, veia cava à direita, ureter e raízes nervosas.&lt;/p&gt;&lt;p&gt;Suas indicações clássicas são a &lt;strong&gt;doença vascular periférica&lt;/strong&gt; com dor isquêmica de repouso ou úlcera em paciente sem opção de revascularização, a &lt;strong&gt;síndrome dolorosa complexa regional&lt;/strong&gt; de membro inferior e a hiperidrose. O efeito imediato é vasodilatação, com &lt;strong&gt;elevação da temperatura cutânea&lt;/strong&gt; do membro — que é justamente o marcador objetivo de sucesso, ao lado da queda da resposta galvânica da pele.&lt;/p&gt;&lt;p&gt;O limite fundamental é conceitual: o bloqueio interrompe fibras &lt;strong&gt;simpáticas eferentes&lt;/strong&gt; e aferentes viscerais, não as vias somáticas. Portanto alivia a dor de origem isquêmica e a dor mantida pelo simpático, mas &lt;em&gt;não&lt;/em&gt; anestesia o dermátomo nem trata dor somática ou neuropática somática.&lt;/p&gt;&lt;p&gt;Complicações incluem punção vascular, injeção subaracnóidea ou peridural, lesão de ureter e, após neurólise, &lt;strong&gt;neuralgia genitofemoral&lt;/strong&gt; em até 10% dos casos, por difusão do agente neurolítico sobre o nervo que corre na face anterior do psoas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o bloqueio não é somático e não abole a dor dos dermátomos; (C) a neuralgia genitofemoral é a complicação mais característica da neurólise lombar; (D) o sucesso se confirma pelo &lt;strong&gt;aumento&lt;/strong&gt; da temperatura cutânea, e não por sua ausência.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A cadeia simpática lombar corre na face &lt;strong&gt;anterolateral dos corpos vertebrais de L2 a L4&lt;/strong&gt;, anteriormente ao músculo psoas, relação anatômica que orienta a punção posterolateral guiada por imagem e explica a proximidade com aorta à esquerda, veia cava à direita, ureter e raízes nervosas.&lt;/p&gt;&lt;p&gt;Suas indicações clássicas são a &lt;strong&gt;doença vascular periférica&lt;/strong&gt; com dor isquêmica de repouso ou úlcera em paciente sem opção de revascularização, a &lt;strong&gt;síndrome dolorosa complexa regional&lt;/strong&gt; de membro inferior e a hiperidrose. O efeito imediato é vasodilatação, com &lt;strong&gt;elevação da temperatura cutânea&lt;/strong&gt; do membro, que é justamente o marcador objetivo de sucesso, ao lado da queda da resposta galvânica da pele.&lt;/p&gt;&lt;p&gt;O limite fundamental é conceitual: o bloqueio interrompe fibras &lt;strong&gt;simpáticas eferentes&lt;/strong&gt; e aferentes viscerais, não as vias somáticas. Portanto alivia a dor de origem isquêmica e a dor mantida pelo simpático, mas &lt;em&gt;não&lt;/em&gt; anestesia o dermátomo nem trata dor somática ou neuropática somática.&lt;/p&gt;&lt;p&gt;Complicações incluem punção vascular, injeção subaracnóidea ou peridural, lesão de ureter e, após neurólise, &lt;strong&gt;neuralgia genitofemoral&lt;/strong&gt; em até 10% dos casos, por difusão do agente neurolítico sobre o nervo que corre na face anterior do psoas.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o bloqueio não é somático e não abole a dor dos dermátomos; (C) a neuralgia genitofemoral é a complicação mais característica da neurólise lombar; (D) o sucesso se confirma pelo &lt;strong&gt;aumento&lt;/strong&gt; da temperatura cutânea, e não por sua ausência.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;gânglio estrelado&lt;/strong&gt;, ou cervicotorácico, resulta da fusão do gânglio cervical &lt;strong&gt;inferior&lt;/strong&gt; com o &lt;strong&gt;primeiro gânglio torácico&lt;/strong&gt; e repousa sobre o colo da &lt;strong&gt;primeira costela&lt;/strong&gt;, junto ao processo transverso de C7. Como o depósito de anestésico ao nível de C6 difunde caudalmente, a referência anatômica clássica na abordagem anterior é o &lt;strong&gt;tubérculo de Chassaignac&lt;/strong&gt;, o tubérculo anterior do processo transverso de &lt;strong&gt;C6&lt;/strong&gt;, com afastamento lateral do feixe carotídeo.&lt;/p&gt;&lt;p&gt;A vizinhança imediata explica as complicações:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Artéria vertebral&lt;/strong&gt;: injeção intra-arterial provoca convulsão e perda de consciência com volumes muito pequenos, mesmo abaixo de 1 mL — daí a obrigatoriedade de dose-teste e aspiração;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Nervo laríngeo recorrente&lt;/strong&gt;: rouquidão e sensação de globus, contraindicando bloqueio bilateral simultâneo;&lt;/li&gt;&lt;li&gt;Nervo frênico, pneumotórax (abordagens baixas), hematoma e injeção peridural ou subaracnóidea.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A &lt;strong&gt;síndrome de Horner&lt;/strong&gt; (ptose, miose, enoftalmia, anidrose facial) indica bloqueio das fibras destinadas à cabeça, mas &lt;em&gt;não&lt;/em&gt; assegura desnervação simpática do membro superior, que depende também das fibras que ascendem por T2-T3, os nervos de Kuntz. Confirma-se pelo aumento da temperatura da mão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a fusão é do gânglio cervical inferior com o primeiro torácico, sobre a primeira costela; (B) Horner não garante bloqueio do membro superior; (C) o tubérculo de Chassaignac está em C6, não em C1.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;gânglio estrelado&lt;/strong&gt;, ou cervicotorácico, resulta da fusão do gânglio cervical &lt;strong&gt;inferior&lt;/strong&gt; com o &lt;strong&gt;primeiro gânglio torácico&lt;/strong&gt; e repousa sobre o colo da &lt;strong&gt;primeira costela&lt;/strong&gt;, junto ao processo transverso de C7. Como o depósito de anestésico ao nível de C6 difunde caudalmente, a referência anatômica clássica na abordagem anterior é o &lt;strong&gt;tubérculo de Chassaignac&lt;/strong&gt;, o tubérculo anterior do processo transverso de &lt;strong&gt;C6&lt;/strong&gt;, com afastamento lateral do feixe carotídeo.&lt;/p&gt;&lt;p&gt;A vizinhança imediata explica as complicações:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Artéria vertebral&lt;/strong&gt;: injeção intra-arterial provoca convulsão e perda de consciência com volumes muito pequenos, mesmo abaixo de 1 mL, o que torna obrigatórias a dose-teste e a aspiração;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Nervo laríngeo recorrente&lt;/strong&gt;: rouquidão e sensação de globus, contraindicando bloqueio bilateral simultâneo;&lt;/li&gt;&lt;li&gt;Nervo frênico, pneumotórax (abordagens baixas), hematoma e injeção peridural ou subaracnóidea.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A &lt;strong&gt;síndrome de Horner&lt;/strong&gt; (ptose, miose, enoftalmia, anidrose facial) indica bloqueio das fibras destinadas à cabeça, mas &lt;em&gt;não&lt;/em&gt; assegura desnervação simpática do membro superior, que depende também das fibras que ascendem por T2-T3, os nervos de Kuntz. Confirma-se pelo aumento da temperatura da mão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a fusão é do gânglio cervical inferior com o primeiro torácico, sobre a primeira costela; (B) Horner não garante bloqueio do membro superior; (C) o tubérculo de Chassaignac está em C6, não em C1.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A fibromialgia é hoje entendida como estado de &lt;strong&gt;sensibilização central&lt;/strong&gt; — dor nociplástica —, com processamento anormal do estímulo, redução do limiar e falha das vias descendentes inibitórias. Não há inflamação, lesão estrutural ou marcador laboratorial: os exames servem para afastar diagnósticos alternativos, como hipotireoidismo, miopatia, doença reumatológica inflamatória e deficiências.&lt;/p&gt;&lt;p&gt;Os critérios evoluíram do exame de &lt;strong&gt;18 pontos dolorosos&lt;/strong&gt; (formulação de 1990) para instrumentos que quantificam a &lt;strong&gt;extensão&lt;/strong&gt; da dor por um índice de dor generalizada e a &lt;strong&gt;gravidade&lt;/strong&gt; dos sintomas associados — fadiga, sono não reparador e sintomas cognitivos —, exigindo persistência por pelo menos &lt;strong&gt;três meses&lt;/strong&gt; e dor em múltiplas regiões corporais. A contagem obrigatória de &lt;em&gt;tender points&lt;/em&gt; deixou de ser requisito.&lt;/p&gt;&lt;p&gt;A doença classifica-se em &lt;strong&gt;primária&lt;/strong&gt;, quando isolada, e &lt;strong&gt;secundária ou concomitante&lt;/strong&gt;, quando surge junto de artrite reumatoide, lúpus, espondiloartrites, hipotireoidismo ou dor crônica regional. Reconhecer a forma secundária importa porque tratar apenas a doença de base deixa o paciente sintomático.&lt;/p&gt;&lt;p&gt;O tratamento é multimodal, com exercício aeróbico gradual, higiene do sono, terapia cognitivo-comportamental e fármacos como amitriptilina, duloxetina e pregabalina; opioides não têm papel.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) não há marcador inflamatório nem alteração eletroneuromiográfica na fibromialgia; (B) a forma secundária é reconhecida e coexiste com a doença de base; (D) o número exato de regiões compõe um índice, e o diagnóstico não se sustenta em um único corte isolado.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A fibromialgia é hoje entendida como estado de &lt;strong&gt;sensibilização central&lt;/strong&gt; (dor nociplástica), com processamento anormal do estímulo, redução do limiar e falha das vias descendentes inibitórias. Não há inflamação, lesão estrutural ou marcador laboratorial: os exames servem para afastar diagnósticos alternativos, como hipotireoidismo, miopatia, doença reumatológica inflamatória e deficiências.&lt;/p&gt;&lt;p&gt;Os critérios evoluíram do exame de &lt;strong&gt;18 pontos dolorosos&lt;/strong&gt; (formulação de 1990) para instrumentos que quantificam a &lt;strong&gt;extensão&lt;/strong&gt; da dor por um índice de dor generalizada e a &lt;strong&gt;gravidade&lt;/strong&gt; dos sintomas associados (fadiga, sono não reparador e sintomas cognitivos), exigindo persistência por pelo menos &lt;strong&gt;três meses&lt;/strong&gt; e dor em múltiplas regiões corporais. A contagem obrigatória de &lt;em&gt;tender points&lt;/em&gt; deixou de ser requisito.&lt;/p&gt;&lt;p&gt;A doença classifica-se em &lt;strong&gt;primária&lt;/strong&gt;, quando isolada, e &lt;strong&gt;secundária ou concomitante&lt;/strong&gt;, quando surge junto de artrite reumatoide, lúpus, espondiloartrites, hipotireoidismo ou dor crônica regional. Reconhecer a forma secundária importa porque tratar apenas a doença de base deixa o paciente sintomático.&lt;/p&gt;&lt;p&gt;O tratamento é multimodal, com exercício aeróbico gradual, higiene do sono, terapia cognitivo-comportamental e fármacos como amitriptilina, duloxetina e pregabalina; opioides não têm papel.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) não há marcador inflamatório nem alteração eletroneuromiográfica na fibromialgia; (B) a forma secundária é reconhecida e coexiste com a doença de base; (D) o número exato de regiões compõe um índice, e o diagnóstico não se sustenta em um único corte isolado.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O princípio central do tratamento da dor oncológica persistente é a administração &lt;strong&gt;em horários fixos&lt;/strong&gt;, pelo relógio, e não sob demanda. A prescrição apenas por demanda deixa o paciente oscilar entre dor intensa e sedação, favorece o comportamento de antecipação ansiosa e, ao contrário do que sugere a intuição, costuma exigir &lt;em&gt;mais&lt;/em&gt; opioide ao longo do dia.&lt;/p&gt;&lt;p&gt;Sobre a dose regular acrescentam-se &lt;strong&gt;doses de resgate&lt;/strong&gt; para a dor irruptiva, calculadas em torno de &lt;strong&gt;10% a 15% da dose diária total&lt;/strong&gt; de opioide, na formulação de liberação imediata. O consumo repetido de resgates é o sinalizador para reajustar a dose de base.&lt;/p&gt;&lt;p&gt;A dor do câncer de pâncreas soma componente &lt;strong&gt;visceral&lt;/strong&gt; a componente &lt;strong&gt;neuropático&lt;/strong&gt; por invasão do plexo celíaco e de raízes — daí a queimação e os choques descritos. Adjuvantes são parte essencial do plano: gabapentinoides e antidepressivos duais ou tricíclicos para o componente neuropático, corticoide para compressão e dor óssea, bisfosfonatos em metástase óssea.&lt;/p&gt;&lt;p&gt;Nesse tumor especificamente, a &lt;strong&gt;neurólise do plexo celíaco&lt;/strong&gt; reduz a dor e o consumo de opioide, com melhor resultado quando realizada precocemente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o esquema exclusivamente por demanda deixa o paciente descoberto e não protege contra tolerância; (C) os adjuvantes são recomendados e somam-se ao opioide; (D) a doença metastática não contraindica a neurólise celíaca, que é justamente uma indicação consagrada.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O princípio central do tratamento da dor oncológica persistente é a administração &lt;strong&gt;em horários fixos&lt;/strong&gt;, pelo relógio, e não sob demanda. A prescrição apenas por demanda deixa o paciente oscilar entre dor intensa e sedação, favorece o comportamento de antecipação ansiosa e, ao contrário do que sugere a intuição, costuma exigir &lt;em&gt;mais&lt;/em&gt; opioide ao longo do dia.&lt;/p&gt;&lt;p&gt;Sobre a dose regular acrescentam-se &lt;strong&gt;doses de resgate&lt;/strong&gt; para a dor irruptiva, calculadas em torno de &lt;strong&gt;10% a 15% da dose diária total&lt;/strong&gt; de opioide, na formulação de liberação imediata. O consumo repetido de resgates é o sinalizador para reajustar a dose de base.&lt;/p&gt;&lt;p&gt;A dor do câncer de pâncreas soma componente &lt;strong&gt;visceral&lt;/strong&gt; a componente &lt;strong&gt;neuropático&lt;/strong&gt; por invasão do plexo celíaco e de raízes; daí a queimação e os choques descritos. Adjuvantes são parte essencial do plano: gabapentinoides e antidepressivos duais ou tricíclicos para o componente neuropático, corticoide para compressão e dor óssea, bisfosfonatos em metástase óssea.&lt;/p&gt;&lt;p&gt;Nesse tumor especificamente, a &lt;strong&gt;neurólise do plexo celíaco&lt;/strong&gt; reduz a dor e o consumo de opioide, com melhor resultado quando realizada precocemente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o esquema exclusivamente por demanda deixa o paciente descoberto e não protege contra tolerância; (C) os adjuvantes são recomendados e somam-se ao opioide; (D) a doença metastática não contraindica a neurólise celíaca, que é justamente uma indicação consagrada.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O plexo celíaco situa-se retroperitonealmente, ao redor do tronco celíaco, anteriormente ao corpo de T12-L1, e recebe as fibras dos nervos esplâncnicos. Sua neurólise interrompe a inervação &lt;strong&gt;simpática&lt;/strong&gt; das vísceras abdominais superiores, deixando a atividade &lt;strong&gt;parassimpática vagal&lt;/strong&gt; sem contraposição.&lt;/p&gt;&lt;p&gt;Daí decorrem as duas complicações mais comuns, ambas esperadas e geralmente transitórias:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Hipotensão ortostática&lt;/strong&gt;, por vasodilatação esplâncnica e sequestro de volume no leito visceral — tratada com hidratação prévia, repouso no leito por algumas horas e mudanças posturais graduais;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Diarreia&lt;/strong&gt;, por aumento relativo da motilidade intestinal, útil inclusive em pacientes com constipação induzida por opioide, mas capaz de causar desidratação.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Complicações raras, porém graves, incluem &lt;strong&gt;paraplegia&lt;/strong&gt; por lesão da artéria de Adamkiewicz ou vasoespasmo medular, pneumotórax, lesão renal, hematoma retroperitoneal e injeção intravascular ou peridural. Dor local transitória no dorso é frequente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) hipotensão postural e diarreia são efeitos previsíveis do bloqueio simpático, não sinais de injeção intravascular, que se manifestaria com toxicidade neurológica imediata; (C) a paraplegia é complicação rara, da ordem de fração de por cento, e não a mais comum; (D) o bloqueio não atinge a inervação simpática cardíaca, e o tratamento é volêmico e postural, eventualmente com vasopressor.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O plexo celíaco situa-se retroperitonealmente, ao redor do tronco celíaco, anteriormente ao corpo de T12-L1, e recebe as fibras dos nervos esplâncnicos. Sua neurólise interrompe a inervação &lt;strong&gt;simpática&lt;/strong&gt; das vísceras abdominais superiores, deixando a atividade &lt;strong&gt;parassimpática vagal&lt;/strong&gt; sem contraposição.&lt;/p&gt;&lt;p&gt;Daí decorrem as duas complicações mais comuns, ambas esperadas e geralmente transitórias:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Hipotensão ortostática&lt;/strong&gt;, por vasodilatação esplâncnica e sequestro de volume no leito visceral, tratada com hidratação prévia, repouso no leito por algumas horas e mudanças posturais graduais;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Diarreia&lt;/strong&gt;, por aumento relativo da motilidade intestinal, útil inclusive em pacientes com constipação induzida por opioide, mas capaz de causar desidratação.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Complicações raras, porém graves, incluem &lt;strong&gt;paraplegia&lt;/strong&gt; por lesão da artéria de Adamkiewicz ou vasoespasmo medular, pneumotórax, lesão renal, hematoma retroperitoneal e injeção intravascular ou peridural. Dor local transitória no dorso é frequente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) hipotensão postural e diarreia são efeitos previsíveis do bloqueio simpático, não sinais de injeção intravascular, que se manifestaria com toxicidade neurológica imediata; (C) a paraplegia é complicação rara, da ordem de fração de por cento, e não a mais comum; (D) o bloqueio não atinge a inervação simpática cardíaca, e o tratamento é volêmico e postural, eventualmente com vasopressor.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>&lt;p&gt;As &lt;strong&gt;cefaleias trigêmino-autonômicas&lt;/strong&gt; compartilham dor unilateral estritamente lateralizada, de forte intensidade, em território de primeira divisão do trigêmeo, acompanhada de sinais autonômicos &lt;em&gt;ipsilaterais&lt;/em&gt;: lacrimejamento, hiperemia conjuntival, congestão ou rinorreia, ptose e miose, edema palpebral. Distinguem-se sobretudo pela &lt;strong&gt;duração e frequência&lt;/strong&gt; das crises.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Cefaleia em salvas&lt;/strong&gt;: predomina em homens, crises de aproximadamente 15 a 180 minutos, de uma a oito por dia, agrupadas em períodos de semanas a meses; despertar noturno e desencadeamento por álcool são típicos, assim como a &lt;strong&gt;agitação psicomotora&lt;/strong&gt; — o paciente não consegue ficar parado, ao contrário do enxaquecoso, que busca imobilidade.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hemicrania paroxística&lt;/strong&gt;: crises &lt;em&gt;mais curtas&lt;/em&gt; (cerca de 2 a 30 minutos) e &lt;em&gt;mais frequentes&lt;/em&gt; (mais de cinco por dia), predomínio feminino e resposta &lt;strong&gt;absoluta à indometacina&lt;/strong&gt;, que serve inclusive como prova terapêutica.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;No tratamento abortivo da salva usam-se &lt;strong&gt;oxigênio a 100% em alto fluxo&lt;/strong&gt;, na ordem de 12 a 15 L/min sob máscara sem reinalação, e &lt;strong&gt;sumatriptano subcutâneo&lt;/strong&gt;. Na profilaxia, o verapamil é o pilar, com corticoide ou bloqueio do nervo occipital maior como ponte.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a enxaqueca cursa com crises de horas a dias, fotofobia e busca de imobilidade; (B) a hemicrania paroxística tem crises mais curtas e mais frequentes, e responde à indometacina, não ao propranolol; (C) a amitriptilina é profilática, sem qualquer efeito abortivo.&lt;/p&gt;</t>
+          <t>&lt;p&gt;As &lt;strong&gt;cefaleias trigêmino-autonômicas&lt;/strong&gt; compartilham dor unilateral estritamente lateralizada, de forte intensidade, em território de primeira divisão do trigêmeo, acompanhada de sinais autonômicos &lt;em&gt;ipsilaterais&lt;/em&gt;: lacrimejamento, hiperemia conjuntival, congestão ou rinorreia, ptose e miose, edema palpebral. Distinguem-se sobretudo pela &lt;strong&gt;duração e frequência&lt;/strong&gt; das crises.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Cefaleia em salvas&lt;/strong&gt;: predomina em homens, crises de aproximadamente 15 a 180 minutos, de uma a oito por dia, agrupadas em períodos de semanas a meses; despertar noturno e desencadeamento por álcool são típicos, assim como a &lt;strong&gt;agitação psicomotora&lt;/strong&gt;; o paciente não consegue ficar parado, ao contrário do enxaquecoso, que busca imobilidade.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hemicrania paroxística&lt;/strong&gt;: crises &lt;em&gt;mais curtas&lt;/em&gt; (cerca de 2 a 30 minutos) e &lt;em&gt;mais frequentes&lt;/em&gt; (mais de cinco por dia), predomínio feminino e resposta &lt;strong&gt;absoluta à indometacina&lt;/strong&gt;, que serve inclusive como prova terapêutica.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;No tratamento abortivo da salva usam-se &lt;strong&gt;oxigênio a 100% em alto fluxo&lt;/strong&gt;, na ordem de 12 a 15 L/min sob máscara sem reinalação, e &lt;strong&gt;sumatriptano subcutâneo&lt;/strong&gt;. Na profilaxia, o verapamil é o pilar, com corticoide ou bloqueio do nervo occipital maior como ponte.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a enxaqueca cursa com crises de horas a dias, fotofobia e busca de imobilidade; (B) a hemicrania paroxística tem crises mais curtas e mais frequentes, e responde à indometacina, não ao propranolol; (C) a amitriptilina é profilática, sem qualquer efeito abortivo.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;neuralgia do trigêmeo&lt;/strong&gt; caracteriza-se por dor paroxística, em choque ou punhalada, de segundos a até dois minutos, restrita a uma ou mais divisões do nervo — mais frequentemente &lt;strong&gt;maxilar (V2) e mandibular (V3)&lt;/strong&gt; —, deflagrada por estímulos triviais em &lt;em&gt;zonas de gatilho&lt;/em&gt;: mastigar, falar, escovar os dentes, tocar a face, vento frio. Entre as crises o exame é normal; déficit sensitivo objetivo ou acometimento bilateral levantam suspeita de causa secundária, como esclerose múltipla ou tumor de ângulo pontocerebelar. A causa clássica é a compressão neurovascular por alça da artéria cerebelar superior na zona de entrada da raiz.&lt;/p&gt;&lt;p&gt;O tratamento de primeira linha é a &lt;strong&gt;carbamazepina&lt;/strong&gt;, com a oxcarbazepina como alternativa de melhor tolerabilidade; ambas bloqueiam canais de sódio dependentes de voltagem e estabilizam a descarga ectópica. Falha ou intolerância abrem espaço a lamotrigina, baclofeno, procedimentos percutâneos no gânglio de Gasser, radiocirurgia e descompressão microvascular.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;neuralgia glossofaríngea&lt;/strong&gt; produz dor em orofaringe, base da língua, tonsila e ouvido, desencadeada por deglutição, bocejo ou tosse, podendo associar-se a bradicardia e síncope pela conexão com o vago. A &lt;strong&gt;neuralgia occipital&lt;/strong&gt; dá dor em choque na região occipital, com sensibilidade sobre o trajeto do nervo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a topografia descrita é trigeminal, não occipital; (C) a neuralgia glossofaríngea acomete a orofaringe e relaciona-se à deglutição e a bradiarritmias; (D) as zonas de gatilho são justamente um dos achados mais característicos da neuralgia trigeminal.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;neuralgia do trigêmeo&lt;/strong&gt; caracteriza-se por dor paroxística, em choque ou punhalada, de segundos a até dois minutos, restrita a uma ou mais divisões do nervo, mais frequentemente &lt;strong&gt;maxilar (V2) e mandibular (V3)&lt;/strong&gt;, deflagrada por estímulos triviais em &lt;em&gt;zonas de gatilho&lt;/em&gt;: mastigar, falar, escovar os dentes, tocar a face, vento frio. Entre as crises o exame é normal; déficit sensitivo objetivo ou acometimento bilateral levantam suspeita de causa secundária, como esclerose múltipla ou tumor de ângulo pontocerebelar. A causa clássica é a compressão neurovascular por alça da artéria cerebelar superior na zona de entrada da raiz.&lt;/p&gt;&lt;p&gt;O tratamento de primeira linha é a &lt;strong&gt;carbamazepina&lt;/strong&gt;, com a oxcarbazepina como alternativa de melhor tolerabilidade; ambas bloqueiam canais de sódio dependentes de voltagem e estabilizam a descarga ectópica. Falha ou intolerância abrem espaço a lamotrigina, baclofeno, procedimentos percutâneos no gânglio de Gasser, radiocirurgia e descompressão microvascular.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;neuralgia glossofaríngea&lt;/strong&gt; produz dor em orofaringe, base da língua, tonsila e ouvido, desencadeada por deglutição, bocejo ou tosse, podendo associar-se a bradicardia e síncope pela conexão com o vago. A &lt;strong&gt;neuralgia occipital&lt;/strong&gt; dá dor em choque na região occipital, com sensibilidade sobre o trajeto do nervo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a topografia descrita é trigeminal, não occipital; (C) a neuralgia glossofaríngea acomete a orofaringe e relaciona-se à deglutição e a bradiarritmias; (D) as zonas de gatilho são justamente um dos achados mais característicos da neuralgia trigeminal.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A orientação das superfícies articulares zigapofisárias determina que movimentos cada segmento permite — e, na prática intervencionista, o ângulo de entrada da agulha.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Cervical&lt;/strong&gt;: superfícies inclinadas cerca de 45 graus em relação ao plano transverso, quase coronais. Permitem flexão, extensão, rotação e inclinação lateral amplas, o que faz da coluna cervical o segmento mais móvel — e a dor facetária cervical é causa comum de cervicalgia e cefaleia cervicogênica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Torácica&lt;/strong&gt;: orientação próxima do plano &lt;strong&gt;coronal&lt;/strong&gt;, favorecendo rotação e inclinação lateral, com flexão e extensão restritas também pelo gradil costal.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Lombar&lt;/strong&gt;: orientação predominantemente &lt;strong&gt;sagital&lt;/strong&gt; nos níveis superiores, tornando-se mais oblíqua em direção a L5-S1. Essa disposição favorece &lt;strong&gt;flexão e extensão&lt;/strong&gt; e &lt;em&gt;limita&lt;/em&gt; a rotação axial — motivo pelo qual cargas rotacionais forçadas lesam a faceta e o disco lombares.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Cada articulação recebe inervação dupla, pelos &lt;strong&gt;ramos mediais&lt;/strong&gt; do ramo dorsal do nível correspondente e do nível acima, razão pela qual o bloqueio diagnóstico exige alvo em dois ramos por articulação. Todo procedimento facetário requer orientação fluoroscópica ou tomográfica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) as facetas cervicais são oblíquas, próximas do plano coronal, e a dor facetária cervical é frequente; (B) as torácicas são coronais e permitem sobretudo rotação, não o inverso; (C) as lombares não são coronais, e imagem é sempre necessária.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A orientação das superfícies articulares zigapofisárias determina que movimentos cada segmento permite e, na prática intervencionista, o ângulo de entrada da agulha.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Cervical&lt;/strong&gt;: superfícies inclinadas cerca de 45 graus em relação ao plano transverso, quase coronais. Permitem flexão, extensão, rotação e inclinação lateral amplas, o que faz da coluna cervical o segmento mais móvel; a dor facetária cervical é causa comum de cervicalgia e cefaleia cervicogênica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Torácica&lt;/strong&gt;: orientação próxima do plano &lt;strong&gt;coronal&lt;/strong&gt;, favorecendo rotação e inclinação lateral, com flexão e extensão restritas também pelo gradil costal.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Lombar&lt;/strong&gt;: orientação predominantemente &lt;strong&gt;sagital&lt;/strong&gt; nos níveis superiores, tornando-se mais oblíqua em direção a L5-S1. Essa disposição favorece &lt;strong&gt;flexão e extensão&lt;/strong&gt; e &lt;em&gt;limita&lt;/em&gt; a rotação axial, motivo pelo qual cargas rotacionais forçadas lesam a faceta e o disco lombares.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Cada articulação recebe inervação dupla, pelos &lt;strong&gt;ramos mediais&lt;/strong&gt; do ramo dorsal do nível correspondente e do nível acima, razão pela qual o bloqueio diagnóstico exige alvo em dois ramos por articulação. Todo procedimento facetário requer orientação fluoroscópica ou tomográfica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) as facetas cervicais são oblíquas, próximas do plano coronal, e a dor facetária cervical é frequente; (B) as torácicas são coronais e permitem sobretudo rotação, não o inverso; (C) as lombares não são coronais, e imagem é sempre necessária.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;estimulação medular&lt;/strong&gt; aplica corrente a eletrodos posicionados no espaço peridural posterior, ativando as fibras &lt;strong&gt;A-beta&lt;/strong&gt; dos funículos posteriores. A explicação clássica é a &lt;em&gt;teoria das comportas&lt;/em&gt;: a aferência de grosso calibre excita interneurônios inibitórios da substância gelatinosa e reduz a transmissão nociceptiva dos neurônios de segunda ordem. Somam-se mecanismos supraespinhais, liberação local de ácido gama-aminobutírico e acetilcolina e, na dor isquêmica, modulação simpática com melhora do balanço entre oferta e consumo de oxigênio.&lt;/p&gt;&lt;p&gt;Indicações mais consolidadas:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Síndrome dolorosa pós-laminectomia&lt;/strong&gt; com dor neuropática de membro predominando sobre a dor axial;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Síndrome dolorosa complexa regional&lt;/strong&gt;;&lt;/li&gt;&lt;li&gt;Neuropatia diabética dolorosa refratária;&lt;/li&gt;&lt;li&gt;Angina refratária e doença arterial periférica inoperável.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;São condições para o implante: falha do tratamento conservador bem conduzido, ausência de lesão cirurgicamente corrigível, expectativa realista e &lt;strong&gt;avaliação psicológica&lt;/strong&gt; — depressão grave não tratada, dependência química ativa e ganho secundário predizem mau resultado. O &lt;strong&gt;teste com eletrodo temporário&lt;/strong&gt;, por alguns dias, é etapa obrigatória: só se implanta o gerador definitivo com resposta significativa, tipicamente redução de pelo menos metade da dor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a fase de teste é justamente o principal filtro de seleção; (C) não há bloqueio de condução nem anestesia do dermátomo, mas modulação; (D) transtorno psiquiátrico grave não tratado é contraindicação relativa, não fator favorável.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;estimulação medular&lt;/strong&gt; aplica corrente a eletrodos posicionados no espaço peridural posterior, ativando as fibras &lt;strong&gt;A-beta&lt;/strong&gt; dos funículos posteriores. A explicação clássica é a &lt;em&gt;teoria das comportas&lt;/em&gt;: a aferência de grosso calibre excita interneurônios inibitórios da substância gelatinosa e reduz a transmissão nociceptiva dos neurônios de segunda ordem. Somam-se mecanismos supraespinhais, liberação local de ácido gama-aminobutírico e acetilcolina e, na dor isquêmica, modulação simpática com melhora do balanço entre oferta e consumo de oxigênio.&lt;/p&gt;&lt;p&gt;Indicações mais consolidadas:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Síndrome dolorosa pós-laminectomia&lt;/strong&gt; com dor neuropática de membro predominando sobre a dor axial;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Síndrome dolorosa complexa regional&lt;/strong&gt;;&lt;/li&gt;&lt;li&gt;Neuropatia diabética dolorosa refratária;&lt;/li&gt;&lt;li&gt;Angina refratária e doença arterial periférica inoperável.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;São condições para o implante: falha do tratamento conservador bem conduzido, ausência de lesão cirurgicamente corrigível, expectativa realista e &lt;strong&gt;avaliação psicológica&lt;/strong&gt;: depressão grave não tratada, dependência química ativa e ganho secundário predizem mau resultado. O &lt;strong&gt;teste com eletrodo temporário&lt;/strong&gt;, por alguns dias, é etapa obrigatória: só se implanta o gerador definitivo com resposta significativa, tipicamente redução de pelo menos metade da dor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a fase de teste é justamente o principal filtro de seleção; (C) não há bloqueio de condução nem anestesia do dermátomo, mas modulação; (D) transtorno psiquiátrico grave não tratado é contraindicação relativa, não fator favorável.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;codeína&lt;/strong&gt; tem afinidade muito baixa pelo receptor mu: sua analgesia depende quase inteiramente da &lt;strong&gt;O-desmetilação em morfina&lt;/strong&gt;, reação catalisada pelo &lt;strong&gt;CYP2D6&lt;/strong&gt;. Apenas cerca de 5% a 10% da dose é convertida, e essa conversão é geneticamente variável.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Metabolizadores lentos&lt;/strong&gt; — em torno de 7% a 10% dos indivíduos de ascendência europeia — produzem pouca ou nenhuma morfina e experimentam &lt;strong&gt;falha analgésica&lt;/strong&gt;, tipicamente sem os efeitos adversos opioides, exatamente o quadro descrito;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Metabolizadores ultrarrápidos&lt;/strong&gt;, por duplicação do gene e mais prevalentes em algumas populações do norte da África e do Oriente Médio, geram picos elevados de morfina e correm risco de &lt;strong&gt;sedação profunda e depressão respiratória&lt;/strong&gt;. É a base dos relatos de óbito em crianças após amigdalectomia e em lactentes amamentados por mães em uso de codeína, que motivaram restrições regulatórias em pediatria.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Inibidores potentes do CYP2D6, como fluoxetina, paroxetina e bupropiona, reproduzem farmacologicamente o fenótipo lento e anulam o efeito da codeína — e também do &lt;strong&gt;tramadol&lt;/strong&gt;, que compartilha essa dependência para gerar o metabólito M1.&lt;/p&gt;&lt;p&gt;Diante da falha, a conduta é trocar por analgésico que não dependa dessa via, e não escalonar a codeína.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) não há tolerância cruzada entre anti-inflamatórios e opioides que explique o quadro; (C) a codeína é um agonista mu fraco e não descarta dor orgânica; (D) o metabolizador ultrarrápido tem efeito &lt;em&gt;exagerado&lt;/em&gt;, e o metabolismo é hepático, não pré-absortivo.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;codeína&lt;/strong&gt; tem afinidade muito baixa pelo receptor mu: sua analgesia depende quase inteiramente da &lt;strong&gt;O-desmetilação em morfina&lt;/strong&gt;, reação catalisada pelo &lt;strong&gt;CYP2D6&lt;/strong&gt;. Apenas cerca de 5% a 10% da dose é convertida, e essa conversão é geneticamente variável.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Metabolizadores lentos&lt;/strong&gt; (em torno de 7% a 10% dos indivíduos de ascendência europeia) produzem pouca ou nenhuma morfina e experimentam &lt;strong&gt;falha analgésica&lt;/strong&gt;, tipicamente sem os efeitos adversos opioides, exatamente o quadro descrito;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Metabolizadores ultrarrápidos&lt;/strong&gt;, por duplicação do gene e mais prevalentes em algumas populações do norte da África e do Oriente Médio, geram picos elevados de morfina e correm risco de &lt;strong&gt;sedação profunda e depressão respiratória&lt;/strong&gt;. É a base dos relatos de óbito em crianças após amigdalectomia e em lactentes amamentados por mães em uso de codeína, que motivaram restrições regulatórias em pediatria.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Inibidores potentes do CYP2D6, como fluoxetina, paroxetina e bupropiona, reproduzem farmacologicamente o fenótipo lento e anulam o efeito da codeína, e também do &lt;strong&gt;tramadol&lt;/strong&gt;, que compartilha essa dependência para gerar o metabólito M1.&lt;/p&gt;&lt;p&gt;Diante da falha, a conduta é trocar por analgésico que não dependa dessa via, e não escalonar a codeína.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) não há tolerância cruzada entre anti-inflamatórios e opioides que explique o quadro; (C) a codeína é um agonista mu fraco e não descarta dor orgânica; (D) o metabolizador ultrarrápido tem efeito &lt;em&gt;exagerado&lt;/em&gt;, e o metabolismo é hepático, não pré-absortivo.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A meperidina sofre N-desmetilação hepática e origina a &lt;strong&gt;normeperidina&lt;/strong&gt;, metabólito com metade da potência analgésica, mas com propriedades &lt;strong&gt;excitatórias&lt;/strong&gt; sobre o sistema nervoso central e meia-vida de eliminação muito mais longa que a do fármaco original — da ordem de &lt;strong&gt;15 a 20 horas&lt;/strong&gt;, contra cerca de 3 horas da meperidina. A eliminação é &lt;strong&gt;renal&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Em doses repetidas, idade avançada e sobretudo &lt;strong&gt;disfunção renal&lt;/strong&gt;, a normeperidina acumula-se e produz um espectro característico: ansiedade, tremor, abalos musculares, &lt;strong&gt;mioclonias multifocais&lt;/strong&gt;, hiper-reflexia e, no extremo, &lt;strong&gt;convulsões generalizadas&lt;/strong&gt;. É um quadro de excitação, não de depressão.&lt;/p&gt;&lt;p&gt;Ponto crítico de conduta: a &lt;strong&gt;naloxona não reverte&lt;/strong&gt; a neurotoxicidade — pode até agravá-la, ao remover o efeito depressor da meperidina sobre o córtex e desmascarar a atividade convulsivante do metabólito. O manejo consiste em suspender a meperidina, hidratar, tratar crises com benzodiazepínico e trocar por outro opioide.&lt;/p&gt;&lt;p&gt;Por essas razões, a meperidina não é opioide adequado para uso continuado, tendo espaço restrito e em dose baixa no tratamento de calafrios pós-anestésicos, por ação em receptores kappa e alfa-2.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o efeito é do metabólito e não responde à naloxona, que pode piorá-lo; (B) a meperidina tem metabólito ativo relevante, e a função renal é determinante; (D) não há abstinência com o opioide ainda em uso, e a suspensão isolada não explica o mecanismo do quadro.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A meperidina sofre N-desmetilação hepática e origina a &lt;strong&gt;normeperidina&lt;/strong&gt;, metabólito com metade da potência analgésica, mas com propriedades &lt;strong&gt;excitatórias&lt;/strong&gt; sobre o sistema nervoso central e meia-vida de eliminação muito mais longa que a do fármaco original, da ordem de &lt;strong&gt;15 a 20 horas&lt;/strong&gt;, contra cerca de 3 horas da meperidina. A eliminação é &lt;strong&gt;renal&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Em doses repetidas, idade avançada e sobretudo &lt;strong&gt;disfunção renal&lt;/strong&gt;, a normeperidina acumula-se e produz um espectro característico: ansiedade, tremor, abalos musculares, &lt;strong&gt;mioclonias multifocais&lt;/strong&gt;, hiper-reflexia e, no extremo, &lt;strong&gt;convulsões generalizadas&lt;/strong&gt;. É um quadro de excitação, não de depressão.&lt;/p&gt;&lt;p&gt;Ponto crítico de conduta: a &lt;strong&gt;naloxona não reverte&lt;/strong&gt; a neurotoxicidade; pode até agravá-la, ao remover o efeito depressor da meperidina sobre o córtex e desmascarar a atividade convulsivante do metabólito. O manejo consiste em suspender a meperidina, hidratar, tratar crises com benzodiazepínico e trocar por outro opioide.&lt;/p&gt;&lt;p&gt;Por essas razões, a meperidina não é opioide adequado para uso continuado, tendo espaço restrito e em dose baixa no tratamento de calafrios pós-anestésicos, por ação em receptores kappa e alfa-2.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o efeito é do metabólito e não responde à naloxona, que pode piorá-lo; (B) a meperidina tem metabólito ativo relevante, e a função renal é determinante; (D) não há abstinência com o opioide ainda em uso, e a suspensão isolada não explica o mecanismo do quadro.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;tramadol&lt;/strong&gt; tem mecanismo duplo, o que explica tanto sua utilidade quanto seus riscos:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Componente &lt;strong&gt;opioide&lt;/strong&gt;: o fármaco original tem baixa afinidade pelo receptor mu; a maior parte do efeito vem do metabólito &lt;strong&gt;M1&lt;/strong&gt; (O-desmetiltramadol), gerado pelo &lt;strong&gt;CYP2D6&lt;/strong&gt; — daí a analgesia falhar em metabolizadores lentos e em usuários de inibidores potentes dessa enzima, como fluoxetina e paroxetina;&lt;/li&gt;&lt;li&gt;Componente &lt;strong&gt;monoaminérgico&lt;/strong&gt;: inibe a recaptação de &lt;strong&gt;noradrenalina e serotonina&lt;/strong&gt;, potencializando as vias descendentes inibitórias — mecanismo que o torna útil na dor com componente neuropático.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A dose máxima habitual é de cerca de &lt;strong&gt;400 mg ao dia&lt;/strong&gt;, reduzida para aproximadamente 300 mg em idosos e ajustada na insuficiência renal ou hepática. Ultrapassar esse teto não aumenta a analgesia e eleva o risco de &lt;strong&gt;convulsão&lt;/strong&gt;, que ocorre mesmo em doses terapêuticas em pacientes predispostos ou em uso de fármacos que baixam o limiar convulsivo.&lt;/p&gt;&lt;p&gt;A combinação com antidepressivos serotoninérgicos, como no caso, exige cautela pelo risco de &lt;strong&gt;síndrome serotoninérgica&lt;/strong&gt; — agitação, clônus, hiper-reflexia, hipertermia e instabilidade autonômica. A naloxona reverte apenas o componente opioide.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o efeito não é apenas opioide e a potência é bem inferior à da morfina; (B) existe teto de dose definido; (C) a interação serotoninérgica é justamente um dos riscos característicos do fármaco.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;tramadol&lt;/strong&gt; tem mecanismo duplo, o que explica tanto sua utilidade quanto seus riscos:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Componente &lt;strong&gt;opioide&lt;/strong&gt;: o fármaco original tem baixa afinidade pelo receptor mu; a maior parte do efeito vem do metabólito &lt;strong&gt;M1&lt;/strong&gt; (O-desmetiltramadol), gerado pelo &lt;strong&gt;CYP2D6&lt;/strong&gt;, daí a analgesia falhar em metabolizadores lentos e em usuários de inibidores potentes dessa enzima, como fluoxetina e paroxetina;&lt;/li&gt;&lt;li&gt;Componente &lt;strong&gt;monoaminérgico&lt;/strong&gt;: inibe a recaptação de &lt;strong&gt;noradrenalina e serotonina&lt;/strong&gt;, potencializando as vias descendentes inibitórias, mecanismo que o torna útil na dor com componente neuropático.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A dose máxima habitual é de cerca de &lt;strong&gt;400 mg ao dia&lt;/strong&gt;, reduzida para aproximadamente 300 mg em idosos e ajustada na insuficiência renal ou hepática. Ultrapassar esse teto não aumenta a analgesia e eleva o risco de &lt;strong&gt;convulsão&lt;/strong&gt;, que ocorre mesmo em doses terapêuticas em pacientes predispostos ou em uso de fármacos que baixam o limiar convulsivo.&lt;/p&gt;&lt;p&gt;A combinação com antidepressivos serotoninérgicos, como no caso, exige cautela pelo risco de &lt;strong&gt;síndrome serotoninérgica&lt;/strong&gt;: agitação, clônus, hiper-reflexia, hipertermia e instabilidade autonômica. A naloxona reverte apenas o componente opioide.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o efeito não é apenas opioide e a potência é bem inferior à da morfina; (B) existe teto de dose definido; (C) a interação serotoninérgica é justamente um dos riscos característicos do fármaco.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;hipotensão intracraniana espontânea&lt;/strong&gt; resulta de perda de líquido cefalorraquidiano por fístula habitualmente &lt;strong&gt;espinhal&lt;/strong&gt; — divertículo meníngeo roto, espícula óssea ou disco calcificado que rasga a dura, ou fístula liquórico-venosa —, frequentemente em pacientes com hiperfrouxidão ligamentar. Compartilha com a &lt;strong&gt;cefaleia pós-punção dural&lt;/strong&gt; a mesma fisiopatologia: queda do volume liquórico, tração de estruturas sensíveis à dor e vasodilatação venosa compensatória.&lt;/p&gt;&lt;p&gt;Daí a semiologia idêntica: cefaleia &lt;strong&gt;ortostática&lt;/strong&gt;, que aparece ou piora em minutos na posição ereta e alivia em decúbito, acompanhada de rigidez de nuca, zumbido, hipoacusia, fotofobia, náusea e, ocasionalmente, diplopia por estiramento do abducente. A diferença é apenas o antecedente: uma segue a violação dural, a outra ocorre sem qualquer punção.&lt;/p&gt;&lt;p&gt;Na investigação, a ressonância mostra achados típicos como &lt;strong&gt;realce paquimeníngeo difuso&lt;/strong&gt;, ingurgitamento venoso, coleções subdurais e descenso das estruturas encefálicas; mielotomografia ou mielorressonância localizam o vazamento.&lt;/p&gt;&lt;p&gt;O tratamento inicia-se com repouso, hidratação, cafeína e analgesia; na falha, o &lt;strong&gt;tampão sanguíneo peridural&lt;/strong&gt; é a intervenção de escolha, eventualmente repetido ou dirigido ao nível da fístula, restando correção cirúrgica para casos refratários.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a fístula liquórica espontânea existe sem punção, e a hipertensão intracraniana idiopática cursa com cefaleia que piora em decúbito e papiledema; (C) a característica é piorar em pé, não deitado; (D) retirar líquido cefalorraquidiano agravaria a hipotensão liquórica.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;hipotensão intracraniana espontânea&lt;/strong&gt; resulta de perda de líquido cefalorraquidiano por fístula habitualmente &lt;strong&gt;espinhal&lt;/strong&gt; (divertículo meníngeo roto, espícula óssea ou disco calcificado que rasga a dura, ou fístula liquórico-venosa), frequentemente em pacientes com hiperfrouxidão ligamentar. Compartilha com a &lt;strong&gt;cefaleia pós-punção dural&lt;/strong&gt; a mesma fisiopatologia: queda do volume liquórico, tração de estruturas sensíveis à dor e vasodilatação venosa compensatória.&lt;/p&gt;&lt;p&gt;Daí a semiologia idêntica: cefaleia &lt;strong&gt;ortostática&lt;/strong&gt;, que aparece ou piora em minutos na posição ereta e alivia em decúbito, acompanhada de rigidez de nuca, zumbido, hipoacusia, fotofobia, náusea e, ocasionalmente, diplopia por estiramento do abducente. A diferença é apenas o antecedente: uma segue a violação dural, a outra ocorre sem qualquer punção.&lt;/p&gt;&lt;p&gt;Na investigação, a ressonância mostra achados típicos como &lt;strong&gt;realce paquimeníngeo difuso&lt;/strong&gt;, ingurgitamento venoso, coleções subdurais e descenso das estruturas encefálicas; mielotomografia ou mielorressonância localizam o vazamento.&lt;/p&gt;&lt;p&gt;O tratamento inicia-se com repouso, hidratação, cafeína e analgesia; na falha, o &lt;strong&gt;tampão sanguíneo peridural&lt;/strong&gt; é a intervenção de escolha, eventualmente repetido ou dirigido ao nível da fístula, restando correção cirúrgica para casos refratários.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a fístula liquórica espontânea existe sem punção, e a hipertensão intracraniana idiopática cursa com cefaleia que piora em decúbito e papiledema; (C) a característica é piorar em pé, não deitado; (D) retirar líquido cefalorraquidiano agravaria a hipotensão liquórica.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
@@ -11409,7 +11409,7 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A crise vaso-oclusiva decorre da polimerização da hemoglobina S em condições de hipóxia, acidose, desidratação, febre ou frio, com falcização, adesão endotelial e obstrução da microcirculação — produzindo isquemia óssea e dor de forte intensidade, sobretudo em ossos longos, dorso e tórax.&lt;/p&gt;&lt;p&gt;Os pilares do tratamento são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Analgesia precoce e titulada&lt;/strong&gt;: opioide parenteral iniciado nos primeiros minutos, frequentemente por analgesia controlada pelo paciente, associado a dipirona ou anti-inflamatório quando não há contraindicação renal. O retardo na analgesia é falha assistencial frequente e prolonga a crise;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hidratação&lt;/strong&gt; adequada para corrigir o déficit, sem sobrecarga — o excesso de volume favorece edema pulmonar e síndrome torácica aguda;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Oxigênio&lt;/strong&gt; quando há hipoxemia, além de aquecimento e tratamento de fatores desencadeantes;&lt;/li&gt;&lt;li&gt;Vigilância ativa para &lt;strong&gt;síndrome torácica aguda&lt;/strong&gt; — novo infiltrado com febre, dor torácica, hipoxemia —, principal causa de morte, cujo tratamento inclui antibiótico, espirometria de incentivo e transfusão.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A &lt;strong&gt;meperidina deve ser evitada&lt;/strong&gt; no uso repetido pelo acúmulo de normeperidina e risco de convulsões, particularmente relevante nesses pacientes, que costumam ter crises recorrentes e podem apresentar disfunção renal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a meperidina é justamente o opioide a evitar; (C) o receio infundado de dependência é causa clássica de subtratamento da dor falciforme; (D) hidratação excessiva é prejudicial e não substitui a analgesia.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A crise vaso-oclusiva decorre da polimerização da hemoglobina S em condições de hipóxia, acidose, desidratação, febre ou frio, com falcização, adesão endotelial e obstrução da microcirculação, o que produz isquemia óssea e dor de forte intensidade, sobretudo em ossos longos, dorso e tórax.&lt;/p&gt;&lt;p&gt;Os pilares do tratamento são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Analgesia precoce e titulada&lt;/strong&gt;: opioide parenteral iniciado nos primeiros minutos, frequentemente por analgesia controlada pelo paciente, associado a dipirona ou anti-inflamatório quando não há contraindicação renal. O retardo na analgesia é falha assistencial frequente e prolonga a crise;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hidratação&lt;/strong&gt; adequada para corrigir o déficit, sem sobrecarga, pois o excesso de volume favorece edema pulmonar e síndrome torácica aguda;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Oxigênio&lt;/strong&gt; quando há hipoxemia, além de aquecimento e tratamento de fatores desencadeantes;&lt;/li&gt;&lt;li&gt;Vigilância ativa para &lt;strong&gt;síndrome torácica aguda&lt;/strong&gt; (novo infiltrado com febre, dor torácica, hipoxemia), principal causa de morte, cujo tratamento inclui antibiótico, espirometria de incentivo e transfusão.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A &lt;strong&gt;meperidina deve ser evitada&lt;/strong&gt; no uso repetido pelo acúmulo de normeperidina e risco de convulsões, particularmente relevante nesses pacientes, que costumam ter crises recorrentes e podem apresentar disfunção renal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a meperidina é justamente o opioide a evitar; (C) o receio infundado de dependência é causa clássica de subtratamento da dor falciforme; (D) hidratação excessiva é prejudicial e não substitui a analgesia.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;vasoespasmo&lt;/strong&gt; após hemorragia subaracnóidea é uma vasculopatia de grandes e pequenos vasos deflagrada pelos produtos de degradação da hemoglobina no espaço subaracnóideo. Sua janela temporal é bem definida: início por volta do &lt;strong&gt;terceiro ao quarto dia&lt;/strong&gt;, pico entre o &lt;strong&gt;sétimo e o décimo dia&lt;/strong&gt; e resolução até cerca do &lt;strong&gt;décimo quarto ao vigésimo primeiro dia&lt;/strong&gt;. Déficit neurológico novo nesse intervalo, sem ressangramento, hidrocefalia, convulsão ou distúrbio metabólico, é isquemia cerebral tardia até prova em contrário.&lt;/p&gt;&lt;p&gt;A detecção combina exame neurológico seriado, &lt;strong&gt;doppler transcraniano&lt;/strong&gt; — velocidades médias crescentes na cerebral média, com índice de Lindegaard elevado diferenciando espasmo de hiperemia — e angiotomografia ou angiografia digital.&lt;/p&gt;&lt;p&gt;O manejo apoia-se em:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Nimodipino oral&lt;/strong&gt;, 60 mg a cada 4 horas por 21 dias — melhora o desfecho neurológico, embora não desfaça o espasmo angiográfico;&lt;/li&gt;&lt;li&gt;Manutenção de &lt;strong&gt;euvolemia&lt;/strong&gt; e &lt;strong&gt;hipertensão induzida&lt;/strong&gt; quando há déficit, estratégia que substituiu a terapia dos três H;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Terapia endovascular&lt;/strong&gt; nos casos refratários: angioplastia com balão em espasmo proximal e infusão intra-arterial de vasodilatador, como verapamil ou nicardipino.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) as primeiras 24 horas são o período de ressangramento, não de vasoespasmo; (B) o nimodipino é usado por via oral, e a via venosa acarreta hipotensão significativa; (C) a hipotensão agrava a isquemia — busca-se elevar a pressão de perfusão.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;vasoespasmo&lt;/strong&gt; após hemorragia subaracnóidea é uma vasculopatia de grandes e pequenos vasos deflagrada pelos produtos de degradação da hemoglobina no espaço subaracnóideo. Sua janela temporal é bem definida: início por volta do &lt;strong&gt;terceiro ao quarto dia&lt;/strong&gt;, pico entre o &lt;strong&gt;sétimo e o décimo dia&lt;/strong&gt; e resolução até cerca do &lt;strong&gt;décimo quarto ao vigésimo primeiro dia&lt;/strong&gt;. Déficit neurológico novo nesse intervalo, sem ressangramento, hidrocefalia, convulsão ou distúrbio metabólico, é isquemia cerebral tardia até prova em contrário.&lt;/p&gt;&lt;p&gt;A detecção combina exame neurológico seriado, &lt;strong&gt;doppler transcraniano&lt;/strong&gt; (velocidades médias crescentes na cerebral média, com índice de Lindegaard elevado diferenciando espasmo de hiperemia) e angiotomografia ou angiografia digital.&lt;/p&gt;&lt;p&gt;O manejo apoia-se em:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Nimodipino oral&lt;/strong&gt;, 60 mg a cada 4 horas por 21 dias: melhora o desfecho neurológico, embora não desfaça o espasmo angiográfico;&lt;/li&gt;&lt;li&gt;Manutenção de &lt;strong&gt;euvolemia&lt;/strong&gt; e &lt;strong&gt;hipertensão induzida&lt;/strong&gt; quando há déficit, estratégia que substituiu a terapia dos três H;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Terapia endovascular&lt;/strong&gt; nos casos refratários: angioplastia com balão em espasmo proximal e infusão intra-arterial de vasodilatador, como verapamil ou nicardipino.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) as primeiras 24 horas são o período de ressangramento, não de vasoespasmo; (B) o nimodipino é usado por via oral, e a via venosa acarreta hipotensão significativa; (C) a hipotensão agrava a isquemia; busca-se elevar a pressão de perfusão.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Diante de coma inexplicado, a primeira bifurcação é entre causa &lt;strong&gt;estrutural&lt;/strong&gt; e causa &lt;strong&gt;tóxico-metabólica&lt;/strong&gt;, e o exame neurológico responde bem a essa pergunta. Lesões estruturais tendem a produzir &lt;strong&gt;assimetria&lt;/strong&gt; — desvio ocular, anisocoria, hemiparesia, postura de decorticação ou descerebração — e alteração dos &lt;strong&gt;reflexos de tronco&lt;/strong&gt;. Quadros metabólicos costumam dar depressão &lt;strong&gt;simétrica e difusa&lt;/strong&gt;, com pupilas pequenas e reagentes e reflexos de tronco preservados, exatamente como descrito.&lt;/p&gt;&lt;p&gt;Na terapia intensiva neurocirúrgica, as causas mais frequentes são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sedativos e opioides residuais&lt;/strong&gt;, acumulados por disfunção renal ou hepática;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Distúrbios do sódio&lt;/strong&gt;: hiponatremia por secreção inapropriada de hormônio antidiurético ou síndrome perdedora de sal cerebral — no caso, 118 mEq/L é valor plenamente capaz de causar coma e convulsão;&lt;/li&gt;&lt;li&gt;Hipoglicemia, uremia, encefalopatia hepática, hipercapnia, hipotireoidismo, sepse;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Estado de mal epiléptico não convulsivo&lt;/strong&gt;, que exige eletroencefalograma para diagnóstico, pois pode não haver qualquer manifestação motora.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A correção da hiponatremia crônica deve ser &lt;strong&gt;gradual&lt;/strong&gt;, evitando elevação superior a cerca de 8 a 10 mEq/L em 24 horas, pelo risco de desmielinização osmótica; salina hipertônica em bolus se reserva a sintomas neurológicos graves, para elevação inicial pequena e controlada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o padrão descrito afasta, e não confirma, lesão de tronco; (B) 118 mEq/L causa coma, e a correção rápida é perigosa; (D) o estado de mal não convulsivo só se exclui com eletroencefalograma.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Diante de coma inexplicado, a primeira bifurcação é entre causa &lt;strong&gt;estrutural&lt;/strong&gt; e causa &lt;strong&gt;tóxico-metabólica&lt;/strong&gt;, e o exame neurológico responde bem a essa pergunta. Lesões estruturais tendem a produzir &lt;strong&gt;assimetria&lt;/strong&gt; (desvio ocular, anisocoria, hemiparesia, postura de decorticação ou descerebração) e alteração dos &lt;strong&gt;reflexos de tronco&lt;/strong&gt;. Quadros metabólicos costumam dar depressão &lt;strong&gt;simétrica e difusa&lt;/strong&gt;, com pupilas pequenas e reagentes e reflexos de tronco preservados, exatamente como descrito.&lt;/p&gt;&lt;p&gt;Na terapia intensiva neurocirúrgica, as causas mais frequentes são:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sedativos e opioides residuais&lt;/strong&gt;, acumulados por disfunção renal ou hepática;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Distúrbios do sódio&lt;/strong&gt;: hiponatremia por secreção inapropriada de hormônio antidiurético ou síndrome perdedora de sal cerebral; no caso, 118 mEq/L é valor plenamente capaz de causar coma e convulsão;&lt;/li&gt;&lt;li&gt;Hipoglicemia, uremia, encefalopatia hepática, hipercapnia, hipotireoidismo, sepse;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Estado de mal epiléptico não convulsivo&lt;/strong&gt;, que exige eletroencefalograma para diagnóstico, pois pode não haver qualquer manifestação motora.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A correção da hiponatremia crônica deve ser &lt;strong&gt;gradual&lt;/strong&gt;, evitando elevação superior a cerca de 8 a 10 mEq/L em 24 horas, pelo risco de desmielinização osmótica; salina hipertônica em bolus se reserva a sintomas neurológicos graves, para elevação inicial pequena e controlada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o padrão descrito afasta, e não confirma, lesão de tronco; (B) 118 mEq/L causa coma, e a correção rápida é perigosa; (D) o estado de mal não convulsivo só se exclui com eletroencefalograma.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Duas ideias distintas se cruzam neste tema.&lt;/p&gt;&lt;p&gt;Nas &lt;strong&gt;lesões expansivas&lt;/strong&gt; (tumor, hematoma, abscesso), vale a doutrina de Monro-Kellie: o crânio é uma caixa rígida e o aumento de um compartimento é inicialmente compensado por deslocamento de líquido cefalorraquidiano e de sangue venoso. A curva de complacência é, portanto, &lt;strong&gt;exponencial&lt;/strong&gt; e não linear — há uma fase plana, em que grandes volumes elevam pouco a pressão, seguida de um joelho a partir do qual pequenos incrementos produzem aumentos abruptos da pressão intracraniana. É por isso que um paciente aparentemente compensado descompensa com uma dose de anestésico volátil ou um episódio de hipercapnia.&lt;/p&gt;&lt;p&gt;Na &lt;strong&gt;malformação arteriovenosa&lt;/strong&gt;, a fisiopatologia dominante não é a expansão, mas o &lt;strong&gt;shunt&lt;/strong&gt; arteriovenoso de baixa resistência. O tecido vizinho vive em hipoperfusão crônica — o chamado roubo de fluxo — com arteríolas cronicamente dilatadas e &lt;strong&gt;autorregulação perdida ou deslocada&lt;/strong&gt;. Retirado o shunt, esse leito recebe subitamente pressão e fluxo normais que não consegue regular, quadro conhecido como ruptura da pressão de perfusão normal, com edema e hemorragia. Daí a regra prática de &lt;strong&gt;controle rigoroso da pressão arterial&lt;/strong&gt;, mantendo-a em níveis normais ou discretamente baixos no despertar e nas primeiras horas, com despertar suave e sem hipertensão ou tosse.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a malformação não age primariamente por efeito de massa; (C) a autorregulação perilesional está comprometida, e hipertensão é justamente o que se evita; (D) a curva de complacência é exponencial.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Duas ideias distintas se cruzam neste tema.&lt;/p&gt;&lt;p&gt;Nas &lt;strong&gt;lesões expansivas&lt;/strong&gt; (tumor, hematoma, abscesso), vale a doutrina de Monro-Kellie: o crânio é uma caixa rígida e o aumento de um compartimento é inicialmente compensado por deslocamento de líquido cefalorraquidiano e de sangue venoso. A curva de complacência é, portanto, &lt;strong&gt;exponencial&lt;/strong&gt; e não linear: há uma fase plana, em que grandes volumes elevam pouco a pressão, seguida de um joelho a partir do qual pequenos incrementos produzem aumentos abruptos da pressão intracraniana. É por isso que um paciente aparentemente compensado descompensa com uma dose de anestésico volátil ou um episódio de hipercapnia.&lt;/p&gt;&lt;p&gt;Na &lt;strong&gt;malformação arteriovenosa&lt;/strong&gt;, a fisiopatologia dominante não é a expansão, mas o &lt;strong&gt;shunt&lt;/strong&gt; arteriovenoso de baixa resistência. O tecido vizinho vive em hipoperfusão crônica (o chamado roubo de fluxo), com arteríolas cronicamente dilatadas e &lt;strong&gt;autorregulação perdida ou deslocada&lt;/strong&gt;. Retirado o shunt, esse leito recebe subitamente pressão e fluxo normais que não consegue regular, quadro conhecido como ruptura da pressão de perfusão normal, com edema e hemorragia. Daí a regra prática de &lt;strong&gt;controle rigoroso da pressão arterial&lt;/strong&gt;, mantendo-a em níveis normais ou discretamente baixos no despertar e nas primeiras horas, com despertar suave e sem hipertensão ou tosse.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a malformação não age primariamente por efeito de massa; (C) a autorregulação perilesional está comprometida, e hipertensão é justamente o que se evita; (D) a curva de complacência é exponencial.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O consumo cerebral de oxigênio divide-se em duas frações: cerca de &lt;strong&gt;60%&lt;/strong&gt; destinados à &lt;strong&gt;atividade elétrica&lt;/strong&gt; — potenciais sinápticos e de ação — e aproximadamente &lt;strong&gt;40%&lt;/strong&gt; à &lt;strong&gt;manutenção da integridade celular&lt;/strong&gt;, sobretudo o funcionamento das bombas iônicas. Os anestésicos suprimem apenas a primeira fração.&lt;/p&gt;&lt;p&gt;Daí a regra fundamental: quando o eletroencefalograma atinge &lt;strong&gt;supressão de surtos&lt;/strong&gt; e, adiante, silêncio elétrico, o consumo metabólico já caiu ao seu mínimo farmacológico, em torno da metade do basal, e &lt;strong&gt;nenhuma dose adicional&lt;/strong&gt; reduz mais o metabolismo. O que se ganha com o excesso é depressão miocárdica, vasodilatação, instabilidade hemodinâmica e despertar prolongado — este último especialmente indesejável em neurocirurgia, onde o exame neurológico precoce é decisivo. Por isso, quando se opta pela dose de proteção, ela é titulada pelo eletroencefalograma.&lt;/p&gt;&lt;p&gt;Os &lt;strong&gt;barbitúricos&lt;/strong&gt; reduzem metabolismo, fluxo e volume sanguíneo cerebrais com acoplamento preservado, mantêm a resposta ao dióxido de carbono e ainda oferecem estabilização de membrana, varredura de radicais livres e efeito anticonvulsivante — características que os consagraram na proteção contra isquemia &lt;strong&gt;focal&lt;/strong&gt;, como no clampeamento temporário. O benefício na isquemia global permanece não demonstrado. Propofol produz efeito metabólico semelhante.&lt;/p&gt;&lt;p&gt;Independentemente do fármaco, a manutenção da pressão de perfusão distal continua sendo a medida mais determinante.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a fração de manutenção celular não é suprimida; (B) o efeito é dose-dependente e guiado pelo eletroencefalograma; (C) barbitúricos deprimem o miocárdio e reduzem a pressão arterial, exigindo suporte vasoativo.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O consumo cerebral de oxigênio divide-se em duas frações: cerca de &lt;strong&gt;60%&lt;/strong&gt; destinados à &lt;strong&gt;atividade elétrica&lt;/strong&gt; (potenciais sinápticos e de ação) e aproximadamente &lt;strong&gt;40%&lt;/strong&gt; à &lt;strong&gt;manutenção da integridade celular&lt;/strong&gt;, sobretudo o funcionamento das bombas iônicas. Os anestésicos suprimem apenas a primeira fração.&lt;/p&gt;&lt;p&gt;Daí a regra fundamental: quando o eletroencefalograma atinge &lt;strong&gt;supressão de surtos&lt;/strong&gt; e, adiante, silêncio elétrico, o consumo metabólico já caiu ao seu mínimo farmacológico, em torno da metade do basal, e &lt;strong&gt;nenhuma dose adicional&lt;/strong&gt; reduz mais o metabolismo. O que se ganha com o excesso é depressão miocárdica, vasodilatação, instabilidade hemodinâmica e despertar prolongado, este último especialmente indesejável em neurocirurgia, onde o exame neurológico precoce é decisivo. Por isso, quando se opta pela dose de proteção, ela é titulada pelo eletroencefalograma.&lt;/p&gt;&lt;p&gt;Os &lt;strong&gt;barbitúricos&lt;/strong&gt; reduzem metabolismo, fluxo e volume sanguíneo cerebrais com acoplamento preservado, mantêm a resposta ao dióxido de carbono e ainda oferecem estabilização de membrana, varredura de radicais livres e efeito anticonvulsivante, características que os consagraram na proteção contra isquemia &lt;strong&gt;focal&lt;/strong&gt;, como no clampeamento temporário. O benefício na isquemia global permanece não demonstrado. Propofol produz efeito metabólico semelhante.&lt;/p&gt;&lt;p&gt;Independentemente do fármaco, a manutenção da pressão de perfusão distal continua sendo a medida mais determinante.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a fração de manutenção celular não é suprimida; (B) o efeito é dose-dependente e guiado pelo eletroencefalograma; (C) barbitúricos deprimem o miocárdio e reduzem a pressão arterial, exigindo suporte vasoativo.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Antes da craniotomia, o crânio é uma caixa fechada e vale a relação pressão-volume de Monro-Kellie. Retirar &lt;strong&gt;líquido cefalorraquidiano&lt;/strong&gt; por uma ventriculostomia é uma das formas mais rápidas e eficazes de reduzir volume intracraniano — soma-se às demais medidas de relaxamento: posicionamento com cabeceira elevada e cabeça neutra, drenagem venosa livre, ventilação sem pressão expiratória final excessiva, ajuste da PaCO&lt;sub&gt;2&lt;/sub&gt; para a faixa baixa da normalidade, anestesia venosa, manitol ou salina hipertônica e plano anestésico adequado para impedir tosse.&lt;/p&gt;&lt;p&gt;Uma vez aberta a dura-máter, a compartimentalização se desfaz: o crânio deixa de ser um compartimento fechado, a leitura de um monitor de pressão perde correspondência com o que ocorre no campo e o parâmetro operacional passa a ser a &lt;strong&gt;tensão encefálica&lt;/strong&gt; julgada pelo cirurgião — cérebro relaxado, tenso ou herniando pela craniotomia. Persistindo edema, a conduta é revisar sistematicamente posição, ventilação, hemodinâmica, profundidade anestésica, natremia e a possibilidade de hematoma ou obstrução venosa.&lt;/p&gt;&lt;p&gt;A drenagem liquórica deve ser &lt;strong&gt;lenta e controlada&lt;/strong&gt;: retirada rápida e volumosa pode gerar gradientes de pressão, colapso ventricular, hemorragia subdural por tração de veias-ponte e, em massas de fossa posterior, herniação ascendente ou descendente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a drenagem rápida e ampla é perigosa; (C) aberta a dura, a pressão intracraniana deixa de traduzir a condição do campo; (D) a ventriculostomia é útil também na fossa posterior, com hidrocefalia obstrutiva frequente, exigindo apenas técnica cuidadosa.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Antes da craniotomia, o crânio é uma caixa fechada e vale a relação pressão-volume de Monro-Kellie. Retirar &lt;strong&gt;líquido cefalorraquidiano&lt;/strong&gt; por uma ventriculostomia é uma das formas mais rápidas e eficazes de reduzir volume intracraniano; soma-se às demais medidas de relaxamento: posicionamento com cabeceira elevada e cabeça neutra, drenagem venosa livre, ventilação sem pressão expiratória final excessiva, ajuste da PaCO&lt;sub&gt;2&lt;/sub&gt; para a faixa baixa da normalidade, anestesia venosa, manitol ou salina hipertônica e plano anestésico adequado para impedir tosse.&lt;/p&gt;&lt;p&gt;Uma vez aberta a dura-máter, a compartimentalização se desfaz: o crânio deixa de ser um compartimento fechado, a leitura de um monitor de pressão perde correspondência com o que ocorre no campo e o parâmetro operacional passa a ser a &lt;strong&gt;tensão encefálica&lt;/strong&gt; julgada pelo cirurgião: cérebro relaxado, tenso ou herniando pela craniotomia. Persistindo edema, a conduta é revisar sistematicamente posição, ventilação, hemodinâmica, profundidade anestésica, natremia e a possibilidade de hematoma ou obstrução venosa.&lt;/p&gt;&lt;p&gt;A drenagem liquórica deve ser &lt;strong&gt;lenta e controlada&lt;/strong&gt;: retirada rápida e volumosa pode gerar gradientes de pressão, colapso ventricular, hemorragia subdural por tração de veias-ponte e, em massas de fossa posterior, herniação ascendente ou descendente.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a drenagem rápida e ampla é perigosa; (C) aberta a dura, a pressão intracraniana deixa de traduzir a condição do campo; (D) a ventriculostomia é útil também na fossa posterior, com hidrocefalia obstrutiva frequente, exigindo apenas técnica cuidadosa.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A indução do paciente com hipertensão intracraniana é um exercício de equilíbrio entre dois erros opostos.&lt;/p&gt;&lt;p&gt;De um lado, a &lt;strong&gt;resposta simpática&lt;/strong&gt; à laringoscopia e à intubação eleva pressão arterial, fluxo e, num encéfalo com autorregulação comprometida, a própria pressão intracraniana, além de favorecer ressangramento. Atenua-se com plano anestésico adequado, opioide, lidocaína e bloqueio neuromuscular pleno antes da laringoscopia, evitando tosse e esforço.&lt;/p&gt;&lt;p&gt;De outro, a &lt;strong&gt;hipotensão&lt;/strong&gt; por dose plena de hipnótico em paciente hipovolêmico ou idoso reduz a pressão de perfusão e converte a lesão primária em isquemia. No caso, a pressão arterial média após a indução é (85 + 2 × 50) ÷ 3 ≈ &lt;strong&gt;62 mmHg&lt;/strong&gt;; com pressão intracraniana de 28 mmHg, a pressão de perfusão cerebral é 62 − 28 ≈ &lt;strong&gt;34 mmHg&lt;/strong&gt;, muito abaixo da meta de 60 a 70 mmHg. A conduta é imediata: vasopressor, volume e aceleração da descompressão cirúrgica.&lt;/p&gt;&lt;p&gt;Um único episódio de hipotensão no traumatismo cranioencefálico grave associa-se a pior desfecho — daí a prática de titular o hipnótico, reduzir a dose, associar opioide e ter vasopressor preparado. A hipertensão intracraniana sustentada com queda da perfusão é o caminho para a &lt;strong&gt;herniação&lt;/strong&gt;, cuja tríade tardia inclui hipertensão com bradicardia e alteração do padrão respiratório, além de anisocoria.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) nenhum efeito farmacológico compensa perfusão insuficiente; (C) o cálculo ignora a subtração da pressão intracraniana; (D) o pico pressórico à intubação deve sim ser atenuado.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A indução do paciente com hipertensão intracraniana é um exercício de equilíbrio entre dois erros opostos.&lt;/p&gt;&lt;p&gt;De um lado, a &lt;strong&gt;resposta simpática&lt;/strong&gt; à laringoscopia e à intubação eleva pressão arterial, fluxo e, num encéfalo com autorregulação comprometida, a própria pressão intracraniana, além de favorecer ressangramento. Atenua-se com plano anestésico adequado, opioide, lidocaína e bloqueio neuromuscular pleno antes da laringoscopia, evitando tosse e esforço.&lt;/p&gt;&lt;p&gt;De outro, a &lt;strong&gt;hipotensão&lt;/strong&gt; por dose plena de hipnótico em paciente hipovolêmico ou idoso reduz a pressão de perfusão e converte a lesão primária em isquemia. No caso, a pressão arterial média após a indução é (85 + 2 × 50) ÷ 3 ≈ &lt;strong&gt;62 mmHg&lt;/strong&gt;; com pressão intracraniana de 28 mmHg, a pressão de perfusão cerebral é 62 − 28 ≈ &lt;strong&gt;34 mmHg&lt;/strong&gt;, muito abaixo da meta de 60 a 70 mmHg. A conduta é imediata: vasopressor, volume e aceleração da descompressão cirúrgica.&lt;/p&gt;&lt;p&gt;Um único episódio de hipotensão no traumatismo cranioencefálico grave associa-se a pior desfecho; daí a prática de titular o hipnótico, reduzir a dose, associar opioide e ter vasopressor preparado. A hipertensão intracraniana sustentada com queda da perfusão é o caminho para a &lt;strong&gt;herniação&lt;/strong&gt;, cuja tríade tardia inclui hipertensão com bradicardia e alteração do padrão respiratório, além de anisocoria.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) nenhum efeito farmacológico compensa perfusão insuficiente; (C) o cálculo ignora a subtração da pressão intracraniana; (D) o pico pressórico à intubação deve sim ser atenuado.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;succinilcolina&lt;/strong&gt; pode produzir elevação &lt;strong&gt;transitória e de pequena magnitude&lt;/strong&gt; da pressão intracraniana. Os mecanismos propostos incluem a estimulação de fusos musculares por fasciculações, com aumento da aferência e da atividade elétrica cerebral, e elevação da pressão venosa central pela contração muscular. O efeito dura poucos minutos.&lt;/p&gt;&lt;p&gt;Do ponto de vista clínico, esse aumento é &lt;strong&gt;muito menos importante&lt;/strong&gt; que os eventos que ocorrem quando a intubação falha ou se prolonga: hipóxia, hipercapnia, tosse e resposta pressórica exagerada elevam a pressão intracraniana de forma muito mais expressiva e perigosa. Assim, em paciente com estômago cheio, via aérea difícil prevista e necessidade de bloqueio rápido e de curta duração, a succinilcolina permanece opção legítima, desde que respeitadas suas contraindicações clássicas — queimadura ou desnervação após as primeiras 24 a 48 horas, hipercalemia, rabdomiólise, história de hipertermia maligna.&lt;/p&gt;&lt;p&gt;O efeito pode ser atenuado por &lt;strong&gt;plano anestésico adequado&lt;/strong&gt;, uso prévio de opioide ou lidocaína e &lt;strong&gt;pré-curarização&lt;/strong&gt; com dose subparalisante de bloqueador adespolarizante — esta última exigindo aumento da dose de succinilcolina e retardando o início. Alternativa igualmente aceitável é o rocurônio em dose de sequência rápida, hoje facilitado pela disponibilidade do sugamadex.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) não há contraindicação absoluta pela pressão intracraniana, e o efeito é modesto; (B) a elevação existe, ainda que pequena; (D) o aumento é transitório, e fracionar a dose apenas prolongaria o tempo até condições ideais de intubação.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;succinilcolina&lt;/strong&gt; pode produzir elevação &lt;strong&gt;transitória e de pequena magnitude&lt;/strong&gt; da pressão intracraniana. Os mecanismos propostos incluem a estimulação de fusos musculares por fasciculações, com aumento da aferência e da atividade elétrica cerebral, e elevação da pressão venosa central pela contração muscular. O efeito dura poucos minutos.&lt;/p&gt;&lt;p&gt;Do ponto de vista clínico, esse aumento é &lt;strong&gt;muito menos importante&lt;/strong&gt; que os eventos que ocorrem quando a intubação falha ou se prolonga: hipóxia, hipercapnia, tosse e resposta pressórica exagerada elevam a pressão intracraniana de forma muito mais expressiva e perigosa. Assim, em paciente com estômago cheio, via aérea difícil prevista e necessidade de bloqueio rápido e de curta duração, a succinilcolina permanece opção legítima, desde que respeitadas suas contraindicações clássicas: queimadura ou desnervação após as primeiras 24 a 48 horas, hipercalemia, rabdomiólise, história de hipertermia maligna.&lt;/p&gt;&lt;p&gt;O efeito pode ser atenuado por &lt;strong&gt;plano anestésico adequado&lt;/strong&gt;, uso prévio de opioide ou lidocaína e &lt;strong&gt;pré-curarização&lt;/strong&gt; com dose subparalisante de bloqueador adespolarizante, esta última exigindo aumento da dose de succinilcolina e retardando o início. Alternativa igualmente aceitável é o rocurônio em dose de sequência rápida, hoje facilitado pela disponibilidade do sugamadex.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) não há contraindicação absoluta pela pressão intracraniana, e o efeito é modesto; (B) a elevação existe, ainda que pequena; (D) o aumento é transitório, e fracionar a dose apenas prolongaria o tempo até condições ideais de intubação.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A resposta está no &lt;strong&gt;tipo de edema&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O edema perilesional dos tumores é predominantemente &lt;strong&gt;vasogênico&lt;/strong&gt;: os capilares neoformados são anormalmente permeáveis, com junções de oclusão deficientes, e extravasam plasma para o interstício da substância branca. Os &lt;strong&gt;corticosteroides&lt;/strong&gt;, e em especial a &lt;strong&gt;dexametasona&lt;/strong&gt; — escolhida por elevada potência glicocorticoide, mínima ação mineralocorticoide e boa penetração —, restauram a integridade dessa barreira e reduzem o edema. A melhora clínica costuma iniciar em horas, com efeito consolidado em &lt;strong&gt;24 a 72 horas&lt;/strong&gt;, o que justifica iniciar o tratamento alguns dias antes da craniotomia eletiva sempre que possível.&lt;/p&gt;&lt;p&gt;No &lt;strong&gt;traumatismo cranioencefálico&lt;/strong&gt;, o edema é sobretudo &lt;strong&gt;citotóxico&lt;/strong&gt;, por falência energética e disfunção de bombas iônicas — mecanismo sobre o qual o corticoide não age. Grandes ensaios clínicos demonstraram &lt;strong&gt;aumento de mortalidade&lt;/strong&gt; com corticosteroide nesses pacientes, e a recomendação atual é não utilizá-lo. Também não há benefício no acidente vascular cerebral isquêmico ou hemorrágico.&lt;/p&gt;&lt;p&gt;Efeitos adversos relevantes incluem hiperglicemia, imunossupressão, miopatia, alterações do humor e complicações gastrintestinais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) os mecanismos de edema são distintos e as indicações, opostas; (C) a dexametasona é altamente eficaz no edema peritumoral, e o manitol é medida pontual, não substituto crônico; (D) o corticosteroide no traumatismo cranioencefálico associou-se a aumento, e não a redução, da mortalidade.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A resposta está no &lt;strong&gt;tipo de edema&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O edema perilesional dos tumores é predominantemente &lt;strong&gt;vasogênico&lt;/strong&gt;: os capilares neoformados são anormalmente permeáveis, com junções de oclusão deficientes, e extravasam plasma para o interstício da substância branca. Os &lt;strong&gt;corticosteroides&lt;/strong&gt;, e em especial a &lt;strong&gt;dexametasona&lt;/strong&gt; (escolhida por elevada potência glicocorticoide, mínima ação mineralocorticoide e boa penetração), restauram a integridade dessa barreira e reduzem o edema. A melhora clínica costuma iniciar em horas, com efeito consolidado em &lt;strong&gt;24 a 72 horas&lt;/strong&gt;, o que justifica iniciar o tratamento alguns dias antes da craniotomia eletiva sempre que possível.&lt;/p&gt;&lt;p&gt;No &lt;strong&gt;traumatismo cranioencefálico&lt;/strong&gt;, o edema é sobretudo &lt;strong&gt;citotóxico&lt;/strong&gt;, por falência energética e disfunção de bombas iônicas, mecanismo sobre o qual o corticoide não age. Grandes ensaios clínicos demonstraram &lt;strong&gt;aumento de mortalidade&lt;/strong&gt; com corticosteroide nesses pacientes, e a recomendação atual é não utilizá-lo. Também não há benefício no acidente vascular cerebral isquêmico ou hemorrágico.&lt;/p&gt;&lt;p&gt;Efeitos adversos relevantes incluem hiperglicemia, imunossupressão, miopatia, alterações do humor e complicações gastrintestinais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) os mecanismos de edema são distintos e as indicações, opostas; (C) a dexametasona é altamente eficaz no edema peritumoral, e o manitol é medida pontual, não substituto crônico; (D) o corticosteroide no traumatismo cranioencefálico associou-se a aumento, e não a redução, da mortalidade.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A fístula liquórica é a complicação característica da cirurgia &lt;strong&gt;transesfenoidal&lt;/strong&gt;, criada pela abertura do assoalho selar e da dura. Enquanto ela persiste, existe comunicação direta entre a nasofaringe — cavidade colonizada — e o espaço subaracnóideo, o que impõe duas preocupações anestésicas.&lt;/p&gt;&lt;p&gt;A primeira é evitar &lt;strong&gt;pressão positiva na nasofaringe&lt;/strong&gt;, que pode insuflar ar através do defeito e produzir &lt;strong&gt;pneumoencéfalo hipertensivo&lt;/strong&gt;, além de empurrar material contaminado para o espaço subaracnóideo, com risco de meningite. Ficam proscritas, portanto, a ventilação sob máscara facial com pressão positiva, a cânula nasofaríngea, a pressão positiva contínua nasal e a ventilação não invasiva no pós-operatório.&lt;/p&gt;&lt;p&gt;A segunda é evitar &lt;strong&gt;aumentos abruptos de pressão intracraniana ou intratorácica&lt;/strong&gt;, que alargam a fístula: tosse, esforço, manobra de Valsalva. Preferem-se, então, indução suave com &lt;strong&gt;intubação orotraqueal&lt;/strong&gt; — eventualmente com pré-oxigenação sem pressão positiva e sequência rápida quando indicado —, boa profundidade anestésica, profilaxia de náusea e vômito e &lt;strong&gt;extubação sem tosse&lt;/strong&gt;, com lidocaína ou extubação em plano.&lt;/p&gt;&lt;p&gt;Sondas nasais, incluindo a nasogástrica, só podem ser passadas sob visão direta, pelo risco descrito de trajeto intracraniano.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a ventilação sob máscara com pressão positiva é justamente a manobra a evitar; (B) a sonda nasogástrica às cegas é perigosa nesse cenário; (C) a pressão positiva nasal está contraindicada enquanto houver fístula.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A fístula liquórica é a complicação característica da cirurgia &lt;strong&gt;transesfenoidal&lt;/strong&gt;, criada pela abertura do assoalho selar e da dura. Enquanto ela persiste, existe comunicação direta entre a nasofaringe (cavidade colonizada) e o espaço subaracnóideo, o que impõe duas preocupações anestésicas.&lt;/p&gt;&lt;p&gt;A primeira é evitar &lt;strong&gt;pressão positiva na nasofaringe&lt;/strong&gt;, que pode insuflar ar através do defeito e produzir &lt;strong&gt;pneumoencéfalo hipertensivo&lt;/strong&gt;, além de empurrar material contaminado para o espaço subaracnóideo, com risco de meningite. Ficam proscritas, portanto, a ventilação sob máscara facial com pressão positiva, a cânula nasofaríngea, a pressão positiva contínua nasal e a ventilação não invasiva no pós-operatório.&lt;/p&gt;&lt;p&gt;A segunda é evitar &lt;strong&gt;aumentos abruptos de pressão intracraniana ou intratorácica&lt;/strong&gt;, que alargam a fístula: tosse, esforço, manobra de Valsalva. Preferem-se, então, indução suave com &lt;strong&gt;intubação orotraqueal&lt;/strong&gt; (eventualmente com pré-oxigenação sem pressão positiva e sequência rápida quando indicado), boa profundidade anestésica, profilaxia de náusea e vômito e &lt;strong&gt;extubação sem tosse&lt;/strong&gt;, com lidocaína ou extubação em plano.&lt;/p&gt;&lt;p&gt;Sondas nasais, incluindo a nasogástrica, só podem ser passadas sob visão direta, pelo risco descrito de trajeto intracraniano.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a ventilação sob máscara com pressão positiva é justamente a manobra a evitar; (B) a sonda nasogástrica às cegas é perigosa nesse cenário; (C) a pressão positiva nasal está contraindicada enquanto houver fístula.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;edema pulmonar neurogênico&lt;/strong&gt; aparece de minutos a poucas horas após uma agressão neurológica aguda e grave — hemorragia subaracnóidea, traumatismo cranioencefálico, estado de mal epiléptico, hipertensão intracraniana súbita.&lt;/p&gt;&lt;p&gt;O mecanismo aceito é uma &lt;strong&gt;descarga simpática maciça&lt;/strong&gt; a partir de centros bulbares e hipotalâmicos. Ela produz vasoconstrição sistêmica e pulmonar intensa, com deslocamento de volume para o leito pulmonar e elevação abrupta das pressões capilares — componente &lt;em&gt;hidrostático&lt;/em&gt;. Somam-se lesão mecânica e inflamatória da &lt;strong&gt;barreira alveolocapilar&lt;/strong&gt;, que torna o edema também &lt;em&gt;permeabilidade-dependente&lt;/em&gt;, com líquido rico em proteínas. Pode haver miocárdio atordoado neurogênico associado, com disfunção ventricular transitória e elevação de troponina.&lt;/p&gt;&lt;p&gt;O quadro clínico é de hipoxemia de instalação rápida, expectoração rósea, estertores e infiltrado bilateral, em paciente sem cardiopatia prévia nem sobrecarga volêmica evidente — precisamente o contraste que o caso oferece.&lt;/p&gt;&lt;p&gt;O tratamento é de &lt;strong&gt;suporte&lt;/strong&gt;: oxigenação e ventilação protetora, com pressão expiratória final positiva titulada para não comprometer o retorno venoso cerebral, controle da hipertensão intracraniana e da descarga adrenérgica e manejo volêmico equilibrado. A resolução costuma ocorrer em &lt;strong&gt;24 a 72 horas&lt;/strong&gt; quando a lesão neurológica é controlada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a cronologia e o padrão bilateral simétrico não correspondem a pneumonia aspirativa; (C) não há sobrecarga volêmica no caso, e a diurese agressiva compromete a perfusão cerebral; (D) o quadro é precoce e habitualmente reversível.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;edema pulmonar neurogênico&lt;/strong&gt; aparece de minutos a poucas horas após uma agressão neurológica aguda e grave: hemorragia subaracnóidea, traumatismo cranioencefálico, estado de mal epiléptico, hipertensão intracraniana súbita.&lt;/p&gt;&lt;p&gt;O mecanismo aceito é uma &lt;strong&gt;descarga simpática maciça&lt;/strong&gt; a partir de centros bulbares e hipotalâmicos. Ela produz vasoconstrição sistêmica e pulmonar intensa, com deslocamento de volume para o leito pulmonar e elevação abrupta das pressões capilares, componente &lt;em&gt;hidrostático&lt;/em&gt;. Somam-se lesão mecânica e inflamatória da &lt;strong&gt;barreira alveolocapilar&lt;/strong&gt;, que torna o edema também &lt;em&gt;permeabilidade-dependente&lt;/em&gt;, com líquido rico em proteínas. Pode haver miocárdio atordoado neurogênico associado, com disfunção ventricular transitória e elevação de troponina.&lt;/p&gt;&lt;p&gt;O quadro clínico é de hipoxemia de instalação rápida, expectoração rósea, estertores e infiltrado bilateral, em paciente sem cardiopatia prévia nem sobrecarga volêmica evidente, precisamente o contraste que o caso oferece.&lt;/p&gt;&lt;p&gt;O tratamento é de &lt;strong&gt;suporte&lt;/strong&gt;: oxigenação e ventilação protetora, com pressão expiratória final positiva titulada para não comprometer o retorno venoso cerebral, controle da hipertensão intracraniana e da descarga adrenérgica e manejo volêmico equilibrado. A resolução costuma ocorrer em &lt;strong&gt;24 a 72 horas&lt;/strong&gt; quando a lesão neurológica é controlada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a cronologia e o padrão bilateral simétrico não correspondem a pneumonia aspirativa; (C) não há sobrecarga volêmica no caso, e a diurese agressiva compromete a perfusão cerebral; (D) o quadro é precoce e habitualmente reversível.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O edema que circunda tumores cerebrais é &lt;strong&gt;vasogênico&lt;/strong&gt;: os vasos neoformados apresentam junções de oclusão defeituosas, fenestrações e expressão aumentada de fator de crescimento endotelial vascular, extravasando plasma para a substância branca. A &lt;strong&gt;dexametasona&lt;/strong&gt; age restaurando a integridade dessa barreira e reduzindo a permeabilidade capilar — mecanismo genômico, que explica a cinética.&lt;/p&gt;&lt;p&gt;Consequências práticas dessa cinética: o efeito não é imediato. A melhora sintomática começa em horas, mas a redução mensurável do edema leva de &lt;strong&gt;24 a 72 horas&lt;/strong&gt;, com efeito máximo em alguns dias. Por isso o corticoide é iniciado &lt;strong&gt;antes&lt;/strong&gt; da craniotomia eletiva e &lt;strong&gt;mantido&lt;/strong&gt; no perioperatório, com desmame gradual depois — nunca suspenso abruptamente na véspera, o que arrisca rebote do edema e insuficiência adrenal relativa. Regimes habituais partem de 4 mg a cada 6 horas, com ou sem dose de ataque, ajustados à resposta.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;hiperglicemia&lt;/strong&gt; é o efeito adverso perioperatório mais relevante e ocorre também em pacientes sem diabetes prévio. Em neurocirurgia ela não é detalhe: a hiperglicemia agrava a lesão isquêmica ao favorecer acidose láctica intracelular no tecido em penumbra, e associa-se a pior desfecho neurológico e a mais infecção de ferida. Impõe-se monitoração seriada e correção com insulina, evitando também a hipoglicemia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) suspender na véspera arrisca rebote do edema; (B) o mecanismo não é diurese osmótica — esse é o do manitol — nem tem efeito em minutos; (D) o controle glicêmico é justamente prioritário no paciente neurocirúrgico.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O edema que circunda tumores cerebrais é &lt;strong&gt;vasogênico&lt;/strong&gt;: os vasos neoformados apresentam junções de oclusão defeituosas, fenestrações e expressão aumentada de fator de crescimento endotelial vascular, extravasando plasma para a substância branca. A &lt;strong&gt;dexametasona&lt;/strong&gt; age restaurando a integridade dessa barreira e reduzindo a permeabilidade capilar, mecanismo genômico, que explica a cinética.&lt;/p&gt;&lt;p&gt;Consequências práticas dessa cinética: o efeito não é imediato. A melhora sintomática começa em horas, mas a redução mensurável do edema leva de &lt;strong&gt;24 a 72 horas&lt;/strong&gt;, com efeito máximo em alguns dias. Por isso o corticoide é iniciado &lt;strong&gt;antes&lt;/strong&gt; da craniotomia eletiva e &lt;strong&gt;mantido&lt;/strong&gt; no perioperatório, com desmame gradual depois; nunca suspenso abruptamente na véspera, o que arrisca rebote do edema e insuficiência adrenal relativa. Regimes habituais partem de 4 mg a cada 6 horas, com ou sem dose de ataque, ajustados à resposta.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;hiperglicemia&lt;/strong&gt; é o efeito adverso perioperatório mais relevante e ocorre também em pacientes sem diabetes prévio. Em neurocirurgia ela não é detalhe: a hiperglicemia agrava a lesão isquêmica ao favorecer acidose láctica intracelular no tecido em penumbra, e associa-se a pior desfecho neurológico e a mais infecção de ferida. Impõe-se monitoração seriada e correção com insulina, evitando também a hipoglicemia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) suspender na véspera arrisca rebote do edema; (B) o mecanismo não é diurese osmótica (esse é o do manitol) nem tem efeito em minutos; (D) o controle glicêmico é justamente prioritário no paciente neurocirúrgico.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;tálamo&lt;/strong&gt; é a grande estação de relé sensitiva: as vias somatossensitivas, visual e auditiva fazem sinapse em seus núcleos antes de alcançar o córtex — núcleo ventral posterolateral para o corpo, ventral posteromedial para a face, corpo geniculado lateral para a visão e medial para a audição. A &lt;strong&gt;via olfatória&lt;/strong&gt; é a exceção clássica: projeta-se do bulbo olfatório ao córtex piriforme e a estruturas límbicas sem relé talâmico obrigatório. O tálamo participa ainda de circuitos motores, límbicos e do nível de consciência, pelos núcleos intralaminares.&lt;/p&gt;&lt;p&gt;Os &lt;strong&gt;núcleos da base&lt;/strong&gt; — caudado, putame, globo pálido, com núcleo subtalâmico e substância negra — funcionam como alça moduladora: recebem do córtex e retornam ao córtex via tálamo, ajustando a seleção e a amplitude do movimento pelas vias direta e indireta. Não se projetam diretamente à medula; a &lt;strong&gt;via final comum&lt;/strong&gt; é o motoneurônio alfa do corno anterior. Suas lesões produzem distúrbios do movimento, como parkinsonismo, coreia e distonia.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;reflexo miotático&lt;/strong&gt;, como o patelar, é o exemplo de arco &lt;strong&gt;monossináptico&lt;/strong&gt;: o estiramento excita o fuso muscular, a aferência Ia faz sinapse direta com o motoneurônio alfa e produz contração, sem interneurônios. Já o reflexo de retirada, nociceptivo, é polissináptico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) os núcleos da base modulam, e não constituem, a via final comum; (C) o reflexo patelar é monossináptico; (D) coordenação e equilíbrio são funções cerebelares, enquanto o hipotálamo regula funções neuroendócrinas e autonômicas.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;tálamo&lt;/strong&gt; é a grande estação de relé sensitiva: as vias somatossensitivas, visual e auditiva fazem sinapse em seus núcleos antes de alcançar o córtex: núcleo ventral posterolateral para o corpo, ventral posteromedial para a face, corpo geniculado lateral para a visão e medial para a audição. A &lt;strong&gt;via olfatória&lt;/strong&gt; é a exceção clássica: projeta-se do bulbo olfatório ao córtex piriforme e a estruturas límbicas sem relé talâmico obrigatório. O tálamo participa ainda de circuitos motores, límbicos e do nível de consciência, pelos núcleos intralaminares.&lt;/p&gt;&lt;p&gt;Os &lt;strong&gt;núcleos da base&lt;/strong&gt; (caudado, putame, globo pálido, com núcleo subtalâmico e substância negra) funcionam como alça moduladora: recebem do córtex e retornam ao córtex via tálamo, ajustando a seleção e a amplitude do movimento pelas vias direta e indireta. Não se projetam diretamente à medula; a &lt;strong&gt;via final comum&lt;/strong&gt; é o motoneurônio alfa do corno anterior. Suas lesões produzem distúrbios do movimento, como parkinsonismo, coreia e distonia.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;reflexo miotático&lt;/strong&gt;, como o patelar, é o exemplo de arco &lt;strong&gt;monossináptico&lt;/strong&gt;: o estiramento excita o fuso muscular, a aferência Ia faz sinapse direta com o motoneurônio alfa e produz contração, sem interneurônios. Já o reflexo de retirada, nociceptivo, é polissináptico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) os núcleos da base modulam, e não constituem, a via final comum; (C) o reflexo patelar é monossináptico; (D) coordenação e equilíbrio são funções cerebelares, enquanto o hipotálamo regula funções neuroendócrinas e autonômicas.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;reflexo oculocardíaco&lt;/strong&gt; é o exemplo didático da integração entre nervos cranianos e sistema autônomo: a tração da musculatura extraocular ou a pressão sobre o globo estimulam terminações cuja aferência trafega pelo ramo oftálmico do &lt;strong&gt;trigêmeo&lt;/strong&gt; até o núcleo trigeminal; o sinal alcança o núcleo motor dorsal do &lt;strong&gt;vago&lt;/strong&gt;, cuja eferência produz &lt;strong&gt;bradicardia&lt;/strong&gt;, podendo chegar a bloqueio ou assistolia. A conduta é interromper o estímulo cirúrgico, garantir oxigenação e plano anestésico e, se necessário, administrar atropina.&lt;/p&gt;&lt;p&gt;A organização autonômica segue duas divisões:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Simpático&lt;/strong&gt;, de origem &lt;strong&gt;toracolombar&lt;/strong&gt; (T1 a L2 ou L3): fibras pré-ganglionares &lt;em&gt;curtas&lt;/em&gt;, gânglios paravertebrais próximos à medula e fibras pós-ganglionares &lt;em&gt;longas&lt;/em&gt;, com ampla divergência — daí a resposta difusa de luta ou fuga. O neurotransmissor pós-ganglionar é a noradrenalina, exceto nas glândulas sudoríparas, colinérgicas, e na medula adrenal, que é um gânglio modificado.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Parassimpático&lt;/strong&gt;, de origem &lt;strong&gt;craniossacral&lt;/strong&gt;: nervos cranianos &lt;strong&gt;III, VII, IX e X&lt;/strong&gt; e raízes &lt;strong&gt;S2 a S4&lt;/strong&gt;. Fibras pré-ganglionares &lt;em&gt;longas&lt;/em&gt;, gânglios junto ao órgão efetor e fibras pós-ganglionares &lt;em&gt;curtas&lt;/em&gt;, com respostas mais discretas e localizadas. O vago responde por cerca de 75% de toda a atividade parassimpática.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Em ambas as divisões, a transmissão ganglionar é colinérgica nicotínica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a aferência é trigeminal e a eferência, vagal; (B) a origem craniossacral é do parassimpático; (D) as características descritas são as do simpático.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;reflexo oculocardíaco&lt;/strong&gt; é o exemplo didático da integração entre nervos cranianos e sistema autônomo: a tração da musculatura extraocular ou a pressão sobre o globo estimulam terminações cuja aferência trafega pelo ramo oftálmico do &lt;strong&gt;trigêmeo&lt;/strong&gt; até o núcleo trigeminal; o sinal alcança o núcleo motor dorsal do &lt;strong&gt;vago&lt;/strong&gt;, cuja eferência produz &lt;strong&gt;bradicardia&lt;/strong&gt;, podendo chegar a bloqueio ou assistolia. A conduta é interromper o estímulo cirúrgico, garantir oxigenação e plano anestésico e, se necessário, administrar atropina.&lt;/p&gt;&lt;p&gt;A organização autonômica segue duas divisões:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Simpático&lt;/strong&gt;, de origem &lt;strong&gt;toracolombar&lt;/strong&gt; (T1 a L2 ou L3): fibras pré-ganglionares &lt;em&gt;curtas&lt;/em&gt;, gânglios paravertebrais próximos à medula e fibras pós-ganglionares &lt;em&gt;longas&lt;/em&gt;, com ampla divergência; daí a resposta difusa de luta ou fuga. O neurotransmissor pós-ganglionar é a noradrenalina, exceto nas glândulas sudoríparas, colinérgicas, e na medula adrenal, que é um gânglio modificado.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Parassimpático&lt;/strong&gt;, de origem &lt;strong&gt;craniossacral&lt;/strong&gt;: nervos cranianos &lt;strong&gt;III, VII, IX e X&lt;/strong&gt; e raízes &lt;strong&gt;S2 a S4&lt;/strong&gt;. Fibras pré-ganglionares &lt;em&gt;longas&lt;/em&gt;, gânglios junto ao órgão efetor e fibras pós-ganglionares &lt;em&gt;curtas&lt;/em&gt;, com respostas mais discretas e localizadas. O vago responde por cerca de 75% de toda a atividade parassimpática.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Em ambas as divisões, a transmissão ganglionar é colinérgica nicotínica.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a aferência é trigeminal e a eferência, vagal; (B) a origem craniossacral é do parassimpático; (D) as características descritas são as do simpático.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A via &lt;strong&gt;nigroestriatal&lt;/strong&gt; — dos neurônios dopaminérgicos da substância negra compacta ao estriado — modula os circuitos dos núcleos da base. Quando a dopamina falta, predomina a atividade colinérgica estriatal e surgem os sinais extrapiramidais.&lt;/p&gt;&lt;p&gt;Na &lt;strong&gt;doença de Parkinson&lt;/strong&gt;, isso acontece por &lt;strong&gt;degeneração&lt;/strong&gt; desses neurônios, com sintomas surgindo após perda de cerca de 60% a 80% deles: bradicinesia, rigidez em roda denteada, tremor de repouso e instabilidade postural.&lt;/p&gt;&lt;p&gt;Farmacologicamente, o mesmo desequilíbrio é reproduzido por &lt;strong&gt;bloqueio de receptores D2&lt;/strong&gt;. A &lt;strong&gt;metoclopramida&lt;/strong&gt; é &lt;em&gt;antagonista&lt;/em&gt; dopaminérgico — é justamente daí que vem seu efeito antiemético, pela ação na zona de gatilho quimiorreceptora — e compartilha esse risco com droperidol, haloperidol, fenotiazinas e prometazina. As manifestações incluem &lt;strong&gt;distonia aguda&lt;/strong&gt; (crise oculógira, torcicolo, trismo, protrusão lingual, em horas após a dose, mais comum em jovens e mulheres), acatisia, parkinsonismo medicamentoso e, tardiamente, discinesia.&lt;/p&gt;&lt;p&gt;A distonia aguda é dramática mas benigna e responde em minutos a &lt;strong&gt;anticolinérgico&lt;/strong&gt; (biperideno) ou &lt;strong&gt;difenidramina&lt;/strong&gt; por via venosa, podendo-se associar benzodiazepínico. O paciente permanece lúcido, o que a distingue de crise convulsiva.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) não há perda de consciência nem atividade epiléptica, e a fenitoína é inócua aqui; (C) a metoclopramida é antagonista, não agonista dopaminérgico; (D) o Parkinson decorre de &lt;em&gt;déficit&lt;/em&gt; de dopamina nigroestriatal.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A via &lt;strong&gt;nigroestriatal&lt;/strong&gt;, dos neurônios dopaminérgicos da substância negra compacta ao estriado, modula os circuitos dos núcleos da base. Quando a dopamina falta, predomina a atividade colinérgica estriatal e surgem os sinais extrapiramidais.&lt;/p&gt;&lt;p&gt;Na &lt;strong&gt;doença de Parkinson&lt;/strong&gt;, isso acontece por &lt;strong&gt;degeneração&lt;/strong&gt; desses neurônios, com sintomas surgindo após perda de cerca de 60% a 80% deles: bradicinesia, rigidez em roda denteada, tremor de repouso e instabilidade postural.&lt;/p&gt;&lt;p&gt;Farmacologicamente, o mesmo desequilíbrio é reproduzido por &lt;strong&gt;bloqueio de receptores D2&lt;/strong&gt;. A &lt;strong&gt;metoclopramida&lt;/strong&gt; é &lt;em&gt;antagonista&lt;/em&gt; dopaminérgico (é justamente daí que vem seu efeito antiemético, pela ação na zona de gatilho quimiorreceptora) e compartilha esse risco com droperidol, haloperidol, fenotiazinas e prometazina. As manifestações incluem &lt;strong&gt;distonia aguda&lt;/strong&gt; (crise oculógira, torcicolo, trismo, protrusão lingual, em horas após a dose, mais comum em jovens e mulheres), acatisia, parkinsonismo medicamentoso e, tardiamente, discinesia.&lt;/p&gt;&lt;p&gt;A distonia aguda é dramática mas benigna e responde em minutos a &lt;strong&gt;anticolinérgico&lt;/strong&gt; (biperideno) ou &lt;strong&gt;difenidramina&lt;/strong&gt; por via venosa, podendo-se associar benzodiazepínico. O paciente permanece lúcido, o que a distingue de crise convulsiva.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) não há perda de consciência nem atividade epiléptica, e a fenitoína é inócua aqui; (C) a metoclopramida é antagonista, não agonista dopaminérgico; (D) o Parkinson decorre de &lt;em&gt;déficit&lt;/em&gt; de dopamina nigroestriatal.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A levodopa tem meia-vida curta, de cerca de 1 a 3 horas, e depende de absorção intestinal. Interrupções de poucas horas podem precipitar rigidez importante, disfagia, insuficiência respiratória e, no extremo, uma &lt;strong&gt;síndrome semelhante à neuroléptica maligna&lt;/strong&gt; por retirada. Por isso a regra é &lt;strong&gt;manter o esquema até a manhã da cirurgia&lt;/strong&gt;, incluindo a dose habitual com um gole de água, priorizar o paciente na escala e &lt;strong&gt;reintroduzir precocemente&lt;/strong&gt;, por sonda enteral se necessário, planejando alternativas quando se prevê jejum prolongado.&lt;/p&gt;&lt;p&gt;Fármacos a evitar:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Antagonistas dopaminérgicos&lt;/strong&gt;: metoclopramida, droperidol, haloperidol, fenotiazinas e prometazina agravam os sintomas parkinsonianos. Para náusea e vômito, preferem-se &lt;strong&gt;ondansetrona&lt;/strong&gt; e dexametasona; a domperidona, que não atravessa bem a barreira hematoencefálica, é alternativa procinética;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Meperidina&lt;/strong&gt; em pacientes que usam &lt;strong&gt;selegilina&lt;/strong&gt;, inibidor da monoaminoxidase B, pela possibilidade de síndrome serotoninérgica — cautela que se estende a outros agentes serotoninérgicos;&lt;/li&gt;&lt;li&gt;Atenção a agentes que causam hipotensão, frequente por disautonomia e pelo próprio tratamento antiparkinsoniano.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Devem-se ainda antecipar risco aumentado de &lt;strong&gt;broncoaspiração&lt;/strong&gt; por disfagia, complicações respiratórias e delirium pós-operatório.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) suspender a levodopa precipita descompensação motora grave; (B) droperidol e haloperidol são antagonistas D2 e pioram o quadro; (C) a prometazina é fenotiazina e deve ser evitada, sendo a ondansetrona a escolha preferencial.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A levodopa tem meia-vida curta, de cerca de 1 a 3 horas, e depende de absorção intestinal. Interrupções de poucas horas podem precipitar rigidez importante, disfagia, insuficiência respiratória e, no extremo, uma &lt;strong&gt;síndrome semelhante à neuroléptica maligna&lt;/strong&gt; por retirada. Por isso a regra é &lt;strong&gt;manter o esquema até a manhã da cirurgia&lt;/strong&gt;, incluindo a dose habitual com um gole de água, priorizar o paciente na escala e &lt;strong&gt;reintroduzir precocemente&lt;/strong&gt;, por sonda enteral se necessário, planejando alternativas quando se prevê jejum prolongado.&lt;/p&gt;&lt;p&gt;Fármacos a evitar:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Antagonistas dopaminérgicos&lt;/strong&gt;: metoclopramida, droperidol, haloperidol, fenotiazinas e prometazina agravam os sintomas parkinsonianos. Para náusea e vômito, preferem-se &lt;strong&gt;ondansetrona&lt;/strong&gt; e dexametasona; a domperidona, que não atravessa bem a barreira hematoencefálica, é alternativa procinética;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Meperidina&lt;/strong&gt; em pacientes que usam &lt;strong&gt;selegilina&lt;/strong&gt;, inibidor da monoaminoxidase B, pela possibilidade de síndrome serotoninérgica, cautela que se estende a outros agentes serotoninérgicos;&lt;/li&gt;&lt;li&gt;Atenção a agentes que causam hipotensão, frequente por disautonomia e pelo próprio tratamento antiparkinsoniano.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Devem-se ainda antecipar risco aumentado de &lt;strong&gt;broncoaspiração&lt;/strong&gt; por disfagia, complicações respiratórias e delirium pós-operatório.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) suspender a levodopa precipita descompensação motora grave; (B) droperidol e haloperidol são antagonistas D2 e pioram o quadro; (C) a prometazina é fenotiazina e deve ser evitada, sendo a ondansetrona a escolha preferencial.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A hipófise tem duas porções de origem embriológica e funcionamento distintos. A &lt;strong&gt;adeno-hipófise&lt;/strong&gt; deriva da bolsa de Rathke e sintetiza seus próprios hormônios — corticotrofina, tireotrofina, hormônio do crescimento, prolactina, hormônio folículo-estimulante e hormônio luteinizante — sob controle de fatores hipotalâmicos que chegam pelo sistema porta-hipofisário. A &lt;strong&gt;neuro-hipófise&lt;/strong&gt; é uma extensão neural do hipotálamo: a ocitocina e a vasopressina são sintetizadas nos corpos celulares dos núcleos &lt;em&gt;supraóptico&lt;/em&gt; e &lt;em&gt;paraventricular&lt;/em&gt;, transportadas por via axonal e apenas armazenadas e liberadas na hipófise posterior.&lt;/p&gt;&lt;p&gt;Essa anatomia explica por que a manipulação cirúrgica da haste pode produzir diabetes insípido transitório ou trifásico, e por que a insuficiência corticotrófica exige reposição de glicocorticoide, não de mineralocorticoide.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o hormônio antidiurético não é produto dos corticotrofos, que secretam corticotrofina; sua síntese é hipotalâmica. (B) o controle da prolactina é predominantemente &lt;em&gt;inibitório&lt;/em&gt;, exercido pela dopamina, razão pela qual antagonistas dopaminérgicos elevam a prolactina e agonistas como a cabergolina a reduzem. (D) o hormônio adrenocorticotrófico é sintetizado e liberado pela hipófise anterior, e não estocado na porção posterior.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A hipófise tem duas porções de origem embriológica e funcionamento distintos. A &lt;strong&gt;adeno-hipófise&lt;/strong&gt; deriva da bolsa de Rathke e sintetiza seus próprios hormônios (corticotrofina, tireotrofina, hormônio do crescimento, prolactina, hormônio folículo-estimulante e hormônio luteinizante) sob controle de fatores hipotalâmicos que chegam pelo sistema porta-hipofisário. A &lt;strong&gt;neuro-hipófise&lt;/strong&gt; é uma extensão neural do hipotálamo: a ocitocina e a vasopressina são sintetizadas nos corpos celulares dos núcleos &lt;em&gt;supraóptico&lt;/em&gt; e &lt;em&gt;paraventricular&lt;/em&gt;, transportadas por via axonal e apenas armazenadas e liberadas na hipófise posterior.&lt;/p&gt;&lt;p&gt;Essa anatomia explica por que a manipulação cirúrgica da haste pode produzir diabetes insípido transitório ou trifásico, e por que a insuficiência corticotrófica exige reposição de glicocorticoide, não de mineralocorticoide.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o hormônio antidiurético não é produto dos corticotrofos, que secretam corticotrofina; sua síntese é hipotalâmica. (B) o controle da prolactina é predominantemente &lt;em&gt;inibitório&lt;/em&gt;, exercido pela dopamina, razão pela qual antagonistas dopaminérgicos elevam a prolactina e agonistas como a cabergolina a reduzem. (D) o hormônio adrenocorticotrófico é sintetizado e liberado pela hipófise anterior, e não estocado na porção posterior.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O estado hiperglicêmico hiperosmolar caracteriza-se por glicemia muito elevada, osmolalidade efetiva acima de 320 mOsm/kg, ausência de cetose significativa e pH próximo do normal — exatamente o padrão descrito. A osmolalidade efetiva é calculada por 2 × sódio + glicemia/18, sem incluir a ureia, que atravessa livremente as membranas e não gera gradiente osmótico efetivo.&lt;/p&gt;&lt;p&gt;O déficit de água costuma ultrapassar 8 a 10 litros, e é a &lt;strong&gt;hipovolemia&lt;/strong&gt;, não a hiperglicemia em si, o principal determinante da hipoperfusão e do rebaixamento. Por isso a prioridade é a &lt;strong&gt;reposição volêmica com cristaloide isotônico&lt;/strong&gt;, seguida de insulina em infusão contínua em doses modestas, com redução gradual da glicemia e da osmolalidade. Quedas abruptas da osmolalidade favorecem edema cerebral.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) bolus alto de insulina antes da reposição desloca água e potássio para o intracelular, podendo agravar o colapso circulatório e precipitar hipocalemia grave. (C) não há acidose relevante — o pH é 7,34 e o bicarbonato, 21 mEq/L —, de modo que o bicarbonato exógeno não tem indicação. (D) a restrição de fluidos é o oposto do necessário; soluções hipotônicas só entram depois da estabilização hemodinâmica, para corrigir lentamente o déficit de água livre.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O estado hiperglicêmico hiperosmolar caracteriza-se por glicemia muito elevada, osmolalidade efetiva acima de 320 mOsm/kg, ausência de cetose significativa e pH próximo do normal, exatamente o padrão descrito. A osmolalidade efetiva é calculada por 2 × sódio + glicemia/18, sem incluir a ureia, que atravessa livremente as membranas e não gera gradiente osmótico efetivo.&lt;/p&gt;&lt;p&gt;O déficit de água costuma ultrapassar 8 a 10 litros, e é a &lt;strong&gt;hipovolemia&lt;/strong&gt;, não a hiperglicemia em si, o principal determinante da hipoperfusão e do rebaixamento. Por isso a prioridade é a &lt;strong&gt;reposição volêmica com cristaloide isotônico&lt;/strong&gt;, seguida de insulina em infusão contínua em doses modestas, com redução gradual da glicemia e da osmolalidade. Quedas abruptas da osmolalidade favorecem edema cerebral.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) bolus alto de insulina antes da reposição desloca água e potássio para o intracelular, podendo agravar o colapso circulatório e precipitar hipocalemia grave. (C) não há acidose relevante (o pH é 7,34 e o bicarbonato, 21 mEq/L), de modo que o bicarbonato exógeno não tem indicação. (D) a restrição de fluidos é o oposto do necessário; soluções hipotônicas só entram depois da estabilização hemodinâmica, para corrigir lentamente o déficit de água livre.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A tríade &lt;strong&gt;poliúria volumosa, urina diluída e hipernatremia com osmolalidade plasmática elevada&lt;/strong&gt; define o diabetes insípido. Se o rim fosse capaz de responder ao hormônio antidiurético, uma osmolalidade plasmática de 302 mOsm/kg produziria urina concentrada; a osmolalidade urinária de 118 mOsm/kg com densidade de 1,003 demonstra que falta o hormônio — quadro típico após manipulação da haste hipofisária, que pode ainda evoluir com padrão trifásico.&lt;/p&gt;&lt;p&gt;O tratamento tem dois componentes: &lt;strong&gt;reposição do déficit de água livre&lt;/strong&gt; com solução hipotônica, corrigindo o sódio de forma gradual, e &lt;strong&gt;desmopressina&lt;/strong&gt;, análogo com ação seletiva em receptores V2 e mínimo efeito vasopressor, titulada pelo débito urinário e pelo sódio sérico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) na secreção inapropriada de hormônio antidiurético ocorre o oposto — oligúria com urina concentrada e hiponatremia; salina hipertônica aqui agravaria a hipernatremia. (B) não houve exposição a agente osmótico, e a diurese osmótica cursa com osmolalidade urinária elevada, não com urina francamente diluída. (C) a síndrome perdedora de sal cursa com hipovolemia e &lt;em&gt;hiponatremia&lt;/em&gt; por natriurese, com sódio urinário alto, o que não corresponde ao caso.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A tríade &lt;strong&gt;poliúria volumosa, urina diluída e hipernatremia com osmolalidade plasmática elevada&lt;/strong&gt; define o diabetes insípido. Se o rim fosse capaz de responder ao hormônio antidiurético, uma osmolalidade plasmática de 302 mOsm/kg produziria urina concentrada; a osmolalidade urinária de 118 mOsm/kg com densidade de 1,003 demonstra que falta o hormônio, quadro típico após manipulação da haste hipofisária, que pode ainda evoluir com padrão trifásico.&lt;/p&gt;&lt;p&gt;O tratamento tem dois componentes: &lt;strong&gt;reposição do déficit de água livre&lt;/strong&gt; com solução hipotônica, corrigindo o sódio de forma gradual, e &lt;strong&gt;desmopressina&lt;/strong&gt;, análogo com ação seletiva em receptores V2 e mínimo efeito vasopressor, titulada pelo débito urinário e pelo sódio sérico.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) na secreção inapropriada de hormônio antidiurético ocorre o oposto: oligúria com urina concentrada e hiponatremia; salina hipertônica aqui agravaria a hipernatremia. (B) não houve exposição a agente osmótico, e a diurese osmótica cursa com osmolalidade urinária elevada, não com urina francamente diluída. (C) a síndrome perdedora de sal cursa com hipovolemia e &lt;em&gt;hiponatremia&lt;/em&gt; por natriurese, com sódio urinário alto, o que não corresponde ao caso.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A crise carcinoide resulta da liberação maciça de serotonina, calicreína, bradicinina, histamina e taquicininas por tumor neuroendócrino com drenagem sistêmica — em geral metástases hepáticas, que escapam da inativação de primeira passagem. Manifesta-se com rubor, broncoespasmo e instabilidade hemodinâmica, mais frequentemente hipotensão, desencadeados por manipulação tumoral, indução ou estresse.&lt;/p&gt;&lt;p&gt;O tratamento específico é a &lt;strong&gt;octreotida&lt;/strong&gt;, análogo da somatostatina que inibe a liberação dos mediadores na origem, em bolus endovenoso seguido de infusão. O preparo inclui octreotida pré-operatória e a escolha de fármacos que não liberem histamina, evitando morfina, atracúrio e mivacúrio.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) as catecolaminas, incluindo adrenalina, ativam a calicreína tumoral e podem &lt;em&gt;intensificar&lt;/em&gt; a liberação de mediadores, agravando a crise; devem ser evitadas como primeira linha, preferindo-se octreotida, volume e vasopressina se necessário. (C) morfina e atracúrio são exatamente os fármacos a evitar, por liberação histamínica. (D) corticoide e anti-histamínico têm papel meramente adjuvante e não bloqueiam a secreção tumoral, que é o mecanismo central da crise.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A crise carcinoide resulta da liberação maciça de serotonina, calicreína, bradicinina, histamina e taquicininas por tumor neuroendócrino com drenagem sistêmica, em geral metástases hepáticas, que escapam da inativação de primeira passagem. Manifesta-se com rubor, broncoespasmo e instabilidade hemodinâmica, mais frequentemente hipotensão, desencadeados por manipulação tumoral, indução ou estresse.&lt;/p&gt;&lt;p&gt;O tratamento específico é a &lt;strong&gt;octreotida&lt;/strong&gt;, análogo da somatostatina que inibe a liberação dos mediadores na origem, em bolus endovenoso seguido de infusão. O preparo inclui octreotida pré-operatória e a escolha de fármacos que não liberem histamina, evitando morfina, atracúrio e mivacúrio.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) as catecolaminas, incluindo adrenalina, ativam a calicreína tumoral e podem &lt;em&gt;intensificar&lt;/em&gt; a liberação de mediadores, agravando a crise; devem ser evitadas como primeira linha, preferindo-se octreotida, volume e vasopressina se necessário. (C) morfina e atracúrio são exatamente os fármacos a evitar, por liberação histamínica. (D) corticoide e anti-histamínico têm papel meramente adjuvante e não bloqueiam a secreção tumoral, que é o mecanismo central da crise.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A crise tireotóxica manifesta-se com hipertermia, taquiarritmia, agitação e instabilidade hemodinâmica, e o principal diagnóstico diferencial no intraoperatório é a hipertermia maligna — afastada aqui pela ausência de rigidez, de hipercapnia progressiva e de elevação da creatinofosfoquinase.&lt;/p&gt;&lt;p&gt;O tratamento tem quatro frentes: bloquear a &lt;strong&gt;síntese&lt;/strong&gt; hormonal com tionamida (o propiltiouracil tem a vantagem adicional de inibir a conversão periférica de T4 em T3); bloquear a &lt;strong&gt;liberação&lt;/strong&gt; do hormônio pré-formado com iodo; bloquear os &lt;strong&gt;efeitos periféricos&lt;/strong&gt; com propranolol; e administrar &lt;strong&gt;hidrocortisona&lt;/strong&gt;, que reduz a conversão periférica e cobre a insuficiência adrenal relativa. A ordem importa: o iodo deve ser dado pelo menos uma hora &lt;em&gt;depois&lt;/em&gt; da tionamida, sob pena de servir de substrato para nova síntese hormonal. Acrescentam-se resfriamento externo, hidratação e tratamento do fator desencadeante.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a sequência e alimenta a síntese hormonal com o próprio iodo administrado. (B) os salicilatos deslocam o hormônio tireoidiano das proteínas carreadoras, elevando a fração livre, e devem ser evitados; prefere-se paracetamol. (C) postergar o betabloqueio deixa sem controle a taquiarritmia, que é a principal causa imediata de deterioração hemodinâmica.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A crise tireotóxica manifesta-se com hipertermia, taquiarritmia, agitação e instabilidade hemodinâmica, e o principal diagnóstico diferencial no intraoperatório é a hipertermia maligna, afastada aqui pela ausência de rigidez, de hipercapnia progressiva e de elevação da creatinofosfoquinase.&lt;/p&gt;&lt;p&gt;O tratamento tem quatro frentes: bloquear a &lt;strong&gt;síntese&lt;/strong&gt; hormonal com tionamida (o propiltiouracil tem a vantagem adicional de inibir a conversão periférica de T4 em T3); bloquear a &lt;strong&gt;liberação&lt;/strong&gt; do hormônio pré-formado com iodo; bloquear os &lt;strong&gt;efeitos periféricos&lt;/strong&gt; com propranolol; e administrar &lt;strong&gt;hidrocortisona&lt;/strong&gt;, que reduz a conversão periférica e cobre a insuficiência adrenal relativa. A ordem importa: o iodo deve ser dado pelo menos uma hora &lt;em&gt;depois&lt;/em&gt; da tionamida, sob pena de servir de substrato para nova síntese hormonal. Acrescentam-se resfriamento externo, hidratação e tratamento do fator desencadeante.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) inverte a sequência e alimenta a síntese hormonal com o próprio iodo administrado. (B) os salicilatos deslocam o hormônio tireoidiano das proteínas carreadoras, elevando a fração livre, e devem ser evitados; prefere-se paracetamol. (C) postergar o betabloqueio deixa sem controle a taquiarritmia, que é a principal causa imediata de deterioração hemodinâmica.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
@@ -13599,7 +13599,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Na doença renal crônica avançada, a capacidade de excretar potássio depende sobretudo da secreção distal mediada pela aldosterona. Fármacos que interferem nesse eixo somam efeitos: os &lt;strong&gt;inibidores da enzima conversora&lt;/strong&gt; reduzem a produção de aldosterona e a &lt;strong&gt;espironolactona&lt;/strong&gt; bloqueia diretamente o receptor mineralocorticoide no túbulo coletor. A associação, em rim com filtração de cerca de 20 mL/min, é uma das causas mais frequentes de hipercalemia grave no pré-operatório, e o paciente já apresenta potássio no limite superior, com acidose metabólica que favorece o desvio do íon para o extracelular.&lt;/p&gt;&lt;p&gt;Quanto à anemia, o alvo com eritropoetina é conservador — em torno de 10 a 11,5 g/dL —, porque a normalização da hemoglobina aumentou eventos tromboembólicos e cerebrovasculares nos estudos comparativos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) buscar hemoglobina acima de 13 g/dL contraria as metas recomendadas e amplia o risco trombótico. (B) os diuréticos de alça são justamente os mais úteis na doença renal crônica, por manterem eficácia com filtração reduzida; não causam acidose tubular renal, e tendem a produzir alcalose metabólica. (D) a furosemida pode converter oligúria em não oligúria, facilitando o manejo de volume, mas não altera a história natural da lesão renal aguda nem reduz a necessidade de diálise.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Na doença renal crônica avançada, a capacidade de excretar potássio depende sobretudo da secreção distal mediada pela aldosterona. Fármacos que interferem nesse eixo somam efeitos: os &lt;strong&gt;inibidores da enzima conversora&lt;/strong&gt; reduzem a produção de aldosterona e a &lt;strong&gt;espironolactona&lt;/strong&gt; bloqueia diretamente o receptor mineralocorticoide no túbulo coletor. A associação, em rim com filtração de cerca de 20 mL/min, é uma das causas mais frequentes de hipercalemia grave no pré-operatório, e o paciente já apresenta potássio no limite superior, com acidose metabólica que favorece o desvio do íon para o extracelular.&lt;/p&gt;&lt;p&gt;Quanto à anemia, o alvo com eritropoetina é conservador (em torno de 10 a 11,5 g/dL), porque a normalização da hemoglobina aumentou eventos tromboembólicos e cerebrovasculares nos estudos comparativos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) buscar hemoglobina acima de 13 g/dL contraria as metas recomendadas e amplia o risco trombótico. (B) os diuréticos de alça são justamente os mais úteis na doença renal crônica, por manterem eficácia com filtração reduzida; não causam acidose tubular renal, e tendem a produzir alcalose metabólica. (D) a furosemida pode converter oligúria em não oligúria, facilitando o manejo de volume, mas não altera a história natural da lesão renal aguda nem reduz a necessidade de diálise.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A distinção entre azotemia pré-renal e necrose tubular aguda apoia-se em um raciocínio simples: o túbulo íntegro, diante de hipoperfusão, responde reabsorvendo sódio e água com avidez; o túbulo lesado perde essa capacidade.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Pré-renal&lt;/strong&gt;: sódio urinário abaixo de 20 mEq/L, fração de excreção de sódio menor que 1%, osmolalidade urinária acima de 500 mOsm/kg, relação ureia/creatinina plasmática elevada e sedimento sem alterações — exatamente o conjunto apresentado.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Necrose tubular aguda&lt;/strong&gt;: sódio urinário acima de 40 mEq/L, fração de excreção de sódio maior que 2%, osmolalidade urinária próxima da plasmática e cilindros granulosos pigmentados.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A conduta é restaurar a perfusão renal com reposição volêmica guiada e suspender nefrotóxicos, evitando que o quadro funcional evolua para lesão estrutural.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a necrose tubular aguda cursaria com urina isostenúrica e sódio urinário elevado, além de cilindros no sedimento. (C) na obstrução, a urina tende a ser isostenúrica e a fração de excreção de sódio, elevada nas fases mais tardias; a osmolalidade alta não sugere obstrução. (D) a nefrite intersticial cursa tipicamente com piúria estéril, eosinofilúria e sódio urinário elevado, não com reabsorção ávida de sódio. Vale lembrar que o uso prévio de diurético invalida a interpretação da fração de excreção de sódio.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A distinção entre azotemia pré-renal e necrose tubular aguda apoia-se em um raciocínio simples: o túbulo íntegro, diante de hipoperfusão, responde reabsorvendo sódio e água com avidez; o túbulo lesado perde essa capacidade.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Pré-renal&lt;/strong&gt;: sódio urinário abaixo de 20 mEq/L, fração de excreção de sódio menor que 1%, osmolalidade urinária acima de 500 mOsm/kg, relação ureia/creatinina plasmática elevada e sedimento sem alterações, exatamente o conjunto apresentado.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Necrose tubular aguda&lt;/strong&gt;: sódio urinário acima de 40 mEq/L, fração de excreção de sódio maior que 2%, osmolalidade urinária próxima da plasmática e cilindros granulosos pigmentados.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;A conduta é restaurar a perfusão renal com reposição volêmica guiada e suspender nefrotóxicos, evitando que o quadro funcional evolua para lesão estrutural.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a necrose tubular aguda cursaria com urina isostenúrica e sódio urinário elevado, além de cilindros no sedimento. (C) na obstrução, a urina tende a ser isostenúrica e a fração de excreção de sódio, elevada nas fases mais tardias; a osmolalidade alta não sugere obstrução. (D) a nefrite intersticial cursa tipicamente com piúria estéril, eosinofilúria e sódio urinário elevado, não com reabsorção ávida de sódio. Vale lembrar que o uso prévio de diurético invalida a interpretação da fração de excreção de sódio.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q181" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>&lt;p&gt;No paciente com doença renal terminal, a escolha farmacológica privilegia moléculas cuja eliminação independa do rim. O &lt;strong&gt;cisatracúrio&lt;/strong&gt; é degradado sobretudo pela &lt;em&gt;eliminação de Hofmann&lt;/em&gt;, processo espontâneo dependente de pH e temperatura, com duração previsível na uremia; diferentemente do atracúrio, produz pouca laudanosina e não libera histamina de forma clinicamente relevante.&lt;/p&gt;&lt;p&gt;Entre os opioides, a &lt;strong&gt;morfina&lt;/strong&gt; gera &lt;em&gt;morfina-6-glicuronídeo&lt;/em&gt;, metabólito ativo de excreção renal que se acumula e prolonga a depressão respiratória — motivo para preferir fentanil, sufentanil ou remifentanil, cujas vias de eliminação não dependem do rim.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o pancurônio depende em grande parte da excreção renal e tem duração marcadamente prolongada na insuficiência renal, sendo uma das escolhas mais inadequadas nesse contexto. (C) a meperidina produz &lt;em&gt;normeperidina&lt;/em&gt;, metabólito neuroexcitatório de eliminação renal, associado a mioclonias e convulsões quando acumulado. (D) o suxametônio pode ser usado em dose única quando o potássio está controlado, mas eleva a caliemia em cerca de 0,5 mEq/L como em qualquer paciente, e doses repetidas na doença renal terminal são conduta insegura.&lt;/p&gt;</t>
+          <t>&lt;p&gt;No paciente com doença renal terminal, a escolha farmacológica privilegia moléculas cuja eliminação independa do rim. O &lt;strong&gt;cisatracúrio&lt;/strong&gt; é degradado sobretudo pela &lt;em&gt;eliminação de Hofmann&lt;/em&gt;, processo espontâneo dependente de pH e temperatura, com duração previsível na uremia; diferentemente do atracúrio, produz pouca laudanosina e não libera histamina de forma clinicamente relevante.&lt;/p&gt;&lt;p&gt;Entre os opioides, a &lt;strong&gt;morfina&lt;/strong&gt; gera &lt;em&gt;morfina-6-glicuronídeo&lt;/em&gt;, metabólito ativo de excreção renal que se acumula e prolonga a depressão respiratória, motivo para preferir fentanil, sufentanil ou remifentanil, cujas vias de eliminação não dependem do rim.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o pancurônio depende em grande parte da excreção renal e tem duração marcadamente prolongada na insuficiência renal, sendo uma das escolhas mais inadequadas nesse contexto. (C) a meperidina produz &lt;em&gt;normeperidina&lt;/em&gt;, metabólito neuroexcitatório de eliminação renal, associado a mioclonias e convulsões quando acumulado. (D) o suxametônio pode ser usado em dose única quando o potássio está controlado, mas eleva a caliemia em cerca de 0,5 mEq/L como em qualquer paciente, e doses repetidas na doença renal terminal são conduta insegura.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O clampeamento aórtico, sobretudo suprarrenal, reduz de forma abrupta o fluxo sanguíneo renal e ativa o sistema renina-angiotensina, com vasoconstrição intrarrenal que persiste mesmo após o desclampeamento. Somam-se ateroembolismo, resposta inflamatória e lesão de isquemia-reperfusão.&lt;/p&gt;&lt;p&gt;Décadas de investigação não confirmaram benefício de nenhum agente farmacológico específico. O que efetivamente protege o rim é &lt;strong&gt;fisiológico&lt;/strong&gt;: manter a volemia adequada e o débito cardíaco, evitar hipotensão sustentada e nefrotóxicos, e &lt;strong&gt;encurtar o tempo de clampeamento&lt;/strong&gt;, cuja duração é o preditor mais consistente de disfunção renal pós-operatória.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a dopamina em dose dita renal aumenta o fluxo urinário por efeito natriurético tubular, mas não previne lesão renal nem melhora desfechos, e acrescenta taquiarritmia e risco de isquemia miocárdica. (B) a furosemida pode converter oligúria em não oligúria e facilitar o controle volêmico, porém não protege o parênquima e pode agravar a lesão se induzir hipovolemia. (C) o manitol tem racional teórico — expansão volêmica, varredura de radicais livres e redução do edema tubular —, mas nunca demonstrou proteção consistente em estudos controlados e não deve ser a estratégia principal.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O clampeamento aórtico, sobretudo suprarrenal, reduz de forma abrupta o fluxo sanguíneo renal e ativa o sistema renina-angiotensina, com vasoconstrição intrarrenal que persiste mesmo após o desclampeamento. Somam-se ateroembolismo, resposta inflamatória e lesão de isquemia-reperfusão.&lt;/p&gt;&lt;p&gt;Décadas de investigação não confirmaram benefício de nenhum agente farmacológico específico. O que efetivamente protege o rim é &lt;strong&gt;fisiológico&lt;/strong&gt;: manter a volemia adequada e o débito cardíaco, evitar hipotensão sustentada e nefrotóxicos, e &lt;strong&gt;encurtar o tempo de clampeamento&lt;/strong&gt;, cuja duração é o preditor mais consistente de disfunção renal pós-operatória.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a dopamina em dose dita renal aumenta o fluxo urinário por efeito natriurético tubular, mas não previne lesão renal nem melhora desfechos, e acrescenta taquiarritmia e risco de isquemia miocárdica. (B) a furosemida pode converter oligúria em não oligúria e facilitar o controle volêmico, porém não protege o parênquima e pode agravar a lesão se induzir hipovolemia. (C) o manitol tem racional teórico (expansão volêmica, varredura de radicais livres e redução do edema tubular), mas nunca demonstrou proteção consistente em estudos controlados e não deve ser a estratégia principal.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q183" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A hipocalcemia por lesão ou desvascularização das paratireoides costuma manifestar-se entre 24 e 72 horas após tireoidectomia total, sobretudo quando houve esvaziamento cervical. A queda do cálcio iônico aumenta a excitabilidade neuromuscular — parestesias periorais, sinais de Chvostek e de Trousseau, tetania e, nos casos graves, laringoespasmo e convulsão — e prolonga o platô do potencial de ação, traduzido em &lt;strong&gt;alargamento do intervalo QT&lt;/strong&gt;, com risco de arritmia ventricular.&lt;/p&gt;&lt;p&gt;Diante de sintomas com cálcio iônico abaixo de 0,9 mmol/L, indica-se &lt;strong&gt;gluconato de cálcio a 10% por via endovenosa lenta&lt;/strong&gt;, sob monitorização, seguido de reposição oral com cálcio e calcitriol. A dosagem e a correção do magnésio são obrigatórias: a hipomagnesemia — presente aqui, com 1,3 mg/dL — reduz a secreção e a ação periférica do paratormônio e torna a hipocalcemia refratária.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a reposição oral isolada tem início demasiado lento para paciente já sintomática e com QT prolongado. (C) a alcalinização aumenta a ligação do cálcio à albumina e &lt;em&gt;reduz&lt;/em&gt; a fração ionizada, podendo precipitar tetania — é exatamente o oposto do desejado. (D) o magnésio precisa ser corrigido, mas em infusão lenta e como adjuvante; em bolus rápido causa hipotensão e não eleva o cálcio de imediato.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A hipocalcemia por lesão ou desvascularização das paratireoides costuma manifestar-se entre 24 e 72 horas após tireoidectomia total, sobretudo quando houve esvaziamento cervical. A queda do cálcio iônico aumenta a excitabilidade neuromuscular (parestesias periorais, sinais de Chvostek e de Trousseau, tetania e, nos casos graves, laringoespasmo e convulsão) e prolonga o platô do potencial de ação, traduzido em &lt;strong&gt;alargamento do intervalo QT&lt;/strong&gt;, com risco de arritmia ventricular.&lt;/p&gt;&lt;p&gt;Diante de sintomas com cálcio iônico abaixo de 0,9 mmol/L, indica-se &lt;strong&gt;gluconato de cálcio a 10% por via endovenosa lenta&lt;/strong&gt;, sob monitorização, seguido de reposição oral com cálcio e calcitriol. A dosagem e a correção do magnésio são obrigatórias: a hipomagnesemia (presente aqui, com 1,3 mg/dL) reduz a secreção e a ação periférica do paratormônio e torna a hipocalcemia refratária.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a reposição oral isolada tem início demasiado lento para paciente já sintomática e com QT prolongado. (C) a alcalinização aumenta a ligação do cálcio à albumina e &lt;em&gt;reduz&lt;/em&gt; a fração ionizada, podendo precipitar tetania; é exatamente o oposto do desejado. (D) o magnésio precisa ser corrigido, mas em infusão lenta e como adjuvante; em bolus rápido causa hipotensão e não eleva o cálcio de imediato.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Osmolaridade é uma propriedade físico-química mensurável; tonicidade depende de quais solutos são &lt;em&gt;efetivos&lt;/em&gt;, isto é, incapazes de cruzar livremente a membrana celular. A &lt;strong&gt;glicose a 5%&lt;/strong&gt; ilustra bem a diferença: com cerca de 278 mOsm/L, é praticamente isosmolar no frasco, mas a glicose é rapidamente captada e metabolizada, restando &lt;strong&gt;água livre&lt;/strong&gt; que se distribui por todos os compartimentos e expande o intracelular. Daí ser proscrita como solução de reposição volêmica e, sobretudo, no paciente neurocirúrgico, em que agrava o edema cerebral e ainda impõe a carga de hiperglicemia.&lt;/p&gt;&lt;p&gt;Para comparação, a salina a 0,9% tem osmolaridade calculada em torno de 308 mOsm/L e o Ringer lactato, cerca de 273 mOsm/L — este último discretamente &lt;em&gt;hipotônico&lt;/em&gt; em relação ao plasma, motivo pelo qual grandes volumes são evitados na hipertensão intracraniana.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o Ringer lactato é levemente hipotônico e, em grande volume, tende a aumentar a água cerebral, não a reduzi-la. (B) a osmolaridade da salina isotônica é de aproximadamente 308 mOsm/L, e ela é discretamente hipertônica em relação ao plasma. (D) o manitol &lt;em&gt;não&lt;/em&gt; atravessa a barreira hematoencefálica íntegra — é justamente essa impermeabilidade que cria o gradiente osmótico responsável por retirar água do parênquima cerebral.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Osmolaridade é uma propriedade físico-química mensurável; tonicidade depende de quais solutos são &lt;em&gt;efetivos&lt;/em&gt;, isto é, incapazes de cruzar livremente a membrana celular. A &lt;strong&gt;glicose a 5%&lt;/strong&gt; ilustra bem a diferença: com cerca de 278 mOsm/L, é praticamente isosmolar no frasco, mas a glicose é rapidamente captada e metabolizada, restando &lt;strong&gt;água livre&lt;/strong&gt; que se distribui por todos os compartimentos e expande o intracelular. Daí ser proscrita como solução de reposição volêmica e, sobretudo, no paciente neurocirúrgico, em que agrava o edema cerebral e ainda impõe a carga de hiperglicemia.&lt;/p&gt;&lt;p&gt;Para comparação, a salina a 0,9% tem osmolaridade calculada em torno de 308 mOsm/L e o Ringer lactato, cerca de 273 mOsm/L, este último discretamente &lt;em&gt;hipotônico&lt;/em&gt; em relação ao plasma, motivo pelo qual grandes volumes são evitados na hipertensão intracraniana.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o Ringer lactato é levemente hipotônico e, em grande volume, tende a aumentar a água cerebral, não a reduzi-la. (B) a osmolaridade da salina isotônica é de aproximadamente 308 mOsm/L, e ela é discretamente hipertônica em relação ao plasma. (D) o manitol &lt;em&gt;não&lt;/em&gt; atravessa a barreira hematoencefálica íntegra; é justamente essa impermeabilidade que cria o gradiente osmótico responsável por retirar água do parênquima cerebral.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A leitura sistemática começa pelo pH: 7,17 indica acidemia. O bicarbonato de 6 mEq/L identifica o componente metabólico como primário. Calcula-se então o &lt;strong&gt;ânion gap&lt;/strong&gt;: 134 − (94 + 6) = 34 mEq/L, muito acima do valor de referência em torno de 8 a 12 mEq/L, compatível com o acúmulo de cetoânions.&lt;/p&gt;&lt;p&gt;A adequação da resposta respiratória é verificada pela fórmula de Winter — PaCO2 esperada = 1,5 × bicarbonato + 8, com variação de 2 —, que fornece aqui 17 mmHg, com faixa aceitável de 15 a 19 mmHg. A PaCO2 medida de 17 mmHg está exatamente no valor previsto: a &lt;strong&gt;compensação respiratória é apropriada&lt;/strong&gt;, e não há distúrbio respiratório primário associado.&lt;/p&gt;&lt;p&gt;Vale ainda o delta-gap: a variação do ânion gap (22) é próxima da queda do bicarbonato (18), com razão em torno de 1,2, o que caracteriza acidose com ânion gap elevado pura, sem componente hiperclorêmico ou alcalose metabólica oculta.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a PaCO2 não está acima do previsto; coincide com o valor calculado. (C) o cloro está normal-baixo e não participa do ânion gap elevado, que decorre dos cetoânions. (D) a hipocapnia é resposta compensatória, e não distúrbio primário — rotulá-la de alcalose respiratória primária confunde compensação com distúrbio adicional.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A leitura sistemática começa pelo pH: 7,17 indica acidemia. O bicarbonato de 6 mEq/L identifica o componente metabólico como primário. Calcula-se então o &lt;strong&gt;ânion gap&lt;/strong&gt;: 134 − (94 + 6) = 34 mEq/L, muito acima do valor de referência em torno de 8 a 12 mEq/L, compatível com o acúmulo de cetoânions.&lt;/p&gt;&lt;p&gt;A adequação da resposta respiratória é verificada pela fórmula de Winter (PaCO2 esperada = 1,5 × bicarbonato + 8, com variação de 2), que fornece aqui 17 mmHg, com faixa aceitável de 15 a 19 mmHg. A PaCO2 medida de 17 mmHg está exatamente no valor previsto: a &lt;strong&gt;compensação respiratória é apropriada&lt;/strong&gt;, e não há distúrbio respiratório primário associado.&lt;/p&gt;&lt;p&gt;Vale ainda o delta-gap: a variação do ânion gap (22) é próxima da queda do bicarbonato (18), com razão em torno de 1,2, o que caracteriza acidose com ânion gap elevado pura, sem componente hiperclorêmico ou alcalose metabólica oculta.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a PaCO2 não está acima do previsto; coincide com o valor calculado. (C) o cloro está normal-baixo e não participa do ânion gap elevado, que decorre dos cetoânions. (D) a hipocapnia é resposta compensatória, e não distúrbio primário; rotulá-la de alcalose respiratória primária confunde compensação com distúrbio adicional.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q186" t="inlineStr">
@@ -14183,7 +14183,7 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A hipercalemia eleva o potencial de repouso da membrana, inativa canais de sódio e lentifica a condução. As manifestações eletrocardiográficas seguem progressão razoavelmente previsível: ondas T apiculadas e simétricas, achatamento e desaparecimento da onda P, alargamento do QRS e, por fim, o padrão sinusoidal que antecede a assistolia ou a fibrilação ventricular.&lt;/p&gt;&lt;p&gt;O tratamento organiza-se em três frentes:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Estabilizar a membrana&lt;/strong&gt; — gluconato ou cloreto de cálcio, que restauram o gradiente entre o potencial de repouso e o limiar de despolarização, com início em minutos e duração de 30 a 60 minutos. &lt;em&gt;Não reduz a caliemia.&lt;/em&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Deslocar potássio para o intracelular&lt;/strong&gt; — insulina com glicose, beta-2-agonista inalatório e bicarbonato quando há acidose metabólica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Remover potássio do organismo&lt;/strong&gt; — diurético, resina de troca e, no anúrico, hemodiálise, único método definitivo.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) confunde o mecanismo do cálcio com o da insulina; o cálcio não redistribui o íon. (C) o bicarbonato atua por redistribuição, é lento e pouco eficaz sem acidose importante, além de ofertar sódio ao paciente dialítico. (D) a insulina apenas redistribui o potássio, com efeito transitório; a remoção definitiva no anúrico depende da diálise.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A hipercalemia eleva o potencial de repouso da membrana, inativa canais de sódio e lentifica a condução. As manifestações eletrocardiográficas seguem progressão razoavelmente previsível: ondas T apiculadas e simétricas, achatamento e desaparecimento da onda P, alargamento do QRS e, por fim, o padrão sinusoidal que antecede a assistolia ou a fibrilação ventricular.&lt;/p&gt;&lt;p&gt;O tratamento organiza-se em três frentes:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Estabilizar a membrana&lt;/strong&gt;: gluconato ou cloreto de cálcio, que restauram o gradiente entre o potencial de repouso e o limiar de despolarização, com início em minutos e duração de 30 a 60 minutos. &lt;em&gt;Não reduz a caliemia.&lt;/em&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Deslocar potássio para o intracelular&lt;/strong&gt;: insulina com glicose, beta-2-agonista inalatório e bicarbonato quando há acidose metabólica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Remover potássio do organismo&lt;/strong&gt;: diurético, resina de troca e, no anúrico, hemodiálise, único método definitivo.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) confunde o mecanismo do cálcio com o da insulina; o cálcio não redistribui o íon. (C) o bicarbonato atua por redistribuição, é lento e pouco eficaz sem acidose importante, além de ofertar sódio ao paciente dialítico. (D) a insulina apenas redistribui o potássio, com efeito transitório; a remoção definitiva no anúrico depende da diálise.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
@@ -14256,7 +14256,7 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O paciente tem um distúrbio de base conhecido — &lt;strong&gt;acidose respiratória crônica&lt;/strong&gt; pela doença pulmonar obstrutiva — e um distúrbio agudo sobreposto pelos vômitos, que removem ácido clorídrico e geram &lt;strong&gt;alcalose metabólica&lt;/strong&gt;. O que denuncia a combinação é a incompatibilidade entre os números e qualquer compensação isolada.&lt;/p&gt;&lt;p&gt;Na acidose respiratória crônica, o bicarbonato sobe cerca de 3,5 mEq/L para cada 10 mmHg de PaCO2 acima de 40. Com PaCO2 de 58 mmHg, esperar-se-ia bicarbonato em torno de 30 mEq/L e pH discretamente &lt;em&gt;abaixo&lt;/em&gt; de 7,40. O valor observado, 42 mEq/L, excede em muito o previsto, e o pH resultante é alcalêmico — só explicável por um processo alcalinizante independente. A hipocloremia de 88 mEq/L e a hipocalemia de 3,0 mEq/L corroboram a perda gástrica. O ânion gap, de 8 mEq/L, é normal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) na alcalose respiratória a PaCO2 estaria &lt;em&gt;baixa&lt;/em&gt;, e não em 58 mmHg. (B) a hipoventilação compensatória da alcalose metabólica raramente ultrapassa PaCO2 de 55 mmHg e não se sustenta como explicação única em paciente com retenção crônica já documentada. (D) o ânion gap é normal e o bicarbonato está elevado, o que afasta acidose metabólica com ânion gap alto.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O paciente tem um distúrbio de base conhecido (&lt;strong&gt;acidose respiratória crônica&lt;/strong&gt; pela doença pulmonar obstrutiva) e um distúrbio agudo sobreposto pelos vômitos, que removem ácido clorídrico e geram &lt;strong&gt;alcalose metabólica&lt;/strong&gt;. O que denuncia a combinação é a incompatibilidade entre os números e qualquer compensação isolada.&lt;/p&gt;&lt;p&gt;Na acidose respiratória crônica, o bicarbonato sobe cerca de 3,5 mEq/L para cada 10 mmHg de PaCO2 acima de 40. Com PaCO2 de 58 mmHg, esperar-se-ia bicarbonato em torno de 30 mEq/L e pH discretamente &lt;em&gt;abaixo&lt;/em&gt; de 7,40. O valor observado, 42 mEq/L, excede em muito o previsto, e o pH resultante é alcalêmico, só explicável por um processo alcalinizante independente. A hipocloremia de 88 mEq/L e a hipocalemia de 3,0 mEq/L corroboram a perda gástrica. O ânion gap, de 8 mEq/L, é normal.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) na alcalose respiratória a PaCO2 estaria &lt;em&gt;baixa&lt;/em&gt;, e não em 58 mmHg. (B) a hipoventilação compensatória da alcalose metabólica raramente ultrapassa PaCO2 de 55 mmHg e não se sustenta como explicação única em paciente com retenção crônica já documentada. (D) o ânion gap é normal e o bicarbonato está elevado, o que afasta acidose metabólica com ânion gap alto.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A morte encefálica cursa com destruição do eixo hipotálamo-hipofisário, e o &lt;strong&gt;diabetes insípido central&lt;/strong&gt; ocorre na maioria dos doadores. O quadro é de poliúria maciça com urina diluída, hipernatremia progressiva, hipovolemia e instabilidade hemodinâmica, agravada pela perda do tônus simpático e pela hipotermia por falência da termorregulação.&lt;/p&gt;&lt;p&gt;O manejo tem duas frentes complementares. A &lt;strong&gt;vasopressina em infusão contínua&lt;/strong&gt; controla a poliúria e, pela ação em receptores V1, reduz de forma consistente a necessidade de catecolaminas — parte do conjunto de medidas de manutenção do doador que inclui reposição hormonal, aquecimento ativo e ventilação protetora. Em paralelo, repõe-se o &lt;strong&gt;déficit de água livre&lt;/strong&gt; com solução hipotônica, corrigindo o sódio gradualmente, já que a hipernatremia acentuada do doador associa-se a pior função do enxerto hepático.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) restringir fluidos em paciente com poliúria de 480 mL/h e hipernatremia de 167 mEq/L aprofunda a hipovolemia; escalonar vasopressor sobre volume inadequado compromete a perfusão dos órgãos a serem doados. (C) a salina a 0,9% tem sódio de 154 mEq/L e não corrige de modo eficiente hipernatremia dessa magnitude, além de ofertar carga adicional de cloro. (D) a furosemida agrava a poliúria e a perda de água livre, piorando a hipernatremia e a hipovolemia.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A morte encefálica cursa com destruição do eixo hipotálamo-hipofisário, e o &lt;strong&gt;diabetes insípido central&lt;/strong&gt; ocorre na maioria dos doadores. O quadro é de poliúria maciça com urina diluída, hipernatremia progressiva, hipovolemia e instabilidade hemodinâmica, agravada pela perda do tônus simpático e pela hipotermia por falência da termorregulação.&lt;/p&gt;&lt;p&gt;O manejo tem duas frentes complementares. A &lt;strong&gt;vasopressina em infusão contínua&lt;/strong&gt; controla a poliúria e, pela ação em receptores V1, reduz de forma consistente a necessidade de catecolaminas. Faz parte do conjunto de medidas de manutenção do doador que inclui reposição hormonal, aquecimento ativo e ventilação protetora. Em paralelo, repõe-se o &lt;strong&gt;déficit de água livre&lt;/strong&gt; com solução hipotônica, corrigindo o sódio gradualmente, já que a hipernatremia acentuada do doador associa-se a pior função do enxerto hepático.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) restringir fluidos em paciente com poliúria de 480 mL/h e hipernatremia de 167 mEq/L aprofunda a hipovolemia; escalonar vasopressor sobre volume inadequado compromete a perfusão dos órgãos a serem doados. (C) a salina a 0,9% tem sódio de 154 mEq/L e não corrige de modo eficiente hipernatremia dessa magnitude, além de ofertar carga adicional de cloro. (D) a furosemida agrava a poliúria e a perda de água livre, piorando a hipernatremia e a hipovolemia.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A transfusão maciça combina três agressões que se reforçam. O &lt;strong&gt;citrato&lt;/strong&gt; presente nos hemocomponentes quela o cálcio ionizado; com fluxo transfusional alto e metabolismo hepático comprometido — como no trauma hepático e na hipotermia —, instala-se hipocalcemia com repercussão sobre a contratilidade miocárdica, o tônus vascular e a própria cascata da coagulação, dependente de cálcio como fator IV. A &lt;strong&gt;hipotermia&lt;/strong&gt; reduz a atividade enzimática dos fatores e a função plaquetária, efeito que os testes laboratoriais realizados a 37 °C não detectam. E a &lt;strong&gt;hipofibrinogenemia&lt;/strong&gt; aparece precocemente, porque o fibrinogênio é o primeiro fator a atingir concentração crítica no sangramento maciço.&lt;/p&gt;&lt;p&gt;A conduta reúne as três correções: cálcio endovenoso guiado pelo cálcio iônico, reaquecimento ativo com fluidos aquecidos e manta térmica, e reposição de fibrinogênio com &lt;strong&gt;crioprecipitado&lt;/strong&gt; ou concentrado de fibrinogênio, com alvo em torno de 150 a 200 mg/dL no sangramento ativo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o plasma contém fibrinogênio em concentração próxima à plasmática e exigiria volumes proibitivos para elevá-lo de 88 mg/dL ao alvo. (B) a acidose é consequência da hipoperfusão e melhora com o controle do sangramento; o bicarbonato não corrige a coagulopatia e ainda reduz o cálcio ionizado. (C) plaquetas de 96.000/mm³ não explicam sangramento difuso; a hipofibrinogenemia, a hipocalcemia e a hipotermia são os fatores dominantes.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A transfusão maciça combina três agressões que se reforçam. O &lt;strong&gt;citrato&lt;/strong&gt; presente nos hemocomponentes quela o cálcio ionizado; com fluxo transfusional alto e metabolismo hepático comprometido (como no trauma hepático e na hipotermia), instala-se hipocalcemia com repercussão sobre a contratilidade miocárdica, o tônus vascular e a própria cascata da coagulação, dependente de cálcio como fator IV. A &lt;strong&gt;hipotermia&lt;/strong&gt; reduz a atividade enzimática dos fatores e a função plaquetária, efeito que os testes laboratoriais realizados a 37 °C não detectam. E a &lt;strong&gt;hipofibrinogenemia&lt;/strong&gt; aparece precocemente, porque o fibrinogênio é o primeiro fator a atingir concentração crítica no sangramento maciço.&lt;/p&gt;&lt;p&gt;A conduta reúne as três correções: cálcio endovenoso guiado pelo cálcio iônico, reaquecimento ativo com fluidos aquecidos e manta térmica, e reposição de fibrinogênio com &lt;strong&gt;crioprecipitado&lt;/strong&gt; ou concentrado de fibrinogênio, com alvo em torno de 150 a 200 mg/dL no sangramento ativo.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o plasma contém fibrinogênio em concentração próxima à plasmática e exigiria volumes proibitivos para elevá-lo de 88 mg/dL ao alvo. (B) a acidose é consequência da hipoperfusão e melhora com o controle do sangramento; o bicarbonato não corrige a coagulopatia e ainda reduz o cálcio ionizado. (C) plaquetas de 96.000/mm³ não explicam sangramento difuso; a hipofibrinogenemia, a hipocalcemia e a hipotermia são os fatores dominantes.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
@@ -14548,7 +14548,7 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A pressão coloidosmótica — ou oncótica — do plasma resulta das proteínas incapazes de atravessar livremente a parede capilar. Seu valor normal gira em torno de &lt;strong&gt;25 a 28 mmHg&lt;/strong&gt;, e a &lt;strong&gt;albumina&lt;/strong&gt; responde por cerca de 70% a 80% desse total, apesar de representar pouco mais da metade da massa proteica: por ter peso molecular menor que o das globulinas, contribui com mais partículas por grama e ainda soma o efeito Gibbs-Donnan, decorrente de sua carga negativa.&lt;/p&gt;&lt;p&gt;Na equação de Starling, a &lt;strong&gt;pressão hidrostática capilar favorece a filtração&lt;/strong&gt; para o interstício, enquanto a pressão oncótica plasmática favorece a reabsorção. O modelo revisado atribui ao &lt;strong&gt;glicocálix&lt;/strong&gt; o papel de barreira efetiva: o gradiente oncótico relevante é o que existe entre o plasma e o espaço subglicocálix, e sua degradação — por sepse, trauma, isquemia-reperfusão ou hipervolemia com liberação de peptídeo natriurético — aumenta o extravasamento de fluido e de proteína.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o valor de 45 mmHg é muito superior ao real, e o principal determinante é a albumina, não as globulinas. (B) o aumento da pressão hidrostática capilar &lt;em&gt;aumenta&lt;/em&gt; a filtração para o interstício, mecanismo do edema na congestão venosa. (D) a lesão do glicocálix &lt;em&gt;aumenta&lt;/em&gt; a permeabilidade capilar e o extravasamento, sendo um dos mecanismos do edema na sepse.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A pressão coloidosmótica (ou oncótica) do plasma resulta das proteínas incapazes de atravessar livremente a parede capilar. Seu valor normal gira em torno de &lt;strong&gt;25 a 28 mmHg&lt;/strong&gt;, e a &lt;strong&gt;albumina&lt;/strong&gt; responde por cerca de 70% a 80% desse total, apesar de representar pouco mais da metade da massa proteica: por ter peso molecular menor que o das globulinas, contribui com mais partículas por grama e ainda soma o efeito Gibbs-Donnan, decorrente de sua carga negativa.&lt;/p&gt;&lt;p&gt;Na equação de Starling, a &lt;strong&gt;pressão hidrostática capilar favorece a filtração&lt;/strong&gt; para o interstício, enquanto a pressão oncótica plasmática favorece a reabsorção. O modelo revisado atribui ao &lt;strong&gt;glicocálix&lt;/strong&gt; o papel de barreira efetiva: o gradiente oncótico relevante é o que existe entre o plasma e o espaço subglicocálix, e sua degradação por sepse, trauma, isquemia-reperfusão ou hipervolemia com liberação de peptídeo natriurético aumenta o extravasamento de fluido e de proteína.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o valor de 45 mmHg é muito superior ao real, e o principal determinante é a albumina, não as globulinas. (B) o aumento da pressão hidrostática capilar &lt;em&gt;aumenta&lt;/em&gt; a filtração para o interstício, mecanismo do edema na congestão venosa. (D) a lesão do glicocálix &lt;em&gt;aumenta&lt;/em&gt; a permeabilidade capilar e o extravasamento, sendo um dos mecanismos do edema na sepse.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
@@ -14621,7 +14621,7 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A tolerância à anemia crônica depende de mecanismos que preservam a oferta e a utilização de oxigênio apesar da queda do conteúdo arterial. O eritrócito responde aumentando a síntese de &lt;strong&gt;2,3-difosfoglicerato&lt;/strong&gt;, que se liga à hemoglobina desoxigenada e estabiliza sua conformação de baixa afinidade. O resultado é o &lt;strong&gt;desvio da curva de dissociação para a direita&lt;/strong&gt;, com elevação da P50 e maior liberação de oxigênio no capilar tecidual para a mesma pressão parcial.&lt;/p&gt;&lt;p&gt;Somam-se a esse mecanismo o &lt;strong&gt;aumento do débito cardíaco&lt;/strong&gt; — favorecido pela redução da viscosidade e pela queda da resistência vascular sistêmica —, a redistribuição do fluxo para territórios de alta extração e o aumento da extração tecidual, que em repouso parte de cerca de 25% e dispõe de ampla reserva. A conduta pré-operatória adequada nessa paciente é corrigir a ferropenia com ferro, preferencialmente endovenoso, dado o intervalo disponível até a cirurgia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o débito cardíaco &lt;em&gt;aumenta&lt;/em&gt; na anemia crônica; a menor viscosidade eleva o retorno venoso e reduz a pós-carga. (C) o desvio para a esquerda aumenta a afinidade e &lt;em&gt;dificulta&lt;/em&gt; a liberação tecidual de oxigênio, sendo o oposto do compensatório. (D) a extração em repouso não alcança valores tão extremos; taxas próximas de 90% indicam esgotamento da reserva e limiar de metabolismo anaeróbio.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A tolerância à anemia crônica depende de mecanismos que preservam a oferta e a utilização de oxigênio apesar da queda do conteúdo arterial. O eritrócito responde aumentando a síntese de &lt;strong&gt;2,3-difosfoglicerato&lt;/strong&gt;, que se liga à hemoglobina desoxigenada e estabiliza sua conformação de baixa afinidade. O resultado é o &lt;strong&gt;desvio da curva de dissociação para a direita&lt;/strong&gt;, com elevação da P50 e maior liberação de oxigênio no capilar tecidual para a mesma pressão parcial.&lt;/p&gt;&lt;p&gt;Somam-se a esse mecanismo o &lt;strong&gt;aumento do débito cardíaco&lt;/strong&gt; (favorecido pela redução da viscosidade e pela queda da resistência vascular sistêmica), a redistribuição do fluxo para territórios de alta extração e o aumento da extração tecidual, que em repouso parte de cerca de 25% e dispõe de ampla reserva. A conduta pré-operatória adequada nessa paciente é corrigir a ferropenia com ferro, preferencialmente endovenoso, dado o intervalo disponível até a cirurgia.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o débito cardíaco &lt;em&gt;aumenta&lt;/em&gt; na anemia crônica; a menor viscosidade eleva o retorno venoso e reduz a pós-carga. (C) o desvio para a esquerda aumenta a afinidade e &lt;em&gt;dificulta&lt;/em&gt; a liberação tecidual de oxigênio, sendo o oposto do compensatório. (D) a extração em repouso não alcança valores tão extremos; taxas próximas de 90% indicam esgotamento da reserva e limiar de metabolismo anaeróbio.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A recusa de hemocomponentes por paciente adulto, capaz e informado deve ser respeitada, e o preparo se desloca inteiramente para a &lt;strong&gt;medicina de conservação sanguínea&lt;/strong&gt;. Um intervalo de quatro semanas é tempo suficiente para uma estratégia estruturada:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Otimização pré-operatória da massa eritrocitária&lt;/strong&gt; — ferro endovenoso, indicado pela ferritina baixa, associado a eritropoetina quando necessário.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Redução do sangramento intraoperatório&lt;/strong&gt; — ácido tranexâmico, técnica cirúrgica meticulosa, normotermia, hipotensão controlada quando apropriada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Técnicas de circuito contínuo&lt;/strong&gt; — recuperação intraoperatória de sangue e hemodiluição normovolêmica aguda, aceitas por muitos pacientes desde que mantida a continuidade com a circulação; a decisão é individual e deve ser documentada antes.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Limiar transfusional restritivo&lt;/strong&gt; e minimização de coletas laboratoriais.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) buscar autorização judicial preventiva contra a vontade expressa de adulto capaz desconsidera a autonomia e não é a via adequada de planejamento. (B) transfundir à revelia de recusa prévia, documentada e reiterada por paciente capaz configura violação do consentimento; a situação difere da do menor de idade sob responsabilidade dos pais. (C) exigir hemoglobina de 10 g/dL como condição para operar é limiar arbitrário e adia sem justificativa a cirurgia oncológica, quando o correto é otimizar em paralelo ao planejamento.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A recusa de hemocomponentes por paciente adulto, capaz e informado deve ser respeitada, e o preparo se desloca inteiramente para a &lt;strong&gt;medicina de conservação sanguínea&lt;/strong&gt;. Um intervalo de quatro semanas é tempo suficiente para uma estratégia estruturada:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Otimização pré-operatória da massa eritrocitária&lt;/strong&gt;: ferro endovenoso, indicado pela ferritina baixa, associado a eritropoetina quando necessário.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Redução do sangramento intraoperatório&lt;/strong&gt;: ácido tranexâmico, técnica cirúrgica meticulosa, normotermia, hipotensão controlada quando apropriada.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Técnicas de circuito contínuo&lt;/strong&gt;: recuperação intraoperatória de sangue e hemodiluição normovolêmica aguda, aceitas por muitos pacientes desde que mantida a continuidade com a circulação; a decisão é individual e deve ser documentada antes.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Limiar transfusional restritivo&lt;/strong&gt; e minimização de coletas laboratoriais.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) buscar autorização judicial preventiva contra a vontade expressa de adulto capaz desconsidera a autonomia e não é a via adequada de planejamento. (B) transfundir à revelia de recusa prévia, documentada e reiterada por paciente capaz configura violação do consentimento; a situação difere da do menor de idade sob responsabilidade dos pais. (C) exigir hemoglobina de 10 g/dL como condição para operar é limiar arbitrário e adia sem justificativa a cirurgia oncológica, quando o correto é otimizar em paralelo ao planejamento.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O poder expansor de uma solução depende de sua distribuição pelos compartimentos. Os &lt;strong&gt;cristaloides isotônicos&lt;/strong&gt; distribuem-se por todo o extracelular, e apenas cerca de um quarto a um terço do volume infundido permanece no intravascular após o equilíbrio — daí a regra prática de repor perda sanguínea em proporção aproximada de &lt;strong&gt;três para um&lt;/strong&gt;. Os &lt;strong&gt;coloides&lt;/strong&gt;, retidos por mais tempo no plasma pela pressão oncótica que exercem, repõem em proporção próxima de &lt;strong&gt;um para um&lt;/strong&gt;, com duração de efeito variável conforme a molécula e a integridade do glicocálix.&lt;/p&gt;&lt;p&gt;Além da perda sanguínea, a reposição deve considerar o jejum, a manutenção e as perdas relacionadas ao trauma cirúrgico, tradicionalmente estimadas em 4 a 6 mL/kg/h nas laparotomias de grande porte. Estimativas mais altas, herdadas da noção de terceiro espaço, foram revistas e hoje se prefere reposição guiada por metas, com atenção aos índices dinâmicos — a variação de pressão de pulso de 9% descrita sugere que não há responsividade a volume no momento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a proporção de um para um subestima grosseiramente a necessidade, pois ignora a redistribuição do cristaloide para o interstício. (C) o cristaloide expande o plasma de forma mensurável, ainda que transitória e parcial. (D) 15 mL/kg/h é estimativa exagerada, e a solução glicosada não é adequada para reposição volêmica, por comportar-se como água livre e causar hiperglicemia.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O poder expansor de uma solução depende de sua distribuição pelos compartimentos. Os &lt;strong&gt;cristaloides isotônicos&lt;/strong&gt; distribuem-se por todo o extracelular, e apenas cerca de um quarto a um terço do volume infundido permanece no intravascular após o equilíbrio; daí a regra prática de repor perda sanguínea em proporção aproximada de &lt;strong&gt;três para um&lt;/strong&gt;. Os &lt;strong&gt;coloides&lt;/strong&gt;, retidos por mais tempo no plasma pela pressão oncótica que exercem, repõem em proporção próxima de &lt;strong&gt;um para um&lt;/strong&gt;, com duração de efeito variável conforme a molécula e a integridade do glicocálix.&lt;/p&gt;&lt;p&gt;Além da perda sanguínea, a reposição deve considerar o jejum, a manutenção e as perdas relacionadas ao trauma cirúrgico, tradicionalmente estimadas em 4 a 6 mL/kg/h nas laparotomias de grande porte. Estimativas mais altas, herdadas da noção de terceiro espaço, foram revistas e hoje se prefere reposição guiada por metas, com atenção aos índices dinâmicos: a variação de pressão de pulso de 9% descrita sugere que não há responsividade a volume no momento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a proporção de um para um subestima grosseiramente a necessidade, pois ignora a redistribuição do cristaloide para o interstício. (C) o cristaloide expande o plasma de forma mensurável, ainda que transitória e parcial. (D) 15 mL/kg/h é estimativa exagerada, e a solução glicosada não é adequada para reposição volêmica, por comportar-se como água livre e causar hiperglicemia.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q196" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Com a triagem sorológica e os testes de ácidos nucleicos, o risco residual de transmissão viral tornou-se da ordem de um em milhões de unidades. O que restou como ameaça dominante são os eventos não infecciosos, e entre os fatais destaca-se a &lt;strong&gt;reação hemolítica aguda por incompatibilidade ABO&lt;/strong&gt;, cuja causa quase invariável não é laboratorial, mas &lt;strong&gt;humana&lt;/strong&gt;: troca de amostra na coleta, rotulagem incorreta do tubo ou administração da bolsa ao paciente errado.&lt;/p&gt;&lt;p&gt;É por isso que a conferência dupla à beira do leito, imediatamente antes da instalação, é a barreira de segurança mais importante do processo. No paciente anestesiado, os sinais precoces — dor, calafrio, dor lombar — ficam mascarados, e a reação pode manifestar-se apenas como hipotensão inexplicada, hemoglobinúria e sangramento difuso por coagulação intravascular disseminada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o risco residual de hepatite C é hoje extremamente baixo e não figura entre os riscos mais frequentes. (C) a contaminação bacteriana é mais frequente nos concentrados de plaquetas, justamente porque são estocados em temperatura ambiente, ao redor de 20 a 24 °C, o que favorece a proliferação; a estocagem a 4 °C das hemácias é fator protetor. (D) a hemólise intravascular aguda grave decorre tipicamente de incompatibilidade ABO, mediada por anticorpos naturais da classe IgM fixadores de complemento; a aloimunização Rh cursa em geral com hemólise extravascular e tardia.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Com a triagem sorológica e os testes de ácidos nucleicos, o risco residual de transmissão viral tornou-se da ordem de um em milhões de unidades. O que restou como ameaça dominante são os eventos não infecciosos, e entre os fatais destaca-se a &lt;strong&gt;reação hemolítica aguda por incompatibilidade ABO&lt;/strong&gt;, cuja causa quase invariável não é laboratorial, mas &lt;strong&gt;humana&lt;/strong&gt;: troca de amostra na coleta, rotulagem incorreta do tubo ou administração da bolsa ao paciente errado.&lt;/p&gt;&lt;p&gt;É por isso que a conferência dupla à beira do leito, imediatamente antes da instalação, é a barreira de segurança mais importante do processo. No paciente anestesiado, os sinais precoces (dor, calafrio, dor lombar) ficam mascarados, e a reação pode manifestar-se apenas como hipotensão inexplicada, hemoglobinúria e sangramento difuso por coagulação intravascular disseminada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o risco residual de hepatite C é hoje extremamente baixo e não figura entre os riscos mais frequentes. (C) a contaminação bacteriana é mais frequente nos concentrados de plaquetas, justamente porque são estocados em temperatura ambiente, ao redor de 20 a 24 °C, o que favorece a proliferação; a estocagem a 4 °C das hemácias é fator protetor. (D) a hemólise intravascular aguda grave decorre tipicamente de incompatibilidade ABO, mediada por anticorpos naturais da classe IgM fixadores de complemento; a aloimunização Rh cursa em geral com hemólise extravascular e tardia.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O hematoma espinhal é complicação rara e devastadora, e sua prevenção baseia-se em intervalos de segurança entre o antitrombótico e a punção ou a retirada do cateter. Para a heparina de baixo peso molecular, o intervalo depende da dose:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Dose profilática&lt;/strong&gt; — aguardar cerca de &lt;strong&gt;12 horas&lt;/strong&gt; após a última administração.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Dose terapêutica&lt;/strong&gt;, como 1 mg/kg a cada 12 horas ou 1,5 mg/kg ao dia — aguardar pelo menos &lt;strong&gt;24 horas&lt;/strong&gt;, prazo que deve ser ampliado quando há disfunção renal, já que a eliminação é predominantemente renal.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;No caso, a última dose foi às 20 horas e a cirurgia está marcada para as 8 horas, ou seja, apenas 12 horas depois: a punção deve ser adiada para completar 24 horas, ou opta-se por anestesia geral. Após a punção, a reintrodução de dose terapêutica respeita intervalo mínimo de 24 horas, e cateteres não devem permanecer com o paciente em anticoagulação plena.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) aplica à dose terapêutica o intervalo da dose profilática, erro conceitual frequente. (B) a dosagem de atividade anti-Xa não é validada como critério de liberação para punção neuroaxial e não substitui o intervalo temporal. (C) a heparina de baixo peso molecular altera pouco o tempo de tromboplastina parcial ativado, que não serve para monitorá-la nem para autorizar o bloqueio.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O hematoma espinhal é complicação rara e devastadora, e sua prevenção baseia-se em intervalos de segurança entre o antitrombótico e a punção ou a retirada do cateter. Para a heparina de baixo peso molecular, o intervalo depende da dose:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Dose profilática&lt;/strong&gt;: aguardar cerca de &lt;strong&gt;12 horas&lt;/strong&gt; após a última administração.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Dose terapêutica&lt;/strong&gt;, como 1 mg/kg a cada 12 horas ou 1,5 mg/kg ao dia: aguardar pelo menos &lt;strong&gt;24 horas&lt;/strong&gt;, prazo que deve ser ampliado quando há disfunção renal, já que a eliminação é predominantemente renal.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;No caso, a última dose foi às 20 horas e a cirurgia está marcada para as 8 horas, ou seja, apenas 12 horas depois: a punção deve ser adiada para completar 24 horas, ou opta-se por anestesia geral. Após a punção, a reintrodução de dose terapêutica respeita intervalo mínimo de 24 horas, e cateteres não devem permanecer com o paciente em anticoagulação plena.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) aplica à dose terapêutica o intervalo da dose profilática, erro conceitual frequente. (B) a dosagem de atividade anti-Xa não é validada como critério de liberação para punção neuroaxial e não substitui o intervalo temporal. (C) a heparina de baixo peso molecular altera pouco o tempo de tromboplastina parcial ativado, que não serve para monitorá-la nem para autorizar o bloqueio.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q198" t="inlineStr">
@@ -14986,7 +14986,7 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O descolamento prematuro de placenta é causa clássica de &lt;strong&gt;coagulação intravascular disseminada&lt;/strong&gt; obstétrica: a exposição de fator tecidual placentário desencadeia geração maciça de trombina, com consumo de fatores e plaquetas, fibrinólise secundária e elevação dos produtos de degradação da fibrina. Na gestante, o fibrinogênio basal é fisiologicamente alto — em torno de 400 a 600 mg/dL —, de modo que um valor de 78 mg/dL representa consumo muito intenso e é o melhor preditor laboratorial de gravidade da hemorragia.&lt;/p&gt;&lt;p&gt;O tratamento associa controle da causa obstétrica, reposição volêmica, antifibrinolítico e correção da hipofibrinogenemia. O &lt;strong&gt;crioprecipitado&lt;/strong&gt; é a fração obtida do descongelamento lento do plasma e concentra &lt;em&gt;fibrinogênio, fator VIII, fator XIII, fator de von Willebrand e fibronectina&lt;/em&gt;, permitindo elevar o fibrinogênio com pequeno volume; alternativamente, usa-se concentrado de fibrinogênio.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) descreve o conteúdo do complexo protrombínico, e não o do crioprecipitado; o crioprecipitado não contém os fatores dependentes de vitamina K em concentração terapêutica. (C) o complexo protrombínico não fornece fibrinogênio e, isoladamente, ainda acrescenta carga pró-trombótica. (D) a heparina só é cogitada em formas predominantemente trombóticas da coagulação intravascular disseminada; diante de sangramento ativo, é conduta perigosa.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O descolamento prematuro de placenta é causa clássica de &lt;strong&gt;coagulação intravascular disseminada&lt;/strong&gt; obstétrica: a exposição de fator tecidual placentário desencadeia geração maciça de trombina, com consumo de fatores e plaquetas, fibrinólise secundária e elevação dos produtos de degradação da fibrina. Na gestante, o fibrinogênio basal é fisiologicamente alto, em torno de 400 a 600 mg/dL, de modo que um valor de 78 mg/dL representa consumo muito intenso e é o melhor preditor laboratorial de gravidade da hemorragia.&lt;/p&gt;&lt;p&gt;O tratamento associa controle da causa obstétrica, reposição volêmica, antifibrinolítico e correção da hipofibrinogenemia. O &lt;strong&gt;crioprecipitado&lt;/strong&gt; é a fração obtida do descongelamento lento do plasma e concentra &lt;em&gt;fibrinogênio, fator VIII, fator XIII, fator de von Willebrand e fibronectina&lt;/em&gt;, permitindo elevar o fibrinogênio com pequeno volume; alternativamente, usa-se concentrado de fibrinogênio.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) descreve o conteúdo do complexo protrombínico, e não o do crioprecipitado; o crioprecipitado não contém os fatores dependentes de vitamina K em concentração terapêutica. (C) o complexo protrombínico não fornece fibrinogênio e, isoladamente, ainda acrescenta carga pró-trombótica. (D) a heparina só é cogitada em formas predominantemente trombóticas da coagulação intravascular disseminada; diante de sangramento ativo, é conduta perigosa.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A hepatopatia avançada produz um estado de &lt;strong&gt;reequilíbrio hemostático&lt;/strong&gt;, e não de anticoagulação simples. O fígado sintetiza tanto os fatores pró-coagulantes — II, V, VII, IX, X — quanto os anticoagulantes naturais: proteína C, proteína S e antitrombina. A queda é paralela, de modo que a geração global de trombina pode permanecer próxima do normal, ainda que a razão normalizada internacional esteja alargada.&lt;/p&gt;&lt;p&gt;O teste de protrombina foi criado e calibrado para monitorar antagonistas da vitamina K e mede apenas a via extrínseca até a formação inicial de fibrina, ignorando completamente os anticoagulantes naturais. Por isso &lt;strong&gt;não prediz risco de sangramento na cirrose&lt;/strong&gt;, e a transfusão profilática de plasma guiada por ela é ineficaz, além de provocar sobrecarga volêmica com aumento da pressão portal e agravamento do sangramento. Testes viscoelásticos e a dosagem de fibrinogênio informam muito mais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) perseguir razão normalizada internacional abaixo de 1,5 com plasma é conduta abandonada, de baixo rendimento e risco relevante. (C) o fator VIII é sintetizado sobretudo no endotélio e encontra-se &lt;em&gt;elevado&lt;/em&gt; na cirrose, tal como o fator de von Willebrand, contribuindo para o reequilíbrio e até para trombose. (D) a vitamina K corrige a coagulopatia por colestase ou desnutrição, mas não a insuficiência de síntese hepatocelular, e seu efeito leva de 12 a 24 horas.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A hepatopatia avançada produz um estado de &lt;strong&gt;reequilíbrio hemostático&lt;/strong&gt;, e não de anticoagulação simples. O fígado sintetiza tanto os fatores pró-coagulantes (II, V, VII, IX, X) quanto os anticoagulantes naturais: proteína C, proteína S e antitrombina. A queda é paralela, de modo que a geração global de trombina pode permanecer próxima do normal, ainda que a razão normalizada internacional esteja alargada.&lt;/p&gt;&lt;p&gt;O teste de protrombina foi criado e calibrado para monitorar antagonistas da vitamina K e mede apenas a via extrínseca até a formação inicial de fibrina, ignorando completamente os anticoagulantes naturais. Por isso &lt;strong&gt;não prediz risco de sangramento na cirrose&lt;/strong&gt;, e a transfusão profilática de plasma guiada por ela é ineficaz, além de provocar sobrecarga volêmica com aumento da pressão portal e agravamento do sangramento. Testes viscoelásticos e a dosagem de fibrinogênio informam muito mais.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) perseguir razão normalizada internacional abaixo de 1,5 com plasma é conduta abandonada, de baixo rendimento e risco relevante. (C) o fator VIII é sintetizado sobretudo no endotélio e encontra-se &lt;em&gt;elevado&lt;/em&gt; na cirrose, tal como o fator de von Willebrand, contribuindo para o reequilíbrio e até para trombose. (D) a vitamina K corrige a coagulopatia por colestase ou desnutrição, mas não a insuficiência de síntese hepatocelular, e seu efeito leva de 12 a 24 horas.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A infecção de vias aéreas superiores aumenta a incidência de &lt;strong&gt;eventos respiratórios adversos&lt;/strong&gt; perioperatórios — laringoespasmo, broncoespasmo, dessaturação, tosse e estridor — porque a inflamação viral produz hiper-reatividade das vias aéreas que persiste por até &lt;strong&gt;quatro a seis semanas&lt;/strong&gt; após a resolução dos sintomas. Adiar por poucos dias, portanto, não elimina o risco e apenas transfere o problema.&lt;/p&gt;&lt;p&gt;A decisão é individualizada. Deve-se &lt;strong&gt;adiar&lt;/strong&gt; quando há sinais de doença grave ou de acometimento de vias aéreas inferiores: febre acima de 38 graus, secreção purulenta, tosse produtiva, sibilos, letargia, comprometimento do estado geral ou criança com comorbidade relevante. Em criança &lt;strong&gt;hígida, afebril, ativa e com secreção clara&lt;/strong&gt;, especialmente quando a coriza é praticamente contínua — como ocorre justamente na hipertrofia adenoamigdaliana que motiva a cirurgia —, prosseguir é razoável.&lt;/p&gt;&lt;p&gt;Reduz-se o risco preferindo a máscara facial ou a máscara laríngea à intubação quando o procedimento permite, hidratando bem, evitando extubação em plano superficial e considerando lidocaína venosa e salbutamol inalatório.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) não há contraindicação absoluta; o critério é clínico. (B) a intubação é o fator que mais aumenta eventos respiratórios nesse cenário, e não protege. (C) 48 horas não são suficientes para reverter a hiper-reatividade brônquica.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A infecção de vias aéreas superiores aumenta a incidência de &lt;strong&gt;eventos respiratórios adversos&lt;/strong&gt; perioperatórios (laringoespasmo, broncoespasmo, dessaturação, tosse e estridor), porque a inflamação viral produz hiper-reatividade das vias aéreas que persiste por até &lt;strong&gt;quatro a seis semanas&lt;/strong&gt; após a resolução dos sintomas. Adiar por poucos dias, portanto, não elimina o risco e apenas transfere o problema.&lt;/p&gt;&lt;p&gt;A decisão é individualizada. Deve-se &lt;strong&gt;adiar&lt;/strong&gt; quando há sinais de doença grave ou de acometimento de vias aéreas inferiores: febre acima de 38 graus, secreção purulenta, tosse produtiva, sibilos, letargia, comprometimento do estado geral ou criança com comorbidade relevante. Em criança &lt;strong&gt;hígida, afebril, ativa e com secreção clara&lt;/strong&gt;, especialmente quando a coriza é praticamente contínua (como ocorre justamente na hipertrofia adenoamigdaliana que motiva a cirurgia), prosseguir é razoável.&lt;/p&gt;&lt;p&gt;Reduz-se o risco preferindo a máscara facial ou a máscara laríngea à intubação quando o procedimento permite, hidratando bem, evitando extubação em plano superficial e considerando lidocaína venosa e salbutamol inalatório.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) não há contraindicação absoluta; o critério é clínico. (B) a intubação é o fator que mais aumenta eventos respiratórios nesse cenário, e não protege. (C) 48 horas não são suficientes para reverter a hiper-reatividade brônquica.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -16008,7 +16008,7 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;síndrome de embolia gordurosa&lt;/strong&gt; é complicação de fraturas de ossos longos e da pelve, especialmente quando há retardo na fixação. Glóbulos de gordura da medula óssea alcançam a circulação venosa e o leito pulmonar; a lesão decorre tanto da obstrução mecânica quanto da hidrólise dos triglicerídeos em ácidos graxos livres, que produzem pneumonite química e resposta inflamatória sistêmica.&lt;/p&gt;&lt;p&gt;O quadro caracteriza-se por uma &lt;strong&gt;tríade&lt;/strong&gt; que surge tipicamente entre &lt;strong&gt;12 e 72 horas&lt;/strong&gt; após o trauma: &lt;strong&gt;insuficiência respiratória hipoxêmica&lt;/strong&gt;, &lt;strong&gt;alterações neurológicas&lt;/strong&gt; (confusão, agitação, rebaixamento) e &lt;strong&gt;rash petequial&lt;/strong&gt; em tórax superior, axilas, pescoço e conjuntivas — o achado mais específico, presente em menos da metade dos casos. Podem ocorrer febre, taquicardia, trombocitopenia e anemia.&lt;/p&gt;&lt;p&gt;O tratamento é &lt;strong&gt;de suporte&lt;/strong&gt;: oxigenoterapia, ventilação com pressão positiva quando necessária, estabilidade hemodinâmica e correção de coagulopatia. A medida preventiva de maior impacto é a &lt;strong&gt;fixação precoce das fraturas&lt;/strong&gt;. Corticoide em altas doses não tem indicação estabelecida como tratamento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a contusão pulmonar exige trauma torácico direto, ausente aqui, e não se trata com drenagem. (C) o pneumotórax hipertensivo cursa com abolição unilateral do murmúrio, desvio de traqueia e colapso hemodinâmico. (D) o tromboembolismo raramente cursa com petéquias e alteração neurológica precoce, e a trombólise em politraumatizado recente é de altíssimo risco.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;síndrome de embolia gordurosa&lt;/strong&gt; é complicação de fraturas de ossos longos e da pelve, especialmente quando há retardo na fixação. Glóbulos de gordura da medula óssea alcançam a circulação venosa e o leito pulmonar; a lesão decorre tanto da obstrução mecânica quanto da hidrólise dos triglicerídeos em ácidos graxos livres, que produzem pneumonite química e resposta inflamatória sistêmica.&lt;/p&gt;&lt;p&gt;O quadro caracteriza-se por uma &lt;strong&gt;tríade&lt;/strong&gt; que surge tipicamente entre &lt;strong&gt;12 e 72 horas&lt;/strong&gt; após o trauma: &lt;strong&gt;insuficiência respiratória hipoxêmica&lt;/strong&gt;, &lt;strong&gt;alterações neurológicas&lt;/strong&gt; (confusão, agitação, rebaixamento) e &lt;strong&gt;rash petequial&lt;/strong&gt; em tórax superior, axilas, pescoço e conjuntivas; este é o achado mais específico, presente em menos da metade dos casos. Podem ocorrer febre, taquicardia, trombocitopenia e anemia.&lt;/p&gt;&lt;p&gt;O tratamento é &lt;strong&gt;de suporte&lt;/strong&gt;: oxigenoterapia, ventilação com pressão positiva quando necessária, estabilidade hemodinâmica e correção de coagulopatia. A medida preventiva de maior impacto é a &lt;strong&gt;fixação precoce das fraturas&lt;/strong&gt;. Corticoide em altas doses não tem indicação estabelecida como tratamento.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a contusão pulmonar exige trauma torácico direto, ausente aqui, e não se trata com drenagem. (C) o pneumotórax hipertensivo cursa com abolição unilateral do murmúrio, desvio de traqueia e colapso hemodinâmico. (D) o tromboembolismo raramente cursa com petéquias e alteração neurológica precoce, e a trombólise em politraumatizado recente é de altíssimo risco.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O monóxido de carbono liga-se à hemoglobina com afinidade cerca de &lt;strong&gt;200 a 250 vezes&lt;/strong&gt; maior que a do oxigênio, formando &lt;strong&gt;carboxi-hemoglobina&lt;/strong&gt; e reduzindo drasticamente o conteúdo arterial de oxigênio. O dano é agravado por dois mecanismos adicionais: o &lt;strong&gt;desvio da curva de dissociação para a esquerda&lt;/strong&gt;, que dificulta a liberação de oxigênio nos tecidos, e a inibição da citocromo-oxidase mitocondrial, que bloqueia a utilização celular do oxigênio — daí o lactato elevado.&lt;/p&gt;&lt;p&gt;O ponto que mais engana à beira do leito é a monitorização. O &lt;strong&gt;oxímetro de pulso convencional&lt;/strong&gt; usa dois comprimentos de onda e não diferencia carboxi-hemoglobina de oxi-hemoglobina, exibindo valores falsamente tranquilizadores. A &lt;strong&gt;PaO2 também permanece normal&lt;/strong&gt;, pois mede oxigênio dissolvido, e a saturação calculada pelo gasômetro a partir da PaO2 repete o erro. O diagnóstico exige &lt;strong&gt;co-oximetria&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O tratamento é &lt;strong&gt;oxigênio a 100%&lt;/strong&gt;, que reduz a meia-vida da carboxi-hemoglobina de cerca de 4 a 6 horas em ar ambiente para aproximadamente 1 hora; a câmara hiperbárica encurta ainda mais esse tempo e é considerada em intoxicação grave, com alteração neurológica, isquemia miocárdica ou gestação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a PaO2 normal é regra na intoxicação e não a exclui. (C) o desvio da curva é para a esquerda. (D) a oferta de oxigênio reduz a meia-vida em várias vezes.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O monóxido de carbono liga-se à hemoglobina com afinidade cerca de &lt;strong&gt;200 a 250 vezes&lt;/strong&gt; maior que a do oxigênio, formando &lt;strong&gt;carboxi-hemoglobina&lt;/strong&gt; e reduzindo drasticamente o conteúdo arterial de oxigênio. O dano é agravado por dois mecanismos adicionais: o &lt;strong&gt;desvio da curva de dissociação para a esquerda&lt;/strong&gt;, que dificulta a liberação de oxigênio nos tecidos, e a inibição da citocromo-oxidase mitocondrial, que bloqueia a utilização celular do oxigênio; daí o lactato elevado.&lt;/p&gt;&lt;p&gt;O ponto que mais engana à beira do leito é a monitorização. O &lt;strong&gt;oxímetro de pulso convencional&lt;/strong&gt; usa dois comprimentos de onda e não diferencia carboxi-hemoglobina de oxi-hemoglobina, exibindo valores falsamente tranquilizadores. A &lt;strong&gt;PaO2 também permanece normal&lt;/strong&gt;, pois mede oxigênio dissolvido, e a saturação calculada pelo gasômetro a partir da PaO2 repete o erro. O diagnóstico exige &lt;strong&gt;co-oximetria&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;O tratamento é &lt;strong&gt;oxigênio a 100%&lt;/strong&gt;, que reduz a meia-vida da carboxi-hemoglobina de cerca de 4 a 6 horas em ar ambiente para aproximadamente 1 hora; a câmara hiperbárica encurta ainda mais esse tempo e é considerada em intoxicação grave, com alteração neurológica, isquemia miocárdica ou gestação.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a PaO2 normal é regra na intoxicação e não a exclui. (C) o desvio da curva é para a esquerda. (D) a oferta de oxigênio reduz a meia-vida em várias vezes.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;síndrome hepatorrenal&lt;/strong&gt; é insuficiência renal &lt;strong&gt;funcional&lt;/strong&gt; que ocorre na hepatopatia avançada com hipertensão portal. A vasodilatação esplâncnica intensa, mediada por óxido nítrico, reduz o volume arterial efetivo e ativa o sistema renina-angiotensina-aldosterona, o sistema nervoso simpático e a vasopressina. O resultado é &lt;strong&gt;vasoconstrição renal grave&lt;/strong&gt; com queda da filtração glomerular, em rins histologicamente normais — tanto que podem ser transplantados com sucesso a outro receptor.&lt;/p&gt;&lt;p&gt;Os critérios diagnósticos são essencialmente de exclusão: cirrose com ascite, elevação da creatinina, &lt;strong&gt;ausência de resposta a dois dias de suspensão de diuréticos e expansão com albumina&lt;/strong&gt;, ausência de choque, ausência de nefrotóxicos e ausência de doença parenquimatosa (sem proteinúria significativa, sem hematúria, ultrassonografia normal). O &lt;strong&gt;sódio urinário muito baixo&lt;/strong&gt; reflete avidez tubular por sódio e distingue o quadro da necrose tubular aguda, na qual o sódio urinário é elevado e há cilindros granulosos.&lt;/p&gt;&lt;p&gt;O tratamento definitivo é o &lt;strong&gt;transplante hepático&lt;/strong&gt;, pois corrige a causa. Como ponte, usam-se vasoconstritores esplâncnicos — terlipressina, ou noradrenalina — associados a albumina.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) na necrose tubular o sódio urinário é alto e há cilindros. (C) não houve exposição a contraste, e o transplante renal isolado não resolve a causa hepática. (D) a ausência de resposta à expansão é justamente o que define a síndrome.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;síndrome hepatorrenal&lt;/strong&gt; é insuficiência renal &lt;strong&gt;funcional&lt;/strong&gt; que ocorre na hepatopatia avançada com hipertensão portal. A vasodilatação esplâncnica intensa, mediada por óxido nítrico, reduz o volume arterial efetivo e ativa o sistema renina-angiotensina-aldosterona, o sistema nervoso simpático e a vasopressina. O resultado é &lt;strong&gt;vasoconstrição renal grave&lt;/strong&gt; com queda da filtração glomerular, em rins histologicamente normais, tanto que podem ser transplantados com sucesso a outro receptor.&lt;/p&gt;&lt;p&gt;Os critérios diagnósticos são essencialmente de exclusão: cirrose com ascite, elevação da creatinina, &lt;strong&gt;ausência de resposta a dois dias de suspensão de diuréticos e expansão com albumina&lt;/strong&gt;, ausência de choque, ausência de nefrotóxicos e ausência de doença parenquimatosa (sem proteinúria significativa, sem hematúria, ultrassonografia normal). O &lt;strong&gt;sódio urinário muito baixo&lt;/strong&gt; reflete avidez tubular por sódio e distingue o quadro da necrose tubular aguda, na qual o sódio urinário é elevado e há cilindros granulosos.&lt;/p&gt;&lt;p&gt;O tratamento definitivo é o &lt;strong&gt;transplante hepático&lt;/strong&gt;, pois corrige a causa. Como ponte, usam-se vasoconstritores esplâncnicos (terlipressina, ou noradrenalina) associados a albumina.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) na necrose tubular o sódio urinário é alto e há cilindros. (C) não houve exposição a contraste, e o transplante renal isolado não resolve a causa hepática. (D) a ausência de resposta à expansão é justamente o que define a síndrome.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
@@ -16446,7 +16446,7 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O risco infeccioso pós-transplante segue uma &lt;strong&gt;linha do tempo&lt;/strong&gt; bastante previsível, útil para orientar a suspeita clínica:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Primeiro mês&lt;/strong&gt;: infecções relacionadas ao ato cirúrgico e à internação — ferida operatória, cateteres, pneumonia associada à ventilação, infecção urinária, bactérias multirresistentes.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Um a seis meses&lt;/strong&gt;: janela de &lt;strong&gt;imunossupressão máxima&lt;/strong&gt; e de infecções oportunistas — citomegalovírus (a mais característica), &lt;em&gt;Pneumocystis jirovecii&lt;/em&gt;, aspergilose, nocardiose, reativação de tuberculose, vírus BK.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Após seis meses&lt;/strong&gt;: predominam infecções adquiridas na comunidade, exceto em quem manteve imunossupressão intensa por rejeição.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Quanto aos fármacos, os &lt;strong&gt;inibidores de calcineurina&lt;/strong&gt; (ciclosporina e tacrolimo) causam nefrotoxicidade dose-dependente, hipertensão, hipercalemia, hipomagnesemia e neurotoxicidade, e &lt;strong&gt;potencializam&lt;/strong&gt; o bloqueio neuromuscular adespolarizante. O &lt;strong&gt;micofenolato&lt;/strong&gt; é o principal responsável por leucopenia e sintomas gastrintestinais como a diarreia descrita, e sua suspensão exige dias para recuperação medular.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) esse é o padrão do primeiro mês, não do terceiro. (B) o tacrolimo potencializa e não antagoniza os adespolarizantes. (D) a leucopenia é atribuída sobretudo ao micofenolato, e a recuperação leva dias.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O risco infeccioso pós-transplante segue uma &lt;strong&gt;linha do tempo&lt;/strong&gt; bastante previsível, útil para orientar a suspeita clínica:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Primeiro mês&lt;/strong&gt;: infecções relacionadas ao ato cirúrgico e à internação, como ferida operatória, cateteres, pneumonia associada à ventilação, infecção urinária, bactérias multirresistentes.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Um a seis meses&lt;/strong&gt;: janela de &lt;strong&gt;imunossupressão máxima&lt;/strong&gt; e de infecções oportunistas, como citomegalovírus (a mais característica), &lt;em&gt;Pneumocystis jirovecii&lt;/em&gt;, aspergilose, nocardiose, reativação de tuberculose, vírus BK.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Após seis meses&lt;/strong&gt;: predominam infecções adquiridas na comunidade, exceto em quem manteve imunossupressão intensa por rejeição.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Quanto aos fármacos, os &lt;strong&gt;inibidores de calcineurina&lt;/strong&gt; (ciclosporina e tacrolimo) causam nefrotoxicidade dose-dependente, hipertensão, hipercalemia, hipomagnesemia e neurotoxicidade, e &lt;strong&gt;potencializam&lt;/strong&gt; o bloqueio neuromuscular adespolarizante. O &lt;strong&gt;micofenolato&lt;/strong&gt; é o principal responsável por leucopenia e sintomas gastrintestinais como a diarreia descrita, e sua suspensão exige dias para recuperação medular.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) esse é o padrão do primeiro mês, não do terceiro. (B) o tacrolimo potencializa e não antagoniza os adespolarizantes. (D) a leucopenia é atribuída sobretudo ao micofenolato, e a recuperação leva dias.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -16738,7 +16738,7 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O fígado recebe cerca de &lt;strong&gt;25% do débito cardíaco&lt;/strong&gt; por meio de dois sistemas complementares. A &lt;strong&gt;veia porta&lt;/strong&gt; traz aproximadamente &lt;strong&gt;75% do fluxo sanguíneo&lt;/strong&gt; hepático, mas com sangue já parcialmente dessaturado, proveniente do território esplâncnico. A &lt;strong&gt;artéria hepática&lt;/strong&gt; traz cerca de &lt;strong&gt;25% do fluxo&lt;/strong&gt;, com sangue plenamente oxigenado. Como o menor fluxo é compensado pelo maior conteúdo de oxigênio, cada sistema acaba fornecendo aproximadamente &lt;strong&gt;metade da oferta total de oxigênio&lt;/strong&gt; ao órgão.&lt;/p&gt;&lt;p&gt;O mecanismo regulador principal é a &lt;strong&gt;resposta tampão da artéria hepática&lt;/strong&gt;: quando o fluxo portal cai, a menor depuração de &lt;strong&gt;adenosina&lt;/strong&gt; no espaço periportal provoca &lt;strong&gt;vasodilatação arterial hepática&lt;/strong&gt;, compensando parcialmente a redução da oferta. Essa resposta é atenuada por anestésicos halogenados, pela ventilação com pressão positiva, pelo pneumoperitônio e pela tração cirúrgica, o que torna o fígado vulnerável durante cirurgia abdominal prolongada — os hepatócitos da zona 3, pericentral, são os primeiros a sofrer isquemia.&lt;/p&gt;&lt;p&gt;Do ponto de vista metabólico, o fígado sintetiza albumina, todos os fatores de coagulação exceto o fator de von Willebrand, colinesterase plasmática, e realiza gliconeogênese, ureagênese e biotransformação de fármacos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) as proporções estão invertidas, e a artéria fornece cerca de metade do oxigênio. (B) a veia porta traz a maior parte do fluxo, com sangue parcialmente dessaturado. (D) a resposta tampão é vasodilatadora, e não vasoconstritora.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O fígado recebe cerca de &lt;strong&gt;25% do débito cardíaco&lt;/strong&gt; por meio de dois sistemas complementares. A &lt;strong&gt;veia porta&lt;/strong&gt; traz aproximadamente &lt;strong&gt;75% do fluxo sanguíneo&lt;/strong&gt; hepático, mas com sangue já parcialmente dessaturado, proveniente do território esplâncnico. A &lt;strong&gt;artéria hepática&lt;/strong&gt; traz cerca de &lt;strong&gt;25% do fluxo&lt;/strong&gt;, com sangue plenamente oxigenado. Como o menor fluxo é compensado pelo maior conteúdo de oxigênio, cada sistema acaba fornecendo aproximadamente &lt;strong&gt;metade da oferta total de oxigênio&lt;/strong&gt; ao órgão.&lt;/p&gt;&lt;p&gt;O mecanismo regulador principal é a &lt;strong&gt;resposta tampão da artéria hepática&lt;/strong&gt;: quando o fluxo portal cai, a menor depuração de &lt;strong&gt;adenosina&lt;/strong&gt; no espaço periportal provoca &lt;strong&gt;vasodilatação arterial hepática&lt;/strong&gt;, compensando parcialmente a redução da oferta. Essa resposta é atenuada por anestésicos halogenados, pela ventilação com pressão positiva, pelo pneumoperitônio e pela tração cirúrgica, o que torna o fígado vulnerável durante cirurgia abdominal prolongada; os hepatócitos da zona 3, pericentral, são os primeiros a sofrer isquemia.&lt;/p&gt;&lt;p&gt;Do ponto de vista metabólico, o fígado sintetiza albumina, todos os fatores de coagulação exceto o fator de von Willebrand, colinesterase plasmática, e realiza gliconeogênese, ureagênese e biotransformação de fármacos.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) as proporções estão invertidas, e a artéria fornece cerca de metade do oxigênio. (B) a veia porta traz a maior parte do fluxo, com sangue parcialmente dessaturado. (D) a resposta tampão é vasodilatadora, e não vasoconstritora.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A &lt;strong&gt;pressão intra-abdominal&lt;/strong&gt; normal no adulto crítico situa-se entre &lt;strong&gt;5 e 7 mmHg&lt;/strong&gt;. Valores sustentados &lt;strong&gt;acima de 12 mmHg&lt;/strong&gt; configuram &lt;strong&gt;hipertensão intra-abdominal&lt;/strong&gt;, graduada em quatro categorias, e valores &lt;strong&gt;acima de 20 mmHg associados a nova disfunção orgânica&lt;/strong&gt; definem a &lt;strong&gt;síndrome compartimental abdominal&lt;/strong&gt;. A medida padronizada é indireta, pela &lt;strong&gt;pressão intravesical&lt;/strong&gt;, com instilação de no máximo &lt;strong&gt;25 mL&lt;/strong&gt; de solução salina, ao final da expiração, em decúbito dorsal, com o zero na linha axilar média ao nível da crista ilíaca. Volumes maiores elevam falsamente o valor pela própria complacência vesical.&lt;/p&gt;&lt;p&gt;As repercussões são multissistêmicas: elevação diafragmática com queda da complacência pulmonar, aumento das pressões de via aérea e hipercapnia; compressão da veia cava inferior com redução do retorno venoso e do débito; redução da pressão de perfusão abdominal (pressão arterial média menos pressão intra-abdominal) com oligúria e lesão renal; isquemia esplâncnica com translocação bacteriana; e elevação da pressão intracraniana.&lt;/p&gt;&lt;p&gt;O manejo inicia por medidas clínicas — sedação, analgesia, bloqueio neuromuscular, drenagem de coleções, descompressão gástrica, balanço hídrico negativo — e evolui para &lt;strong&gt;laparotomia descompressiva&lt;/strong&gt; quando há falha e disfunção orgânica progressiva.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o valor normal é de 5 a 7 mmHg. (C) mais volume agrava a hipertensão intra-abdominal. (D) o volume instilado deve ser de até 25 mL.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A &lt;strong&gt;pressão intra-abdominal&lt;/strong&gt; normal no adulto crítico situa-se entre &lt;strong&gt;5 e 7 mmHg&lt;/strong&gt;. Valores sustentados &lt;strong&gt;acima de 12 mmHg&lt;/strong&gt; configuram &lt;strong&gt;hipertensão intra-abdominal&lt;/strong&gt;, graduada em quatro categorias, e valores &lt;strong&gt;acima de 20 mmHg associados a nova disfunção orgânica&lt;/strong&gt; definem a &lt;strong&gt;síndrome compartimental abdominal&lt;/strong&gt;. A medida padronizada é indireta, pela &lt;strong&gt;pressão intravesical&lt;/strong&gt;, com instilação de no máximo &lt;strong&gt;25 mL&lt;/strong&gt; de solução salina, ao final da expiração, em decúbito dorsal, com o zero na linha axilar média ao nível da crista ilíaca. Volumes maiores elevam falsamente o valor pela própria complacência vesical.&lt;/p&gt;&lt;p&gt;As repercussões são multissistêmicas: elevação diafragmática com queda da complacência pulmonar, aumento das pressões de via aérea e hipercapnia; compressão da veia cava inferior com redução do retorno venoso e do débito; redução da pressão de perfusão abdominal (pressão arterial média menos pressão intra-abdominal) com oligúria e lesão renal; isquemia esplâncnica com translocação bacteriana; e elevação da pressão intracraniana.&lt;/p&gt;&lt;p&gt;O manejo inicia por medidas clínicas (sedação, analgesia, bloqueio neuromuscular, drenagem de coleções, descompressão gástrica, balanço hídrico negativo) e evolui para &lt;strong&gt;laparotomia descompressiva&lt;/strong&gt; quando há falha e disfunção orgânica progressiva.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o valor normal é de 5 a 7 mmHg. (C) mais volume agrava a hipertensão intra-abdominal. (D) o volume instilado deve ser de até 25 mL.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A derivação gástrica em Y de Roux combina restrição e disabsorção, excluindo do trânsito o duodeno e o jejuno proximal — justamente onde se absorvem ferro, cálcio e tiamina — e reduzindo a produção de ácido e de fator intrínseco, essenciais à absorção de vitamina B&lt;sub&gt;12&lt;/sub&gt;. As carências mais frequentes envolvem &lt;strong&gt;ferro, vitamina B&lt;sub&gt;12&lt;/sub&gt;, folato, cálcio, vitamina D, zinco e tiamina&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;deficiência de tiamina (vitamina B&lt;sub&gt;1&lt;/sub&gt;)&lt;/strong&gt; merece destaque porque as reservas corporais duram apenas duas a três semanas e se esgotam rapidamente diante de &lt;strong&gt;vômitos persistentes&lt;/strong&gt;. A tríade clássica da &lt;strong&gt;encefalopatia de Wernicke&lt;/strong&gt; — &lt;strong&gt;oftalmoplegia com nistagmo, ataxia e confusão mental&lt;/strong&gt; — é a que melhor explica o quadro descrito. A polineuropatia periférica com parestesias completa o espectro do beribéri.&lt;/p&gt;&lt;p&gt;O ponto de aplicação prática imediata é que a &lt;strong&gt;tiamina é cofator da piruvato desidrogenase&lt;/strong&gt;: administrar glicose a um paciente depletado consome o pouco que resta e pode &lt;strong&gt;precipitar ou agravar a encefalopatia&lt;/strong&gt;. Por isso, a tiamina parenteral deve ser administrada &lt;strong&gt;antes&lt;/strong&gt; de qualquer solução glicosada, e o tratamento não deve aguardar confirmação laboratorial.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a B&lt;sub&gt;12&lt;/sub&gt; causa neuropatia e degeneração combinada subaguda, não oftalmoplegia aguda, e a via oral é inadequada aqui. (B) a ferropenia causa anemia, não ataxia com nistagmo. (C) hipocalcemia produz tetania e parestesias periorais, não oftalmoplegia.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A derivação gástrica em Y de Roux combina restrição e disabsorção, excluindo do trânsito o duodeno e o jejuno proximal (justamente onde se absorvem ferro, cálcio e tiamina) e reduzindo a produção de ácido e de fator intrínseco, essenciais à absorção de vitamina B&lt;sub&gt;12&lt;/sub&gt;. As carências mais frequentes envolvem &lt;strong&gt;ferro, vitamina B&lt;sub&gt;12&lt;/sub&gt;, folato, cálcio, vitamina D, zinco e tiamina&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;deficiência de tiamina (vitamina B&lt;sub&gt;1&lt;/sub&gt;)&lt;/strong&gt; merece destaque porque as reservas corporais duram apenas duas a três semanas e se esgotam rapidamente diante de &lt;strong&gt;vômitos persistentes&lt;/strong&gt;. A tríade clássica da &lt;strong&gt;encefalopatia de Wernicke&lt;/strong&gt; (&lt;strong&gt;oftalmoplegia com nistagmo, ataxia e confusão mental&lt;/strong&gt;) é a que melhor explica o quadro descrito. A polineuropatia periférica com parestesias completa o espectro do beribéri.&lt;/p&gt;&lt;p&gt;O ponto de aplicação prática imediata é que a &lt;strong&gt;tiamina é cofator da piruvato desidrogenase&lt;/strong&gt;: administrar glicose a um paciente depletado consome o pouco que resta e pode &lt;strong&gt;precipitar ou agravar a encefalopatia&lt;/strong&gt;. Por isso, a tiamina parenteral deve ser administrada &lt;strong&gt;antes&lt;/strong&gt; de qualquer solução glicosada, e o tratamento não deve aguardar confirmação laboratorial.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a B&lt;sub&gt;12&lt;/sub&gt; causa neuropatia e degeneração combinada subaguda, não oftalmoplegia aguda, e a via oral é inadequada aqui. (B) a ferropenia causa anemia, não ataxia com nistagmo. (C) hipocalcemia produz tetania e parestesias periorais, não oftalmoplegia.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
@@ -16957,7 +16957,7 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A perda de potenciais evocados durante artrodese de coluna é uma emergência que exige resposta coordenada e imediata, pois a reversão do déficit depende do tempo até a correção da causa. A primeira providência é &lt;strong&gt;excluir causas anestésicas e sistêmicas&lt;/strong&gt; antes de atribuir o achado à manipulação cirúrgica, mas as duas frentes devem ser conduzidas ao mesmo tempo.&lt;/p&gt;&lt;p&gt;Do lado anestésico, verifica-se se houve aprofundamento do plano, bolus de halogenado ou de bloqueador neuromuscular — &lt;strong&gt;os potenciais evocados motores são extremamente sensíveis aos halogenados e ao relaxamento muscular&lt;/strong&gt;, o que explica a preferência pela anestesia venosa total nesses casos. Corrigem-se também &lt;strong&gt;hipotensão, anemia e hipotermia&lt;/strong&gt;, pois a perfusão medular depende da pressão arterial média e do conteúdo arterial de oxigênio.&lt;/p&gt;&lt;p&gt;Do lado cirúrgico, solicita-se &lt;strong&gt;redução da distração&lt;/strong&gt; ou remoção do implante, reposicionamento e inspeção. A elevação da pressão arterial média para valores em torno de &lt;strong&gt;85 a 90 mmHg&lt;/strong&gt; é a manobra hemodinâmica de escolha, aumentando a pressão de perfusão medular. Quando não há monitorização eletrofisiológica disponível, recorre-se ao teste de despertar intraoperatório.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o halogenado abole os potenciais motores e não protege a medula. (C) manter hipotensão e anemia perpetua a isquemia. (D) a hipotensão induzida é exatamente o oposto do necessário nesse momento.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A perda de potenciais evocados durante artrodese de coluna é uma emergência que exige resposta coordenada e imediata, pois a reversão do déficit depende do tempo até a correção da causa. A primeira providência é &lt;strong&gt;excluir causas anestésicas e sistêmicas&lt;/strong&gt; antes de atribuir o achado à manipulação cirúrgica, mas as duas frentes devem ser conduzidas ao mesmo tempo.&lt;/p&gt;&lt;p&gt;Do lado anestésico, verifica-se se houve aprofundamento do plano, bolus de halogenado ou de bloqueador neuromuscular: &lt;strong&gt;os potenciais evocados motores são extremamente sensíveis aos halogenados e ao relaxamento muscular&lt;/strong&gt;, o que explica a preferência pela anestesia venosa total nesses casos. Corrigem-se também &lt;strong&gt;hipotensão, anemia e hipotermia&lt;/strong&gt;, pois a perfusão medular depende da pressão arterial média e do conteúdo arterial de oxigênio.&lt;/p&gt;&lt;p&gt;Do lado cirúrgico, solicita-se &lt;strong&gt;redução da distração&lt;/strong&gt; ou remoção do implante, reposicionamento e inspeção. A elevação da pressão arterial média para valores em torno de &lt;strong&gt;85 a 90 mmHg&lt;/strong&gt; é a manobra hemodinâmica de escolha, aumentando a pressão de perfusão medular. Quando não há monitorização eletrofisiológica disponível, recorre-se ao teste de despertar intraoperatório.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) o halogenado abole os potenciais motores e não protege a medula. (C) manter hipotensão e anemia perpetua a isquemia. (D) a hipotensão induzida é exatamente o oposto do necessário nesse momento.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O trauma ocular aberto cria um conflito clássico: a criança tem &lt;strong&gt;estômago cheio&lt;/strong&gt;, o que exigiria indução em sequência rápida com suxametônio, mas qualquer elevação da &lt;strong&gt;pressão intraocular&lt;/strong&gt; pode expulsar humor vítreo, cristalino e coroide pela ferida, com perda definitiva da visão.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;suxametônio&lt;/strong&gt; eleva a pressão intraocular em torno de &lt;strong&gt;5 a 10 mmHg&lt;/strong&gt;, com pico em cerca de um a quatro minutos e retorno ao basal em torno de sete minutos. O mecanismo envolve contração tônica da musculatura extraocular, cujas fibras multi-inervadas se comportam de modo particular, além de vasodilatação coroideia. Embora existam relatos de uso sem complicações, e nenhuma técnica de pré-tratamento aboliu de forma consistente esse efeito, o consenso atual é &lt;strong&gt;preferir o rocurônio em dose de 1,0 a 1,2 mg/kg&lt;/strong&gt;, que oferece condições de intubação em torno de 60 segundos sem elevar a pressão intraocular, com a segurança adicional do sugamadex como reversor.&lt;/p&gt;&lt;p&gt;Igualmente importante é evitar tosse, esforço, laringoscopia em plano superficial, compressão externa do globo pela máscara e vômitos — fatores que elevam a pressão intraocular muito mais do que o próprio relaxante. A indução deve ser profunda, com opioide adequado e lidocaína venosa.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o suxametônio aumenta a pressão intraocular. (C) a indução inalatória lenta é inadequada no estômago cheio e cursa com fase de excitação. (D) o bloqueio peribulbar em olho aberto e em criança agitada é contraindicado pelo risco de extrusão.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O trauma ocular aberto cria um conflito clássico: a criança tem &lt;strong&gt;estômago cheio&lt;/strong&gt;, o que exigiria indução em sequência rápida com suxametônio, mas qualquer elevação da &lt;strong&gt;pressão intraocular&lt;/strong&gt; pode expulsar humor vítreo, cristalino e coroide pela ferida, com perda definitiva da visão.&lt;/p&gt;&lt;p&gt;O &lt;strong&gt;suxametônio&lt;/strong&gt; eleva a pressão intraocular em torno de &lt;strong&gt;5 a 10 mmHg&lt;/strong&gt;, com pico em cerca de um a quatro minutos e retorno ao basal em torno de sete minutos. O mecanismo envolve contração tônica da musculatura extraocular, cujas fibras multi-inervadas se comportam de modo particular, além de vasodilatação coroideia. Embora existam relatos de uso sem complicações, e nenhuma técnica de pré-tratamento aboliu de forma consistente esse efeito, o consenso atual é &lt;strong&gt;preferir o rocurônio em dose de 1,0 a 1,2 mg/kg&lt;/strong&gt;, que oferece condições de intubação em torno de 60 segundos sem elevar a pressão intraocular, com a segurança adicional do sugamadex como reversor.&lt;/p&gt;&lt;p&gt;Igualmente importante é evitar tosse, esforço, laringoscopia em plano superficial, compressão externa do globo pela máscara e vômitos, fatores que elevam a pressão intraocular muito mais do que o próprio relaxante. A indução deve ser profunda, com opioide adequado e lidocaína venosa.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) o suxametônio aumenta a pressão intraocular. (C) a indução inalatória lenta é inadequada no estômago cheio e cursa com fase de excitação. (D) o bloqueio peribulbar em olho aberto e em criança agitada é contraindicado pelo risco de extrusão.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
@@ -17176,7 +17176,7 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dois aspectos definem a conduta anestésica na litotripsia extracorpórea com banho de imersão.&lt;/p&gt;&lt;p&gt;O primeiro é a &lt;strong&gt;sincronização das ondas de choque&lt;/strong&gt;. O pulso é disparado cerca de &lt;strong&gt;20 milissegundos após a onda R&lt;/strong&gt;, ou seja, no &lt;strong&gt;período refratário ventricular&lt;/strong&gt;. Disparar fora dessa janela, particularmente sobre a onda T, corresponde ao fenômeno R sobre T e pode desencadear arritmias ventriculares. Essa sincronização limita a frequência de disparos à frequência cardíaca do paciente. Em portadores de &lt;strong&gt;marca-passo&lt;/strong&gt; ou cardiodesfibrilador, avalia-se o dispositivo antes e depois, evita-se posicioná-lo próximo ao foco das ondas e considera-se programação assíncrona ou desativação de terapias antitaquicardia.&lt;/p&gt;&lt;p&gt;O segundo é a &lt;strong&gt;imersão em água aquecida&lt;/strong&gt;. A pressão hidrostática comprime o leito venoso periférico e desloca sangue para o tórax, &lt;strong&gt;aumentando o retorno venoso, a pressão venosa central e a pressão de artéria pulmonar&lt;/strong&gt; — mal tolerado em disfunção ventricular. Simultaneamente, a compressão torácica e a elevação diafragmática &lt;strong&gt;reduzem a capacidade residual funcional&lt;/strong&gt; e a complacência pulmonar, favorecendo atelectasias e hipoxemia. Ao sair da água, a queda abrupta da pressão hidrostática pode causar hipotensão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a sincronização com a onda T é justamente o cenário arritmogênico, e o retorno venoso aumenta. (B) o disparo não é aleatório, e a capacidade residual funcional diminui. (C) a onda P não é a referência, e a mecânica respiratória se altera de forma expressiva.&lt;/p&gt;</t>
+          <t>&lt;p&gt;Dois aspectos definem a conduta anestésica na litotripsia extracorpórea com banho de imersão.&lt;/p&gt;&lt;p&gt;O primeiro é a &lt;strong&gt;sincronização das ondas de choque&lt;/strong&gt;. O pulso é disparado cerca de &lt;strong&gt;20 milissegundos após a onda R&lt;/strong&gt;, ou seja, no &lt;strong&gt;período refratário ventricular&lt;/strong&gt;. Disparar fora dessa janela, particularmente sobre a onda T, corresponde ao fenômeno R sobre T e pode desencadear arritmias ventriculares. Essa sincronização limita a frequência de disparos à frequência cardíaca do paciente. Em portadores de &lt;strong&gt;marca-passo&lt;/strong&gt; ou cardiodesfibrilador, avalia-se o dispositivo antes e depois, evita-se posicioná-lo próximo ao foco das ondas e considera-se programação assíncrona ou desativação de terapias antitaquicardia.&lt;/p&gt;&lt;p&gt;O segundo é a &lt;strong&gt;imersão em água aquecida&lt;/strong&gt;. A pressão hidrostática comprime o leito venoso periférico e desloca sangue para o tórax, &lt;strong&gt;aumentando o retorno venoso, a pressão venosa central e a pressão de artéria pulmonar&lt;/strong&gt;, mal tolerado em disfunção ventricular. Simultaneamente, a compressão torácica e a elevação diafragmática &lt;strong&gt;reduzem a capacidade residual funcional&lt;/strong&gt; e a complacência pulmonar, favorecendo atelectasias e hipoxemia. Ao sair da água, a queda abrupta da pressão hidrostática pode causar hipotensão.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a sincronização com a onda T é justamente o cenário arritmogênico, e o retorno venoso aumenta. (B) o disparo não é aleatório, e a capacidade residual funcional diminui. (C) a onda P não é a referência, e a mecânica respiratória se altera de forma expressiva.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
@@ -17468,7 +17468,7 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>&lt;p&gt;O &lt;strong&gt;consumo cerebral de oxigênio&lt;/strong&gt; tem dois componentes: cerca de &lt;strong&gt;60% destina-se à atividade funcional&lt;/strong&gt; — geração de potenciais de ação e neurotransmissão, refletida no eletroencefalograma — e cerca de &lt;strong&gt;40% à manutenção da integridade celular&lt;/strong&gt;, o metabolismo basal que sustenta gradientes iônicos e síntese proteica.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;temperatura age sobre os dois componentes&lt;/strong&gt;, e é justamente aí que reside a superioridade teórica da hipotermia sobre os anestésicos na proteção cerebral: barbitúricos e propofol suprimem apenas o componente funcional, atingindo um platô quando o eletroencefalograma se torna isoelétrico, enquanto a hipotermia continua reduzindo o consumo abaixo desse ponto.&lt;/p&gt;&lt;p&gt;Na direção oposta, cada grau de &lt;strong&gt;elevação&lt;/strong&gt; da temperatura aumenta o consumo cerebral de oxigênio em torno de &lt;strong&gt;5 a 7%&lt;/strong&gt;, ampliando o descompasso entre oferta e demanda — razão pela qual a febre agrava o desfecho de qualquer lesão neurológica aguda e a normotermia deve ser mantida rigorosamente após parada cardíaca ou trauma craniano. Acima de aproximadamente &lt;strong&gt;42 graus&lt;/strong&gt;, contudo, ocorre &lt;strong&gt;desnaturação proteica e falência enzimática&lt;/strong&gt;, e o consumo cai — uma queda que significa lesão, não proteção.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) até 42 graus o consumo aumenta, não diminui. (B) a hipotermia reduz também o componente basal, o que a diferencia dos anestésicos. (C) a temperatura é um dos determinantes mais potentes do metabolismo cerebral.&lt;/p&gt;</t>
+          <t>&lt;p&gt;O &lt;strong&gt;consumo cerebral de oxigênio&lt;/strong&gt; tem dois componentes: cerca de &lt;strong&gt;60% destina-se à atividade funcional&lt;/strong&gt; (geração de potenciais de ação e neurotransmissão, refletida no eletroencefalograma) e cerca de &lt;strong&gt;40% à manutenção da integridade celular&lt;/strong&gt;, o metabolismo basal que sustenta gradientes iônicos e síntese proteica.&lt;/p&gt;&lt;p&gt;A &lt;strong&gt;temperatura age sobre os dois componentes&lt;/strong&gt;, e é justamente aí que reside a superioridade teórica da hipotermia sobre os anestésicos na proteção cerebral: barbitúricos e propofol suprimem apenas o componente funcional, atingindo um platô quando o eletroencefalograma se torna isoelétrico, enquanto a hipotermia continua reduzindo o consumo abaixo desse ponto.&lt;/p&gt;&lt;p&gt;Na direção oposta, cada grau de &lt;strong&gt;elevação&lt;/strong&gt; da temperatura aumenta o consumo cerebral de oxigênio em torno de &lt;strong&gt;5 a 7%&lt;/strong&gt;, ampliando o descompasso entre oferta e demanda, razão pela qual a febre agrava o desfecho de qualquer lesão neurológica aguda e a normotermia deve ser mantida rigorosamente após parada cardíaca ou trauma craniano. Acima de aproximadamente &lt;strong&gt;42 graus&lt;/strong&gt;, contudo, ocorre &lt;strong&gt;desnaturação proteica e falência enzimática&lt;/strong&gt;, e o consumo cai, uma queda que significa lesão, não proteção.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) até 42 graus o consumo aumenta, não diminui. (B) a hipotermia reduz também o componente basal, o que a diferencia dos anestésicos. (C) a temperatura é um dos determinantes mais potentes do metabolismo cerebral.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
@@ -17614,7 +17614,7 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A relação entre temperatura e metabolismo é descrita pelo &lt;strong&gt;coeficiente Q10&lt;/strong&gt;, que expressa a variação da taxa metabólica para cada &lt;strong&gt;10 graus&lt;/strong&gt; de mudança térmica. No cérebro humano, o Q10 situa-se entre &lt;strong&gt;2 e 3&lt;/strong&gt;, o que significa que cada queda de 10 graus reduz o &lt;strong&gt;consumo cerebral de oxigênio à metade ou menos&lt;/strong&gt;. Em termos aproximados, a redução é de cerca de &lt;strong&gt;6 a 7% por grau&lt;/strong&gt;. A 18 graus, portanto, o consumo cerebral situa-se em torno de &lt;strong&gt;15 a 20% do basal&lt;/strong&gt;, e não em 60% — margem que fundamenta janelas de parada circulatória de aproximadamente 30 a 40 minutos, ainda assim com risco neurológico crescente a partir daí.&lt;/p&gt;&lt;p&gt;O ponto conceitual central é que a hipotermia atua sobre &lt;strong&gt;ambos os componentes&lt;/strong&gt; do metabolismo cerebral: o funcional e o basal. Os barbitúricos e o propofol suprimem apenas o funcional e atingem um &lt;strong&gt;teto quando o eletroencefalograma se torna isoelétrico&lt;/strong&gt;, momento em que persiste todo o consumo destinado à manutenção da integridade celular. A hipotermia continua reduzindo o consumo &lt;strong&gt;abaixo do ponto de isoeletricidade&lt;/strong&gt;, e acrescenta efeitos não metabólicos relevantes: menor liberação de glutamato e de aminoácidos excitatórios, redução da produção de radicais livres, preservação da barreira hematoencefálica e atenuação da resposta inflamatória.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) subestima grosseiramente a redução obtida a 18 graus. (C) a hipotermia não se limita à supressão elétrica, ao contrário dos barbitúricos. (D) mesmo com traçado isoelétrico persiste o consumo basal celular.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A relação entre temperatura e metabolismo é descrita pelo &lt;strong&gt;coeficiente Q10&lt;/strong&gt;, que expressa a variação da taxa metabólica para cada &lt;strong&gt;10 graus&lt;/strong&gt; de mudança térmica. No cérebro humano, o Q10 situa-se entre &lt;strong&gt;2 e 3&lt;/strong&gt;, o que significa que cada queda de 10 graus reduz o &lt;strong&gt;consumo cerebral de oxigênio à metade ou menos&lt;/strong&gt;. Em termos aproximados, a redução é de cerca de &lt;strong&gt;6 a 7% por grau&lt;/strong&gt;. A 18 graus, portanto, o consumo cerebral situa-se em torno de &lt;strong&gt;15 a 20% do basal&lt;/strong&gt;, e não em 60%, margem que fundamenta janelas de parada circulatória de aproximadamente 30 a 40 minutos, ainda assim com risco neurológico crescente a partir daí.&lt;/p&gt;&lt;p&gt;O ponto conceitual central é que a hipotermia atua sobre &lt;strong&gt;ambos os componentes&lt;/strong&gt; do metabolismo cerebral: o funcional e o basal. Os barbitúricos e o propofol suprimem apenas o funcional e atingem um &lt;strong&gt;teto quando o eletroencefalograma se torna isoelétrico&lt;/strong&gt;, momento em que persiste todo o consumo destinado à manutenção da integridade celular. A hipotermia continua reduzindo o consumo &lt;strong&gt;abaixo do ponto de isoeletricidade&lt;/strong&gt;, e acrescenta efeitos não metabólicos relevantes: menor liberação de glutamato e de aminoácidos excitatórios, redução da produção de radicais livres, preservação da barreira hematoencefálica e atenuação da resposta inflamatória.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) subestima grosseiramente a redução obtida a 18 graus. (C) a hipotermia não se limita à supressão elétrica, ao contrário dos barbitúricos. (D) mesmo com traçado isoelétrico persiste o consumo basal celular.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
@@ -17760,7 +17760,7 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A escolha da estatística depende do &lt;strong&gt;tipo de variável&lt;/strong&gt; e da &lt;strong&gt;forma da distribuição&lt;/strong&gt;. O tempo até a alta é variável &lt;strong&gt;contínua&lt;/strong&gt;; a assimetria acentuada e a presença de valores extremos afastam a suposição de normalidade.&lt;/p&gt;&lt;p&gt;Em distribuições assimétricas, a &lt;strong&gt;média é arrastada pelos valores extremos&lt;/strong&gt;, enquanto a &lt;strong&gt;mediana&lt;/strong&gt; — valor que divide a amostra ordenada em duas metades — é robusta a esses valores e descreve melhor a tendência central. A dispersão correspondente é expressa pelo &lt;strong&gt;intervalo interquartil&lt;/strong&gt;. Consequentemente, o teste apropriado para comparar dois grupos independentes é o &lt;strong&gt;não paramétrico de Mann-Whitney&lt;/strong&gt;, baseado em postos.&lt;/p&gt;&lt;p&gt;Convém fixar as distinções mais cobradas:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Desvio-padrão&lt;/strong&gt;: mede a &lt;strong&gt;dispersão dos dados&lt;/strong&gt; em torno da média.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Erro-padrão da média&lt;/strong&gt;: mede a &lt;strong&gt;precisão da estimativa&lt;/strong&gt; da média populacional; é o desvio-padrão dividido pela raiz do tamanho amostral, e por isso diminui com amostras maiores.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Teste t&lt;/strong&gt;: dois grupos, variável contínua com distribuição normal. &lt;strong&gt;ANOVA&lt;/strong&gt;: três ou mais grupos.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Qui-quadrado&lt;/strong&gt;: variáveis &lt;strong&gt;categóricas&lt;/strong&gt;, em tabelas de contingência.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Metanálise&lt;/strong&gt;: combina estudos; a heterogeneidade é quantificada pelo &lt;strong&gt;I²&lt;/strong&gt;, e valores altos favorecem o modelo de efeitos aleatórios.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a média é justamente distorcida pelos extremos. (C) as definições estão trocadas. (D) o qui-quadrado não se aplica a variáveis contínuas.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A escolha da estatística depende do &lt;strong&gt;tipo de variável&lt;/strong&gt; e da &lt;strong&gt;forma da distribuição&lt;/strong&gt;. O tempo até a alta é variável &lt;strong&gt;contínua&lt;/strong&gt;; a assimetria acentuada e a presença de valores extremos afastam a suposição de normalidade.&lt;/p&gt;&lt;p&gt;Em distribuições assimétricas, a &lt;strong&gt;média é arrastada pelos valores extremos&lt;/strong&gt;, enquanto a &lt;strong&gt;mediana&lt;/strong&gt; (valor que divide a amostra ordenada em duas metades) é robusta a esses valores e descreve melhor a tendência central. A dispersão correspondente é expressa pelo &lt;strong&gt;intervalo interquartil&lt;/strong&gt;. Consequentemente, o teste apropriado para comparar dois grupos independentes é o &lt;strong&gt;não paramétrico de Mann-Whitney&lt;/strong&gt;, baseado em postos.&lt;/p&gt;&lt;p&gt;Convém fixar as distinções mais cobradas:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Desvio-padrão&lt;/strong&gt;: mede a &lt;strong&gt;dispersão dos dados&lt;/strong&gt; em torno da média.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Erro-padrão da média&lt;/strong&gt;: mede a &lt;strong&gt;precisão da estimativa&lt;/strong&gt; da média populacional; é o desvio-padrão dividido pela raiz do tamanho amostral, e por isso diminui com amostras maiores.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Teste t&lt;/strong&gt;: dois grupos, variável contínua com distribuição normal. &lt;strong&gt;ANOVA&lt;/strong&gt;: três ou mais grupos.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Qui-quadrado&lt;/strong&gt;: variáveis &lt;strong&gt;categóricas&lt;/strong&gt;, em tabelas de contingência.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Metanálise&lt;/strong&gt;: combina estudos; a heterogeneidade é quantificada pelo &lt;strong&gt;I²&lt;/strong&gt;, e valores altos favorecem o modelo de efeitos aleatórios.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (B) a média é justamente distorcida pelos extremos. (C) as definições estão trocadas. (D) o qui-quadrado não se aplica a variáveis contínuas.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
@@ -17833,7 +17833,7 @@
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A anestesiologia figura de forma desproporcional entre as especialidades em programas de tratamento de dependência química, fenômeno atribuído ao &lt;strong&gt;acesso facilitado a fármacos potentes&lt;/strong&gt;, à exposição ocupacional a traços desses agentes, ao estresse crônico e à cultura de autossuficiência.&lt;/p&gt;&lt;p&gt;As substâncias mais implicadas são os &lt;strong&gt;opioides de alta potência&lt;/strong&gt; — fentanil e sufentanil —, seguidos pelo &lt;strong&gt;propofol&lt;/strong&gt;, cuja incidência tem crescido e cuja margem entre efeito desejado e apneia é estreitíssima. A característica mais temida desse perfil é que, diferentemente do alcoolismo, cuja deterioração é lenta e visível, a dependência de opioides e de propofol pode ter como &lt;strong&gt;primeira manifestação a overdose fatal&lt;/strong&gt;, encontrada em vestiários, plantões ou domicílio.&lt;/p&gt;&lt;p&gt;Os &lt;strong&gt;sinais de alerta&lt;/strong&gt; são comportamentais e administrativos: preferência por trabalhar sozinho, recusa de pausas e de substituições, oferta de plantões extras, presença no hospital em folgas, isolamento, mudanças de humor e de aparência, uso de mangas longas e, de modo bastante sugestivo, &lt;strong&gt;discrepância entre as doses registradas de opioide e a dor relatada pelos pacientes&lt;/strong&gt;, além de anomalias no controle de psicotrópicos.&lt;/p&gt;&lt;p&gt;A dependência química é reconhecida como &lt;strong&gt;doença&lt;/strong&gt;, e a conduta correta combina afastamento imediato da atividade assistencial, tratamento especializado, apoio institucional e reabilitação com retorno supervisionado e monitorado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) os opioides superam o álcool nessa população. (C) o retorno supervisionado é possível e recomendado em programas estruturados. (D) trata-se de doença, e não de mera falta disciplinar.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A anestesiologia figura de forma desproporcional entre as especialidades em programas de tratamento de dependência química, fenômeno atribuído ao &lt;strong&gt;acesso facilitado a fármacos potentes&lt;/strong&gt;, à exposição ocupacional a traços desses agentes, ao estresse crônico e à cultura de autossuficiência.&lt;/p&gt;&lt;p&gt;As substâncias mais implicadas são os &lt;strong&gt;opioides de alta potência&lt;/strong&gt; (fentanil e sufentanil), seguidos pelo &lt;strong&gt;propofol&lt;/strong&gt;, cuja incidência tem crescido e cuja margem entre efeito desejado e apneia é estreitíssima. A característica mais temida desse perfil é que, diferentemente do alcoolismo, cuja deterioração é lenta e visível, a dependência de opioides e de propofol pode ter como &lt;strong&gt;primeira manifestação a overdose fatal&lt;/strong&gt;, encontrada em vestiários, plantões ou domicílio.&lt;/p&gt;&lt;p&gt;Os &lt;strong&gt;sinais de alerta&lt;/strong&gt; são comportamentais e administrativos: preferência por trabalhar sozinho, recusa de pausas e de substituições, oferta de plantões extras, presença no hospital em folgas, isolamento, mudanças de humor e de aparência, uso de mangas longas e, de modo bastante sugestivo, &lt;strong&gt;discrepância entre as doses registradas de opioide e a dor relatada pelos pacientes&lt;/strong&gt;, além de anomalias no controle de psicotrópicos.&lt;/p&gt;&lt;p&gt;A dependência química é reconhecida como &lt;strong&gt;doença&lt;/strong&gt;, e a conduta correta combina afastamento imediato da atividade assistencial, tratamento especializado, apoio institucional e reabilitação com retorno supervisionado e monitorado.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) os opioides superam o álcool nessa população. (C) o retorno supervisionado é possível e recomendado em programas estruturados. (D) trata-se de doença, e não de mera falta disciplinar.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
@@ -17906,7 +17906,7 @@
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>&lt;p&gt;A data fundadora da especialidade é &lt;strong&gt;16 de outubro de 1846&lt;/strong&gt;, no anfiteatro cirúrgico do &lt;strong&gt;Massachusetts General Hospital&lt;/strong&gt;, em Boston. O dentista &lt;strong&gt;William Thomas Green Morton&lt;/strong&gt; administrou &lt;strong&gt;éter dietílico&lt;/strong&gt; por meio de um inalador de vidro enquanto John Collins Warren removia um tumor cervical do paciente Gilbert Abbott. O sucesso público e reprodutível dessa demonstração — imortalizada na expressão atribuída a Warren de que aquilo não era embuste — difundiu rapidamente a prática pelo mundo, e o local passou a ser chamado de Éter Dome.&lt;/p&gt;&lt;p&gt;Os demais marcos frequentemente confundidos:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Crawford Long&lt;/strong&gt;, na Geórgia, usou éter em 1842, antes de Morton, mas &lt;strong&gt;não publicou&lt;/strong&gt; à época, o que lhe custou a precedência histórica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Horace Wells&lt;/strong&gt;, dentista, tentou demonstrar publicamente o &lt;strong&gt;óxido nitroso&lt;/strong&gt; em 1845, com fracasso retumbante.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;James Young Simpson&lt;/strong&gt; introduziu o &lt;strong&gt;clorofórmio&lt;/strong&gt; em obstetrícia, na Escócia, em 1847.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Carl Koller&lt;/strong&gt; descreveu em 1884 o uso tópico da &lt;strong&gt;cocaína&lt;/strong&gt; em cirurgia oftalmológica, inaugurando a anestesia local.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;August Bier&lt;/strong&gt; realizou em 1898 a primeira &lt;strong&gt;raquianestesia&lt;/strong&gt;, testada nele próprio e em seu assistente.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a demonstração de 1846 usou éter, e o clorofórmio veio no ano seguinte. (B) a raquianestesia é atribuída a Bier, não a Koller. (D) Long trabalhou com éter, e a tentativa pública com óxido nitroso, malsucedida, foi de Wells.&lt;/p&gt;</t>
+          <t>&lt;p&gt;A data fundadora da especialidade é &lt;strong&gt;16 de outubro de 1846&lt;/strong&gt;, no anfiteatro cirúrgico do &lt;strong&gt;Massachusetts General Hospital&lt;/strong&gt;, em Boston. O dentista &lt;strong&gt;William Thomas Green Morton&lt;/strong&gt; administrou &lt;strong&gt;éter dietílico&lt;/strong&gt; por meio de um inalador de vidro enquanto John Collins Warren removia um tumor cervical do paciente Gilbert Abbott. O sucesso público e reprodutível dessa demonstração (imortalizada na expressão atribuída a Warren de que aquilo não era embuste) difundiu rapidamente a prática pelo mundo, e o local passou a ser chamado de Éter Dome.&lt;/p&gt;&lt;p&gt;Os demais marcos frequentemente confundidos:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Crawford Long&lt;/strong&gt;, na Geórgia, usou éter em 1842, antes de Morton, mas &lt;strong&gt;não publicou&lt;/strong&gt; à época, o que lhe custou a precedência histórica.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Horace Wells&lt;/strong&gt;, dentista, tentou demonstrar publicamente o &lt;strong&gt;óxido nitroso&lt;/strong&gt; em 1845, com fracasso retumbante.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;James Young Simpson&lt;/strong&gt; introduziu o &lt;strong&gt;clorofórmio&lt;/strong&gt; em obstetrícia, na Escócia, em 1847.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Carl Koller&lt;/strong&gt; descreveu em 1884 o uso tópico da &lt;strong&gt;cocaína&lt;/strong&gt; em cirurgia oftalmológica, inaugurando a anestesia local.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;August Bier&lt;/strong&gt; realizou em 1898 a primeira &lt;strong&gt;raquianestesia&lt;/strong&gt;, testada nele próprio e em seu assistente.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a demonstração de 1846 usou éter, e o clorofórmio veio no ano seguinte. (B) a raquianestesia é atribuída a Bier, não a Koller. (D) Long trabalhou com éter, e a tentativa pública com óxido nitroso, malsucedida, foi de Wells.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>&lt;p&gt;No Brasil, a retirada &lt;em&gt;post mortem&lt;/em&gt; de órgãos sólidos para transplante é condicionada ao &lt;strong&gt;diagnóstico de morte encefálica&lt;/strong&gt;, realizado segundo protocolo com dois exames clínicos por médicos diferentes, teste de apneia e exame complementar comprobatório, conforme regulamentação do Conselho Federal de Medicina. A doação após parada circulatória, praticada em alguns países com período de observação sem toque após a assistolia, &lt;strong&gt;não é modalidade estabelecida na rotina nacional&lt;/strong&gt; para órgãos sólidos.&lt;/p&gt;&lt;p&gt;Dois princípios éticos estruturam o tema. O primeiro é a &lt;strong&gt;regra do doador morto&lt;/strong&gt;: a retirada não pode ser a causa da morte nem antecipá-la. O segundo é a &lt;strong&gt;separação estrita entre as equipes&lt;/strong&gt;: o médico que diagnostica a morte encefálica e a equipe assistencial do paciente não podem integrar as equipes de remoção e de transplante. Essa separação existe para eliminar conflito de interesse e preservar a confiança pública no sistema — decisões de fim de vida jamais podem ser contaminadas pelo interesse em órgãos.&lt;/p&gt;&lt;p&gt;Além disso, a legislação brasileira vigente exige &lt;strong&gt;autorização de familiar&lt;/strong&gt;, cônjuge ou parente até segundo grau, firmada em documento com duas testemunhas. A antiga sistemática de doação presumida por anotação em documento de identidade foi revogada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a doação após parada circulatória não é prática regulamentada de rotina para órgãos sólidos no país. (B) a participação do anestesiologista da captação nessas decisões viola a separação de equipes. (C) a autorização familiar é obrigatória.&lt;/p&gt;</t>
+          <t>&lt;p&gt;No Brasil, a retirada &lt;em&gt;post mortem&lt;/em&gt; de órgãos sólidos para transplante é condicionada ao &lt;strong&gt;diagnóstico de morte encefálica&lt;/strong&gt;, realizado segundo protocolo com dois exames clínicos por médicos diferentes, teste de apneia e exame complementar comprobatório, conforme regulamentação do Conselho Federal de Medicina. A doação após parada circulatória, praticada em alguns países com período de observação sem toque após a assistolia, &lt;strong&gt;não é modalidade estabelecida na rotina nacional&lt;/strong&gt; para órgãos sólidos.&lt;/p&gt;&lt;p&gt;Dois princípios éticos estruturam o tema. O primeiro é a &lt;strong&gt;regra do doador morto&lt;/strong&gt;: a retirada não pode ser a causa da morte nem antecipá-la. O segundo é a &lt;strong&gt;separação estrita entre as equipes&lt;/strong&gt;: o médico que diagnostica a morte encefálica e a equipe assistencial do paciente não podem integrar as equipes de remoção e de transplante. Essa separação existe para eliminar conflito de interesse e preservar a confiança pública no sistema: decisões de fim de vida jamais podem ser contaminadas pelo interesse em órgãos.&lt;/p&gt;&lt;p&gt;Além disso, a legislação brasileira vigente exige &lt;strong&gt;autorização de familiar&lt;/strong&gt;, cônjuge ou parente até segundo grau, firmada em documento com duas testemunhas. A antiga sistemática de doação presumida por anotação em documento de identidade foi revogada.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Por que as demais estão incorretas:&lt;/strong&gt; (A) a doação após parada circulatória não é prática regulamentada de rotina para órgãos sólidos no país. (B) a participação do anestesiologista da captação nessas decisões viola a separação de equipes. (C) a autorização familiar é obrigatória.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
